--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CACEE9-40BE-4FCE-BB30-C409E7BC1FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -798,11 +799,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;\-0\ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1006,7 +1007,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1038,9 +1039,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1072,6 +1091,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1247,9 +1284,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" customWidth="1"/>
@@ -1258,7 +1295,7 @@
     <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1275,7 +1312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>71</v>
       </c>
@@ -1286,7 +1323,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -1303,7 +1340,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -1318,7 +1355,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -1333,7 +1370,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -1342,7 +1379,7 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -1357,7 +1394,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -1372,7 +1409,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -1387,7 +1424,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -1402,7 +1439,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -1417,7 +1454,7 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -1432,7 +1469,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>72</v>
       </c>
@@ -1441,7 +1478,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -1458,7 +1495,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -1473,7 +1510,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -1490,7 +1527,7 @@
         <v>1231231</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -1505,7 +1542,7 @@
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -1520,7 +1557,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -1537,7 +1574,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -1552,7 +1589,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -1567,7 +1604,7 @@
       </c>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -1582,7 +1619,7 @@
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -1597,7 +1634,7 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>73</v>
       </c>
@@ -1606,7 +1643,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -1623,7 +1660,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -1640,7 +1677,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -1657,7 +1694,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -1674,7 +1711,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -1691,7 +1728,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -1706,7 +1743,7 @@
       </c>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -1723,7 +1760,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -1740,7 +1777,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -1757,7 +1794,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -1772,7 +1809,7 @@
       </c>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -1787,7 +1824,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -1802,7 +1839,7 @@
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>74</v>
       </c>
@@ -1811,7 +1848,7 @@
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -1826,7 +1863,7 @@
       </c>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -1843,7 +1880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -1860,7 +1897,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -1877,7 +1914,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -1892,7 +1929,7 @@
       </c>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -1907,7 +1944,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>75</v>
       </c>
@@ -1916,7 +1953,7 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -1931,7 +1968,7 @@
       </c>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -1946,7 +1983,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -1961,7 +1998,7 @@
       </c>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -1976,7 +2013,7 @@
       </c>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -1991,7 +2028,7 @@
       </c>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -2008,7 +2045,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -2025,7 +2062,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -2042,7 +2079,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -2059,7 +2096,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -2076,7 +2113,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -2091,7 +2128,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -2106,7 +2143,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>76</v>
       </c>
@@ -2115,7 +2152,7 @@
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -2130,7 +2167,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -2147,7 +2184,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -2164,7 +2201,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -2181,7 +2218,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -2196,7 +2233,7 @@
       </c>
       <c r="E62" s="6"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -2211,7 +2248,7 @@
       </c>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -2226,7 +2263,7 @@
       </c>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -2243,7 +2280,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -2260,7 +2297,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -2277,7 +2314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -2292,7 +2329,7 @@
       </c>
       <c r="E68" s="6"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -2307,7 +2344,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -2322,7 +2359,7 @@
       </c>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -2339,7 +2376,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -2356,7 +2393,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -2373,7 +2410,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -2388,7 +2425,7 @@
       </c>
       <c r="E74" s="6"/>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -2403,7 +2440,7 @@
       </c>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>77</v>
       </c>
@@ -2412,7 +2449,7 @@
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -2427,7 +2464,7 @@
       </c>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -2442,7 +2479,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -2457,7 +2494,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -2472,7 +2509,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>78</v>
       </c>
@@ -2481,7 +2518,7 @@
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -2496,7 +2533,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -2511,7 +2548,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -2526,7 +2563,7 @@
       </c>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -2543,8 +2580,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E33" r:id="rId1"/>
-    <hyperlink ref="E54" r:id="rId2"/>
+    <hyperlink ref="E33" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E54" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId3"/>
@@ -2552,9 +2589,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E107"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.5703125" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
@@ -2563,7 +2600,7 @@
     <col min="5" max="5" width="34.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -2580,7 +2617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>129</v>
       </c>
@@ -2591,7 +2628,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -2608,7 +2645,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -2623,7 +2660,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -2638,7 +2675,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -2653,7 +2690,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -2668,7 +2705,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -2683,7 +2720,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -2698,7 +2735,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -2713,7 +2750,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>70</v>
       </c>
@@ -2722,7 +2759,7 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -2737,7 +2774,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -2752,7 +2789,7 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -2767,7 +2804,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -2782,7 +2819,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>217</v>
       </c>
@@ -2791,7 +2828,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -2808,7 +2845,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -2825,7 +2862,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -2842,7 +2879,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -2859,7 +2896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -2876,7 +2913,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -2893,7 +2930,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -2910,7 +2947,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -2927,7 +2964,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2944,7 +2981,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2961,7 +2998,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -2978,7 +3015,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -2993,7 +3030,7 @@
       </c>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -3010,7 +3047,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -3025,7 +3062,7 @@
       </c>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -3040,7 +3077,7 @@
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>72</v>
       </c>
@@ -3049,7 +3086,7 @@
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -3066,7 +3103,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -3081,7 +3118,7 @@
       </c>
       <c r="E34" s="10"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -3096,7 +3133,7 @@
       </c>
       <c r="E35" s="10"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -3113,7 +3150,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -3128,7 +3165,7 @@
       </c>
       <c r="E37" s="10"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -3143,7 +3180,7 @@
       </c>
       <c r="E38" s="10"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -3160,7 +3197,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -3175,7 +3212,7 @@
       </c>
       <c r="E40" s="10"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -3190,7 +3227,7 @@
       </c>
       <c r="E41" s="10"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -3207,7 +3244,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -3222,7 +3259,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -3237,7 +3274,7 @@
       </c>
       <c r="E44" s="10"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -3254,7 +3291,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -3269,7 +3306,7 @@
       </c>
       <c r="E46" s="10"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -3284,7 +3321,7 @@
       </c>
       <c r="E47" s="10"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -3301,7 +3338,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -3316,7 +3353,7 @@
       </c>
       <c r="E49" s="10"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -3331,7 +3368,7 @@
       </c>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -3348,7 +3385,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>50</v>
       </c>
@@ -3363,7 +3400,7 @@
       </c>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>51</v>
       </c>
@@ -3378,7 +3415,7 @@
       </c>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>52</v>
       </c>
@@ -3395,7 +3432,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>53</v>
       </c>
@@ -3410,7 +3447,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>54</v>
       </c>
@@ -3425,7 +3462,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>55</v>
       </c>
@@ -3442,7 +3479,7 @@
         <v>44594</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>56</v>
       </c>
@@ -3459,7 +3496,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>57</v>
       </c>
@@ -3474,7 +3511,7 @@
       </c>
       <c r="E59" s="2"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>58</v>
       </c>
@@ -3489,7 +3526,7 @@
       </c>
       <c r="E60" s="2"/>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>59</v>
       </c>
@@ -3504,7 +3541,7 @@
       </c>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>60</v>
       </c>
@@ -3519,7 +3556,7 @@
       </c>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>61</v>
       </c>
@@ -3534,7 +3571,7 @@
       </c>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>62</v>
       </c>
@@ -3549,7 +3586,7 @@
       </c>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>63</v>
       </c>
@@ -3566,7 +3603,7 @@
         <v>3234</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>64</v>
       </c>
@@ -3583,7 +3620,7 @@
         <v>13234</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>65</v>
       </c>
@@ -3598,7 +3635,7 @@
       </c>
       <c r="E67" s="2"/>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>66</v>
       </c>
@@ -3613,7 +3650,7 @@
       </c>
       <c r="E68" s="2"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>67</v>
       </c>
@@ -3628,7 +3665,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>68</v>
       </c>
@@ -3643,7 +3680,7 @@
       </c>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>118</v>
       </c>
@@ -3652,7 +3689,7 @@
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>70</v>
       </c>
@@ -3667,7 +3704,7 @@
       </c>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>71</v>
       </c>
@@ -3684,7 +3721,7 @@
         <v>7826423</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>72</v>
       </c>
@@ -3701,7 +3738,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>73</v>
       </c>
@@ -3718,7 +3755,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>74</v>
       </c>
@@ -3735,7 +3772,7 @@
         <v>3478323</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>75</v>
       </c>
@@ -3750,7 +3787,7 @@
       </c>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>76</v>
       </c>
@@ -3765,7 +3802,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>77</v>
       </c>
@@ -3780,7 +3817,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="14">
         <v>78</v>
       </c>
@@ -3795,7 +3832,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
         <v>123</v>
       </c>
@@ -3804,7 +3841,7 @@
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="15">
         <v>80</v>
       </c>
@@ -3819,7 +3856,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="15">
         <v>81</v>
       </c>
@@ -3836,7 +3873,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="15">
         <v>82</v>
       </c>
@@ -3853,7 +3890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="15">
         <v>83</v>
       </c>
@@ -3870,7 +3907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="15">
         <v>84</v>
       </c>
@@ -3887,7 +3924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="15">
         <v>85</v>
       </c>
@@ -3902,7 +3939,7 @@
       </c>
       <c r="E87" s="2"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="15">
         <v>86</v>
       </c>
@@ -3917,7 +3954,7 @@
       </c>
       <c r="E88" s="2"/>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="15">
         <v>87</v>
       </c>
@@ -3932,7 +3969,7 @@
       </c>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="15">
         <v>88</v>
       </c>
@@ -3949,7 +3986,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="15">
         <v>89</v>
       </c>
@@ -3966,7 +4003,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="15">
         <v>90</v>
       </c>
@@ -3983,7 +4020,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="15">
         <v>91</v>
       </c>
@@ -4000,7 +4037,7 @@
         <v>3478323</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="15">
         <v>92</v>
       </c>
@@ -4015,7 +4052,7 @@
       </c>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="15">
         <v>93</v>
       </c>
@@ -4030,7 +4067,7 @@
       </c>
       <c r="E95" s="2"/>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
         <v>124</v>
       </c>
@@ -4039,7 +4076,7 @@
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="15">
         <v>95</v>
       </c>
@@ -4054,7 +4091,7 @@
       </c>
       <c r="E97" s="2"/>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="15">
         <v>96</v>
       </c>
@@ -4069,7 +4106,7 @@
       </c>
       <c r="E98" s="2"/>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="15">
         <v>97</v>
       </c>
@@ -4084,7 +4121,7 @@
       </c>
       <c r="E99" s="2"/>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="15">
         <v>98</v>
       </c>
@@ -4099,7 +4136,7 @@
       </c>
       <c r="E100" s="2"/>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="15">
         <v>99</v>
       </c>
@@ -4114,7 +4151,7 @@
       </c>
       <c r="E101" s="2"/>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="15">
         <v>100</v>
       </c>
@@ -4129,7 +4166,7 @@
       </c>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="15" t="s">
         <v>128</v>
       </c>
@@ -4138,7 +4175,7 @@
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="15">
         <v>101</v>
       </c>
@@ -4153,7 +4190,7 @@
       </c>
       <c r="E104" s="2"/>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="15">
         <v>102</v>
       </c>
@@ -4168,7 +4205,7 @@
       </c>
       <c r="E105" s="2"/>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="15">
         <v>103</v>
       </c>
@@ -4183,7 +4220,7 @@
       </c>
       <c r="E106" s="2"/>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="15">
         <v>104</v>
       </c>
@@ -4205,9 +4242,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E160"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.7109375" style="17" customWidth="1"/>
     <col min="2" max="2" width="35.28515625" style="17" customWidth="1"/>
@@ -4217,7 +4254,7 @@
     <col min="6" max="16384" width="9.140625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -4234,7 +4271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>130</v>
       </c>
@@ -4245,7 +4282,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -4262,7 +4299,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -4277,7 +4314,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -4292,7 +4329,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -4307,7 +4344,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -4322,7 +4359,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -4337,7 +4374,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -4352,7 +4389,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -4367,7 +4404,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -4384,7 +4421,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>146</v>
       </c>
@@ -4393,7 +4430,7 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -4408,7 +4445,7 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -4423,7 +4460,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -4440,7 +4477,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -4457,7 +4494,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -4474,7 +4511,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -4491,7 +4528,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -4508,7 +4545,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -4525,7 +4562,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -4542,7 +4579,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -4557,7 +4594,7 @@
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -4572,7 +4609,7 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -4587,7 +4624,7 @@
       </c>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -4604,7 +4641,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -4621,7 +4658,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -4638,7 +4675,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -4653,7 +4690,7 @@
       </c>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -4668,7 +4705,7 @@
       </c>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>164</v>
       </c>
@@ -4677,7 +4714,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -4692,7 +4729,7 @@
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -4707,7 +4744,7 @@
       </c>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -4722,7 +4759,7 @@
       </c>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -4739,7 +4776,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -4754,7 +4791,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -4769,7 +4806,7 @@
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -4784,7 +4821,7 @@
       </c>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -4799,7 +4836,7 @@
       </c>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -4814,7 +4851,7 @@
       </c>
       <c r="E39" s="2"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>167</v>
       </c>
@@ -4823,7 +4860,7 @@
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -4840,7 +4877,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -4857,7 +4894,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -4874,7 +4911,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -4889,7 +4926,7 @@
       </c>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -4906,7 +4943,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -4921,7 +4958,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -4938,7 +4975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -4953,7 +4990,7 @@
       </c>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -4970,7 +5007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -4985,7 +5022,7 @@
       </c>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -5002,7 +5039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -5017,7 +5054,7 @@
       </c>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -5034,7 +5071,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -5049,7 +5086,7 @@
       </c>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -5066,7 +5103,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -5081,7 +5118,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -5096,7 +5133,7 @@
       </c>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -5111,7 +5148,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>181</v>
       </c>
@@ -5120,7 +5157,7 @@
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -5137,7 +5174,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -5152,7 +5189,7 @@
       </c>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -5167,7 +5204,7 @@
       </c>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -5184,7 +5221,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -5201,7 +5238,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -5216,7 +5253,7 @@
       </c>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -5227,7 +5264,7 @@
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -5244,7 +5281,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -5261,7 +5298,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -5276,7 +5313,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -5291,7 +5328,7 @@
       </c>
       <c r="E70" s="6"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -5308,7 +5345,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -5323,7 +5360,7 @@
       </c>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -5340,7 +5377,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -5355,7 +5392,7 @@
       </c>
       <c r="E74" s="2"/>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -5370,7 +5407,7 @@
       </c>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>76</v>
       </c>
@@ -5385,7 +5422,7 @@
       </c>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -5402,7 +5439,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -5417,7 +5454,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -5432,7 +5469,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -5447,7 +5484,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>81</v>
       </c>
@@ -5464,7 +5501,7 @@
         <v>3.4628376482734602E+18</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -5479,7 +5516,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -5494,7 +5531,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -5509,7 +5546,7 @@
       </c>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -5526,7 +5563,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>86</v>
       </c>
@@ -5541,7 +5578,7 @@
       </c>
       <c r="E86" s="2"/>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>87</v>
       </c>
@@ -5556,7 +5593,7 @@
       </c>
       <c r="E87" s="2"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>88</v>
       </c>
@@ -5571,7 +5608,7 @@
       </c>
       <c r="E88" s="2"/>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>89</v>
       </c>
@@ -5588,7 +5625,7 @@
         <v>3.4628376482734602E+18</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>90</v>
       </c>
@@ -5603,7 +5640,7 @@
       </c>
       <c r="E90" s="2"/>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>91</v>
       </c>
@@ -5618,7 +5655,7 @@
       </c>
       <c r="E91" s="2"/>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>92</v>
       </c>
@@ -5635,7 +5672,7 @@
         <v>44854</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>93</v>
       </c>
@@ -5652,7 +5689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>94</v>
       </c>
@@ -5667,7 +5704,7 @@
       </c>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>95</v>
       </c>
@@ -5682,7 +5719,7 @@
       </c>
       <c r="E95" s="2"/>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>96</v>
       </c>
@@ -5697,7 +5734,7 @@
       </c>
       <c r="E96" s="2"/>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>97</v>
       </c>
@@ -5712,7 +5749,7 @@
       </c>
       <c r="E97" s="2"/>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>98</v>
       </c>
@@ -5727,7 +5764,7 @@
       </c>
       <c r="E98" s="2"/>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>118</v>
       </c>
@@ -5736,7 +5773,7 @@
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>100</v>
       </c>
@@ -5751,7 +5788,7 @@
       </c>
       <c r="E100" s="2"/>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>101</v>
       </c>
@@ -5768,7 +5805,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>102</v>
       </c>
@@ -5783,7 +5820,7 @@
       </c>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>103</v>
       </c>
@@ -5798,7 +5835,7 @@
       </c>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>104</v>
       </c>
@@ -5815,7 +5852,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>105</v>
       </c>
@@ -5832,7 +5869,7 @@
         <v>7600</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>106</v>
       </c>
@@ -5849,7 +5886,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -5866,7 +5903,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>108</v>
       </c>
@@ -5881,7 +5918,7 @@
       </c>
       <c r="E108" s="2"/>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>109</v>
       </c>
@@ -5896,7 +5933,7 @@
       </c>
       <c r="E109" s="2"/>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>131</v>
       </c>
@@ -5905,7 +5942,7 @@
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>111</v>
       </c>
@@ -5920,7 +5957,7 @@
       </c>
       <c r="E111" s="2"/>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>112</v>
       </c>
@@ -5935,7 +5972,7 @@
       </c>
       <c r="E112" s="2"/>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>113</v>
       </c>
@@ -5950,7 +5987,7 @@
       </c>
       <c r="E113" s="2"/>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>114</v>
       </c>
@@ -5965,7 +6002,7 @@
       </c>
       <c r="E114" s="2"/>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>115</v>
       </c>
@@ -5980,7 +6017,7 @@
       </c>
       <c r="E115" s="2"/>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>116</v>
       </c>
@@ -5995,7 +6032,7 @@
       </c>
       <c r="E116" s="2"/>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>117</v>
       </c>
@@ -6010,7 +6047,7 @@
       </c>
       <c r="E117" s="2"/>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>118</v>
       </c>
@@ -6025,7 +6062,7 @@
       </c>
       <c r="E118" s="2"/>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>119</v>
       </c>
@@ -6040,7 +6077,7 @@
       </c>
       <c r="E119" s="2"/>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>120</v>
       </c>
@@ -6057,7 +6094,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>121</v>
       </c>
@@ -6074,7 +6111,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>122</v>
       </c>
@@ -6091,7 +6128,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>123</v>
       </c>
@@ -6108,7 +6145,7 @@
         <v>12323</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>124</v>
       </c>
@@ -6123,7 +6160,7 @@
       </c>
       <c r="E124" s="2"/>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>125</v>
       </c>
@@ -6138,7 +6175,7 @@
       </c>
       <c r="E125" s="2"/>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>126</v>
       </c>
@@ -6153,7 +6190,7 @@
       </c>
       <c r="E126" s="2"/>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>253</v>
       </c>
@@ -6162,7 +6199,7 @@
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>128</v>
       </c>
@@ -6177,7 +6214,7 @@
       </c>
       <c r="E128" s="2"/>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>129</v>
       </c>
@@ -6192,7 +6229,7 @@
       </c>
       <c r="E129" s="2"/>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>130</v>
       </c>
@@ -6207,7 +6244,7 @@
       </c>
       <c r="E130" s="2"/>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>131</v>
       </c>
@@ -6222,7 +6259,7 @@
       </c>
       <c r="E131" s="2"/>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>132</v>
       </c>
@@ -6239,7 +6276,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>133</v>
       </c>
@@ -6254,7 +6291,7 @@
       </c>
       <c r="E133" s="2"/>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>134</v>
       </c>
@@ -6269,7 +6306,7 @@
       </c>
       <c r="E134" s="2"/>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>139</v>
       </c>
@@ -6278,7 +6315,7 @@
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>136</v>
       </c>
@@ -6293,7 +6330,7 @@
       </c>
       <c r="E136" s="2"/>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>137</v>
       </c>
@@ -6308,7 +6345,7 @@
       </c>
       <c r="E137" s="2"/>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>138</v>
       </c>
@@ -6323,7 +6360,7 @@
       </c>
       <c r="E138" s="2"/>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>139</v>
       </c>
@@ -6338,7 +6375,7 @@
       </c>
       <c r="E139" s="2"/>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>140</v>
       </c>
@@ -6353,7 +6390,7 @@
       </c>
       <c r="E140" s="2"/>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>141</v>
       </c>
@@ -6368,7 +6405,7 @@
       </c>
       <c r="E141" s="2"/>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>141</v>
       </c>
@@ -6377,7 +6414,7 @@
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>143</v>
       </c>
@@ -6392,7 +6429,7 @@
       </c>
       <c r="E143" s="2"/>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>144</v>
       </c>
@@ -6407,7 +6444,7 @@
       </c>
       <c r="E144" s="2"/>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>145</v>
       </c>
@@ -6422,7 +6459,7 @@
       </c>
       <c r="E145" s="2"/>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>146</v>
       </c>
@@ -6437,7 +6474,7 @@
       </c>
       <c r="E146" s="2"/>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>128</v>
       </c>
@@ -6446,7 +6483,7 @@
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>148</v>
       </c>
@@ -6461,7 +6498,7 @@
       </c>
       <c r="E148" s="2"/>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>149</v>
       </c>
@@ -6476,7 +6513,7 @@
       </c>
       <c r="E149" s="2"/>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>150</v>
       </c>
@@ -6491,7 +6528,7 @@
       </c>
       <c r="E150" s="2"/>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>151</v>
       </c>
@@ -6506,7 +6543,7 @@
       </c>
       <c r="E151" s="2"/>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>152</v>
       </c>
@@ -6521,7 +6558,7 @@
       </c>
       <c r="E152" s="2"/>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>200</v>
       </c>
@@ -6530,7 +6567,7 @@
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>154</v>
       </c>
@@ -6545,7 +6582,7 @@
       </c>
       <c r="E154" s="2"/>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>155</v>
       </c>
@@ -6560,7 +6597,7 @@
       </c>
       <c r="E155" s="2"/>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>156</v>
       </c>
@@ -6575,7 +6612,7 @@
       </c>
       <c r="E156" s="2"/>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>157</v>
       </c>
@@ -6590,7 +6627,7 @@
       </c>
       <c r="E157" s="2"/>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>158</v>
       </c>
@@ -6605,7 +6642,7 @@
       </c>
       <c r="E158" s="2"/>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>159</v>
       </c>
@@ -6620,7 +6657,7 @@
       </c>
       <c r="E159" s="2"/>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>160</v>
       </c>
@@ -6638,7 +6675,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E18" r:id="rId1"/>
+    <hyperlink ref="E18" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId2"/>
@@ -6646,9 +6683,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E116"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" customWidth="1"/>
@@ -6657,7 +6694,7 @@
     <col min="5" max="5" width="52.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -6674,7 +6711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>129</v>
       </c>
@@ -6685,7 +6722,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -6702,7 +6739,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -6717,7 +6754,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -6732,7 +6769,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -6747,7 +6784,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -6762,7 +6799,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -6777,7 +6814,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -6792,7 +6829,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>204</v>
       </c>
@@ -6801,7 +6838,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -6818,7 +6855,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -6835,7 +6872,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -6852,7 +6889,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -6869,7 +6906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -6886,7 +6923,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -6903,7 +6940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -6920,7 +6957,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -6937,7 +6974,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -6954,7 +6991,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -6971,7 +7008,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -6988,7 +7025,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -7005,7 +7042,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -7018,9 +7055,9 @@
       <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="E23" s="6"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -7035,7 +7072,7 @@
       </c>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -7050,7 +7087,7 @@
       </c>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -7065,7 +7102,7 @@
       </c>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -7080,7 +7117,7 @@
       </c>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -7095,7 +7132,7 @@
       </c>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -7112,7 +7149,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>146</v>
       </c>
@@ -7121,7 +7158,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -7136,7 +7173,7 @@
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -7151,7 +7188,7 @@
       </c>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -7168,7 +7205,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -7185,7 +7222,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -7202,7 +7239,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -7219,7 +7256,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -7236,7 +7273,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -7253,7 +7290,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -7270,7 +7307,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -7285,7 +7322,7 @@
       </c>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -7300,7 +7337,7 @@
       </c>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -7315,7 +7352,7 @@
       </c>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -7330,7 +7367,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -7345,7 +7382,7 @@
       </c>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -7362,7 +7399,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -7377,7 +7414,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -7394,7 +7431,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -7411,7 +7448,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -7428,7 +7465,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -7443,7 +7480,7 @@
       </c>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -7460,7 +7497,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -7475,7 +7512,7 @@
       </c>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -7492,7 +7529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -7507,7 +7544,7 @@
       </c>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -7524,7 +7561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -7539,7 +7576,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -7556,7 +7593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -7571,7 +7608,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -7588,7 +7625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -7605,7 +7642,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -7620,7 +7657,7 @@
       </c>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -7635,7 +7672,7 @@
       </c>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -7650,7 +7687,7 @@
       </c>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>205</v>
       </c>
@@ -7659,7 +7696,7 @@
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -7674,7 +7711,7 @@
       </c>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -7689,7 +7726,7 @@
       </c>
       <c r="E66" s="2"/>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -7704,7 +7741,7 @@
       </c>
       <c r="E67" s="6"/>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -7719,7 +7756,7 @@
       </c>
       <c r="E68" s="2"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -7734,7 +7771,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -7749,7 +7786,7 @@
       </c>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -7764,7 +7801,7 @@
       </c>
       <c r="E71" s="2"/>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -7779,7 +7816,7 @@
       </c>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -7794,31 +7831,31 @@
       </c>
       <c r="E73" s="2"/>
     </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="2">
-        <v>74</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C74" s="2" t="s">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="6"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>75</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="6"/>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
+      <c r="D75" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E75" s="6"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>76</v>
       </c>
@@ -7833,7 +7870,7 @@
       </c>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -7848,7 +7885,7 @@
       </c>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -7863,7 +7900,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -7878,7 +7915,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -7893,7 +7930,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>81</v>
       </c>
@@ -7908,7 +7945,7 @@
       </c>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -7925,7 +7962,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -7940,7 +7977,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -7955,7 +7992,7 @@
       </c>
       <c r="E84" s="10"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -7970,7 +8007,7 @@
       </c>
       <c r="E85" s="2"/>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>86</v>
       </c>
@@ -7987,7 +8024,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>87</v>
       </c>
@@ -8002,7 +8039,7 @@
       </c>
       <c r="E87" s="6"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>88</v>
       </c>
@@ -8019,7 +8056,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>89</v>
       </c>
@@ -8034,7 +8071,7 @@
       </c>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>90</v>
       </c>
@@ -8051,7 +8088,7 @@
         <v>10340</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>91</v>
       </c>
@@ -8066,7 +8103,7 @@
       </c>
       <c r="E91" s="2"/>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>92</v>
       </c>
@@ -8081,7 +8118,7 @@
       </c>
       <c r="E92" s="2"/>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>93</v>
       </c>
@@ -8096,7 +8133,7 @@
       </c>
       <c r="E93" s="2"/>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>94</v>
       </c>
@@ -8111,7 +8148,7 @@
       </c>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>95</v>
       </c>
@@ -8126,7 +8163,7 @@
       </c>
       <c r="E95" s="2"/>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>96</v>
       </c>
@@ -8141,7 +8178,7 @@
       </c>
       <c r="E96" s="2"/>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>97</v>
       </c>
@@ -8156,7 +8193,7 @@
       </c>
       <c r="E97" s="2"/>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>141</v>
       </c>
@@ -8165,7 +8202,7 @@
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>99</v>
       </c>
@@ -8180,7 +8217,7 @@
       </c>
       <c r="E99" s="2"/>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>100</v>
       </c>
@@ -8195,7 +8232,7 @@
       </c>
       <c r="E100" s="2"/>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>101</v>
       </c>
@@ -8210,7 +8247,7 @@
       </c>
       <c r="E101" s="2"/>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>102</v>
       </c>
@@ -8225,7 +8262,7 @@
       </c>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>103</v>
       </c>
@@ -8240,7 +8277,7 @@
       </c>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>104</v>
       </c>
@@ -8255,7 +8292,7 @@
       </c>
       <c r="E104" s="2"/>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>128</v>
       </c>
@@ -8264,7 +8301,7 @@
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>106</v>
       </c>
@@ -8279,7 +8316,7 @@
       </c>
       <c r="E106" s="2"/>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -8294,7 +8331,7 @@
       </c>
       <c r="E107" s="2"/>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>108</v>
       </c>
@@ -8309,7 +8346,7 @@
       </c>
       <c r="E108" s="2"/>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>109</v>
       </c>
@@ -8324,7 +8361,7 @@
       </c>
       <c r="E109" s="2"/>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>110</v>
       </c>
@@ -8339,7 +8376,7 @@
       </c>
       <c r="E110" s="2"/>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>111</v>
       </c>
@@ -8354,7 +8391,7 @@
       </c>
       <c r="E111" s="2"/>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>112</v>
       </c>
@@ -8369,7 +8406,7 @@
       </c>
       <c r="E112" s="2"/>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>113</v>
       </c>
@@ -8384,7 +8421,7 @@
       </c>
       <c r="E113" s="2"/>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>114</v>
       </c>
@@ -8399,7 +8436,7 @@
       </c>
       <c r="E114" s="2"/>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>115</v>
       </c>
@@ -8414,7 +8451,7 @@
       </c>
       <c r="E115" s="2"/>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>116</v>
       </c>
@@ -8431,7 +8468,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E36" r:id="rId1"/>
+    <hyperlink ref="E36" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId2"/>
@@ -8439,9 +8476,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E58"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.140625" customWidth="1"/>
@@ -8450,7 +8487,7 @@
     <col min="5" max="5" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -8467,7 +8504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>252</v>
       </c>
@@ -8478,7 +8515,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -8495,7 +8532,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -8510,7 +8547,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -8525,7 +8562,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -8540,7 +8577,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -8555,7 +8592,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -8570,7 +8607,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -8585,7 +8622,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -8600,7 +8637,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -8617,7 +8654,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -8632,7 +8669,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -8647,7 +8684,7 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -8662,7 +8699,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -8677,7 +8714,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -8692,7 +8729,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -8707,7 +8744,7 @@
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -8722,7 +8759,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -8737,7 +8774,7 @@
       </c>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -8752,7 +8789,7 @@
       </c>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -8767,7 +8804,7 @@
       </c>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -8782,7 +8819,7 @@
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -8797,7 +8834,7 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -8812,7 +8849,7 @@
       </c>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -8827,7 +8864,7 @@
       </c>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -8842,7 +8879,7 @@
       </c>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -8857,7 +8894,7 @@
       </c>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -8872,7 +8909,7 @@
       </c>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -8887,7 +8924,7 @@
       </c>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -8902,7 +8939,7 @@
       </c>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -8917,7 +8954,7 @@
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -8932,7 +8969,7 @@
       </c>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -8947,7 +8984,7 @@
       </c>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -8962,7 +8999,7 @@
       </c>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -8977,7 +9014,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -8992,7 +9029,7 @@
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -9007,7 +9044,7 @@
       </c>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -9022,7 +9059,7 @@
       </c>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -9037,7 +9074,7 @@
       </c>
       <c r="E39" s="2"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>141</v>
       </c>
@@ -9046,7 +9083,7 @@
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -9061,7 +9098,7 @@
       </c>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -9076,7 +9113,7 @@
       </c>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -9091,7 +9128,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -9106,7 +9143,7 @@
       </c>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>128</v>
       </c>
@@ -9115,7 +9152,7 @@
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -9130,7 +9167,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -9145,7 +9182,7 @@
       </c>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -9160,7 +9197,7 @@
       </c>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -9175,7 +9212,7 @@
       </c>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -9190,7 +9227,7 @@
       </c>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>200</v>
       </c>
@@ -9199,7 +9236,7 @@
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -9214,7 +9251,7 @@
       </c>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -9229,7 +9266,7 @@
       </c>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -9244,7 +9281,7 @@
       </c>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -9259,7 +9296,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -9274,7 +9311,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -9289,7 +9326,7 @@
       </c>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -9310,9 +9347,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.140625" customWidth="1"/>
@@ -9321,7 +9358,7 @@
     <col min="5" max="5" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -9338,7 +9375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>243</v>
       </c>
@@ -9349,7 +9386,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -9366,7 +9403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -9381,7 +9418,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -9396,7 +9433,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -9411,7 +9448,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -9426,7 +9463,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -9441,7 +9478,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -9456,7 +9493,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -9473,7 +9510,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -9490,7 +9527,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -9505,7 +9542,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -9522,7 +9559,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -9537,7 +9574,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -9552,7 +9589,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -9567,105 +9604,105 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="4"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="4"/>
       <c r="C18" s="2"/>
       <c r="D18" s="4"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="4"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="4"/>
       <c r="C20" s="2"/>
       <c r="D20" s="4"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="4"/>
       <c r="C21" s="2"/>
       <c r="D21" s="4"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="4"/>
       <c r="C22" s="2"/>
       <c r="D22" s="4"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="4"/>
       <c r="C23" s="2"/>
       <c r="D23" s="4"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="4"/>
       <c r="C24" s="2"/>
       <c r="D24" s="4"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="4"/>
       <c r="C26" s="2"/>
       <c r="D26" s="4"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="4"/>
       <c r="C27" s="2"/>
       <c r="D27" s="4"/>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="4"/>
       <c r="C28" s="2"/>
       <c r="D28" s="4"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="4"/>
       <c r="C29" s="2"/>
       <c r="D29" s="4"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="4"/>
       <c r="C30" s="2"/>
       <c r="D30" s="4"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="4"/>
       <c r="C31" s="2"/>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CACEE9-40BE-4FCE-BB30-C409E7BC1FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1775AB-CB74-470A-BA63-5D8C0DD5BEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -13,14 +13,15 @@
     <sheet name="Deduction" sheetId="3" r:id="rId3"/>
     <sheet name="Challan Mapping" sheetId="4" r:id="rId4"/>
     <sheet name="Predict Default" sheetId="5" r:id="rId5"/>
-    <sheet name="Ereturn" sheetId="6" r:id="rId6"/>
+    <sheet name="Regression Test" sheetId="8" r:id="rId6"/>
+    <sheet name="Ereturn" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3016" uniqueCount="258">
   <si>
     <t>Keyword</t>
   </si>
@@ -9347,8 +9348,6854 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279E6F6B-0D50-4643-8FCD-F621627AC8FF}">
+  <dimension ref="A1:E447"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="49.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1231231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>22</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>26</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>28</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>30</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="6"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>33</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>34</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="5"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>35</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>36</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>38</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>39</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>40</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>41</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>42</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>43</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>45</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>46</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>47</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>48</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>49</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>50</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>52</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>53</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>54</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>55</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>56</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>58</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>59</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>60</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>61</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>62</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="6"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>63</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>64</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>65</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>66</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>67</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>68</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="6"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>69</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>70</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="2"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>71</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>72</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>73</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>74</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="6"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>75</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>1</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>2</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>3</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>4</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>5</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>6</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>7</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>8</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>10</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>11</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>12</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>13</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="2"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>15</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>16</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>17</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>18</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>19</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>20</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>21</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>22</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>23</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>24</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="2">
+        <v>12122</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>25</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="2">
+        <v>2311323</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>26</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="2"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>27</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>29</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104" s="2"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>30</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="2"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>31</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E107" s="8">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>32</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" s="10"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>33</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="10"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>34</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E110" s="8">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>35</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="10"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>36</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="10"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>37</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E113" s="8">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>38</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="10"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>39</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="10"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>40</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E116" s="8">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>41</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="2"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>42</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="10"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>43</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E119" s="8">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>44</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" s="10"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <v>45</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" s="10"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <v>46</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E122" s="8">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
+        <v>47</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" s="10"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <v>48</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="2"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <v>49</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E125" s="8">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>50</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" s="2"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="2">
+        <v>51</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="2"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="2">
+        <v>52</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="2">
+        <v>53</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="2"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
+        <v>54</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" s="2"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="2">
+        <v>55</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E131" s="11">
+        <v>44594</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>56</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="2">
+        <v>57</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="2"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>58</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="2"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="2">
+        <v>59</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" s="2"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
+        <v>60</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="2"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>61</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="2"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
+        <v>62</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="2"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="2">
+        <v>63</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="8">
+        <v>3234</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
+        <v>64</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="12">
+        <v>13234</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="2">
+        <v>65</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" s="2"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
+        <v>66</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" s="2"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="2">
+        <v>67</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="2"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
+        <v>68</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" s="2"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
+        <v>70</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="2"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="2">
+        <v>71</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="8">
+        <v>7826423</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
+        <v>72</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <v>73</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
+        <v>74</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="2">
+        <v>3478323</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="2">
+        <v>75</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E151" s="2"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <v>76</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="2"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="2">
+        <v>77</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="2"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <v>78</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E154" s="2"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B155" s="4"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>80</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" s="2"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>81</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E157" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>82</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E158" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="2">
+        <v>83</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E159" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <v>84</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E160" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="2">
+        <v>85</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E161" s="2"/>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="2">
+        <v>86</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" s="2"/>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="2">
+        <v>87</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E163" s="2"/>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="2">
+        <v>88</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E164" s="8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="2">
+        <v>89</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="2">
+        <v>90</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="2">
+        <v>91</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E167" s="2">
+        <v>3478323</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="2">
+        <v>92</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E168" s="2"/>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="2">
+        <v>93</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" s="2"/>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="2">
+        <v>3</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="2">
+        <v>4</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E172" s="2"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="2">
+        <v>5</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" s="2"/>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="2">
+        <v>6</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" s="2"/>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="2">
+        <v>7</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="2"/>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="2">
+        <v>8</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" s="2"/>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="2">
+        <v>9</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E177" s="2"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="2">
+        <v>10</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E178" s="2"/>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="2">
+        <v>11</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="2"/>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="2">
+        <v>13</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E181" s="2"/>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="2">
+        <v>14</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E182" s="2"/>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="2">
+        <v>15</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="2">
+        <v>16</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="2">
+        <v>17</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="2">
+        <v>18</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E186" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="2">
+        <v>19</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="2">
+        <v>20</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="2">
+        <v>21</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="2">
+        <v>22</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E190" s="2"/>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="2">
+        <v>23</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E191" s="2"/>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="2">
+        <v>24</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E192" s="2"/>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="2">
+        <v>25</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="2">
+        <v>26</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="2">
+        <v>27</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E195" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="2">
+        <v>28</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E196" s="2"/>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="2">
+        <v>29</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" s="2"/>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
+      <c r="E198" s="2"/>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="2">
+        <v>31</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" s="2"/>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" s="2">
+        <v>32</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E200" s="2"/>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" s="2">
+        <v>33</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E201" s="2"/>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" s="2">
+        <v>34</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" s="2">
+        <v>35</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E203" s="2"/>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" s="2">
+        <v>36</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E204" s="2"/>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" s="2">
+        <v>37</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E205" s="2"/>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" s="2">
+        <v>38</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" s="2"/>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" s="2">
+        <v>39</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" s="2"/>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B208" s="2"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="2"/>
+      <c r="E208" s="2"/>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" s="2">
+        <v>41</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E209" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" s="2">
+        <v>42</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E210" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" s="2">
+        <v>43</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E211" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" s="2">
+        <v>44</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E212" s="2"/>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" s="2">
+        <v>45</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E213" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" s="2">
+        <v>46</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E214" s="2"/>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" s="2">
+        <v>47</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E215" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" s="2">
+        <v>48</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E216" s="2"/>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" s="2">
+        <v>49</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E217" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" s="2">
+        <v>50</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E218" s="2"/>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" s="2">
+        <v>51</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E219" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" s="2">
+        <v>52</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E220" s="2"/>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" s="2">
+        <v>53</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E221" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" s="2">
+        <v>54</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E222" s="2"/>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" s="2">
+        <v>55</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" s="2">
+        <v>56</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E224" s="2"/>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" s="2">
+        <v>57</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E225" s="2"/>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" s="2">
+        <v>58</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E226" s="2"/>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B227" s="2"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
+      <c r="E227" s="2"/>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" s="2">
+        <v>60</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" s="2">
+        <v>61</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" s="2"/>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" s="2">
+        <v>62</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E230" s="2"/>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" s="2">
+        <v>63</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E231" s="16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" s="2">
+        <v>64</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E232" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" s="2">
+        <v>65</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E233" s="2"/>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" s="2">
+        <v>66</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
+      <c r="E234" s="2"/>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" s="2">
+        <v>67</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E235" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" s="2">
+        <v>68</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E236" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" s="2">
+        <v>69</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E237" s="2"/>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" s="2">
+        <v>70</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E238" s="6"/>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" s="2">
+        <v>71</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E239" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" s="2">
+        <v>72</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E240" s="2"/>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" s="2">
+        <v>73</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E241" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" s="2">
+        <v>74</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E242" s="2"/>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" s="2">
+        <v>75</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E243" s="2"/>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" s="2">
+        <v>76</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E244" s="2"/>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" s="2">
+        <v>77</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E245" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" s="2">
+        <v>78</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E246" s="2"/>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" s="2">
+        <v>79</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E247" s="2"/>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" s="2">
+        <v>80</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E248" s="2"/>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" s="2">
+        <v>81</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E249" s="8">
+        <v>3.4628376482734602E+18</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" s="2">
+        <v>82</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E250" s="2"/>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" s="2">
+        <v>83</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E251" s="2"/>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" s="2">
+        <v>84</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E252" s="2"/>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" s="2">
+        <v>85</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E253" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" s="2">
+        <v>86</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E254" s="2"/>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" s="2">
+        <v>87</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E255" s="2"/>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" s="2">
+        <v>88</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E256" s="2"/>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" s="2">
+        <v>89</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E257" s="8">
+        <v>3.4628376482734602E+18</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" s="2">
+        <v>90</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E258" s="2"/>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259" s="2">
+        <v>91</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E259" s="2"/>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260" s="2">
+        <v>92</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E260" s="11">
+        <v>44854</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261" s="2">
+        <v>93</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E261" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262" s="2">
+        <v>94</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E262" s="2"/>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263" s="2">
+        <v>95</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E263" s="2"/>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" s="2">
+        <v>96</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E264" s="2"/>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" s="2">
+        <v>97</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E265" s="2"/>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" s="2">
+        <v>98</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E266" s="2"/>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B267" s="2"/>
+      <c r="C267" s="2"/>
+      <c r="D267" s="2"/>
+      <c r="E267" s="2"/>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" s="2">
+        <v>100</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E268" s="2"/>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" s="2">
+        <v>101</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" s="2">
+        <v>102</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E270" s="2"/>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" s="2">
+        <v>103</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E271" s="2"/>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" s="2">
+        <v>104</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E272" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" s="2">
+        <v>105</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E273" s="2">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" s="2">
+        <v>106</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E274" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" s="2">
+        <v>107</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" s="2">
+        <v>108</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E276" s="2"/>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" s="2">
+        <v>109</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E277" s="2"/>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B278" s="2"/>
+      <c r="C278" s="2"/>
+      <c r="D278" s="2"/>
+      <c r="E278" s="2"/>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279" s="2">
+        <v>111</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E279" s="2"/>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280" s="2">
+        <v>112</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E280" s="2"/>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281" s="2">
+        <v>113</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E281" s="2"/>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A282" s="2">
+        <v>114</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E282" s="2"/>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A283" s="2">
+        <v>115</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E283" s="2"/>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A284" s="2">
+        <v>116</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E284" s="2"/>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A285" s="2">
+        <v>117</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E285" s="2"/>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A286" s="2">
+        <v>118</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E286" s="2"/>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A287" s="2">
+        <v>119</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E287" s="2"/>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A288" s="2">
+        <v>120</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E288" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289" s="2">
+        <v>121</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E289" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290" s="2">
+        <v>122</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E290" s="2">
+        <v>2311323</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291" s="2">
+        <v>123</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E291" s="2">
+        <v>12323</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292" s="2">
+        <v>124</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E292" s="2"/>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293" s="2">
+        <v>125</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E293" s="2"/>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294" s="2">
+        <v>126</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E294" s="2"/>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B295" s="2"/>
+      <c r="C295" s="2"/>
+      <c r="D295" s="2"/>
+      <c r="E295" s="2"/>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296" s="2">
+        <v>128</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E296" s="2"/>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297" s="2">
+        <v>129</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E297" s="2"/>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298" s="2">
+        <v>130</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E298" s="2"/>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299" s="2">
+        <v>131</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E299" s="2"/>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300" s="2">
+        <v>132</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E300" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A301" s="2">
+        <v>133</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E301" s="2"/>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A302" s="2">
+        <v>134</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E302" s="2"/>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C303" s="2"/>
+      <c r="D303" s="2"/>
+      <c r="E303" s="2"/>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A304" s="2">
+        <v>3</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E304" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A305" s="2">
+        <v>4</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E305" s="2"/>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A306" s="2">
+        <v>5</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E306" s="2"/>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A307" s="2">
+        <v>6</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E307" s="2"/>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A308" s="2">
+        <v>7</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E308" s="2"/>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A309" s="2">
+        <v>8</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E309" s="2"/>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A310" s="2">
+        <v>9</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E310" s="2"/>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A311" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B311" s="2"/>
+      <c r="C311" s="2"/>
+      <c r="D311" s="2"/>
+      <c r="E311" s="2"/>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A312" s="2">
+        <v>11</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E312" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A313" s="2">
+        <v>12</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E313" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A314" s="2">
+        <v>13</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E314" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A315" s="2">
+        <v>14</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E315" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A316" s="2">
+        <v>15</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E316" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A317" s="2">
+        <v>16</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E317" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A318" s="2">
+        <v>17</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E318" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A319" s="2">
+        <v>18</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E319" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A320" s="2">
+        <v>19</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E320" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A321" s="2">
+        <v>20</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E321" s="2">
+        <v>12122</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A322" s="2">
+        <v>21</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E322" s="2">
+        <v>2311323</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A323" s="2">
+        <v>22</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E323" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A324" s="2">
+        <v>23</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E324" s="6"/>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A325" s="2">
+        <v>24</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E325" s="2"/>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A326" s="2">
+        <v>25</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E326" s="2"/>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A327" s="2">
+        <v>26</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E327" s="2"/>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A328" s="2">
+        <v>27</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E328" s="2"/>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A329" s="2">
+        <v>28</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E329" s="2"/>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A330" s="2">
+        <v>29</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E330" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A331" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B331" s="2"/>
+      <c r="C331" s="2"/>
+      <c r="D331" s="2"/>
+      <c r="E331" s="2"/>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A332" s="2">
+        <v>31</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E332" s="2"/>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A333" s="2">
+        <v>32</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E333" s="2"/>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A334" s="2">
+        <v>33</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E334" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A335" s="2">
+        <v>34</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E335" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A336" s="2">
+        <v>35</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E336" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A337" s="2">
+        <v>36</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E337" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A338" s="2">
+        <v>37</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C338" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E338" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A339" s="2">
+        <v>38</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A340" s="2">
+        <v>39</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E340" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A341" s="2">
+        <v>40</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E341" s="2"/>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A342" s="2">
+        <v>41</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E342" s="2"/>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A343" s="2">
+        <v>42</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E343" s="2"/>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A344" s="2">
+        <v>43</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E344" s="2"/>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A345" s="2">
+        <v>44</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E345" s="2"/>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A346" s="2">
+        <v>45</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E346" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A347" s="2">
+        <v>46</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E347" s="2"/>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A348" s="2">
+        <v>47</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E348" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A349" s="2">
+        <v>48</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E349" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A350" s="2">
+        <v>49</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E350" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A351" s="2">
+        <v>50</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E351" s="2"/>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A352" s="2">
+        <v>51</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E352" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A353" s="2">
+        <v>52</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E353" s="2"/>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A354" s="2">
+        <v>53</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E354" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A355" s="2">
+        <v>54</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E355" s="2"/>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A356" s="2">
+        <v>55</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E356" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A357" s="2">
+        <v>56</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E357" s="2"/>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A358" s="2">
+        <v>57</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E358" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A359" s="2">
+        <v>58</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E359" s="2"/>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A360" s="2">
+        <v>59</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E360" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A361" s="2">
+        <v>60</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E361" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A362" s="2">
+        <v>61</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E362" s="2"/>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A363" s="2">
+        <v>62</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E363" s="2"/>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A364" s="2">
+        <v>63</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E364" s="2"/>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A365" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B365" s="2"/>
+      <c r="C365" s="2"/>
+      <c r="D365" s="2"/>
+      <c r="E365" s="2"/>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A366" s="2">
+        <v>65</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E366" s="2"/>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A367" s="2">
+        <v>66</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E367" s="2"/>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A368" s="2">
+        <v>67</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C368" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E368" s="6"/>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A369" s="2">
+        <v>68</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E369" s="2"/>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A370" s="2">
+        <v>69</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E370" s="2"/>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A371" s="2">
+        <v>70</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E371" s="2"/>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A372" s="2">
+        <v>71</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E372" s="2"/>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A373" s="2">
+        <v>72</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E373" s="2"/>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A374" s="2">
+        <v>73</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E374" s="2"/>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A375" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C375" s="2"/>
+      <c r="D375" s="2"/>
+      <c r="E375" s="2"/>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A376" s="2">
+        <v>3</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E376" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A377" s="2">
+        <v>4</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E377" s="2"/>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A378" s="2">
+        <v>5</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D378" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E378" s="2"/>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A379" s="2">
+        <v>6</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D379" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E379" s="2"/>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A380" s="2">
+        <v>7</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D380" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E380" s="2"/>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A381" s="2">
+        <v>8</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E381" s="2"/>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A382" s="2">
+        <v>9</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D382" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E382" s="2"/>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A383" s="2">
+        <v>10</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D383" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E383" s="2"/>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A384" s="2">
+        <v>11</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D384" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E384" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A385" s="2">
+        <v>12</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D385" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E385" s="2"/>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A386" s="2">
+        <v>13</v>
+      </c>
+      <c r="B386" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E386" s="2"/>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A387" s="2">
+        <v>14</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E387" s="2"/>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A388" s="2">
+        <v>15</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D388" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E388" s="2"/>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A389" s="2">
+        <v>16</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D389" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E389" s="2"/>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A390" s="2">
+        <v>17</v>
+      </c>
+      <c r="B390" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D390" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E390" s="2"/>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A391" s="2">
+        <v>18</v>
+      </c>
+      <c r="B391" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D391" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E391" s="2"/>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A392" s="2">
+        <v>19</v>
+      </c>
+      <c r="B392" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D392" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E392" s="2"/>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A393" s="2">
+        <v>20</v>
+      </c>
+      <c r="B393" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D393" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E393" s="2"/>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A394" s="2">
+        <v>21</v>
+      </c>
+      <c r="B394" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D394" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E394" s="2"/>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A395" s="2">
+        <v>22</v>
+      </c>
+      <c r="B395" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D395" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E395" s="2"/>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A396" s="2">
+        <v>23</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D396" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E396" s="2"/>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A397" s="2">
+        <v>24</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D397" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E397" s="2"/>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A398" s="2">
+        <v>25</v>
+      </c>
+      <c r="B398" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D398" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E398" s="2"/>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A399" s="2">
+        <v>26</v>
+      </c>
+      <c r="B399" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D399" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E399" s="2"/>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A400" s="2">
+        <v>27</v>
+      </c>
+      <c r="B400" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D400" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E400" s="2"/>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A401" s="2">
+        <v>28</v>
+      </c>
+      <c r="B401" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D401" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E401" s="2"/>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A402" s="2">
+        <v>29</v>
+      </c>
+      <c r="B402" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C402" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D402" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E402" s="2"/>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A403" s="2">
+        <v>30</v>
+      </c>
+      <c r="B403" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D403" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E403" s="2"/>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A404" s="2">
+        <v>31</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C404" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D404" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E404" s="2"/>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A405" s="2">
+        <v>32</v>
+      </c>
+      <c r="B405" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C405" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D405" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E405" s="2"/>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A406" s="2">
+        <v>33</v>
+      </c>
+      <c r="B406" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C406" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D406" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E406" s="2"/>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A407" s="2">
+        <v>34</v>
+      </c>
+      <c r="B407" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C407" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D407" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E407" s="2"/>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A408" s="2">
+        <v>35</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C408" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D408" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E408" s="2"/>
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A409" s="2">
+        <v>36</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C409" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D409" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E409" s="2"/>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A410" s="2">
+        <v>37</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C410" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D410" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E410" s="2"/>
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A411" s="2">
+        <v>38</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C411" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D411" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E411" s="2"/>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A412" s="2">
+        <v>39</v>
+      </c>
+      <c r="B412" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C412" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D412" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E412" s="2"/>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A413" s="2"/>
+      <c r="B413" s="4"/>
+      <c r="C413" s="2"/>
+      <c r="D413" s="2"/>
+      <c r="E413" s="2"/>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A414" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C414" s="2"/>
+      <c r="D414" s="2"/>
+      <c r="E414" s="2"/>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A415" s="2">
+        <v>3</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C415" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D415" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E415" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A416" s="2">
+        <v>4</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C416" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D416" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E416" s="2"/>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A417" s="2">
+        <v>5</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C417" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D417" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E417" s="2"/>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A418" s="2">
+        <v>6</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C418" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D418" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E418" s="2"/>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A419" s="2">
+        <v>7</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C419" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D419" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E419" s="2"/>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A420" s="2">
+        <v>8</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C420" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D420" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E420" s="2"/>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A421" s="2">
+        <v>9</v>
+      </c>
+      <c r="B421" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C421" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E421" s="2"/>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A422" s="2">
+        <v>10</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D422" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E422" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A423" s="2">
+        <v>11</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E423" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A424" s="2">
+        <v>12</v>
+      </c>
+      <c r="B424" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D424" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E424" s="2"/>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A425" s="2">
+        <v>13</v>
+      </c>
+      <c r="B425" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D425" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E425" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A426" s="2">
+        <v>14</v>
+      </c>
+      <c r="B426" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C426" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D426" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E426" s="2"/>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A427" s="2">
+        <v>15</v>
+      </c>
+      <c r="B427" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C427" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D427" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E427" s="2"/>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A428" s="2">
+        <v>16</v>
+      </c>
+      <c r="B428" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C428" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D428" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E428" s="2"/>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A429" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B429" s="2"/>
+      <c r="C429" s="2"/>
+      <c r="D429" s="2"/>
+      <c r="E429" s="2"/>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A430" s="2">
+        <v>143</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C430" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D430" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E430" s="2"/>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A431" s="2">
+        <v>144</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C431" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D431" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E431" s="2"/>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A432" s="2">
+        <v>145</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C432" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D432" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E432" s="2"/>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A433" s="2">
+        <v>146</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C433" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D433" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E433" s="2"/>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A434" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B434" s="2"/>
+      <c r="C434" s="2"/>
+      <c r="D434" s="2"/>
+      <c r="E434" s="2"/>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A435" s="2">
+        <v>148</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C435" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D435" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E435" s="2"/>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A436" s="2">
+        <v>149</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D436" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E436" s="2"/>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A437" s="2">
+        <v>150</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C437" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D437" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E437" s="2"/>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A438" s="2">
+        <v>151</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C438" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D438" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E438" s="2"/>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A439" s="2">
+        <v>152</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C439" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D439" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E439" s="2"/>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A440" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B440" s="2"/>
+      <c r="C440" s="2"/>
+      <c r="D440" s="2"/>
+      <c r="E440" s="2"/>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A441" s="2">
+        <v>154</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D441" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E441" s="2"/>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A442" s="2">
+        <v>155</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C442" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D442" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E442" s="2"/>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A443" s="2">
+        <v>156</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D443" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E443" s="2"/>
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A444" s="2">
+        <v>157</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C444" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D444" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E444" s="2"/>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A445" s="2">
+        <v>158</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C445" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D445" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E445" s="2"/>
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A446" s="2">
+        <v>159</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C446" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D446" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E446" s="2"/>
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A447" s="2">
+        <v>160</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C447" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D447" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E447" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E337" r:id="rId1" xr:uid="{3049D288-8E1D-4116-A8D0-763E1CE8AE8F}"/>
+    <hyperlink ref="E186" r:id="rId2" xr:uid="{AD643CED-9C04-4D51-8C00-8CC9D238E2E0}"/>
+    <hyperlink ref="E54" r:id="rId3" xr:uid="{CF726344-B0F5-41B3-92F1-04A7398AF1DB}"/>
+    <hyperlink ref="E33" r:id="rId4" xr:uid="{21F16D33-C79B-4D20-A11A-DE1429767799}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
@@ -9604,111 +16451,6 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1775AB-CB74-470A-BA63-5D8C0DD5BEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3016" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3017" uniqueCount="258">
   <si>
     <t>Keyword</t>
   </si>
@@ -800,11 +799,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;\-0\ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1008,7 +1007,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1040,27 +1039,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1092,24 +1073,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1285,9 +1248,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" customWidth="1"/>
@@ -1296,7 +1259,7 @@
     <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1313,7 +1276,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>71</v>
       </c>
@@ -1324,7 +1287,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -1341,7 +1304,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -1356,7 +1319,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -1371,16 +1334,18 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -1395,7 +1360,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -1410,7 +1375,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -1425,7 +1390,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -1440,7 +1405,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -1455,7 +1420,7 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -1470,7 +1435,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
         <v>72</v>
       </c>
@@ -1479,7 +1444,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -1496,7 +1461,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -1511,7 +1476,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -1528,7 +1493,7 @@
         <v>1231231</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -1543,7 +1508,7 @@
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -1558,7 +1523,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -1575,7 +1540,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -1590,7 +1555,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -1605,7 +1570,7 @@
       </c>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -1620,7 +1585,7 @@
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -1635,7 +1600,7 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
         <v>73</v>
       </c>
@@ -1644,7 +1609,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -1661,7 +1626,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -1678,7 +1643,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -1695,7 +1660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -1712,7 +1677,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -1729,7 +1694,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -1744,7 +1709,7 @@
       </c>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -1761,7 +1726,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -1778,7 +1743,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -1795,7 +1760,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -1810,7 +1775,7 @@
       </c>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -1825,7 +1790,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -1840,7 +1805,7 @@
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
         <v>74</v>
       </c>
@@ -1849,7 +1814,7 @@
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -1864,7 +1829,7 @@
       </c>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -1881,7 +1846,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -1898,7 +1863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -1915,7 +1880,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -1930,7 +1895,7 @@
       </c>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -1945,7 +1910,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>75</v>
       </c>
@@ -1954,7 +1919,7 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -1969,7 +1934,7 @@
       </c>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -1984,7 +1949,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -1999,7 +1964,7 @@
       </c>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -2014,7 +1979,7 @@
       </c>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -2029,7 +1994,7 @@
       </c>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -2046,7 +2011,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -2063,7 +2028,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -2080,7 +2045,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -2097,7 +2062,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -2114,7 +2079,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -2129,7 +2094,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -2144,7 +2109,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" s="2" t="s">
         <v>76</v>
       </c>
@@ -2153,7 +2118,7 @@
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -2168,7 +2133,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -2185,7 +2150,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -2202,7 +2167,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -2219,7 +2184,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -2234,7 +2199,7 @@
       </c>
       <c r="E62" s="6"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -2249,7 +2214,7 @@
       </c>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -2264,7 +2229,7 @@
       </c>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -2281,7 +2246,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -2298,7 +2263,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -2315,7 +2280,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -2330,7 +2295,7 @@
       </c>
       <c r="E68" s="6"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -2345,7 +2310,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -2360,7 +2325,7 @@
       </c>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -2377,7 +2342,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -2394,7 +2359,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -2411,7 +2376,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -2426,7 +2391,7 @@
       </c>
       <c r="E74" s="6"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -2441,7 +2406,7 @@
       </c>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" s="2" t="s">
         <v>77</v>
       </c>
@@ -2450,7 +2415,7 @@
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -2465,7 +2430,7 @@
       </c>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -2480,7 +2445,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -2495,7 +2460,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -2510,7 +2475,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" s="2" t="s">
         <v>78</v>
       </c>
@@ -2519,7 +2484,7 @@
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -2534,7 +2499,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -2549,7 +2514,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -2564,7 +2529,7 @@
       </c>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -2581,8 +2546,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E33" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E54" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E33" r:id="rId1"/>
+    <hyperlink ref="E54" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId3"/>
@@ -2590,9 +2555,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E107"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.5703125" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
@@ -2601,7 +2566,7 @@
     <col min="5" max="5" width="34.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -2618,7 +2583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>129</v>
       </c>
@@ -2629,7 +2594,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -2646,7 +2611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -2661,7 +2626,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -2676,7 +2641,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -2691,7 +2656,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -2706,7 +2671,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -2721,7 +2686,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -2736,7 +2701,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -2751,7 +2716,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>70</v>
       </c>
@@ -2760,7 +2725,7 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -2775,7 +2740,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -2790,7 +2755,7 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -2805,7 +2770,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -2820,7 +2785,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
         <v>217</v>
       </c>
@@ -2829,7 +2794,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -2846,7 +2811,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -2863,7 +2828,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -2880,7 +2845,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -2897,7 +2862,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -2914,7 +2879,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -2931,7 +2896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -2948,7 +2913,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -2965,7 +2930,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2982,7 +2947,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2999,7 +2964,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -3016,7 +2981,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -3031,7 +2996,7 @@
       </c>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -3048,7 +3013,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -3063,7 +3028,7 @@
       </c>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -3078,7 +3043,7 @@
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
         <v>72</v>
       </c>
@@ -3087,7 +3052,7 @@
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -3104,7 +3069,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -3119,7 +3084,7 @@
       </c>
       <c r="E34" s="10"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -3134,7 +3099,7 @@
       </c>
       <c r="E35" s="10"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -3151,7 +3116,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -3166,7 +3131,7 @@
       </c>
       <c r="E37" s="10"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -3181,7 +3146,7 @@
       </c>
       <c r="E38" s="10"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -3198,7 +3163,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -3213,7 +3178,7 @@
       </c>
       <c r="E40" s="10"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -3228,7 +3193,7 @@
       </c>
       <c r="E41" s="10"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -3245,7 +3210,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -3260,7 +3225,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -3275,7 +3240,7 @@
       </c>
       <c r="E44" s="10"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -3292,7 +3257,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -3307,7 +3272,7 @@
       </c>
       <c r="E46" s="10"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -3322,7 +3287,7 @@
       </c>
       <c r="E47" s="10"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -3339,7 +3304,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -3354,7 +3319,7 @@
       </c>
       <c r="E49" s="10"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -3369,7 +3334,7 @@
       </c>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -3386,7 +3351,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" s="2">
         <v>50</v>
       </c>
@@ -3401,7 +3366,7 @@
       </c>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" s="2">
         <v>51</v>
       </c>
@@ -3416,7 +3381,7 @@
       </c>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" s="2">
         <v>52</v>
       </c>
@@ -3433,7 +3398,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" s="2">
         <v>53</v>
       </c>
@@ -3448,7 +3413,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" s="2">
         <v>54</v>
       </c>
@@ -3463,7 +3428,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" s="2">
         <v>55</v>
       </c>
@@ -3480,7 +3445,7 @@
         <v>44594</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" s="2">
         <v>56</v>
       </c>
@@ -3497,7 +3462,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" s="2">
         <v>57</v>
       </c>
@@ -3512,7 +3477,7 @@
       </c>
       <c r="E59" s="2"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" s="2">
         <v>58</v>
       </c>
@@ -3527,7 +3492,7 @@
       </c>
       <c r="E60" s="2"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" s="2">
         <v>59</v>
       </c>
@@ -3542,7 +3507,7 @@
       </c>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" s="2">
         <v>60</v>
       </c>
@@ -3557,7 +3522,7 @@
       </c>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" s="2">
         <v>61</v>
       </c>
@@ -3572,7 +3537,7 @@
       </c>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" s="2">
         <v>62</v>
       </c>
@@ -3587,7 +3552,7 @@
       </c>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" s="2">
         <v>63</v>
       </c>
@@ -3604,7 +3569,7 @@
         <v>3234</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" s="2">
         <v>64</v>
       </c>
@@ -3621,7 +3586,7 @@
         <v>13234</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" s="2">
         <v>65</v>
       </c>
@@ -3636,7 +3601,7 @@
       </c>
       <c r="E67" s="2"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" s="2">
         <v>66</v>
       </c>
@@ -3651,7 +3616,7 @@
       </c>
       <c r="E68" s="2"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" s="2">
         <v>67</v>
       </c>
@@ -3666,7 +3631,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" s="2">
         <v>68</v>
       </c>
@@ -3681,7 +3646,7 @@
       </c>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" s="2" t="s">
         <v>118</v>
       </c>
@@ -3690,7 +3655,7 @@
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" s="2">
         <v>70</v>
       </c>
@@ -3705,7 +3670,7 @@
       </c>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" s="2">
         <v>71</v>
       </c>
@@ -3722,7 +3687,7 @@
         <v>7826423</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" s="2">
         <v>72</v>
       </c>
@@ -3739,7 +3704,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" s="2">
         <v>73</v>
       </c>
@@ -3756,7 +3721,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" s="2">
         <v>74</v>
       </c>
@@ -3773,7 +3738,7 @@
         <v>3478323</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77" s="2">
         <v>75</v>
       </c>
@@ -3788,7 +3753,7 @@
       </c>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" s="2">
         <v>76</v>
       </c>
@@ -3803,7 +3768,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79" s="2">
         <v>77</v>
       </c>
@@ -3818,7 +3783,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80" s="14">
         <v>78</v>
       </c>
@@ -3833,7 +3798,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" s="15" t="s">
         <v>123</v>
       </c>
@@ -3842,7 +3807,7 @@
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" s="15">
         <v>80</v>
       </c>
@@ -3857,7 +3822,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" s="15">
         <v>81</v>
       </c>
@@ -3874,7 +3839,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" s="15">
         <v>82</v>
       </c>
@@ -3891,7 +3856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" s="15">
         <v>83</v>
       </c>
@@ -3908,7 +3873,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86" s="15">
         <v>84</v>
       </c>
@@ -3925,7 +3890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87" s="15">
         <v>85</v>
       </c>
@@ -3940,7 +3905,7 @@
       </c>
       <c r="E87" s="2"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
       <c r="A88" s="15">
         <v>86</v>
       </c>
@@ -3955,7 +3920,7 @@
       </c>
       <c r="E88" s="2"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89" s="15">
         <v>87</v>
       </c>
@@ -3970,7 +3935,7 @@
       </c>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90" s="15">
         <v>88</v>
       </c>
@@ -3987,7 +3952,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
       <c r="A91" s="15">
         <v>89</v>
       </c>
@@ -4004,7 +3969,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92" s="15">
         <v>90</v>
       </c>
@@ -4021,7 +3986,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93" s="15">
         <v>91</v>
       </c>
@@ -4038,7 +4003,7 @@
         <v>3478323</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94" s="15">
         <v>92</v>
       </c>
@@ -4053,7 +4018,7 @@
       </c>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95" s="15">
         <v>93</v>
       </c>
@@ -4068,7 +4033,7 @@
       </c>
       <c r="E95" s="2"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96" s="15" t="s">
         <v>124</v>
       </c>
@@ -4077,7 +4042,7 @@
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" s="15">
         <v>95</v>
       </c>
@@ -4092,7 +4057,7 @@
       </c>
       <c r="E97" s="2"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98" s="15">
         <v>96</v>
       </c>
@@ -4107,7 +4072,7 @@
       </c>
       <c r="E98" s="2"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99" s="15">
         <v>97</v>
       </c>
@@ -4122,7 +4087,7 @@
       </c>
       <c r="E99" s="2"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100" s="15">
         <v>98</v>
       </c>
@@ -4137,7 +4102,7 @@
       </c>
       <c r="E100" s="2"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5">
       <c r="A101" s="15">
         <v>99</v>
       </c>
@@ -4152,7 +4117,7 @@
       </c>
       <c r="E101" s="2"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5">
       <c r="A102" s="15">
         <v>100</v>
       </c>
@@ -4167,7 +4132,7 @@
       </c>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5">
       <c r="A103" s="15" t="s">
         <v>128</v>
       </c>
@@ -4176,7 +4141,7 @@
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5">
       <c r="A104" s="15">
         <v>101</v>
       </c>
@@ -4191,7 +4156,7 @@
       </c>
       <c r="E104" s="2"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5">
       <c r="A105" s="15">
         <v>102</v>
       </c>
@@ -4206,7 +4171,7 @@
       </c>
       <c r="E105" s="2"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5">
       <c r="A106" s="15">
         <v>103</v>
       </c>
@@ -4221,7 +4186,7 @@
       </c>
       <c r="E106" s="2"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5">
       <c r="A107" s="15">
         <v>104</v>
       </c>
@@ -4243,9 +4208,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E160"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="53.7109375" style="17" customWidth="1"/>
     <col min="2" max="2" width="35.28515625" style="17" customWidth="1"/>
@@ -4255,7 +4220,7 @@
     <col min="6" max="16384" width="9.140625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -4272,7 +4237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>130</v>
       </c>
@@ -4283,7 +4248,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -4300,7 +4265,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -4315,7 +4280,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -4330,7 +4295,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -4345,7 +4310,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -4360,7 +4325,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -4375,7 +4340,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -4390,7 +4355,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -4405,7 +4370,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -4422,7 +4387,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>146</v>
       </c>
@@ -4431,7 +4396,7 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -4446,7 +4411,7 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -4461,7 +4426,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -4478,7 +4443,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -4495,7 +4460,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -4512,7 +4477,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -4529,7 +4494,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -4546,7 +4511,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -4563,7 +4528,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -4580,7 +4545,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -4595,7 +4560,7 @@
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -4610,7 +4575,7 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -4625,7 +4590,7 @@
       </c>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -4642,7 +4607,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -4659,7 +4624,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -4676,7 +4641,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -4691,7 +4656,7 @@
       </c>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -4706,7 +4671,7 @@
       </c>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
         <v>164</v>
       </c>
@@ -4715,7 +4680,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -4730,7 +4695,7 @@
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -4745,7 +4710,7 @@
       </c>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -4760,7 +4725,7 @@
       </c>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -4777,7 +4742,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -4792,7 +4757,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -4807,7 +4772,7 @@
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -4822,7 +4787,7 @@
       </c>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -4837,7 +4802,7 @@
       </c>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -4852,7 +4817,7 @@
       </c>
       <c r="E39" s="2"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
         <v>167</v>
       </c>
@@ -4861,7 +4826,7 @@
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -4878,7 +4843,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -4895,7 +4860,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -4912,7 +4877,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -4927,7 +4892,7 @@
       </c>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -4944,7 +4909,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -4959,7 +4924,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -4976,7 +4941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -4991,7 +4956,7 @@
       </c>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -5008,7 +4973,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -5023,7 +4988,7 @@
       </c>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -5040,7 +5005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -5055,7 +5020,7 @@
       </c>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -5072,7 +5037,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -5087,7 +5052,7 @@
       </c>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -5104,7 +5069,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -5119,7 +5084,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -5134,7 +5099,7 @@
       </c>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -5149,7 +5114,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" s="2" t="s">
         <v>181</v>
       </c>
@@ -5158,7 +5123,7 @@
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -5175,7 +5140,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -5190,7 +5155,7 @@
       </c>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -5205,7 +5170,7 @@
       </c>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -5222,7 +5187,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -5239,7 +5204,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -5254,7 +5219,7 @@
       </c>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -5265,7 +5230,7 @@
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -5282,7 +5247,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -5299,7 +5264,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -5314,7 +5279,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -5329,7 +5294,7 @@
       </c>
       <c r="E70" s="6"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -5346,7 +5311,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -5361,7 +5326,7 @@
       </c>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -5378,7 +5343,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -5393,7 +5358,7 @@
       </c>
       <c r="E74" s="2"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -5408,7 +5373,7 @@
       </c>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" s="2">
         <v>76</v>
       </c>
@@ -5423,7 +5388,7 @@
       </c>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -5440,7 +5405,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -5455,7 +5420,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -5470,7 +5435,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -5485,7 +5450,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" s="2">
         <v>81</v>
       </c>
@@ -5502,7 +5467,7 @@
         <v>3.4628376482734602E+18</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -5517,7 +5482,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -5532,7 +5497,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -5547,7 +5512,7 @@
       </c>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -5564,7 +5529,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86" s="2">
         <v>86</v>
       </c>
@@ -5579,7 +5544,7 @@
       </c>
       <c r="E86" s="2"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87" s="2">
         <v>87</v>
       </c>
@@ -5594,7 +5559,7 @@
       </c>
       <c r="E87" s="2"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
       <c r="A88" s="2">
         <v>88</v>
       </c>
@@ -5609,7 +5574,7 @@
       </c>
       <c r="E88" s="2"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89" s="2">
         <v>89</v>
       </c>
@@ -5626,7 +5591,7 @@
         <v>3.4628376482734602E+18</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90" s="2">
         <v>90</v>
       </c>
@@ -5641,7 +5606,7 @@
       </c>
       <c r="E90" s="2"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
       <c r="A91" s="2">
         <v>91</v>
       </c>
@@ -5656,7 +5621,7 @@
       </c>
       <c r="E91" s="2"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92" s="2">
         <v>92</v>
       </c>
@@ -5673,7 +5638,7 @@
         <v>44854</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93" s="2">
         <v>93</v>
       </c>
@@ -5690,7 +5655,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94" s="2">
         <v>94</v>
       </c>
@@ -5705,7 +5670,7 @@
       </c>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95" s="2">
         <v>95</v>
       </c>
@@ -5720,7 +5685,7 @@
       </c>
       <c r="E95" s="2"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96" s="2">
         <v>96</v>
       </c>
@@ -5735,7 +5700,7 @@
       </c>
       <c r="E96" s="2"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" s="2">
         <v>97</v>
       </c>
@@ -5750,7 +5715,7 @@
       </c>
       <c r="E97" s="2"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98" s="2">
         <v>98</v>
       </c>
@@ -5765,7 +5730,7 @@
       </c>
       <c r="E98" s="2"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99" s="2" t="s">
         <v>118</v>
       </c>
@@ -5774,7 +5739,7 @@
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100" s="2">
         <v>100</v>
       </c>
@@ -5789,7 +5754,7 @@
       </c>
       <c r="E100" s="2"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5">
       <c r="A101" s="2">
         <v>101</v>
       </c>
@@ -5806,7 +5771,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5">
       <c r="A102" s="2">
         <v>102</v>
       </c>
@@ -5821,7 +5786,7 @@
       </c>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5">
       <c r="A103" s="2">
         <v>103</v>
       </c>
@@ -5836,7 +5801,7 @@
       </c>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5">
       <c r="A104" s="2">
         <v>104</v>
       </c>
@@ -5853,7 +5818,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5">
       <c r="A105" s="2">
         <v>105</v>
       </c>
@@ -5870,7 +5835,7 @@
         <v>7600</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5">
       <c r="A106" s="2">
         <v>106</v>
       </c>
@@ -5887,7 +5852,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -5904,7 +5869,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5">
       <c r="A108" s="2">
         <v>108</v>
       </c>
@@ -5919,7 +5884,7 @@
       </c>
       <c r="E108" s="2"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5">
       <c r="A109" s="2">
         <v>109</v>
       </c>
@@ -5934,7 +5899,7 @@
       </c>
       <c r="E109" s="2"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5">
       <c r="A110" s="2" t="s">
         <v>131</v>
       </c>
@@ -5943,7 +5908,7 @@
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5">
       <c r="A111" s="2">
         <v>111</v>
       </c>
@@ -5958,7 +5923,7 @@
       </c>
       <c r="E111" s="2"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5">
       <c r="A112" s="2">
         <v>112</v>
       </c>
@@ -5973,7 +5938,7 @@
       </c>
       <c r="E112" s="2"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5">
       <c r="A113" s="2">
         <v>113</v>
       </c>
@@ -5988,7 +5953,7 @@
       </c>
       <c r="E113" s="2"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5">
       <c r="A114" s="2">
         <v>114</v>
       </c>
@@ -6003,7 +5968,7 @@
       </c>
       <c r="E114" s="2"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5">
       <c r="A115" s="2">
         <v>115</v>
       </c>
@@ -6018,7 +5983,7 @@
       </c>
       <c r="E115" s="2"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5">
       <c r="A116" s="2">
         <v>116</v>
       </c>
@@ -6033,7 +5998,7 @@
       </c>
       <c r="E116" s="2"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5">
       <c r="A117" s="2">
         <v>117</v>
       </c>
@@ -6048,7 +6013,7 @@
       </c>
       <c r="E117" s="2"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5">
       <c r="A118" s="2">
         <v>118</v>
       </c>
@@ -6063,7 +6028,7 @@
       </c>
       <c r="E118" s="2"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5">
       <c r="A119" s="2">
         <v>119</v>
       </c>
@@ -6078,7 +6043,7 @@
       </c>
       <c r="E119" s="2"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5">
       <c r="A120" s="2">
         <v>120</v>
       </c>
@@ -6095,7 +6060,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5">
       <c r="A121" s="2">
         <v>121</v>
       </c>
@@ -6112,7 +6077,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5">
       <c r="A122" s="2">
         <v>122</v>
       </c>
@@ -6129,7 +6094,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5">
       <c r="A123" s="2">
         <v>123</v>
       </c>
@@ -6146,7 +6111,7 @@
         <v>12323</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5">
       <c r="A124" s="2">
         <v>124</v>
       </c>
@@ -6161,7 +6126,7 @@
       </c>
       <c r="E124" s="2"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5">
       <c r="A125" s="2">
         <v>125</v>
       </c>
@@ -6176,7 +6141,7 @@
       </c>
       <c r="E125" s="2"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5">
       <c r="A126" s="2">
         <v>126</v>
       </c>
@@ -6191,7 +6156,7 @@
       </c>
       <c r="E126" s="2"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5">
       <c r="A127" s="2" t="s">
         <v>253</v>
       </c>
@@ -6200,7 +6165,7 @@
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5">
       <c r="A128" s="2">
         <v>128</v>
       </c>
@@ -6215,7 +6180,7 @@
       </c>
       <c r="E128" s="2"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5">
       <c r="A129" s="2">
         <v>129</v>
       </c>
@@ -6230,7 +6195,7 @@
       </c>
       <c r="E129" s="2"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5">
       <c r="A130" s="2">
         <v>130</v>
       </c>
@@ -6245,7 +6210,7 @@
       </c>
       <c r="E130" s="2"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5">
       <c r="A131" s="2">
         <v>131</v>
       </c>
@@ -6260,7 +6225,7 @@
       </c>
       <c r="E131" s="2"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5">
       <c r="A132" s="2">
         <v>132</v>
       </c>
@@ -6277,7 +6242,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5">
       <c r="A133" s="2">
         <v>133</v>
       </c>
@@ -6292,7 +6257,7 @@
       </c>
       <c r="E133" s="2"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5">
       <c r="A134" s="2">
         <v>134</v>
       </c>
@@ -6307,7 +6272,7 @@
       </c>
       <c r="E134" s="2"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5">
       <c r="A135" s="2" t="s">
         <v>139</v>
       </c>
@@ -6316,7 +6281,7 @@
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5">
       <c r="A136" s="2">
         <v>136</v>
       </c>
@@ -6331,7 +6296,7 @@
       </c>
       <c r="E136" s="2"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5">
       <c r="A137" s="2">
         <v>137</v>
       </c>
@@ -6346,7 +6311,7 @@
       </c>
       <c r="E137" s="2"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5">
       <c r="A138" s="2">
         <v>138</v>
       </c>
@@ -6361,7 +6326,7 @@
       </c>
       <c r="E138" s="2"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5">
       <c r="A139" s="2">
         <v>139</v>
       </c>
@@ -6376,7 +6341,7 @@
       </c>
       <c r="E139" s="2"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5">
       <c r="A140" s="2">
         <v>140</v>
       </c>
@@ -6391,7 +6356,7 @@
       </c>
       <c r="E140" s="2"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5">
       <c r="A141" s="2">
         <v>141</v>
       </c>
@@ -6406,7 +6371,7 @@
       </c>
       <c r="E141" s="2"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5">
       <c r="A142" s="2" t="s">
         <v>141</v>
       </c>
@@ -6415,7 +6380,7 @@
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5">
       <c r="A143" s="2">
         <v>143</v>
       </c>
@@ -6430,7 +6395,7 @@
       </c>
       <c r="E143" s="2"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5">
       <c r="A144" s="2">
         <v>144</v>
       </c>
@@ -6445,7 +6410,7 @@
       </c>
       <c r="E144" s="2"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5">
       <c r="A145" s="2">
         <v>145</v>
       </c>
@@ -6460,7 +6425,7 @@
       </c>
       <c r="E145" s="2"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5">
       <c r="A146" s="2">
         <v>146</v>
       </c>
@@ -6475,7 +6440,7 @@
       </c>
       <c r="E146" s="2"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5">
       <c r="A147" s="2" t="s">
         <v>128</v>
       </c>
@@ -6484,7 +6449,7 @@
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5">
       <c r="A148" s="2">
         <v>148</v>
       </c>
@@ -6499,7 +6464,7 @@
       </c>
       <c r="E148" s="2"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5">
       <c r="A149" s="2">
         <v>149</v>
       </c>
@@ -6514,7 +6479,7 @@
       </c>
       <c r="E149" s="2"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5">
       <c r="A150" s="2">
         <v>150</v>
       </c>
@@ -6529,7 +6494,7 @@
       </c>
       <c r="E150" s="2"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5">
       <c r="A151" s="2">
         <v>151</v>
       </c>
@@ -6544,7 +6509,7 @@
       </c>
       <c r="E151" s="2"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5">
       <c r="A152" s="2">
         <v>152</v>
       </c>
@@ -6559,7 +6524,7 @@
       </c>
       <c r="E152" s="2"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5">
       <c r="A153" s="2" t="s">
         <v>200</v>
       </c>
@@ -6568,7 +6533,7 @@
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5">
       <c r="A154" s="2">
         <v>154</v>
       </c>
@@ -6583,7 +6548,7 @@
       </c>
       <c r="E154" s="2"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5">
       <c r="A155" s="2">
         <v>155</v>
       </c>
@@ -6598,7 +6563,7 @@
       </c>
       <c r="E155" s="2"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5">
       <c r="A156" s="2">
         <v>156</v>
       </c>
@@ -6613,7 +6578,7 @@
       </c>
       <c r="E156" s="2"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5">
       <c r="A157" s="2">
         <v>157</v>
       </c>
@@ -6628,7 +6593,7 @@
       </c>
       <c r="E157" s="2"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5">
       <c r="A158" s="2">
         <v>158</v>
       </c>
@@ -6643,7 +6608,7 @@
       </c>
       <c r="E158" s="2"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5">
       <c r="A159" s="2">
         <v>159</v>
       </c>
@@ -6658,7 +6623,7 @@
       </c>
       <c r="E159" s="2"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5">
       <c r="A160" s="2">
         <v>160</v>
       </c>
@@ -6676,7 +6641,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E18" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="E18" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId2"/>
@@ -6684,9 +6649,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E116"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" customWidth="1"/>
@@ -6695,7 +6660,7 @@
     <col min="5" max="5" width="52.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -6712,7 +6677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>129</v>
       </c>
@@ -6723,7 +6688,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -6740,7 +6705,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -6755,7 +6720,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -6770,7 +6735,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -6785,7 +6750,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -6800,7 +6765,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -6815,7 +6780,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -6830,7 +6795,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
         <v>204</v>
       </c>
@@ -6839,7 +6804,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -6856,7 +6821,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -6873,7 +6838,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -6890,7 +6855,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -6907,7 +6872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -6924,7 +6889,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -6941,7 +6906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -6958,7 +6923,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -6975,7 +6940,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -6992,7 +6957,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -7009,7 +6974,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -7026,7 +6991,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -7043,7 +7008,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -7058,7 +7023,7 @@
       </c>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -7073,7 +7038,7 @@
       </c>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -7088,7 +7053,7 @@
       </c>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -7103,7 +7068,7 @@
       </c>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -7118,7 +7083,7 @@
       </c>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -7133,7 +7098,7 @@
       </c>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -7150,7 +7115,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
         <v>146</v>
       </c>
@@ -7159,7 +7124,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -7174,7 +7139,7 @@
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -7189,7 +7154,7 @@
       </c>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -7206,7 +7171,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -7223,7 +7188,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -7240,7 +7205,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -7257,7 +7222,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -7274,7 +7239,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -7291,7 +7256,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -7308,7 +7273,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -7323,7 +7288,7 @@
       </c>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -7338,7 +7303,7 @@
       </c>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -7353,7 +7318,7 @@
       </c>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -7368,7 +7333,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -7383,7 +7348,7 @@
       </c>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -7400,7 +7365,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -7415,7 +7380,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -7432,7 +7397,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -7449,7 +7414,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -7466,7 +7431,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -7481,7 +7446,7 @@
       </c>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -7498,7 +7463,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -7513,7 +7478,7 @@
       </c>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -7530,7 +7495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -7545,7 +7510,7 @@
       </c>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -7562,7 +7527,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -7577,7 +7542,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -7594,7 +7559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -7609,7 +7574,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -7626,7 +7591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -7643,7 +7608,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -7658,7 +7623,7 @@
       </c>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -7673,7 +7638,7 @@
       </c>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -7688,7 +7653,7 @@
       </c>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
         <v>205</v>
       </c>
@@ -7697,7 +7662,7 @@
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -7712,7 +7677,7 @@
       </c>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -7727,7 +7692,7 @@
       </c>
       <c r="E66" s="2"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -7742,7 +7707,7 @@
       </c>
       <c r="E67" s="6"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -7757,7 +7722,7 @@
       </c>
       <c r="E68" s="2"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -7772,7 +7737,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -7787,7 +7752,7 @@
       </c>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -7802,7 +7767,7 @@
       </c>
       <c r="E71" s="2"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -7817,7 +7782,7 @@
       </c>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -7832,7 +7797,7 @@
       </c>
       <c r="E73" s="2"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" s="2" t="s">
         <v>141</v>
       </c>
@@ -7841,7 +7806,7 @@
       <c r="D74" s="2"/>
       <c r="E74" s="6"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -7856,7 +7821,7 @@
       </c>
       <c r="E75" s="6"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" s="2">
         <v>76</v>
       </c>
@@ -7871,7 +7836,7 @@
       </c>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -7886,7 +7851,7 @@
       </c>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -7901,7 +7866,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -7916,7 +7881,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -7931,7 +7896,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" s="2">
         <v>81</v>
       </c>
@@ -7946,7 +7911,7 @@
       </c>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -7963,7 +7928,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -7978,7 +7943,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -7993,7 +7958,7 @@
       </c>
       <c r="E84" s="10"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -8008,7 +7973,7 @@
       </c>
       <c r="E85" s="2"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86" s="2">
         <v>86</v>
       </c>
@@ -8025,7 +7990,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87" s="2">
         <v>87</v>
       </c>
@@ -8040,7 +8005,7 @@
       </c>
       <c r="E87" s="6"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
       <c r="A88" s="2">
         <v>88</v>
       </c>
@@ -8057,7 +8022,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89" s="2">
         <v>89</v>
       </c>
@@ -8072,7 +8037,7 @@
       </c>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90" s="2">
         <v>90</v>
       </c>
@@ -8089,7 +8054,7 @@
         <v>10340</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
       <c r="A91" s="2">
         <v>91</v>
       </c>
@@ -8104,7 +8069,7 @@
       </c>
       <c r="E91" s="2"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92" s="2">
         <v>92</v>
       </c>
@@ -8119,7 +8084,7 @@
       </c>
       <c r="E92" s="2"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93" s="2">
         <v>93</v>
       </c>
@@ -8134,7 +8099,7 @@
       </c>
       <c r="E93" s="2"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94" s="2">
         <v>94</v>
       </c>
@@ -8149,7 +8114,7 @@
       </c>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95" s="2">
         <v>95</v>
       </c>
@@ -8164,7 +8129,7 @@
       </c>
       <c r="E95" s="2"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96" s="2">
         <v>96</v>
       </c>
@@ -8179,7 +8144,7 @@
       </c>
       <c r="E96" s="2"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" s="2">
         <v>97</v>
       </c>
@@ -8194,7 +8159,7 @@
       </c>
       <c r="E97" s="2"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98" s="2" t="s">
         <v>141</v>
       </c>
@@ -8203,7 +8168,7 @@
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99" s="2">
         <v>99</v>
       </c>
@@ -8218,7 +8183,7 @@
       </c>
       <c r="E99" s="2"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100" s="2">
         <v>100</v>
       </c>
@@ -8233,7 +8198,7 @@
       </c>
       <c r="E100" s="2"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5">
       <c r="A101" s="2">
         <v>101</v>
       </c>
@@ -8248,7 +8213,7 @@
       </c>
       <c r="E101" s="2"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5">
       <c r="A102" s="2">
         <v>102</v>
       </c>
@@ -8263,7 +8228,7 @@
       </c>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5">
       <c r="A103" s="2">
         <v>103</v>
       </c>
@@ -8278,7 +8243,7 @@
       </c>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5">
       <c r="A104" s="2">
         <v>104</v>
       </c>
@@ -8293,7 +8258,7 @@
       </c>
       <c r="E104" s="2"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5">
       <c r="A105" s="2" t="s">
         <v>128</v>
       </c>
@@ -8302,7 +8267,7 @@
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5">
       <c r="A106" s="2">
         <v>106</v>
       </c>
@@ -8317,7 +8282,7 @@
       </c>
       <c r="E106" s="2"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -8332,7 +8297,7 @@
       </c>
       <c r="E107" s="2"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5">
       <c r="A108" s="2">
         <v>108</v>
       </c>
@@ -8347,7 +8312,7 @@
       </c>
       <c r="E108" s="2"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5">
       <c r="A109" s="2">
         <v>109</v>
       </c>
@@ -8362,7 +8327,7 @@
       </c>
       <c r="E109" s="2"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5">
       <c r="A110" s="2">
         <v>110</v>
       </c>
@@ -8377,7 +8342,7 @@
       </c>
       <c r="E110" s="2"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5">
       <c r="A111" s="2">
         <v>111</v>
       </c>
@@ -8392,7 +8357,7 @@
       </c>
       <c r="E111" s="2"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5">
       <c r="A112" s="2">
         <v>112</v>
       </c>
@@ -8407,7 +8372,7 @@
       </c>
       <c r="E112" s="2"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5">
       <c r="A113" s="2">
         <v>113</v>
       </c>
@@ -8422,7 +8387,7 @@
       </c>
       <c r="E113" s="2"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5">
       <c r="A114" s="2">
         <v>114</v>
       </c>
@@ -8437,7 +8402,7 @@
       </c>
       <c r="E114" s="2"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5">
       <c r="A115" s="2">
         <v>115</v>
       </c>
@@ -8452,7 +8417,7 @@
       </c>
       <c r="E115" s="2"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5">
       <c r="A116" s="2">
         <v>116</v>
       </c>
@@ -8469,7 +8434,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E36" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="E36" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId2"/>
@@ -8477,9 +8442,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.140625" customWidth="1"/>
@@ -8488,7 +8453,7 @@
     <col min="5" max="5" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -8505,7 +8470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>252</v>
       </c>
@@ -8516,7 +8481,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -8533,7 +8498,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -8548,7 +8513,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -8563,7 +8528,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -8578,7 +8543,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -8593,7 +8558,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -8608,7 +8573,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -8623,7 +8588,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -8638,7 +8603,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -8655,7 +8620,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -8670,7 +8635,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -8685,7 +8650,7 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -8700,7 +8665,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -8715,7 +8680,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -8730,7 +8695,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -8745,7 +8710,7 @@
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -8760,7 +8725,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -8775,7 +8740,7 @@
       </c>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -8790,7 +8755,7 @@
       </c>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -8805,7 +8770,7 @@
       </c>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -8820,7 +8785,7 @@
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -8835,7 +8800,7 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -8850,7 +8815,7 @@
       </c>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -8865,7 +8830,7 @@
       </c>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -8880,7 +8845,7 @@
       </c>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -8895,7 +8860,7 @@
       </c>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -8910,7 +8875,7 @@
       </c>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -8925,7 +8890,7 @@
       </c>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -8940,7 +8905,7 @@
       </c>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -8955,7 +8920,7 @@
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -8970,7 +8935,7 @@
       </c>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -8985,7 +8950,7 @@
       </c>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -9000,7 +8965,7 @@
       </c>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -9015,7 +8980,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -9030,7 +8995,7 @@
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -9045,7 +9010,7 @@
       </c>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -9060,7 +9025,7 @@
       </c>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -9075,7 +9040,7 @@
       </c>
       <c r="E39" s="2"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
         <v>141</v>
       </c>
@@ -9084,7 +9049,7 @@
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -9099,7 +9064,7 @@
       </c>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -9114,7 +9079,7 @@
       </c>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -9129,7 +9094,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -9144,7 +9109,7 @@
       </c>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" s="2" t="s">
         <v>128</v>
       </c>
@@ -9153,7 +9118,7 @@
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -9168,7 +9133,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -9183,7 +9148,7 @@
       </c>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -9198,7 +9163,7 @@
       </c>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -9213,7 +9178,7 @@
       </c>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -9228,7 +9193,7 @@
       </c>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" s="2" t="s">
         <v>200</v>
       </c>
@@ -9237,7 +9202,7 @@
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -9252,7 +9217,7 @@
       </c>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -9267,7 +9232,7 @@
       </c>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -9282,7 +9247,7 @@
       </c>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -9297,7 +9262,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -9312,7 +9277,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -9327,7 +9292,7 @@
       </c>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -9348,9 +9313,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279E6F6B-0D50-4643-8FCD-F621627AC8FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E447"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
     <col min="2" max="2" width="26.140625" customWidth="1"/>
@@ -9359,7 +9324,7 @@
     <col min="5" max="5" width="49.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -9376,7 +9341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>71</v>
       </c>
@@ -9387,7 +9352,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -9404,7 +9369,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -9419,7 +9384,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -9434,7 +9399,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -9443,7 +9408,7 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -9458,7 +9423,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -9473,7 +9438,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -9488,7 +9453,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -9503,7 +9468,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -9518,7 +9483,7 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -9533,7 +9498,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
         <v>72</v>
       </c>
@@ -9542,7 +9507,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -9559,7 +9524,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -9574,7 +9539,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -9591,7 +9556,7 @@
         <v>1231231</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -9606,7 +9571,7 @@
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -9621,7 +9586,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -9638,7 +9603,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -9653,7 +9618,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -9668,7 +9633,7 @@
       </c>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -9683,7 +9648,7 @@
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -9698,7 +9663,7 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
         <v>73</v>
       </c>
@@ -9707,7 +9672,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -9724,7 +9689,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -9741,7 +9706,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -9758,7 +9723,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -9775,7 +9740,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -9792,7 +9757,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -9807,7 +9772,7 @@
       </c>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -9824,7 +9789,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -9841,7 +9806,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -9858,7 +9823,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -9873,7 +9838,7 @@
       </c>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -9888,7 +9853,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -9903,7 +9868,7 @@
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
         <v>74</v>
       </c>
@@ -9912,7 +9877,7 @@
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -9927,7 +9892,7 @@
       </c>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -9944,7 +9909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -9961,7 +9926,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -9978,7 +9943,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -9993,7 +9958,7 @@
       </c>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -10008,7 +9973,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>75</v>
       </c>
@@ -10017,7 +9982,7 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -10032,7 +9997,7 @@
       </c>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -10047,7 +10012,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -10062,7 +10027,7 @@
       </c>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -10077,7 +10042,7 @@
       </c>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -10092,7 +10057,7 @@
       </c>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -10109,7 +10074,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -10126,7 +10091,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -10143,7 +10108,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -10160,7 +10125,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -10177,7 +10142,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -10192,7 +10157,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -10207,7 +10172,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" s="2" t="s">
         <v>76</v>
       </c>
@@ -10216,7 +10181,7 @@
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -10231,7 +10196,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -10248,7 +10213,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -10265,7 +10230,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -10282,7 +10247,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -10297,7 +10262,7 @@
       </c>
       <c r="E62" s="6"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -10312,7 +10277,7 @@
       </c>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -10327,7 +10292,7 @@
       </c>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -10344,7 +10309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -10361,7 +10326,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -10378,7 +10343,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -10393,7 +10358,7 @@
       </c>
       <c r="E68" s="6"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -10408,7 +10373,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -10423,7 +10388,7 @@
       </c>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -10440,7 +10405,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -10457,7 +10422,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -10474,7 +10439,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -10489,7 +10454,7 @@
       </c>
       <c r="E74" s="6"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -10504,7 +10469,7 @@
       </c>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" s="2" t="s">
         <v>129</v>
       </c>
@@ -10515,7 +10480,7 @@
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77" s="2">
         <v>1</v>
       </c>
@@ -10532,7 +10497,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" s="2">
         <v>2</v>
       </c>
@@ -10547,7 +10512,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79" s="2">
         <v>3</v>
       </c>
@@ -10562,7 +10527,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80" s="2">
         <v>4</v>
       </c>
@@ -10577,7 +10542,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" s="2">
         <v>5</v>
       </c>
@@ -10592,7 +10557,7 @@
       </c>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" s="2">
         <v>6</v>
       </c>
@@ -10607,7 +10572,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" s="2">
         <v>7</v>
       </c>
@@ -10622,7 +10587,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" s="2">
         <v>8</v>
       </c>
@@ -10637,7 +10602,7 @@
       </c>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" s="2" t="s">
         <v>70</v>
       </c>
@@ -10646,7 +10611,7 @@
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86" s="2">
         <v>10</v>
       </c>
@@ -10661,7 +10626,7 @@
       </c>
       <c r="E86" s="2"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87" s="2">
         <v>11</v>
       </c>
@@ -10676,7 +10641,7 @@
       </c>
       <c r="E87" s="2"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
       <c r="A88" s="2">
         <v>12</v>
       </c>
@@ -10691,7 +10656,7 @@
       </c>
       <c r="E88" s="2"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89" s="2">
         <v>13</v>
       </c>
@@ -10706,7 +10671,7 @@
       </c>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90" s="2" t="s">
         <v>217</v>
       </c>
@@ -10715,7 +10680,7 @@
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
       <c r="A91" s="2">
         <v>15</v>
       </c>
@@ -10732,7 +10697,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92" s="2">
         <v>16</v>
       </c>
@@ -10749,7 +10714,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93" s="2">
         <v>17</v>
       </c>
@@ -10766,7 +10731,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94" s="2">
         <v>18</v>
       </c>
@@ -10783,7 +10748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95" s="2">
         <v>19</v>
       </c>
@@ -10800,7 +10765,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96" s="2">
         <v>20</v>
       </c>
@@ -10817,7 +10782,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" s="2">
         <v>21</v>
       </c>
@@ -10834,7 +10799,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98" s="2">
         <v>22</v>
       </c>
@@ -10851,7 +10816,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99" s="2">
         <v>23</v>
       </c>
@@ -10868,7 +10833,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100" s="2">
         <v>24</v>
       </c>
@@ -10885,7 +10850,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5">
       <c r="A101" s="2">
         <v>25</v>
       </c>
@@ -10902,7 +10867,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5">
       <c r="A102" s="2">
         <v>26</v>
       </c>
@@ -10917,7 +10882,7 @@
       </c>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5">
       <c r="A103" s="2">
         <v>27</v>
       </c>
@@ -10934,7 +10899,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5">
       <c r="A104" s="2">
         <v>29</v>
       </c>
@@ -10949,7 +10914,7 @@
       </c>
       <c r="E104" s="2"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5">
       <c r="A105" s="2">
         <v>30</v>
       </c>
@@ -10964,7 +10929,7 @@
       </c>
       <c r="E105" s="2"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5">
       <c r="A106" s="2" t="s">
         <v>72</v>
       </c>
@@ -10973,7 +10938,7 @@
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5">
       <c r="A107" s="2">
         <v>31</v>
       </c>
@@ -10990,7 +10955,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5">
       <c r="A108" s="2">
         <v>32</v>
       </c>
@@ -11005,7 +10970,7 @@
       </c>
       <c r="E108" s="10"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5">
       <c r="A109" s="2">
         <v>33</v>
       </c>
@@ -11020,7 +10985,7 @@
       </c>
       <c r="E109" s="10"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5">
       <c r="A110" s="2">
         <v>34</v>
       </c>
@@ -11037,7 +11002,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5">
       <c r="A111" s="2">
         <v>35</v>
       </c>
@@ -11052,7 +11017,7 @@
       </c>
       <c r="E111" s="10"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5">
       <c r="A112" s="2">
         <v>36</v>
       </c>
@@ -11067,7 +11032,7 @@
       </c>
       <c r="E112" s="10"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5">
       <c r="A113" s="2">
         <v>37</v>
       </c>
@@ -11084,7 +11049,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5">
       <c r="A114" s="2">
         <v>38</v>
       </c>
@@ -11099,7 +11064,7 @@
       </c>
       <c r="E114" s="10"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5">
       <c r="A115" s="2">
         <v>39</v>
       </c>
@@ -11114,7 +11079,7 @@
       </c>
       <c r="E115" s="10"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5">
       <c r="A116" s="2">
         <v>40</v>
       </c>
@@ -11131,7 +11096,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5">
       <c r="A117" s="2">
         <v>41</v>
       </c>
@@ -11146,7 +11111,7 @@
       </c>
       <c r="E117" s="2"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5">
       <c r="A118" s="2">
         <v>42</v>
       </c>
@@ -11161,7 +11126,7 @@
       </c>
       <c r="E118" s="10"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5">
       <c r="A119" s="2">
         <v>43</v>
       </c>
@@ -11178,7 +11143,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5">
       <c r="A120" s="2">
         <v>44</v>
       </c>
@@ -11193,7 +11158,7 @@
       </c>
       <c r="E120" s="10"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5">
       <c r="A121" s="2">
         <v>45</v>
       </c>
@@ -11208,7 +11173,7 @@
       </c>
       <c r="E121" s="10"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5">
       <c r="A122" s="2">
         <v>46</v>
       </c>
@@ -11225,7 +11190,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5">
       <c r="A123" s="2">
         <v>47</v>
       </c>
@@ -11240,7 +11205,7 @@
       </c>
       <c r="E123" s="10"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5">
       <c r="A124" s="2">
         <v>48</v>
       </c>
@@ -11255,7 +11220,7 @@
       </c>
       <c r="E124" s="2"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5">
       <c r="A125" s="2">
         <v>49</v>
       </c>
@@ -11272,7 +11237,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5">
       <c r="A126" s="2">
         <v>50</v>
       </c>
@@ -11287,7 +11252,7 @@
       </c>
       <c r="E126" s="2"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5">
       <c r="A127" s="2">
         <v>51</v>
       </c>
@@ -11302,7 +11267,7 @@
       </c>
       <c r="E127" s="2"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5">
       <c r="A128" s="2">
         <v>52</v>
       </c>
@@ -11319,7 +11284,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5">
       <c r="A129" s="2">
         <v>53</v>
       </c>
@@ -11334,7 +11299,7 @@
       </c>
       <c r="E129" s="2"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5">
       <c r="A130" s="2">
         <v>54</v>
       </c>
@@ -11349,7 +11314,7 @@
       </c>
       <c r="E130" s="2"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5">
       <c r="A131" s="2">
         <v>55</v>
       </c>
@@ -11366,7 +11331,7 @@
         <v>44594</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5">
       <c r="A132" s="2">
         <v>56</v>
       </c>
@@ -11383,7 +11348,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5">
       <c r="A133" s="2">
         <v>57</v>
       </c>
@@ -11398,7 +11363,7 @@
       </c>
       <c r="E133" s="2"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5">
       <c r="A134" s="2">
         <v>58</v>
       </c>
@@ -11413,7 +11378,7 @@
       </c>
       <c r="E134" s="2"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5">
       <c r="A135" s="2">
         <v>59</v>
       </c>
@@ -11428,7 +11393,7 @@
       </c>
       <c r="E135" s="2"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5">
       <c r="A136" s="2">
         <v>60</v>
       </c>
@@ -11443,7 +11408,7 @@
       </c>
       <c r="E136" s="2"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5">
       <c r="A137" s="2">
         <v>61</v>
       </c>
@@ -11458,7 +11423,7 @@
       </c>
       <c r="E137" s="2"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5">
       <c r="A138" s="2">
         <v>62</v>
       </c>
@@ -11473,7 +11438,7 @@
       </c>
       <c r="E138" s="2"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5">
       <c r="A139" s="2">
         <v>63</v>
       </c>
@@ -11490,7 +11455,7 @@
         <v>3234</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5">
       <c r="A140" s="2">
         <v>64</v>
       </c>
@@ -11507,7 +11472,7 @@
         <v>13234</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5">
       <c r="A141" s="2">
         <v>65</v>
       </c>
@@ -11522,7 +11487,7 @@
       </c>
       <c r="E141" s="2"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5">
       <c r="A142" s="2">
         <v>66</v>
       </c>
@@ -11537,7 +11502,7 @@
       </c>
       <c r="E142" s="2"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5">
       <c r="A143" s="2">
         <v>67</v>
       </c>
@@ -11552,7 +11517,7 @@
       </c>
       <c r="E143" s="2"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5">
       <c r="A144" s="2">
         <v>68</v>
       </c>
@@ -11567,7 +11532,7 @@
       </c>
       <c r="E144" s="2"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5">
       <c r="A145" s="2" t="s">
         <v>118</v>
       </c>
@@ -11576,7 +11541,7 @@
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5">
       <c r="A146" s="2">
         <v>70</v>
       </c>
@@ -11591,7 +11556,7 @@
       </c>
       <c r="E146" s="2"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5">
       <c r="A147" s="2">
         <v>71</v>
       </c>
@@ -11608,7 +11573,7 @@
         <v>7826423</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5">
       <c r="A148" s="2">
         <v>72</v>
       </c>
@@ -11625,7 +11590,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5">
       <c r="A149" s="2">
         <v>73</v>
       </c>
@@ -11642,7 +11607,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5">
       <c r="A150" s="2">
         <v>74</v>
       </c>
@@ -11659,7 +11624,7 @@
         <v>3478323</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5">
       <c r="A151" s="2">
         <v>75</v>
       </c>
@@ -11674,7 +11639,7 @@
       </c>
       <c r="E151" s="2"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5">
       <c r="A152" s="2">
         <v>76</v>
       </c>
@@ -11689,7 +11654,7 @@
       </c>
       <c r="E152" s="2"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5">
       <c r="A153" s="2">
         <v>77</v>
       </c>
@@ -11704,7 +11669,7 @@
       </c>
       <c r="E153" s="2"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5">
       <c r="A154" s="2">
         <v>78</v>
       </c>
@@ -11719,7 +11684,7 @@
       </c>
       <c r="E154" s="2"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5">
       <c r="A155" s="2" t="s">
         <v>123</v>
       </c>
@@ -11728,7 +11693,7 @@
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5">
       <c r="A156" s="2">
         <v>80</v>
       </c>
@@ -11743,7 +11708,7 @@
       </c>
       <c r="E156" s="2"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5">
       <c r="A157" s="2">
         <v>81</v>
       </c>
@@ -11760,7 +11725,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5">
       <c r="A158" s="2">
         <v>82</v>
       </c>
@@ -11777,7 +11742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5">
       <c r="A159" s="2">
         <v>83</v>
       </c>
@@ -11794,7 +11759,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5">
       <c r="A160" s="2">
         <v>84</v>
       </c>
@@ -11811,7 +11776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5">
       <c r="A161" s="2">
         <v>85</v>
       </c>
@@ -11826,7 +11791,7 @@
       </c>
       <c r="E161" s="2"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5">
       <c r="A162" s="2">
         <v>86</v>
       </c>
@@ -11841,7 +11806,7 @@
       </c>
       <c r="E162" s="2"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5">
       <c r="A163" s="2">
         <v>87</v>
       </c>
@@ -11856,7 +11821,7 @@
       </c>
       <c r="E163" s="2"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5">
       <c r="A164" s="2">
         <v>88</v>
       </c>
@@ -11873,7 +11838,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5">
       <c r="A165" s="2">
         <v>89</v>
       </c>
@@ -11890,7 +11855,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5">
       <c r="A166" s="2">
         <v>90</v>
       </c>
@@ -11907,7 +11872,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5">
       <c r="A167" s="2">
         <v>91</v>
       </c>
@@ -11924,7 +11889,7 @@
         <v>3478323</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5">
       <c r="A168" s="2">
         <v>92</v>
       </c>
@@ -11939,7 +11904,7 @@
       </c>
       <c r="E168" s="2"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5">
       <c r="A169" s="2">
         <v>93</v>
       </c>
@@ -11954,7 +11919,7 @@
       </c>
       <c r="E169" s="2"/>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5">
       <c r="A170" s="2" t="s">
         <v>130</v>
       </c>
@@ -11965,7 +11930,7 @@
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5">
       <c r="A171" s="2">
         <v>3</v>
       </c>
@@ -11982,7 +11947,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5">
       <c r="A172" s="2">
         <v>4</v>
       </c>
@@ -11997,7 +11962,7 @@
       </c>
       <c r="E172" s="2"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5">
       <c r="A173" s="2">
         <v>5</v>
       </c>
@@ -12012,7 +11977,7 @@
       </c>
       <c r="E173" s="2"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5">
       <c r="A174" s="2">
         <v>6</v>
       </c>
@@ -12027,7 +11992,7 @@
       </c>
       <c r="E174" s="2"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5">
       <c r="A175" s="2">
         <v>7</v>
       </c>
@@ -12042,7 +12007,7 @@
       </c>
       <c r="E175" s="2"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5">
       <c r="A176" s="2">
         <v>8</v>
       </c>
@@ -12057,7 +12022,7 @@
       </c>
       <c r="E176" s="2"/>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5">
       <c r="A177" s="2">
         <v>9</v>
       </c>
@@ -12072,7 +12037,7 @@
       </c>
       <c r="E177" s="2"/>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5">
       <c r="A178" s="2">
         <v>10</v>
       </c>
@@ -12087,7 +12052,7 @@
       </c>
       <c r="E178" s="2"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5">
       <c r="A179" s="2">
         <v>11</v>
       </c>
@@ -12104,7 +12069,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5">
       <c r="A180" s="2" t="s">
         <v>146</v>
       </c>
@@ -12113,7 +12078,7 @@
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5">
       <c r="A181" s="2">
         <v>13</v>
       </c>
@@ -12128,7 +12093,7 @@
       </c>
       <c r="E181" s="2"/>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5">
       <c r="A182" s="2">
         <v>14</v>
       </c>
@@ -12143,7 +12108,7 @@
       </c>
       <c r="E182" s="2"/>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5">
       <c r="A183" s="2">
         <v>15</v>
       </c>
@@ -12160,7 +12125,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5">
       <c r="A184" s="2">
         <v>16</v>
       </c>
@@ -12177,7 +12142,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5">
       <c r="A185" s="2">
         <v>17</v>
       </c>
@@ -12194,7 +12159,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5">
       <c r="A186" s="2">
         <v>18</v>
       </c>
@@ -12211,7 +12176,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5">
       <c r="A187" s="2">
         <v>19</v>
       </c>
@@ -12228,7 +12193,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5">
       <c r="A188" s="2">
         <v>20</v>
       </c>
@@ -12245,7 +12210,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5">
       <c r="A189" s="2">
         <v>21</v>
       </c>
@@ -12262,7 +12227,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5">
       <c r="A190" s="2">
         <v>22</v>
       </c>
@@ -12277,7 +12242,7 @@
       </c>
       <c r="E190" s="2"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5">
       <c r="A191" s="2">
         <v>23</v>
       </c>
@@ -12292,7 +12257,7 @@
       </c>
       <c r="E191" s="2"/>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5">
       <c r="A192" s="2">
         <v>24</v>
       </c>
@@ -12307,7 +12272,7 @@
       </c>
       <c r="E192" s="2"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5">
       <c r="A193" s="2">
         <v>25</v>
       </c>
@@ -12324,7 +12289,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5">
       <c r="A194" s="2">
         <v>26</v>
       </c>
@@ -12341,7 +12306,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5">
       <c r="A195" s="2">
         <v>27</v>
       </c>
@@ -12358,7 +12323,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5">
       <c r="A196" s="2">
         <v>28</v>
       </c>
@@ -12373,7 +12338,7 @@
       </c>
       <c r="E196" s="2"/>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5">
       <c r="A197" s="2">
         <v>29</v>
       </c>
@@ -12388,7 +12353,7 @@
       </c>
       <c r="E197" s="2"/>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5">
       <c r="A198" s="2" t="s">
         <v>164</v>
       </c>
@@ -12397,7 +12362,7 @@
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5">
       <c r="A199" s="2">
         <v>31</v>
       </c>
@@ -12412,7 +12377,7 @@
       </c>
       <c r="E199" s="2"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5">
       <c r="A200" s="2">
         <v>32</v>
       </c>
@@ -12427,7 +12392,7 @@
       </c>
       <c r="E200" s="2"/>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5">
       <c r="A201" s="2">
         <v>33</v>
       </c>
@@ -12442,7 +12407,7 @@
       </c>
       <c r="E201" s="2"/>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5">
       <c r="A202" s="2">
         <v>34</v>
       </c>
@@ -12459,7 +12424,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5">
       <c r="A203" s="2">
         <v>35</v>
       </c>
@@ -12474,7 +12439,7 @@
       </c>
       <c r="E203" s="2"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5">
       <c r="A204" s="2">
         <v>36</v>
       </c>
@@ -12489,7 +12454,7 @@
       </c>
       <c r="E204" s="2"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5">
       <c r="A205" s="2">
         <v>37</v>
       </c>
@@ -12504,7 +12469,7 @@
       </c>
       <c r="E205" s="2"/>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5">
       <c r="A206" s="2">
         <v>38</v>
       </c>
@@ -12519,7 +12484,7 @@
       </c>
       <c r="E206" s="2"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5">
       <c r="A207" s="2">
         <v>39</v>
       </c>
@@ -12534,7 +12499,7 @@
       </c>
       <c r="E207" s="2"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5">
       <c r="A208" s="2" t="s">
         <v>167</v>
       </c>
@@ -12543,7 +12508,7 @@
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5">
       <c r="A209" s="2">
         <v>41</v>
       </c>
@@ -12560,7 +12525,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5">
       <c r="A210" s="2">
         <v>42</v>
       </c>
@@ -12577,7 +12542,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5">
       <c r="A211" s="2">
         <v>43</v>
       </c>
@@ -12594,7 +12559,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5">
       <c r="A212" s="2">
         <v>44</v>
       </c>
@@ -12609,7 +12574,7 @@
       </c>
       <c r="E212" s="2"/>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5">
       <c r="A213" s="2">
         <v>45</v>
       </c>
@@ -12626,7 +12591,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5">
       <c r="A214" s="2">
         <v>46</v>
       </c>
@@ -12641,7 +12606,7 @@
       </c>
       <c r="E214" s="2"/>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5">
       <c r="A215" s="2">
         <v>47</v>
       </c>
@@ -12658,7 +12623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5">
       <c r="A216" s="2">
         <v>48</v>
       </c>
@@ -12673,7 +12638,7 @@
       </c>
       <c r="E216" s="2"/>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5">
       <c r="A217" s="2">
         <v>49</v>
       </c>
@@ -12690,7 +12655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5">
       <c r="A218" s="2">
         <v>50</v>
       </c>
@@ -12705,7 +12670,7 @@
       </c>
       <c r="E218" s="2"/>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5">
       <c r="A219" s="2">
         <v>51</v>
       </c>
@@ -12722,7 +12687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5">
       <c r="A220" s="2">
         <v>52</v>
       </c>
@@ -12737,7 +12702,7 @@
       </c>
       <c r="E220" s="2"/>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5">
       <c r="A221" s="2">
         <v>53</v>
       </c>
@@ -12754,7 +12719,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5">
       <c r="A222" s="2">
         <v>54</v>
       </c>
@@ -12769,7 +12734,7 @@
       </c>
       <c r="E222" s="2"/>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5">
       <c r="A223" s="2">
         <v>55</v>
       </c>
@@ -12786,7 +12751,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5">
       <c r="A224" s="2">
         <v>56</v>
       </c>
@@ -12801,7 +12766,7 @@
       </c>
       <c r="E224" s="2"/>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5">
       <c r="A225" s="2">
         <v>57</v>
       </c>
@@ -12816,7 +12781,7 @@
       </c>
       <c r="E225" s="2"/>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5">
       <c r="A226" s="2">
         <v>58</v>
       </c>
@@ -12831,7 +12796,7 @@
       </c>
       <c r="E226" s="2"/>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5">
       <c r="A227" s="2" t="s">
         <v>181</v>
       </c>
@@ -12840,7 +12805,7 @@
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5">
       <c r="A228" s="2">
         <v>60</v>
       </c>
@@ -12857,7 +12822,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5">
       <c r="A229" s="2">
         <v>61</v>
       </c>
@@ -12872,7 +12837,7 @@
       </c>
       <c r="E229" s="2"/>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5">
       <c r="A230" s="2">
         <v>62</v>
       </c>
@@ -12887,7 +12852,7 @@
       </c>
       <c r="E230" s="2"/>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5">
       <c r="A231" s="2">
         <v>63</v>
       </c>
@@ -12904,7 +12869,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5">
       <c r="A232" s="2">
         <v>64</v>
       </c>
@@ -12921,7 +12886,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5">
       <c r="A233" s="2">
         <v>65</v>
       </c>
@@ -12936,7 +12901,7 @@
       </c>
       <c r="E233" s="2"/>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5">
       <c r="A234" s="2">
         <v>66</v>
       </c>
@@ -12947,7 +12912,7 @@
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5">
       <c r="A235" s="2">
         <v>67</v>
       </c>
@@ -12964,7 +12929,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5">
       <c r="A236" s="2">
         <v>68</v>
       </c>
@@ -12981,7 +12946,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5">
       <c r="A237" s="2">
         <v>69</v>
       </c>
@@ -12996,7 +12961,7 @@
       </c>
       <c r="E237" s="2"/>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5">
       <c r="A238" s="2">
         <v>70</v>
       </c>
@@ -13011,7 +12976,7 @@
       </c>
       <c r="E238" s="6"/>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5">
       <c r="A239" s="2">
         <v>71</v>
       </c>
@@ -13028,7 +12993,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5">
       <c r="A240" s="2">
         <v>72</v>
       </c>
@@ -13043,7 +13008,7 @@
       </c>
       <c r="E240" s="2"/>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5">
       <c r="A241" s="2">
         <v>73</v>
       </c>
@@ -13060,7 +13025,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5">
       <c r="A242" s="2">
         <v>74</v>
       </c>
@@ -13075,7 +13040,7 @@
       </c>
       <c r="E242" s="2"/>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5">
       <c r="A243" s="2">
         <v>75</v>
       </c>
@@ -13090,7 +13055,7 @@
       </c>
       <c r="E243" s="2"/>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5">
       <c r="A244" s="2">
         <v>76</v>
       </c>
@@ -13105,7 +13070,7 @@
       </c>
       <c r="E244" s="2"/>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5">
       <c r="A245" s="2">
         <v>77</v>
       </c>
@@ -13122,7 +13087,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5">
       <c r="A246" s="2">
         <v>78</v>
       </c>
@@ -13137,7 +13102,7 @@
       </c>
       <c r="E246" s="2"/>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5">
       <c r="A247" s="2">
         <v>79</v>
       </c>
@@ -13152,7 +13117,7 @@
       </c>
       <c r="E247" s="2"/>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5">
       <c r="A248" s="2">
         <v>80</v>
       </c>
@@ -13167,7 +13132,7 @@
       </c>
       <c r="E248" s="2"/>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5">
       <c r="A249" s="2">
         <v>81</v>
       </c>
@@ -13184,7 +13149,7 @@
         <v>3.4628376482734602E+18</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5">
       <c r="A250" s="2">
         <v>82</v>
       </c>
@@ -13199,7 +13164,7 @@
       </c>
       <c r="E250" s="2"/>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5">
       <c r="A251" s="2">
         <v>83</v>
       </c>
@@ -13214,7 +13179,7 @@
       </c>
       <c r="E251" s="2"/>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5">
       <c r="A252" s="2">
         <v>84</v>
       </c>
@@ -13229,7 +13194,7 @@
       </c>
       <c r="E252" s="2"/>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5">
       <c r="A253" s="2">
         <v>85</v>
       </c>
@@ -13246,7 +13211,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5">
       <c r="A254" s="2">
         <v>86</v>
       </c>
@@ -13261,7 +13226,7 @@
       </c>
       <c r="E254" s="2"/>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5">
       <c r="A255" s="2">
         <v>87</v>
       </c>
@@ -13276,7 +13241,7 @@
       </c>
       <c r="E255" s="2"/>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5">
       <c r="A256" s="2">
         <v>88</v>
       </c>
@@ -13291,7 +13256,7 @@
       </c>
       <c r="E256" s="2"/>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5">
       <c r="A257" s="2">
         <v>89</v>
       </c>
@@ -13308,7 +13273,7 @@
         <v>3.4628376482734602E+18</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5">
       <c r="A258" s="2">
         <v>90</v>
       </c>
@@ -13323,7 +13288,7 @@
       </c>
       <c r="E258" s="2"/>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5">
       <c r="A259" s="2">
         <v>91</v>
       </c>
@@ -13338,7 +13303,7 @@
       </c>
       <c r="E259" s="2"/>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5">
       <c r="A260" s="2">
         <v>92</v>
       </c>
@@ -13355,7 +13320,7 @@
         <v>44854</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5">
       <c r="A261" s="2">
         <v>93</v>
       </c>
@@ -13372,7 +13337,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5">
       <c r="A262" s="2">
         <v>94</v>
       </c>
@@ -13387,7 +13352,7 @@
       </c>
       <c r="E262" s="2"/>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5">
       <c r="A263" s="2">
         <v>95</v>
       </c>
@@ -13402,7 +13367,7 @@
       </c>
       <c r="E263" s="2"/>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5">
       <c r="A264" s="2">
         <v>96</v>
       </c>
@@ -13417,7 +13382,7 @@
       </c>
       <c r="E264" s="2"/>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5">
       <c r="A265" s="2">
         <v>97</v>
       </c>
@@ -13432,7 +13397,7 @@
       </c>
       <c r="E265" s="2"/>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5">
       <c r="A266" s="2">
         <v>98</v>
       </c>
@@ -13447,7 +13412,7 @@
       </c>
       <c r="E266" s="2"/>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5">
       <c r="A267" s="2" t="s">
         <v>118</v>
       </c>
@@ -13456,7 +13421,7 @@
       <c r="D267" s="2"/>
       <c r="E267" s="2"/>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5">
       <c r="A268" s="2">
         <v>100</v>
       </c>
@@ -13471,7 +13436,7 @@
       </c>
       <c r="E268" s="2"/>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5">
       <c r="A269" s="2">
         <v>101</v>
       </c>
@@ -13488,7 +13453,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5">
       <c r="A270" s="2">
         <v>102</v>
       </c>
@@ -13503,7 +13468,7 @@
       </c>
       <c r="E270" s="2"/>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5">
       <c r="A271" s="2">
         <v>103</v>
       </c>
@@ -13518,7 +13483,7 @@
       </c>
       <c r="E271" s="2"/>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5">
       <c r="A272" s="2">
         <v>104</v>
       </c>
@@ -13535,7 +13500,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5">
       <c r="A273" s="2">
         <v>105</v>
       </c>
@@ -13552,7 +13517,7 @@
         <v>7600</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5">
       <c r="A274" s="2">
         <v>106</v>
       </c>
@@ -13569,7 +13534,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5">
       <c r="A275" s="2">
         <v>107</v>
       </c>
@@ -13586,7 +13551,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5">
       <c r="A276" s="2">
         <v>108</v>
       </c>
@@ -13601,7 +13566,7 @@
       </c>
       <c r="E276" s="2"/>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5">
       <c r="A277" s="2">
         <v>109</v>
       </c>
@@ -13616,7 +13581,7 @@
       </c>
       <c r="E277" s="2"/>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5">
       <c r="A278" s="2" t="s">
         <v>131</v>
       </c>
@@ -13625,7 +13590,7 @@
       <c r="D278" s="2"/>
       <c r="E278" s="2"/>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5">
       <c r="A279" s="2">
         <v>111</v>
       </c>
@@ -13640,7 +13605,7 @@
       </c>
       <c r="E279" s="2"/>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5">
       <c r="A280" s="2">
         <v>112</v>
       </c>
@@ -13655,7 +13620,7 @@
       </c>
       <c r="E280" s="2"/>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5">
       <c r="A281" s="2">
         <v>113</v>
       </c>
@@ -13670,7 +13635,7 @@
       </c>
       <c r="E281" s="2"/>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5">
       <c r="A282" s="2">
         <v>114</v>
       </c>
@@ -13685,7 +13650,7 @@
       </c>
       <c r="E282" s="2"/>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5">
       <c r="A283" s="2">
         <v>115</v>
       </c>
@@ -13700,7 +13665,7 @@
       </c>
       <c r="E283" s="2"/>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5">
       <c r="A284" s="2">
         <v>116</v>
       </c>
@@ -13715,7 +13680,7 @@
       </c>
       <c r="E284" s="2"/>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5">
       <c r="A285" s="2">
         <v>117</v>
       </c>
@@ -13730,7 +13695,7 @@
       </c>
       <c r="E285" s="2"/>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5">
       <c r="A286" s="2">
         <v>118</v>
       </c>
@@ -13745,7 +13710,7 @@
       </c>
       <c r="E286" s="2"/>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:5">
       <c r="A287" s="2">
         <v>119</v>
       </c>
@@ -13760,7 +13725,7 @@
       </c>
       <c r="E287" s="2"/>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5">
       <c r="A288" s="2">
         <v>120</v>
       </c>
@@ -13777,7 +13742,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5">
       <c r="A289" s="2">
         <v>121</v>
       </c>
@@ -13794,7 +13759,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5">
       <c r="A290" s="2">
         <v>122</v>
       </c>
@@ -13811,7 +13776,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5">
       <c r="A291" s="2">
         <v>123</v>
       </c>
@@ -13828,7 +13793,7 @@
         <v>12323</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5">
       <c r="A292" s="2">
         <v>124</v>
       </c>
@@ -13843,7 +13808,7 @@
       </c>
       <c r="E292" s="2"/>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:5">
       <c r="A293" s="2">
         <v>125</v>
       </c>
@@ -13858,7 +13823,7 @@
       </c>
       <c r="E293" s="2"/>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5">
       <c r="A294" s="2">
         <v>126</v>
       </c>
@@ -13873,7 +13838,7 @@
       </c>
       <c r="E294" s="2"/>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5">
       <c r="A295" s="2" t="s">
         <v>253</v>
       </c>
@@ -13882,7 +13847,7 @@
       <c r="D295" s="2"/>
       <c r="E295" s="2"/>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5">
       <c r="A296" s="2">
         <v>128</v>
       </c>
@@ -13897,7 +13862,7 @@
       </c>
       <c r="E296" s="2"/>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:5">
       <c r="A297" s="2">
         <v>129</v>
       </c>
@@ -13912,7 +13877,7 @@
       </c>
       <c r="E297" s="2"/>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:5">
       <c r="A298" s="2">
         <v>130</v>
       </c>
@@ -13927,7 +13892,7 @@
       </c>
       <c r="E298" s="2"/>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:5">
       <c r="A299" s="2">
         <v>131</v>
       </c>
@@ -13942,7 +13907,7 @@
       </c>
       <c r="E299" s="2"/>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5">
       <c r="A300" s="2">
         <v>132</v>
       </c>
@@ -13959,7 +13924,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5">
       <c r="A301" s="2">
         <v>133</v>
       </c>
@@ -13974,7 +13939,7 @@
       </c>
       <c r="E301" s="2"/>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5">
       <c r="A302" s="2">
         <v>134</v>
       </c>
@@ -13989,7 +13954,7 @@
       </c>
       <c r="E302" s="2"/>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5">
       <c r="A303" s="2" t="s">
         <v>129</v>
       </c>
@@ -14000,7 +13965,7 @@
       <c r="D303" s="2"/>
       <c r="E303" s="2"/>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:5">
       <c r="A304" s="2">
         <v>3</v>
       </c>
@@ -14017,7 +13982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:5">
       <c r="A305" s="2">
         <v>4</v>
       </c>
@@ -14032,7 +13997,7 @@
       </c>
       <c r="E305" s="2"/>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:5">
       <c r="A306" s="2">
         <v>5</v>
       </c>
@@ -14047,7 +14012,7 @@
       </c>
       <c r="E306" s="2"/>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:5">
       <c r="A307" s="2">
         <v>6</v>
       </c>
@@ -14062,7 +14027,7 @@
       </c>
       <c r="E307" s="2"/>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:5">
       <c r="A308" s="2">
         <v>7</v>
       </c>
@@ -14077,7 +14042,7 @@
       </c>
       <c r="E308" s="2"/>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:5">
       <c r="A309" s="2">
         <v>8</v>
       </c>
@@ -14092,7 +14057,7 @@
       </c>
       <c r="E309" s="2"/>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:5">
       <c r="A310" s="2">
         <v>9</v>
       </c>
@@ -14107,7 +14072,7 @@
       </c>
       <c r="E310" s="2"/>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:5">
       <c r="A311" s="2" t="s">
         <v>204</v>
       </c>
@@ -14116,7 +14081,7 @@
       <c r="D311" s="2"/>
       <c r="E311" s="2"/>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:5">
       <c r="A312" s="2">
         <v>11</v>
       </c>
@@ -14133,7 +14098,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:5">
       <c r="A313" s="2">
         <v>12</v>
       </c>
@@ -14150,7 +14115,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:5">
       <c r="A314" s="2">
         <v>13</v>
       </c>
@@ -14167,7 +14132,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:5">
       <c r="A315" s="2">
         <v>14</v>
       </c>
@@ -14184,7 +14149,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:5">
       <c r="A316" s="2">
         <v>15</v>
       </c>
@@ -14201,7 +14166,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:5">
       <c r="A317" s="2">
         <v>16</v>
       </c>
@@ -14218,7 +14183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:5">
       <c r="A318" s="2">
         <v>17</v>
       </c>
@@ -14235,7 +14200,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:5">
       <c r="A319" s="2">
         <v>18</v>
       </c>
@@ -14252,7 +14217,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:5">
       <c r="A320" s="2">
         <v>19</v>
       </c>
@@ -14269,7 +14234,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:5">
       <c r="A321" s="2">
         <v>20</v>
       </c>
@@ -14286,7 +14251,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:5">
       <c r="A322" s="2">
         <v>21</v>
       </c>
@@ -14303,7 +14268,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:5">
       <c r="A323" s="2">
         <v>22</v>
       </c>
@@ -14320,7 +14285,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5">
       <c r="A324" s="2">
         <v>23</v>
       </c>
@@ -14335,7 +14300,7 @@
       </c>
       <c r="E324" s="6"/>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:5">
       <c r="A325" s="2">
         <v>24</v>
       </c>
@@ -14350,7 +14315,7 @@
       </c>
       <c r="E325" s="2"/>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:5">
       <c r="A326" s="2">
         <v>25</v>
       </c>
@@ -14365,7 +14330,7 @@
       </c>
       <c r="E326" s="2"/>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:5">
       <c r="A327" s="2">
         <v>26</v>
       </c>
@@ -14380,7 +14345,7 @@
       </c>
       <c r="E327" s="2"/>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:5">
       <c r="A328" s="2">
         <v>27</v>
       </c>
@@ -14395,7 +14360,7 @@
       </c>
       <c r="E328" s="2"/>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:5">
       <c r="A329" s="2">
         <v>28</v>
       </c>
@@ -14410,7 +14375,7 @@
       </c>
       <c r="E329" s="2"/>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:5">
       <c r="A330" s="2">
         <v>29</v>
       </c>
@@ -14427,7 +14392,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:5">
       <c r="A331" s="2" t="s">
         <v>146</v>
       </c>
@@ -14436,7 +14401,7 @@
       <c r="D331" s="2"/>
       <c r="E331" s="2"/>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:5">
       <c r="A332" s="2">
         <v>31</v>
       </c>
@@ -14451,7 +14416,7 @@
       </c>
       <c r="E332" s="2"/>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:5">
       <c r="A333" s="2">
         <v>32</v>
       </c>
@@ -14466,7 +14431,7 @@
       </c>
       <c r="E333" s="2"/>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:5">
       <c r="A334" s="2">
         <v>33</v>
       </c>
@@ -14483,7 +14448,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:5">
       <c r="A335" s="2">
         <v>34</v>
       </c>
@@ -14500,7 +14465,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:5">
       <c r="A336" s="2">
         <v>35</v>
       </c>
@@ -14517,7 +14482,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5">
       <c r="A337" s="2">
         <v>36</v>
       </c>
@@ -14534,7 +14499,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:5">
       <c r="A338" s="2">
         <v>37</v>
       </c>
@@ -14551,7 +14516,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:5">
       <c r="A339" s="2">
         <v>38</v>
       </c>
@@ -14568,7 +14533,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:5">
       <c r="A340" s="2">
         <v>39</v>
       </c>
@@ -14585,7 +14550,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:5">
       <c r="A341" s="2">
         <v>40</v>
       </c>
@@ -14600,7 +14565,7 @@
       </c>
       <c r="E341" s="2"/>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:5">
       <c r="A342" s="2">
         <v>41</v>
       </c>
@@ -14615,7 +14580,7 @@
       </c>
       <c r="E342" s="2"/>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:5">
       <c r="A343" s="2">
         <v>42</v>
       </c>
@@ -14630,7 +14595,7 @@
       </c>
       <c r="E343" s="2"/>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:5">
       <c r="A344" s="2">
         <v>43</v>
       </c>
@@ -14645,7 +14610,7 @@
       </c>
       <c r="E344" s="2"/>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:5">
       <c r="A345" s="2">
         <v>44</v>
       </c>
@@ -14660,7 +14625,7 @@
       </c>
       <c r="E345" s="2"/>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:5">
       <c r="A346" s="2">
         <v>45</v>
       </c>
@@ -14677,7 +14642,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:5">
       <c r="A347" s="2">
         <v>46</v>
       </c>
@@ -14692,7 +14657,7 @@
       </c>
       <c r="E347" s="2"/>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:5">
       <c r="A348" s="2">
         <v>47</v>
       </c>
@@ -14709,7 +14674,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:5">
       <c r="A349" s="2">
         <v>48</v>
       </c>
@@ -14726,7 +14691,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:5">
       <c r="A350" s="2">
         <v>49</v>
       </c>
@@ -14743,7 +14708,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:5">
       <c r="A351" s="2">
         <v>50</v>
       </c>
@@ -14758,7 +14723,7 @@
       </c>
       <c r="E351" s="2"/>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:5">
       <c r="A352" s="2">
         <v>51</v>
       </c>
@@ -14775,7 +14740,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:5">
       <c r="A353" s="2">
         <v>52</v>
       </c>
@@ -14790,7 +14755,7 @@
       </c>
       <c r="E353" s="2"/>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:5">
       <c r="A354" s="2">
         <v>53</v>
       </c>
@@ -14807,7 +14772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:5">
       <c r="A355" s="2">
         <v>54</v>
       </c>
@@ -14822,7 +14787,7 @@
       </c>
       <c r="E355" s="2"/>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:5">
       <c r="A356" s="2">
         <v>55</v>
       </c>
@@ -14839,7 +14804,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:5">
       <c r="A357" s="2">
         <v>56</v>
       </c>
@@ -14854,7 +14819,7 @@
       </c>
       <c r="E357" s="2"/>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:5">
       <c r="A358" s="2">
         <v>57</v>
       </c>
@@ -14871,7 +14836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:5">
       <c r="A359" s="2">
         <v>58</v>
       </c>
@@ -14886,7 +14851,7 @@
       </c>
       <c r="E359" s="2"/>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:5">
       <c r="A360" s="2">
         <v>59</v>
       </c>
@@ -14903,7 +14868,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:5">
       <c r="A361" s="2">
         <v>60</v>
       </c>
@@ -14920,7 +14885,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:5">
       <c r="A362" s="2">
         <v>61</v>
       </c>
@@ -14935,7 +14900,7 @@
       </c>
       <c r="E362" s="2"/>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:5">
       <c r="A363" s="2">
         <v>62</v>
       </c>
@@ -14950,7 +14915,7 @@
       </c>
       <c r="E363" s="2"/>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:5">
       <c r="A364" s="2">
         <v>63</v>
       </c>
@@ -14965,7 +14930,7 @@
       </c>
       <c r="E364" s="2"/>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:5">
       <c r="A365" s="2" t="s">
         <v>205</v>
       </c>
@@ -14974,7 +14939,7 @@
       <c r="D365" s="2"/>
       <c r="E365" s="2"/>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:5">
       <c r="A366" s="2">
         <v>65</v>
       </c>
@@ -14989,7 +14954,7 @@
       </c>
       <c r="E366" s="2"/>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:5">
       <c r="A367" s="2">
         <v>66</v>
       </c>
@@ -15004,7 +14969,7 @@
       </c>
       <c r="E367" s="2"/>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:5">
       <c r="A368" s="2">
         <v>67</v>
       </c>
@@ -15019,7 +14984,7 @@
       </c>
       <c r="E368" s="6"/>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:5">
       <c r="A369" s="2">
         <v>68</v>
       </c>
@@ -15034,7 +14999,7 @@
       </c>
       <c r="E369" s="2"/>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:5">
       <c r="A370" s="2">
         <v>69</v>
       </c>
@@ -15049,7 +15014,7 @@
       </c>
       <c r="E370" s="2"/>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:5">
       <c r="A371" s="2">
         <v>70</v>
       </c>
@@ -15064,7 +15029,7 @@
       </c>
       <c r="E371" s="2"/>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:5">
       <c r="A372" s="2">
         <v>71</v>
       </c>
@@ -15079,7 +15044,7 @@
       </c>
       <c r="E372" s="2"/>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:5">
       <c r="A373" s="2">
         <v>72</v>
       </c>
@@ -15094,7 +15059,7 @@
       </c>
       <c r="E373" s="2"/>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:5">
       <c r="A374" s="2">
         <v>73</v>
       </c>
@@ -15109,7 +15074,7 @@
       </c>
       <c r="E374" s="2"/>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:5">
       <c r="A375" s="2" t="s">
         <v>252</v>
       </c>
@@ -15120,7 +15085,7 @@
       <c r="D375" s="2"/>
       <c r="E375" s="2"/>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:5">
       <c r="A376" s="2">
         <v>3</v>
       </c>
@@ -15137,7 +15102,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:5">
       <c r="A377" s="2">
         <v>4</v>
       </c>
@@ -15152,7 +15117,7 @@
       </c>
       <c r="E377" s="2"/>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:5">
       <c r="A378" s="2">
         <v>5</v>
       </c>
@@ -15167,7 +15132,7 @@
       </c>
       <c r="E378" s="2"/>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:5">
       <c r="A379" s="2">
         <v>6</v>
       </c>
@@ -15182,7 +15147,7 @@
       </c>
       <c r="E379" s="2"/>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:5">
       <c r="A380" s="2">
         <v>7</v>
       </c>
@@ -15197,7 +15162,7 @@
       </c>
       <c r="E380" s="2"/>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:5">
       <c r="A381" s="2">
         <v>8</v>
       </c>
@@ -15212,7 +15177,7 @@
       </c>
       <c r="E381" s="2"/>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:5">
       <c r="A382" s="2">
         <v>9</v>
       </c>
@@ -15227,7 +15192,7 @@
       </c>
       <c r="E382" s="2"/>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:5">
       <c r="A383" s="2">
         <v>10</v>
       </c>
@@ -15242,7 +15207,7 @@
       </c>
       <c r="E383" s="2"/>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:5">
       <c r="A384" s="2">
         <v>11</v>
       </c>
@@ -15259,7 +15224,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:5">
       <c r="A385" s="2">
         <v>12</v>
       </c>
@@ -15274,7 +15239,7 @@
       </c>
       <c r="E385" s="2"/>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:5">
       <c r="A386" s="2">
         <v>13</v>
       </c>
@@ -15289,7 +15254,7 @@
       </c>
       <c r="E386" s="2"/>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:5">
       <c r="A387" s="2">
         <v>14</v>
       </c>
@@ -15304,7 +15269,7 @@
       </c>
       <c r="E387" s="2"/>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:5">
       <c r="A388" s="2">
         <v>15</v>
       </c>
@@ -15319,7 +15284,7 @@
       </c>
       <c r="E388" s="2"/>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:5">
       <c r="A389" s="2">
         <v>16</v>
       </c>
@@ -15334,7 +15299,7 @@
       </c>
       <c r="E389" s="2"/>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:5">
       <c r="A390" s="2">
         <v>17</v>
       </c>
@@ -15349,7 +15314,7 @@
       </c>
       <c r="E390" s="2"/>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:5">
       <c r="A391" s="2">
         <v>18</v>
       </c>
@@ -15364,7 +15329,7 @@
       </c>
       <c r="E391" s="2"/>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:5">
       <c r="A392" s="2">
         <v>19</v>
       </c>
@@ -15379,7 +15344,7 @@
       </c>
       <c r="E392" s="2"/>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:5">
       <c r="A393" s="2">
         <v>20</v>
       </c>
@@ -15394,7 +15359,7 @@
       </c>
       <c r="E393" s="2"/>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:5">
       <c r="A394" s="2">
         <v>21</v>
       </c>
@@ -15409,7 +15374,7 @@
       </c>
       <c r="E394" s="2"/>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:5">
       <c r="A395" s="2">
         <v>22</v>
       </c>
@@ -15424,7 +15389,7 @@
       </c>
       <c r="E395" s="2"/>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:5">
       <c r="A396" s="2">
         <v>23</v>
       </c>
@@ -15439,7 +15404,7 @@
       </c>
       <c r="E396" s="2"/>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:5">
       <c r="A397" s="2">
         <v>24</v>
       </c>
@@ -15454,7 +15419,7 @@
       </c>
       <c r="E397" s="2"/>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:5">
       <c r="A398" s="2">
         <v>25</v>
       </c>
@@ -15469,7 +15434,7 @@
       </c>
       <c r="E398" s="2"/>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:5">
       <c r="A399" s="2">
         <v>26</v>
       </c>
@@ -15484,7 +15449,7 @@
       </c>
       <c r="E399" s="2"/>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:5">
       <c r="A400" s="2">
         <v>27</v>
       </c>
@@ -15499,7 +15464,7 @@
       </c>
       <c r="E400" s="2"/>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:5">
       <c r="A401" s="2">
         <v>28</v>
       </c>
@@ -15514,7 +15479,7 @@
       </c>
       <c r="E401" s="2"/>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:5">
       <c r="A402" s="2">
         <v>29</v>
       </c>
@@ -15529,7 +15494,7 @@
       </c>
       <c r="E402" s="2"/>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:5">
       <c r="A403" s="2">
         <v>30</v>
       </c>
@@ -15544,7 +15509,7 @@
       </c>
       <c r="E403" s="2"/>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:5">
       <c r="A404" s="2">
         <v>31</v>
       </c>
@@ -15559,7 +15524,7 @@
       </c>
       <c r="E404" s="2"/>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:5">
       <c r="A405" s="2">
         <v>32</v>
       </c>
@@ -15574,7 +15539,7 @@
       </c>
       <c r="E405" s="2"/>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:5">
       <c r="A406" s="2">
         <v>33</v>
       </c>
@@ -15589,7 +15554,7 @@
       </c>
       <c r="E406" s="2"/>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:5">
       <c r="A407" s="2">
         <v>34</v>
       </c>
@@ -15604,7 +15569,7 @@
       </c>
       <c r="E407" s="2"/>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:5">
       <c r="A408" s="2">
         <v>35</v>
       </c>
@@ -15619,7 +15584,7 @@
       </c>
       <c r="E408" s="2"/>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:5">
       <c r="A409" s="2">
         <v>36</v>
       </c>
@@ -15634,7 +15599,7 @@
       </c>
       <c r="E409" s="2"/>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:5">
       <c r="A410" s="2">
         <v>37</v>
       </c>
@@ -15649,7 +15614,7 @@
       </c>
       <c r="E410" s="2"/>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:5">
       <c r="A411" s="2">
         <v>38</v>
       </c>
@@ -15664,7 +15629,7 @@
       </c>
       <c r="E411" s="2"/>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:5">
       <c r="A412" s="2">
         <v>39</v>
       </c>
@@ -15679,14 +15644,14 @@
       </c>
       <c r="E412" s="2"/>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:5">
       <c r="A413" s="2"/>
       <c r="B413" s="4"/>
       <c r="C413" s="2"/>
       <c r="D413" s="2"/>
       <c r="E413" s="2"/>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:5">
       <c r="A414" s="2" t="s">
         <v>243</v>
       </c>
@@ -15697,7 +15662,7 @@
       <c r="D414" s="2"/>
       <c r="E414" s="2"/>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:5">
       <c r="A415" s="2">
         <v>3</v>
       </c>
@@ -15714,7 +15679,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:5">
       <c r="A416" s="2">
         <v>4</v>
       </c>
@@ -15729,7 +15694,7 @@
       </c>
       <c r="E416" s="2"/>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:5">
       <c r="A417" s="2">
         <v>5</v>
       </c>
@@ -15744,7 +15709,7 @@
       </c>
       <c r="E417" s="2"/>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:5">
       <c r="A418" s="2">
         <v>6</v>
       </c>
@@ -15759,7 +15724,7 @@
       </c>
       <c r="E418" s="2"/>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:5">
       <c r="A419" s="2">
         <v>7</v>
       </c>
@@ -15774,7 +15739,7 @@
       </c>
       <c r="E419" s="2"/>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:5">
       <c r="A420" s="2">
         <v>8</v>
       </c>
@@ -15789,7 +15754,7 @@
       </c>
       <c r="E420" s="2"/>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:5">
       <c r="A421" s="2">
         <v>9</v>
       </c>
@@ -15804,7 +15769,7 @@
       </c>
       <c r="E421" s="2"/>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:5">
       <c r="A422" s="2">
         <v>10</v>
       </c>
@@ -15821,7 +15786,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:5">
       <c r="A423" s="2">
         <v>11</v>
       </c>
@@ -15838,7 +15803,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:5">
       <c r="A424" s="2">
         <v>12</v>
       </c>
@@ -15853,7 +15818,7 @@
       </c>
       <c r="E424" s="2"/>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:5">
       <c r="A425" s="2">
         <v>13</v>
       </c>
@@ -15870,7 +15835,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:5">
       <c r="A426" s="2">
         <v>14</v>
       </c>
@@ -15885,7 +15850,7 @@
       </c>
       <c r="E426" s="2"/>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:5">
       <c r="A427" s="2">
         <v>15</v>
       </c>
@@ -15900,7 +15865,7 @@
       </c>
       <c r="E427" s="2"/>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:5">
       <c r="A428" s="2">
         <v>16</v>
       </c>
@@ -15915,7 +15880,7 @@
       </c>
       <c r="E428" s="2"/>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:5">
       <c r="A429" s="2" t="s">
         <v>141</v>
       </c>
@@ -15924,7 +15889,7 @@
       <c r="D429" s="2"/>
       <c r="E429" s="2"/>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:5">
       <c r="A430" s="2">
         <v>143</v>
       </c>
@@ -15939,7 +15904,7 @@
       </c>
       <c r="E430" s="2"/>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:5">
       <c r="A431" s="2">
         <v>144</v>
       </c>
@@ -15954,7 +15919,7 @@
       </c>
       <c r="E431" s="2"/>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:5">
       <c r="A432" s="2">
         <v>145</v>
       </c>
@@ -15969,7 +15934,7 @@
       </c>
       <c r="E432" s="2"/>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:5">
       <c r="A433" s="2">
         <v>146</v>
       </c>
@@ -15984,7 +15949,7 @@
       </c>
       <c r="E433" s="2"/>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:5">
       <c r="A434" s="2" t="s">
         <v>128</v>
       </c>
@@ -15993,7 +15958,7 @@
       <c r="D434" s="2"/>
       <c r="E434" s="2"/>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:5">
       <c r="A435" s="2">
         <v>148</v>
       </c>
@@ -16008,7 +15973,7 @@
       </c>
       <c r="E435" s="2"/>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:5">
       <c r="A436" s="2">
         <v>149</v>
       </c>
@@ -16023,7 +15988,7 @@
       </c>
       <c r="E436" s="2"/>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:5">
       <c r="A437" s="2">
         <v>150</v>
       </c>
@@ -16038,7 +16003,7 @@
       </c>
       <c r="E437" s="2"/>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:5">
       <c r="A438" s="2">
         <v>151</v>
       </c>
@@ -16053,7 +16018,7 @@
       </c>
       <c r="E438" s="2"/>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:5">
       <c r="A439" s="2">
         <v>152</v>
       </c>
@@ -16068,7 +16033,7 @@
       </c>
       <c r="E439" s="2"/>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:5">
       <c r="A440" s="2" t="s">
         <v>200</v>
       </c>
@@ -16077,7 +16042,7 @@
       <c r="D440" s="2"/>
       <c r="E440" s="2"/>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:5">
       <c r="A441" s="2">
         <v>154</v>
       </c>
@@ -16092,7 +16057,7 @@
       </c>
       <c r="E441" s="2"/>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:5">
       <c r="A442" s="2">
         <v>155</v>
       </c>
@@ -16107,7 +16072,7 @@
       </c>
       <c r="E442" s="2"/>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:5">
       <c r="A443" s="2">
         <v>156</v>
       </c>
@@ -16122,7 +16087,7 @@
       </c>
       <c r="E443" s="2"/>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:5">
       <c r="A444" s="2">
         <v>157</v>
       </c>
@@ -16137,7 +16102,7 @@
       </c>
       <c r="E444" s="2"/>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:5">
       <c r="A445" s="2">
         <v>158</v>
       </c>
@@ -16152,7 +16117,7 @@
       </c>
       <c r="E445" s="2"/>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:5">
       <c r="A446" s="2">
         <v>159</v>
       </c>
@@ -16167,7 +16132,7 @@
       </c>
       <c r="E446" s="2"/>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:5">
       <c r="A447" s="2">
         <v>160</v>
       </c>
@@ -16184,19 +16149,19 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E337" r:id="rId1" xr:uid="{3049D288-8E1D-4116-A8D0-763E1CE8AE8F}"/>
-    <hyperlink ref="E186" r:id="rId2" xr:uid="{AD643CED-9C04-4D51-8C00-8CC9D238E2E0}"/>
-    <hyperlink ref="E54" r:id="rId3" xr:uid="{CF726344-B0F5-41B3-92F1-04A7398AF1DB}"/>
-    <hyperlink ref="E33" r:id="rId4" xr:uid="{21F16D33-C79B-4D20-A11A-DE1429767799}"/>
+    <hyperlink ref="E337" r:id="rId1"/>
+    <hyperlink ref="E186" r:id="rId2"/>
+    <hyperlink ref="E54" r:id="rId3"/>
+    <hyperlink ref="E33" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.140625" customWidth="1"/>
@@ -16205,7 +16170,7 @@
     <col min="5" max="5" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -16222,7 +16187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>243</v>
       </c>
@@ -16233,7 +16198,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -16250,7 +16215,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -16265,7 +16230,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -16280,7 +16245,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -16295,7 +16260,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -16310,7 +16275,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -16325,7 +16290,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -16340,7 +16305,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -16357,7 +16322,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -16374,7 +16339,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -16389,7 +16354,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -16406,7 +16371,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -16421,7 +16386,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -16436,7 +16401,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="2">
         <v>16</v>
       </c>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3036" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3037" uniqueCount="260">
   <si>
     <t>Keyword</t>
   </si>
@@ -2506,7 +2506,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.5703125" customWidth="1"/>
@@ -2607,53 +2607,47 @@
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
+      <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -2662,52 +2656,52 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="2">
-        <v>10</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
@@ -2716,13 +2710,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>11</v>
@@ -2731,71 +2725,69 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="2">
-        <v>15</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2">
-        <v>10000</v>
-      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="2">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -2806,252 +2798,254 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="2">
-        <v>120</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="2">
-        <v>10</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="2">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>90</v>
+      <c r="E25" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E27" s="2">
-        <v>12122</v>
+      <c r="E27" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="2">
-        <v>2311323</v>
+        <v>12122</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>219</v>
+        <v>88</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2311323</v>
+      </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
+        <v>29</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2">
         <v>30</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="2" t="s">
+      <c r="D33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="2">
-        <v>31</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="6">
-        <v>22343244410021</v>
-      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="E35" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>33</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>11</v>
@@ -3060,45 +3054,45 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>34</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>3</v>
+        <v>33</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="6">
-        <v>22343244410021</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E37" s="7"/>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="E38" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>36</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>17</v>
+        <v>35</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>11</v>
@@ -3107,45 +3101,45 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>37</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>3</v>
+        <v>36</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="6">
-        <v>22343244410021</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E40" s="7"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="E41" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>39</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>11</v>
@@ -3154,92 +3148,92 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>40</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>3</v>
+        <v>39</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="6">
-        <v>22343244410021</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E44" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>42</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="7"/>
+      <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>43</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>3</v>
+        <v>42</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="6">
-        <v>22343244410021</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E46" s="7"/>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="E47" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>45</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>17</v>
+        <v>44</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>11</v>
@@ -3248,92 +3242,92 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>3</v>
+        <v>45</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="6">
-        <v>22343244410021</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E49" s="7"/>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="E50" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>48</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>17</v>
+        <v>47</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" s="7"/>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>49</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>3</v>
+        <v>48</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="6">
-        <v>22343244410021</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E52" s="2"/>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E53" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>51</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>17</v>
+        <v>50</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>11</v>
@@ -3342,45 +3336,45 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>52</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>3</v>
+        <v>51</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="2">
-        <v>12</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E55" s="2"/>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E56" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>54</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>17</v>
+        <v>53</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>11</v>
@@ -3389,62 +3383,62 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>55</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>3</v>
+        <v>54</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>218</v>
+        <v>110</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E58" s="8">
-        <v>44594</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>88</v>
+        <v>218</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="2">
-        <v>12</v>
+        <v>117</v>
+      </c>
+      <c r="E59" s="8">
+        <v>44594</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>57</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>17</v>
+        <v>56</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E60" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>58</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>5</v>
+        <v>57</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>11</v>
@@ -3453,13 +3447,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>59</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>11</v>
@@ -3468,107 +3462,107 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>60</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>5</v>
+        <v>59</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E66" s="6">
-        <v>3234</v>
-      </c>
+      <c r="E66" s="2"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E67" s="9">
-        <v>13234</v>
+      <c r="E67" s="6">
+        <v>3234</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E68" s="9">
+        <v>13234</v>
+      </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>66</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>17</v>
+        <v>65</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>11</v>
@@ -3577,165 +3571,165 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>67</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>5</v>
+        <v>66</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E70" s="2"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
+        <v>67</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="2">
         <v>68</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C71" s="2" t="s">
+      <c r="B72" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" s="2"/>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="2" t="s">
+      <c r="D72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="2"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="2">
-        <v>70</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E74" s="6">
-        <v>7826423</v>
-      </c>
+      <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>121</v>
+      <c r="E75" s="6">
+        <v>7826423</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E77" s="2">
-        <v>3478323</v>
+      <c r="E77" s="5" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E78" s="2"/>
+      <c r="E78" s="2">
+        <v>3478323</v>
+      </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>220</v>
+        <v>67</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>77</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>17</v>
+        <v>76</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>11</v>
@@ -3744,80 +3738,78 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
+        <v>77</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="2">
         <v>78</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C81" s="2" t="s">
+      <c r="B82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="2" t="s">
+      <c r="D82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B82" s="3"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="2">
-        <v>80</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B83" s="3"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E84" s="2">
-        <v>1000</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E85" s="2">
-        <v>10</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>3</v>
@@ -3834,13 +3826,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>8</v>
@@ -3851,55 +3843,57 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E88" s="2"/>
+      <c r="E88" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>88</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>3</v>
+        <v>87</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>79</v>
@@ -3907,163 +3901,163 @@
       <c r="D91" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="6">
-        <v>200</v>
-      </c>
+      <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E92" s="5" t="s">
-        <v>121</v>
+      <c r="E92" s="6">
+        <v>200</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="2">
-        <v>3478323</v>
+      <c r="E94" s="5" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E95" s="2"/>
+      <c r="E95" s="2">
+        <v>3478323</v>
+      </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
+        <v>92</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="2"/>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="2">
         <v>93</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="B97" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" s="2"/>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="2" t="s">
+      <c r="D97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="2"/>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="2">
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="2">
         <v>95</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C98" s="2" t="s">
+      <c r="B99" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" s="2"/>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2" t="s">
+      <c r="D99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="2">
-        <v>96</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
       <c r="E100" s="2"/>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E101" s="2"/>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>11</v>
@@ -4072,13 +4066,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>11</v>
@@ -4087,52 +4081,52 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
+        <v>99</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="2"/>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="2">
         <v>100</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B105" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C105" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="2"/>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="2" t="s">
+      <c r="D105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="2"/>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="2">
-        <v>101</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
       <c r="E106" s="2"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>11</v>
@@ -4141,13 +4135,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>11</v>
@@ -4156,18 +4150,33 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
+        <v>103</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="2"/>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="2">
         <v>104</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B110" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C110" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D109" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E109" s="2"/>
+      <c r="D110" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C5EE2A-261A-4A3C-834D-867C1812A955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3037" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="268">
   <si>
     <t>Keyword</t>
   </si>
@@ -800,16 +801,40 @@
   </si>
   <si>
     <t>FRESH</t>
+  </si>
+  <si>
+    <t>viewerror</t>
+  </si>
+  <si>
+    <t>closeerror</t>
+  </si>
+  <si>
+    <t>viewerroredit</t>
+  </si>
+  <si>
+    <t>verifyerrorone</t>
+  </si>
+  <si>
+    <t>verifyerrortwo</t>
+  </si>
+  <si>
+    <t>veifyerrorthree</t>
+  </si>
+  <si>
+    <t>verifyerrorfour</t>
+  </si>
+  <si>
+    <t>verifyerrorfive</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;\-0\ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -852,7 +877,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -875,12 +900,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -896,6 +947,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -957,7 +1010,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -989,9 +1042,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1023,6 +1094,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1198,9 +1287,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" customWidth="1"/>
@@ -1209,7 +1298,7 @@
     <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1226,7 +1315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>71</v>
       </c>
@@ -1237,7 +1326,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -1254,7 +1343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -1269,7 +1358,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -1284,7 +1373,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -1295,7 +1384,7 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -1310,7 +1399,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -1325,7 +1414,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -1340,7 +1429,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -1355,7 +1444,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -1370,7 +1459,7 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -1385,7 +1474,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>72</v>
       </c>
@@ -1394,7 +1483,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -1411,7 +1500,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -1426,7 +1515,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -1443,7 +1532,7 @@
         <v>1231231</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -1458,7 +1547,7 @@
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -1473,7 +1562,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -1490,7 +1579,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -1505,7 +1594,7 @@
       </c>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -1520,7 +1609,7 @@
       </c>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -1535,7 +1624,7 @@
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -1550,7 +1639,7 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>73</v>
       </c>
@@ -1559,7 +1648,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -1576,7 +1665,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -1593,7 +1682,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -1610,7 +1699,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -1627,7 +1716,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -1644,7 +1733,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -1659,7 +1748,7 @@
       </c>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -1676,7 +1765,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -1693,7 +1782,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -1710,7 +1799,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -1725,7 +1814,7 @@
       </c>
       <c r="E34" s="4"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -1740,7 +1829,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -1755,7 +1844,7 @@
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>74</v>
       </c>
@@ -1764,7 +1853,7 @@
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -1779,7 +1868,7 @@
       </c>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -1796,7 +1885,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -1813,7 +1902,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -1830,7 +1919,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -1845,7 +1934,7 @@
       </c>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -1860,7 +1949,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>75</v>
       </c>
@@ -1869,7 +1958,7 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -1884,7 +1973,7 @@
       </c>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -1899,7 +1988,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -1914,7 +2003,7 @@
       </c>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -1929,7 +2018,7 @@
       </c>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -1944,7 +2033,7 @@
       </c>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -1961,7 +2050,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -1978,7 +2067,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -1995,7 +2084,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -2012,7 +2101,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -2029,7 +2118,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -2044,7 +2133,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -2059,7 +2148,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>76</v>
       </c>
@@ -2068,7 +2157,7 @@
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -2083,7 +2172,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -2100,7 +2189,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -2117,7 +2206,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -2134,7 +2223,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -2149,7 +2238,7 @@
       </c>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -2164,7 +2253,7 @@
       </c>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -2179,7 +2268,7 @@
       </c>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -2196,7 +2285,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -2213,7 +2302,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -2230,7 +2319,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -2245,7 +2334,7 @@
       </c>
       <c r="E68" s="5"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -2260,7 +2349,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -2275,7 +2364,7 @@
       </c>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -2292,7 +2381,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -2309,7 +2398,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -2326,7 +2415,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -2341,7 +2430,7 @@
       </c>
       <c r="E74" s="5"/>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -2356,7 +2445,7 @@
       </c>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>77</v>
       </c>
@@ -2365,7 +2454,7 @@
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -2380,7 +2469,7 @@
       </c>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -2395,7 +2484,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -2410,7 +2499,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -2425,7 +2514,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>78</v>
       </c>
@@ -2434,7 +2523,7 @@
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -2449,7 +2538,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -2464,7 +2553,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -2479,7 +2568,7 @@
       </c>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -2496,8 +2585,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E33" r:id="rId1"/>
-    <hyperlink ref="E54" r:id="rId2"/>
+    <hyperlink ref="E33" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E54" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId3"/>
@@ -2505,9 +2594,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.5703125" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
@@ -2516,7 +2605,7 @@
     <col min="5" max="5" width="34.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -2533,7 +2622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>129</v>
       </c>
@@ -2544,7 +2633,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -2561,7 +2650,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -2576,7 +2665,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -2591,7 +2680,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -2606,7 +2695,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>255</v>
@@ -2615,7 +2704,7 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -2630,7 +2719,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>255</v>
@@ -2639,7 +2728,7 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>6</v>
       </c>
@@ -2654,7 +2743,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>7</v>
       </c>
@@ -2669,7 +2758,7 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>8</v>
       </c>
@@ -2684,7 +2773,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>70</v>
       </c>
@@ -2693,7 +2782,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>10</v>
       </c>
@@ -2708,7 +2797,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>11</v>
       </c>
@@ -2723,7 +2812,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>12</v>
       </c>
@@ -2738,7 +2827,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -2753,7 +2842,7 @@
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>217</v>
       </c>
@@ -2762,7 +2851,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>15</v>
       </c>
@@ -2779,7 +2868,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>16</v>
       </c>
@@ -2796,7 +2885,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>17</v>
       </c>
@@ -2813,7 +2902,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>18</v>
       </c>
@@ -2830,7 +2919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>19</v>
       </c>
@@ -2847,7 +2936,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>20</v>
       </c>
@@ -2864,7 +2953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>21</v>
       </c>
@@ -2881,7 +2970,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>22</v>
       </c>
@@ -2898,7 +2987,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>23</v>
       </c>
@@ -2915,7 +3004,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>24</v>
       </c>
@@ -2932,7 +3021,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>25</v>
       </c>
@@ -2949,7 +3038,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>26</v>
       </c>
@@ -2964,7 +3053,7 @@
       </c>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>27</v>
       </c>
@@ -2981,7 +3070,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -2996,7 +3085,7 @@
       </c>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -3011,7 +3100,7 @@
       </c>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>72</v>
       </c>
@@ -3020,7 +3109,7 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>31</v>
       </c>
@@ -3037,7 +3126,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>32</v>
       </c>
@@ -3052,7 +3141,7 @@
       </c>
       <c r="E36" s="7"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>33</v>
       </c>
@@ -3067,7 +3156,7 @@
       </c>
       <c r="E37" s="7"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>34</v>
       </c>
@@ -3084,7 +3173,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>35</v>
       </c>
@@ -3099,7 +3188,7 @@
       </c>
       <c r="E39" s="7"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>36</v>
       </c>
@@ -3114,7 +3203,7 @@
       </c>
       <c r="E40" s="7"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>37</v>
       </c>
@@ -3131,7 +3220,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>38</v>
       </c>
@@ -3146,7 +3235,7 @@
       </c>
       <c r="E42" s="7"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>39</v>
       </c>
@@ -3161,7 +3250,7 @@
       </c>
       <c r="E43" s="7"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>40</v>
       </c>
@@ -3178,7 +3267,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>41</v>
       </c>
@@ -3193,7 +3282,7 @@
       </c>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>42</v>
       </c>
@@ -3208,7 +3297,7 @@
       </c>
       <c r="E46" s="7"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>43</v>
       </c>
@@ -3225,7 +3314,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>44</v>
       </c>
@@ -3240,7 +3329,7 @@
       </c>
       <c r="E48" s="7"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>45</v>
       </c>
@@ -3255,7 +3344,7 @@
       </c>
       <c r="E49" s="7"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>46</v>
       </c>
@@ -3272,7 +3361,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>47</v>
       </c>
@@ -3287,7 +3376,7 @@
       </c>
       <c r="E51" s="7"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>48</v>
       </c>
@@ -3302,7 +3391,7 @@
       </c>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>49</v>
       </c>
@@ -3319,7 +3408,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>50</v>
       </c>
@@ -3334,7 +3423,7 @@
       </c>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>51</v>
       </c>
@@ -3349,7 +3438,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>52</v>
       </c>
@@ -3366,7 +3455,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>53</v>
       </c>
@@ -3381,7 +3470,7 @@
       </c>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>54</v>
       </c>
@@ -3396,7 +3485,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>55</v>
       </c>
@@ -3413,7 +3502,7 @@
         <v>44594</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>56</v>
       </c>
@@ -3430,7 +3519,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>57</v>
       </c>
@@ -3445,7 +3534,7 @@
       </c>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>58</v>
       </c>
@@ -3460,7 +3549,7 @@
       </c>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>59</v>
       </c>
@@ -3475,7 +3564,7 @@
       </c>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>60</v>
       </c>
@@ -3490,7 +3579,7 @@
       </c>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>61</v>
       </c>
@@ -3505,7 +3594,7 @@
       </c>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>62</v>
       </c>
@@ -3520,7 +3609,7 @@
       </c>
       <c r="E66" s="2"/>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>63</v>
       </c>
@@ -3537,7 +3626,7 @@
         <v>3234</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>64</v>
       </c>
@@ -3554,7 +3643,7 @@
         <v>13234</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>65</v>
       </c>
@@ -3569,7 +3658,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>66</v>
       </c>
@@ -3584,7 +3673,7 @@
       </c>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>67</v>
       </c>
@@ -3599,7 +3688,7 @@
       </c>
       <c r="E71" s="2"/>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>68</v>
       </c>
@@ -3614,7 +3703,7 @@
       </c>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>118</v>
       </c>
@@ -3623,7 +3712,7 @@
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>70</v>
       </c>
@@ -3638,7 +3727,7 @@
       </c>
       <c r="E74" s="2"/>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>71</v>
       </c>
@@ -3655,7 +3744,7 @@
         <v>7826423</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>72</v>
       </c>
@@ -3672,7 +3761,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>73</v>
       </c>
@@ -3689,7 +3778,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>74</v>
       </c>
@@ -3706,7 +3795,7 @@
         <v>3478323</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>75</v>
       </c>
@@ -3721,7 +3810,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>76</v>
       </c>
@@ -3736,7 +3825,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>77</v>
       </c>
@@ -3751,7 +3840,7 @@
       </c>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>78</v>
       </c>
@@ -3766,7 +3855,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>123</v>
       </c>
@@ -3775,7 +3864,7 @@
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>80</v>
       </c>
@@ -3790,7 +3879,7 @@
       </c>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>81</v>
       </c>
@@ -3807,7 +3896,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>82</v>
       </c>
@@ -3824,7 +3913,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>83</v>
       </c>
@@ -3841,7 +3930,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>84</v>
       </c>
@@ -3858,7 +3947,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>85</v>
       </c>
@@ -3873,7 +3962,7 @@
       </c>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>86</v>
       </c>
@@ -3888,7 +3977,7 @@
       </c>
       <c r="E90" s="2"/>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>87</v>
       </c>
@@ -3903,7 +3992,7 @@
       </c>
       <c r="E91" s="2"/>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>88</v>
       </c>
@@ -3920,7 +4009,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>89</v>
       </c>
@@ -3937,7 +4026,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>90</v>
       </c>
@@ -3954,7 +4043,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>91</v>
       </c>
@@ -3971,7 +4060,7 @@
         <v>3478323</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>92</v>
       </c>
@@ -3986,7 +4075,7 @@
       </c>
       <c r="E96" s="2"/>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>93</v>
       </c>
@@ -4001,7 +4090,7 @@
       </c>
       <c r="E97" s="2"/>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>124</v>
       </c>
@@ -4010,7 +4099,7 @@
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>95</v>
       </c>
@@ -4025,7 +4114,7 @@
       </c>
       <c r="E99" s="2"/>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2" t="s">
         <v>255</v>
@@ -4034,7 +4123,7 @@
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>96</v>
       </c>
@@ -4049,7 +4138,7 @@
       </c>
       <c r="E101" s="2"/>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>97</v>
       </c>
@@ -4064,7 +4153,7 @@
       </c>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>98</v>
       </c>
@@ -4079,7 +4168,7 @@
       </c>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>99</v>
       </c>
@@ -4094,7 +4183,7 @@
       </c>
       <c r="E104" s="2"/>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>100</v>
       </c>
@@ -4109,7 +4198,7 @@
       </c>
       <c r="E105" s="2"/>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>128</v>
       </c>
@@ -4118,7 +4207,7 @@
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>101</v>
       </c>
@@ -4133,7 +4222,7 @@
       </c>
       <c r="E107" s="2"/>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>102</v>
       </c>
@@ -4148,7 +4237,7 @@
       </c>
       <c r="E108" s="2"/>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>103</v>
       </c>
@@ -4163,7 +4252,7 @@
       </c>
       <c r="E109" s="2"/>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>104</v>
       </c>
@@ -4185,9 +4274,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E166"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.7109375" style="11" customWidth="1"/>
     <col min="2" max="2" width="35.28515625" style="11" customWidth="1"/>
@@ -4197,7 +4286,7 @@
     <col min="6" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -4214,7 +4303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>130</v>
       </c>
@@ -4225,7 +4314,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -4242,7 +4331,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -4257,7 +4346,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -4272,7 +4361,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -4287,7 +4376,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -4302,7 +4391,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -4317,7 +4406,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>255</v>
@@ -4326,7 +4415,7 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4341,7 +4430,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -4356,7 +4445,7 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -4373,7 +4462,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>146</v>
       </c>
@@ -4382,7 +4471,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -4397,7 +4486,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>255</v>
@@ -4406,7 +4495,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -4421,7 +4510,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -4438,7 +4527,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -4455,7 +4544,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -4472,7 +4561,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -4489,7 +4578,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -4506,7 +4595,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -4523,7 +4612,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -4540,7 +4629,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -4555,7 +4644,7 @@
       </c>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -4570,7 +4659,7 @@
       </c>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -4585,7 +4674,7 @@
       </c>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -4602,7 +4691,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -4619,7 +4708,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -4636,7 +4725,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -4651,7 +4740,7 @@
       </c>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -4666,7 +4755,7 @@
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>164</v>
       </c>
@@ -4675,7 +4764,7 @@
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -4690,7 +4779,7 @@
       </c>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
         <v>255</v>
@@ -4699,7 +4788,7 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -4714,7 +4803,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>33</v>
       </c>
@@ -4729,7 +4818,7 @@
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>34</v>
       </c>
@@ -4746,7 +4835,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>35</v>
       </c>
@@ -4761,7 +4850,7 @@
       </c>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>36</v>
       </c>
@@ -4776,7 +4865,7 @@
       </c>
       <c r="E39" s="2"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>37</v>
       </c>
@@ -4791,7 +4880,7 @@
       </c>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>38</v>
       </c>
@@ -4806,7 +4895,7 @@
       </c>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>39</v>
       </c>
@@ -4821,7 +4910,7 @@
       </c>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>167</v>
       </c>
@@ -4830,7 +4919,7 @@
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>41</v>
       </c>
@@ -4847,7 +4936,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>42</v>
       </c>
@@ -4864,7 +4953,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>43</v>
       </c>
@@ -4881,7 +4970,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>44</v>
       </c>
@@ -4896,7 +4985,7 @@
       </c>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>45</v>
       </c>
@@ -4913,7 +5002,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>46</v>
       </c>
@@ -4928,7 +5017,7 @@
       </c>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>47</v>
       </c>
@@ -4945,7 +5034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>48</v>
       </c>
@@ -4960,7 +5049,7 @@
       </c>
       <c r="E51" s="2"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>49</v>
       </c>
@@ -4977,7 +5066,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>50</v>
       </c>
@@ -4992,7 +5081,7 @@
       </c>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>51</v>
       </c>
@@ -5009,7 +5098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>52</v>
       </c>
@@ -5024,7 +5113,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>53</v>
       </c>
@@ -5041,7 +5130,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>54</v>
       </c>
@@ -5056,7 +5145,7 @@
       </c>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>55</v>
       </c>
@@ -5073,7 +5162,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>56</v>
       </c>
@@ -5088,7 +5177,7 @@
       </c>
       <c r="E59" s="2"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>57</v>
       </c>
@@ -5103,7 +5192,7 @@
       </c>
       <c r="E60" s="2"/>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>58</v>
       </c>
@@ -5118,7 +5207,7 @@
       </c>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>181</v>
       </c>
@@ -5127,7 +5216,7 @@
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>60</v>
       </c>
@@ -5144,7 +5233,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>61</v>
       </c>
@@ -5159,7 +5248,7 @@
       </c>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>62</v>
       </c>
@@ -5174,7 +5263,7 @@
       </c>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>63</v>
       </c>
@@ -5191,7 +5280,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>64</v>
       </c>
@@ -5208,7 +5297,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>65</v>
       </c>
@@ -5223,7 +5312,7 @@
       </c>
       <c r="E68" s="2"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>66</v>
       </c>
@@ -5234,7 +5323,7 @@
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>67</v>
       </c>
@@ -5251,7 +5340,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>68</v>
       </c>
@@ -5268,7 +5357,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>69</v>
       </c>
@@ -5283,7 +5372,7 @@
       </c>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>70</v>
       </c>
@@ -5298,7 +5387,7 @@
       </c>
       <c r="E73" s="5"/>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>71</v>
       </c>
@@ -5315,7 +5404,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>72</v>
       </c>
@@ -5330,7 +5419,7 @@
       </c>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>73</v>
       </c>
@@ -5347,7 +5436,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>74</v>
       </c>
@@ -5362,7 +5451,7 @@
       </c>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>75</v>
       </c>
@@ -5377,7 +5466,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>76</v>
       </c>
@@ -5392,7 +5481,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>77</v>
       </c>
@@ -5409,7 +5498,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>78</v>
       </c>
@@ -5424,7 +5513,7 @@
       </c>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>79</v>
       </c>
@@ -5439,7 +5528,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>80</v>
       </c>
@@ -5454,7 +5543,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>81</v>
       </c>
@@ -5471,7 +5560,7 @@
         <v>3.4628376482734602E+18</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>82</v>
       </c>
@@ -5486,7 +5575,7 @@
       </c>
       <c r="E85" s="2"/>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>83</v>
       </c>
@@ -5501,7 +5590,7 @@
       </c>
       <c r="E86" s="2"/>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>84</v>
       </c>
@@ -5516,7 +5605,7 @@
       </c>
       <c r="E87" s="2"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>85</v>
       </c>
@@ -5533,7 +5622,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>86</v>
       </c>
@@ -5548,7 +5637,7 @@
       </c>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>87</v>
       </c>
@@ -5563,7 +5652,7 @@
       </c>
       <c r="E90" s="2"/>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>88</v>
       </c>
@@ -5578,7 +5667,7 @@
       </c>
       <c r="E91" s="2"/>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>89</v>
       </c>
@@ -5595,7 +5684,7 @@
         <v>3.4628376482734602E+18</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>90</v>
       </c>
@@ -5610,7 +5699,7 @@
       </c>
       <c r="E93" s="2"/>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>91</v>
       </c>
@@ -5625,7 +5714,7 @@
       </c>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>92</v>
       </c>
@@ -5642,7 +5731,7 @@
         <v>44854</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>93</v>
       </c>
@@ -5659,7 +5748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>94</v>
       </c>
@@ -5674,7 +5763,7 @@
       </c>
       <c r="E97" s="2"/>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>95</v>
       </c>
@@ -5689,7 +5778,7 @@
       </c>
       <c r="E98" s="2"/>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>96</v>
       </c>
@@ -5704,7 +5793,7 @@
       </c>
       <c r="E99" s="2"/>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>97</v>
       </c>
@@ -5719,7 +5808,7 @@
       </c>
       <c r="E100" s="2"/>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>98</v>
       </c>
@@ -5734,7 +5823,7 @@
       </c>
       <c r="E101" s="2"/>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>118</v>
       </c>
@@ -5743,7 +5832,7 @@
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>100</v>
       </c>
@@ -5758,7 +5847,7 @@
       </c>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>101</v>
       </c>
@@ -5775,7 +5864,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>102</v>
       </c>
@@ -5790,7 +5879,7 @@
       </c>
       <c r="E105" s="2"/>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>103</v>
       </c>
@@ -5805,7 +5894,7 @@
       </c>
       <c r="E106" s="2"/>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>104</v>
       </c>
@@ -5822,7 +5911,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>105</v>
       </c>
@@ -5839,7 +5928,7 @@
         <v>7600</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>106</v>
       </c>
@@ -5856,7 +5945,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>107</v>
       </c>
@@ -5873,7 +5962,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>108</v>
       </c>
@@ -5888,7 +5977,7 @@
       </c>
       <c r="E111" s="2"/>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>109</v>
       </c>
@@ -5903,7 +5992,7 @@
       </c>
       <c r="E112" s="2"/>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>131</v>
       </c>
@@ -5912,7 +6001,7 @@
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>111</v>
       </c>
@@ -5927,7 +6016,7 @@
       </c>
       <c r="E114" s="2"/>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2" t="s">
         <v>255</v>
@@ -5936,7 +6025,7 @@
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>112</v>
       </c>
@@ -5951,7 +6040,7 @@
       </c>
       <c r="E116" s="2"/>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>113</v>
       </c>
@@ -5966,7 +6055,7 @@
       </c>
       <c r="E117" s="2"/>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>114</v>
       </c>
@@ -5981,7 +6070,7 @@
       </c>
       <c r="E118" s="2"/>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>115</v>
       </c>
@@ -5996,7 +6085,7 @@
       </c>
       <c r="E119" s="2"/>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>116</v>
       </c>
@@ -6011,7 +6100,7 @@
       </c>
       <c r="E120" s="2"/>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>117</v>
       </c>
@@ -6026,7 +6115,7 @@
       </c>
       <c r="E121" s="2"/>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>118</v>
       </c>
@@ -6041,7 +6130,7 @@
       </c>
       <c r="E122" s="2"/>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>119</v>
       </c>
@@ -6056,7 +6145,7 @@
       </c>
       <c r="E123" s="2"/>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>120</v>
       </c>
@@ -6073,7 +6162,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>121</v>
       </c>
@@ -6090,7 +6179,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>122</v>
       </c>
@@ -6107,7 +6196,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>123</v>
       </c>
@@ -6124,7 +6213,7 @@
         <v>12323</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>124</v>
       </c>
@@ -6139,7 +6228,7 @@
       </c>
       <c r="E128" s="2"/>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>125</v>
       </c>
@@ -6154,7 +6243,7 @@
       </c>
       <c r="E129" s="2"/>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>126</v>
       </c>
@@ -6169,7 +6258,7 @@
       </c>
       <c r="E130" s="2"/>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>253</v>
       </c>
@@ -6178,7 +6267,7 @@
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>128</v>
       </c>
@@ -6193,7 +6282,7 @@
       </c>
       <c r="E132" s="2"/>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2" t="s">
         <v>255</v>
@@ -6202,7 +6291,7 @@
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>129</v>
       </c>
@@ -6217,7 +6306,7 @@
       </c>
       <c r="E134" s="2"/>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>130</v>
       </c>
@@ -6232,7 +6321,7 @@
       </c>
       <c r="E135" s="2"/>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>131</v>
       </c>
@@ -6247,7 +6336,7 @@
       </c>
       <c r="E136" s="2"/>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>132</v>
       </c>
@@ -6264,7 +6353,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>133</v>
       </c>
@@ -6279,7 +6368,7 @@
       </c>
       <c r="E138" s="2"/>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>134</v>
       </c>
@@ -6294,7 +6383,7 @@
       </c>
       <c r="E139" s="2"/>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>139</v>
       </c>
@@ -6303,7 +6392,7 @@
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>136</v>
       </c>
@@ -6318,7 +6407,7 @@
       </c>
       <c r="E141" s="2"/>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2" t="s">
         <v>255</v>
@@ -6327,7 +6416,7 @@
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>137</v>
       </c>
@@ -6342,7 +6431,7 @@
       </c>
       <c r="E143" s="2"/>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>138</v>
       </c>
@@ -6357,7 +6446,7 @@
       </c>
       <c r="E144" s="2"/>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>139</v>
       </c>
@@ -6372,7 +6461,7 @@
       </c>
       <c r="E145" s="2"/>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>140</v>
       </c>
@@ -6387,7 +6476,7 @@
       </c>
       <c r="E146" s="2"/>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>141</v>
       </c>
@@ -6402,7 +6491,7 @@
       </c>
       <c r="E147" s="2"/>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>141</v>
       </c>
@@ -6411,7 +6500,7 @@
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>143</v>
       </c>
@@ -6426,7 +6515,7 @@
       </c>
       <c r="E149" s="2"/>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>144</v>
       </c>
@@ -6441,7 +6530,7 @@
       </c>
       <c r="E150" s="2"/>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>145</v>
       </c>
@@ -6456,7 +6545,7 @@
       </c>
       <c r="E151" s="2"/>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>146</v>
       </c>
@@ -6471,7 +6560,7 @@
       </c>
       <c r="E152" s="2"/>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>128</v>
       </c>
@@ -6480,7 +6569,7 @@
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>148</v>
       </c>
@@ -6495,7 +6584,7 @@
       </c>
       <c r="E154" s="2"/>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>149</v>
       </c>
@@ -6510,7 +6599,7 @@
       </c>
       <c r="E155" s="2"/>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>150</v>
       </c>
@@ -6525,7 +6614,7 @@
       </c>
       <c r="E156" s="2"/>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>151</v>
       </c>
@@ -6540,7 +6629,7 @@
       </c>
       <c r="E157" s="2"/>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>152</v>
       </c>
@@ -6555,7 +6644,7 @@
       </c>
       <c r="E158" s="2"/>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>200</v>
       </c>
@@ -6564,7 +6653,7 @@
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>154</v>
       </c>
@@ -6579,7 +6668,7 @@
       </c>
       <c r="E160" s="2"/>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>155</v>
       </c>
@@ -6594,7 +6683,7 @@
       </c>
       <c r="E161" s="2"/>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>156</v>
       </c>
@@ -6609,7 +6698,7 @@
       </c>
       <c r="E162" s="2"/>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>157</v>
       </c>
@@ -6624,7 +6713,7 @@
       </c>
       <c r="E163" s="2"/>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>158</v>
       </c>
@@ -6639,7 +6728,7 @@
       </c>
       <c r="E164" s="2"/>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>159</v>
       </c>
@@ -6654,7 +6743,7 @@
       </c>
       <c r="E165" s="2"/>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>160</v>
       </c>
@@ -6672,7 +6761,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E20" r:id="rId1"/>
+    <hyperlink ref="E20" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId2"/>
@@ -6680,9 +6769,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E124"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" customWidth="1"/>
@@ -6691,7 +6780,7 @@
     <col min="5" max="5" width="52.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -6708,7 +6797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>129</v>
       </c>
@@ -6719,7 +6808,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -6736,7 +6825,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -6751,7 +6840,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -6766,7 +6855,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -6781,7 +6870,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -6796,7 +6885,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>259</v>
@@ -6805,7 +6894,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -6820,7 +6909,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -6835,7 +6924,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>204</v>
       </c>
@@ -6844,7 +6933,7 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -6861,7 +6950,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -6878,7 +6967,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -6895,7 +6984,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -6912,7 +7001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -6929,7 +7018,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -6946,7 +7035,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -6963,7 +7052,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -6980,7 +7069,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -6997,7 +7086,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -7014,7 +7103,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -7031,7 +7120,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -7048,7 +7137,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -7063,7 +7152,7 @@
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -7078,7 +7167,7 @@
       </c>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -7093,7 +7182,7 @@
       </c>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -7108,7 +7197,7 @@
       </c>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
         <v>255</v>
@@ -7117,7 +7206,7 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -7132,7 +7221,7 @@
       </c>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -7147,7 +7236,7 @@
       </c>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -7164,7 +7253,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>146</v>
       </c>
@@ -7173,7 +7262,7 @@
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -7188,7 +7277,7 @@
       </c>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -7203,7 +7292,7 @@
       </c>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -7220,7 +7309,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -7237,7 +7326,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -7254,7 +7343,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -7271,7 +7360,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -7288,7 +7377,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -7305,7 +7394,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -7322,7 +7411,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -7337,7 +7426,7 @@
       </c>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -7352,7 +7441,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -7367,7 +7456,7 @@
       </c>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
         <v>255</v>
@@ -7376,7 +7465,7 @@
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>43</v>
       </c>
@@ -7391,7 +7480,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>44</v>
       </c>
@@ -7406,7 +7495,7 @@
       </c>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>45</v>
       </c>
@@ -7423,7 +7512,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>46</v>
       </c>
@@ -7438,7 +7527,7 @@
       </c>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>47</v>
       </c>
@@ -7455,7 +7544,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>48</v>
       </c>
@@ -7472,7 +7561,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>49</v>
       </c>
@@ -7489,7 +7578,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>50</v>
       </c>
@@ -7504,7 +7593,7 @@
       </c>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>51</v>
       </c>
@@ -7521,7 +7610,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>52</v>
       </c>
@@ -7536,7 +7625,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>53</v>
       </c>
@@ -7553,7 +7642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>54</v>
       </c>
@@ -7568,7 +7657,7 @@
       </c>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>55</v>
       </c>
@@ -7585,7 +7674,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>56</v>
       </c>
@@ -7600,7 +7689,7 @@
       </c>
       <c r="E59" s="2"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>57</v>
       </c>
@@ -7617,7 +7706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>58</v>
       </c>
@@ -7632,7 +7721,7 @@
       </c>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>59</v>
       </c>
@@ -7649,7 +7738,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>60</v>
       </c>
@@ -7666,7 +7755,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>61</v>
       </c>
@@ -7681,7 +7770,7 @@
       </c>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>62</v>
       </c>
@@ -7696,7 +7785,7 @@
       </c>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>63</v>
       </c>
@@ -7711,7 +7800,7 @@
       </c>
       <c r="E66" s="2"/>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>205</v>
       </c>
@@ -7720,7 +7809,7 @@
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>65</v>
       </c>
@@ -7735,7 +7824,7 @@
       </c>
       <c r="E68" s="2"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>66</v>
       </c>
@@ -7750,7 +7839,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
         <v>255</v>
@@ -7759,7 +7848,7 @@
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>67</v>
       </c>
@@ -7774,7 +7863,7 @@
       </c>
       <c r="E71" s="5"/>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>68</v>
       </c>
@@ -7789,7 +7878,7 @@
       </c>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>69</v>
       </c>
@@ -7804,7 +7893,7 @@
       </c>
       <c r="E73" s="2"/>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>70</v>
       </c>
@@ -7819,7 +7908,7 @@
       </c>
       <c r="E74" s="2"/>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>71</v>
       </c>
@@ -7834,7 +7923,7 @@
       </c>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>72</v>
       </c>
@@ -7849,7 +7938,7 @@
       </c>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>73</v>
       </c>
@@ -7864,7 +7953,7 @@
       </c>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>141</v>
       </c>
@@ -7873,7 +7962,7 @@
       <c r="D78" s="2"/>
       <c r="E78" s="5"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>75</v>
       </c>
@@ -7888,7 +7977,7 @@
       </c>
       <c r="E79" s="5"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
         <v>255</v>
@@ -7897,7 +7986,7 @@
       <c r="D80" s="2"/>
       <c r="E80" s="5"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>76</v>
       </c>
@@ -7912,7 +8001,7 @@
       </c>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>77</v>
       </c>
@@ -7927,7 +8016,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>78</v>
       </c>
@@ -7942,7 +8031,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>79</v>
       </c>
@@ -7957,7 +8046,7 @@
       </c>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>80</v>
       </c>
@@ -7972,7 +8061,7 @@
       </c>
       <c r="E85" s="2"/>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>81</v>
       </c>
@@ -7987,7 +8076,7 @@
       </c>
       <c r="E86" s="2"/>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>82</v>
       </c>
@@ -8004,7 +8093,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>83</v>
       </c>
@@ -8019,7 +8108,7 @@
       </c>
       <c r="E88" s="2"/>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>84</v>
       </c>
@@ -8034,7 +8123,7 @@
       </c>
       <c r="E89" s="7"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>85</v>
       </c>
@@ -8049,7 +8138,7 @@
       </c>
       <c r="E90" s="2"/>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>86</v>
       </c>
@@ -8066,7 +8155,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>87</v>
       </c>
@@ -8081,7 +8170,7 @@
       </c>
       <c r="E92" s="5"/>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>88</v>
       </c>
@@ -8098,7 +8187,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>89</v>
       </c>
@@ -8113,7 +8202,7 @@
       </c>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>90</v>
       </c>
@@ -8130,7 +8219,7 @@
         <v>10340</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>91</v>
       </c>
@@ -8145,7 +8234,7 @@
       </c>
       <c r="E96" s="2"/>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>92</v>
       </c>
@@ -8160,7 +8249,7 @@
       </c>
       <c r="E97" s="2"/>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>93</v>
       </c>
@@ -8175,7 +8264,7 @@
       </c>
       <c r="E98" s="2"/>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2" t="s">
         <v>255</v>
@@ -8184,7 +8273,7 @@
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>94</v>
       </c>
@@ -8199,7 +8288,7 @@
       </c>
       <c r="E100" s="2"/>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>95</v>
       </c>
@@ -8214,7 +8303,7 @@
       </c>
       <c r="E101" s="2"/>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>96</v>
       </c>
@@ -8229,7 +8318,7 @@
       </c>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>97</v>
       </c>
@@ -8244,7 +8333,7 @@
       </c>
       <c r="E103" s="2"/>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>141</v>
       </c>
@@ -8253,7 +8342,7 @@
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>99</v>
       </c>
@@ -8268,7 +8357,7 @@
       </c>
       <c r="E105" s="2"/>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2" t="s">
         <v>255</v>
@@ -8277,7 +8366,7 @@
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>100</v>
       </c>
@@ -8292,7 +8381,7 @@
       </c>
       <c r="E107" s="2"/>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>101</v>
       </c>
@@ -8307,7 +8396,7 @@
       </c>
       <c r="E108" s="2"/>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>102</v>
       </c>
@@ -8322,7 +8411,7 @@
       </c>
       <c r="E109" s="2"/>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>103</v>
       </c>
@@ -8337,7 +8426,7 @@
       </c>
       <c r="E110" s="2"/>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>104</v>
       </c>
@@ -8352,7 +8441,7 @@
       </c>
       <c r="E111" s="2"/>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>128</v>
       </c>
@@ -8361,7 +8450,7 @@
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>106</v>
       </c>
@@ -8376,7 +8465,7 @@
       </c>
       <c r="E113" s="2"/>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2" t="s">
         <v>255</v>
@@ -8385,7 +8474,7 @@
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>107</v>
       </c>
@@ -8400,7 +8489,7 @@
       </c>
       <c r="E115" s="2"/>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>108</v>
       </c>
@@ -8415,7 +8504,7 @@
       </c>
       <c r="E116" s="2"/>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>109</v>
       </c>
@@ -8430,7 +8519,7 @@
       </c>
       <c r="E117" s="2"/>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>110</v>
       </c>
@@ -8445,7 +8534,7 @@
       </c>
       <c r="E118" s="2"/>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>111</v>
       </c>
@@ -8460,7 +8549,7 @@
       </c>
       <c r="E119" s="2"/>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>112</v>
       </c>
@@ -8475,7 +8564,7 @@
       </c>
       <c r="E120" s="2"/>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>113</v>
       </c>
@@ -8490,7 +8579,7 @@
       </c>
       <c r="E121" s="2"/>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>114</v>
       </c>
@@ -8505,7 +8594,7 @@
       </c>
       <c r="E122" s="2"/>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>115</v>
       </c>
@@ -8520,7 +8609,7 @@
       </c>
       <c r="E123" s="2"/>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>116</v>
       </c>
@@ -8537,7 +8626,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E38" r:id="rId1"/>
+    <hyperlink ref="E38" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId2"/>
@@ -8545,9 +8634,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E60"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.140625" customWidth="1"/>
@@ -8556,7 +8645,7 @@
     <col min="5" max="5" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -8573,7 +8662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>252</v>
       </c>
@@ -8584,7 +8673,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -8601,7 +8690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -8616,7 +8705,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -8631,7 +8720,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -8646,7 +8735,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -8661,7 +8750,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -8676,7 +8765,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>255</v>
@@ -8685,7 +8774,7 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -8700,7 +8789,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -8715,7 +8804,7 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -8732,7 +8821,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -8747,7 +8836,7 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -8762,7 +8851,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -8777,7 +8866,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -8792,7 +8881,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -8807,7 +8896,7 @@
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -8822,7 +8911,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -8837,7 +8926,7 @@
       </c>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -8852,7 +8941,7 @@
       </c>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -8867,7 +8956,7 @@
       </c>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -8882,7 +8971,7 @@
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -8897,7 +8986,7 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -8912,7 +9001,7 @@
       </c>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -8927,7 +9016,7 @@
       </c>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -8942,7 +9031,7 @@
       </c>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -8957,7 +9046,7 @@
       </c>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -8972,7 +9061,7 @@
       </c>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -8987,7 +9076,7 @@
       </c>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -9002,7 +9091,7 @@
       </c>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -9017,7 +9106,7 @@
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -9032,7 +9121,7 @@
       </c>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -9047,7 +9136,7 @@
       </c>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -9062,7 +9151,7 @@
       </c>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -9077,7 +9166,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -9092,7 +9181,7 @@
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -9107,7 +9196,7 @@
       </c>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -9122,7 +9211,7 @@
       </c>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
         <v>255</v>
@@ -9131,7 +9220,7 @@
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -9146,7 +9235,7 @@
       </c>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -9161,7 +9250,7 @@
       </c>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>141</v>
       </c>
@@ -9170,7 +9259,7 @@
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -9185,7 +9274,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -9200,7 +9289,7 @@
       </c>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -9215,7 +9304,7 @@
       </c>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -9230,7 +9319,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>128</v>
       </c>
@@ -9239,7 +9328,7 @@
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>45</v>
       </c>
@@ -9254,7 +9343,7 @@
       </c>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>46</v>
       </c>
@@ -9269,7 +9358,7 @@
       </c>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>47</v>
       </c>
@@ -9284,7 +9373,7 @@
       </c>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>48</v>
       </c>
@@ -9299,7 +9388,7 @@
       </c>
       <c r="E51" s="2"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>49</v>
       </c>
@@ -9314,7 +9403,7 @@
       </c>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>200</v>
       </c>
@@ -9323,7 +9412,7 @@
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>52</v>
       </c>
@@ -9338,7 +9427,7 @@
       </c>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>53</v>
       </c>
@@ -9353,7 +9442,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>54</v>
       </c>
@@ -9368,7 +9457,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>55</v>
       </c>
@@ -9383,7 +9472,7 @@
       </c>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>56</v>
       </c>
@@ -9398,7 +9487,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>57</v>
       </c>
@@ -9413,7 +9502,7 @@
       </c>
       <c r="E59" s="2"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>58</v>
       </c>
@@ -9434,9 +9523,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E447"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
     <col min="2" max="2" width="26.140625" customWidth="1"/>
@@ -9445,7 +9534,7 @@
     <col min="5" max="5" width="49.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -9462,7 +9551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>71</v>
       </c>
@@ -9473,7 +9562,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -9490,7 +9579,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -9505,7 +9594,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -9520,7 +9609,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -9529,7 +9618,7 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -9544,7 +9633,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -9559,7 +9648,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -9574,7 +9663,7 @@
       </c>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -9589,7 +9678,7 @@
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -9604,7 +9693,7 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -9619,7 +9708,7 @@
       </c>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>72</v>
       </c>
@@ -9628,7 +9717,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -9645,7 +9734,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -9660,7 +9749,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -9677,7 +9766,7 @@
         <v>1231231</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -9692,7 +9781,7 @@
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -9707,7 +9796,7 @@
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -9724,7 +9813,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -9739,7 +9828,7 @@
       </c>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -9754,7 +9843,7 @@
       </c>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -9769,7 +9858,7 @@
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -9784,7 +9873,7 @@
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>73</v>
       </c>
@@ -9793,7 +9882,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -9810,7 +9899,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -9827,7 +9916,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -9844,7 +9933,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -9861,7 +9950,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -9878,7 +9967,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -9893,7 +9982,7 @@
       </c>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -9910,7 +9999,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -9927,7 +10016,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -9944,7 +10033,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -9959,7 +10048,7 @@
       </c>
       <c r="E34" s="4"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -9974,7 +10063,7 @@
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -9989,7 +10078,7 @@
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>74</v>
       </c>
@@ -9998,7 +10087,7 @@
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -10013,7 +10102,7 @@
       </c>
       <c r="E38" s="2"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -10030,7 +10119,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -10047,7 +10136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -10064,7 +10153,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -10079,7 +10168,7 @@
       </c>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -10094,7 +10183,7 @@
       </c>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>75</v>
       </c>
@@ -10103,7 +10192,7 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -10118,7 +10207,7 @@
       </c>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -10133,7 +10222,7 @@
       </c>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -10148,7 +10237,7 @@
       </c>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -10163,7 +10252,7 @@
       </c>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -10178,7 +10267,7 @@
       </c>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -10195,7 +10284,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -10212,7 +10301,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -10229,7 +10318,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -10246,7 +10335,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -10263,7 +10352,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -10278,7 +10367,7 @@
       </c>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -10293,7 +10382,7 @@
       </c>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>76</v>
       </c>
@@ -10302,7 +10391,7 @@
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -10317,7 +10406,7 @@
       </c>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -10334,7 +10423,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -10351,7 +10440,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -10368,7 +10457,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -10383,7 +10472,7 @@
       </c>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -10398,7 +10487,7 @@
       </c>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -10413,7 +10502,7 @@
       </c>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -10430,7 +10519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -10447,7 +10536,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -10464,7 +10553,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -10479,7 +10568,7 @@
       </c>
       <c r="E68" s="5"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -10494,7 +10583,7 @@
       </c>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -10509,7 +10598,7 @@
       </c>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -10526,7 +10615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -10543,7 +10632,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -10560,7 +10649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -10575,7 +10664,7 @@
       </c>
       <c r="E74" s="5"/>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -10590,7 +10679,7 @@
       </c>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>129</v>
       </c>
@@ -10601,7 +10690,7 @@
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>1</v>
       </c>
@@ -10618,7 +10707,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>2</v>
       </c>
@@ -10633,7 +10722,7 @@
       </c>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>3</v>
       </c>
@@ -10648,7 +10737,7 @@
       </c>
       <c r="E79" s="2"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>4</v>
       </c>
@@ -10663,7 +10752,7 @@
       </c>
       <c r="E80" s="2"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>5</v>
       </c>
@@ -10678,7 +10767,7 @@
       </c>
       <c r="E81" s="2"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>6</v>
       </c>
@@ -10693,7 +10782,7 @@
       </c>
       <c r="E82" s="2"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>7</v>
       </c>
@@ -10708,7 +10797,7 @@
       </c>
       <c r="E83" s="2"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>8</v>
       </c>
@@ -10723,7 +10812,7 @@
       </c>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>70</v>
       </c>
@@ -10732,7 +10821,7 @@
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>10</v>
       </c>
@@ -10747,7 +10836,7 @@
       </c>
       <c r="E86" s="2"/>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>11</v>
       </c>
@@ -10762,7 +10851,7 @@
       </c>
       <c r="E87" s="2"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>12</v>
       </c>
@@ -10777,7 +10866,7 @@
       </c>
       <c r="E88" s="2"/>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>13</v>
       </c>
@@ -10792,7 +10881,7 @@
       </c>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>217</v>
       </c>
@@ -10801,7 +10890,7 @@
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>15</v>
       </c>
@@ -10818,7 +10907,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>16</v>
       </c>
@@ -10835,7 +10924,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>17</v>
       </c>
@@ -10852,7 +10941,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>18</v>
       </c>
@@ -10869,7 +10958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>19</v>
       </c>
@@ -10886,7 +10975,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>20</v>
       </c>
@@ -10903,7 +10992,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>21</v>
       </c>
@@ -10920,7 +11009,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>22</v>
       </c>
@@ -10937,7 +11026,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>23</v>
       </c>
@@ -10954,7 +11043,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>24</v>
       </c>
@@ -10971,7 +11060,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>25</v>
       </c>
@@ -10988,7 +11077,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>26</v>
       </c>
@@ -11003,7 +11092,7 @@
       </c>
       <c r="E102" s="2"/>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>27</v>
       </c>
@@ -11020,7 +11109,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>29</v>
       </c>
@@ -11035,7 +11124,7 @@
       </c>
       <c r="E104" s="2"/>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>30</v>
       </c>
@@ -11050,7 +11139,7 @@
       </c>
       <c r="E105" s="2"/>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>72</v>
       </c>
@@ -11059,7 +11148,7 @@
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>31</v>
       </c>
@@ -11076,7 +11165,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>32</v>
       </c>
@@ -11091,7 +11180,7 @@
       </c>
       <c r="E108" s="7"/>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>33</v>
       </c>
@@ -11106,7 +11195,7 @@
       </c>
       <c r="E109" s="7"/>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>34</v>
       </c>
@@ -11123,7 +11212,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>35</v>
       </c>
@@ -11138,7 +11227,7 @@
       </c>
       <c r="E111" s="7"/>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>36</v>
       </c>
@@ -11153,7 +11242,7 @@
       </c>
       <c r="E112" s="7"/>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>37</v>
       </c>
@@ -11170,7 +11259,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>38</v>
       </c>
@@ -11185,7 +11274,7 @@
       </c>
       <c r="E114" s="7"/>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>39</v>
       </c>
@@ -11200,7 +11289,7 @@
       </c>
       <c r="E115" s="7"/>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>40</v>
       </c>
@@ -11217,7 +11306,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>41</v>
       </c>
@@ -11232,7 +11321,7 @@
       </c>
       <c r="E117" s="2"/>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>42</v>
       </c>
@@ -11247,7 +11336,7 @@
       </c>
       <c r="E118" s="7"/>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>43</v>
       </c>
@@ -11264,7 +11353,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>44</v>
       </c>
@@ -11279,7 +11368,7 @@
       </c>
       <c r="E120" s="7"/>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>45</v>
       </c>
@@ -11294,7 +11383,7 @@
       </c>
       <c r="E121" s="7"/>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>46</v>
       </c>
@@ -11311,7 +11400,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>47</v>
       </c>
@@ -11326,7 +11415,7 @@
       </c>
       <c r="E123" s="7"/>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>48</v>
       </c>
@@ -11341,7 +11430,7 @@
       </c>
       <c r="E124" s="2"/>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>49</v>
       </c>
@@ -11358,7 +11447,7 @@
         <v>22343244410021</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>50</v>
       </c>
@@ -11373,7 +11462,7 @@
       </c>
       <c r="E126" s="2"/>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>51</v>
       </c>
@@ -11388,7 +11477,7 @@
       </c>
       <c r="E127" s="2"/>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>52</v>
       </c>
@@ -11405,7 +11494,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>53</v>
       </c>
@@ -11420,7 +11509,7 @@
       </c>
       <c r="E129" s="2"/>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>54</v>
       </c>
@@ -11435,7 +11524,7 @@
       </c>
       <c r="E130" s="2"/>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>55</v>
       </c>
@@ -11452,7 +11541,7 @@
         <v>44594</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>56</v>
       </c>
@@ -11469,7 +11558,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>57</v>
       </c>
@@ -11484,7 +11573,7 @@
       </c>
       <c r="E133" s="2"/>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>58</v>
       </c>
@@ -11499,7 +11588,7 @@
       </c>
       <c r="E134" s="2"/>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>59</v>
       </c>
@@ -11514,7 +11603,7 @@
       </c>
       <c r="E135" s="2"/>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>60</v>
       </c>
@@ -11529,7 +11618,7 @@
       </c>
       <c r="E136" s="2"/>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>61</v>
       </c>
@@ -11544,7 +11633,7 @@
       </c>
       <c r="E137" s="2"/>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>62</v>
       </c>
@@ -11559,7 +11648,7 @@
       </c>
       <c r="E138" s="2"/>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>63</v>
       </c>
@@ -11576,7 +11665,7 @@
         <v>3234</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>64</v>
       </c>
@@ -11593,7 +11682,7 @@
         <v>13234</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>65</v>
       </c>
@@ -11608,7 +11697,7 @@
       </c>
       <c r="E141" s="2"/>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>66</v>
       </c>
@@ -11623,7 +11712,7 @@
       </c>
       <c r="E142" s="2"/>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>67</v>
       </c>
@@ -11638,7 +11727,7 @@
       </c>
       <c r="E143" s="2"/>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>68</v>
       </c>
@@ -11653,7 +11742,7 @@
       </c>
       <c r="E144" s="2"/>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>118</v>
       </c>
@@ -11662,7 +11751,7 @@
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>70</v>
       </c>
@@ -11677,7 +11766,7 @@
       </c>
       <c r="E146" s="2"/>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>71</v>
       </c>
@@ -11694,7 +11783,7 @@
         <v>7826423</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>72</v>
       </c>
@@ -11711,7 +11800,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>73</v>
       </c>
@@ -11728,7 +11817,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>74</v>
       </c>
@@ -11745,7 +11834,7 @@
         <v>3478323</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>75</v>
       </c>
@@ -11760,7 +11849,7 @@
       </c>
       <c r="E151" s="2"/>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>76</v>
       </c>
@@ -11775,7 +11864,7 @@
       </c>
       <c r="E152" s="2"/>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>77</v>
       </c>
@@ -11790,7 +11879,7 @@
       </c>
       <c r="E153" s="2"/>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>78</v>
       </c>
@@ -11805,7 +11894,7 @@
       </c>
       <c r="E154" s="2"/>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>123</v>
       </c>
@@ -11814,7 +11903,7 @@
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>80</v>
       </c>
@@ -11829,7 +11918,7 @@
       </c>
       <c r="E156" s="2"/>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>81</v>
       </c>
@@ -11846,7 +11935,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>82</v>
       </c>
@@ -11863,7 +11952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>83</v>
       </c>
@@ -11880,7 +11969,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>84</v>
       </c>
@@ -11897,7 +11986,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>85</v>
       </c>
@@ -11912,7 +12001,7 @@
       </c>
       <c r="E161" s="2"/>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>86</v>
       </c>
@@ -11927,7 +12016,7 @@
       </c>
       <c r="E162" s="2"/>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>87</v>
       </c>
@@ -11942,7 +12031,7 @@
       </c>
       <c r="E163" s="2"/>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>88</v>
       </c>
@@ -11959,7 +12048,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>89</v>
       </c>
@@ -11976,7 +12065,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>90</v>
       </c>
@@ -11993,7 +12082,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>91</v>
       </c>
@@ -12010,7 +12099,7 @@
         <v>3478323</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>92</v>
       </c>
@@ -12025,7 +12114,7 @@
       </c>
       <c r="E168" s="2"/>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>93</v>
       </c>
@@ -12040,7 +12129,7 @@
       </c>
       <c r="E169" s="2"/>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>130</v>
       </c>
@@ -12051,7 +12140,7 @@
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>3</v>
       </c>
@@ -12068,7 +12157,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>4</v>
       </c>
@@ -12083,7 +12172,7 @@
       </c>
       <c r="E172" s="2"/>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>5</v>
       </c>
@@ -12098,7 +12187,7 @@
       </c>
       <c r="E173" s="2"/>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>6</v>
       </c>
@@ -12113,7 +12202,7 @@
       </c>
       <c r="E174" s="2"/>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>7</v>
       </c>
@@ -12128,7 +12217,7 @@
       </c>
       <c r="E175" s="2"/>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>8</v>
       </c>
@@ -12143,7 +12232,7 @@
       </c>
       <c r="E176" s="2"/>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>9</v>
       </c>
@@ -12158,7 +12247,7 @@
       </c>
       <c r="E177" s="2"/>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>10</v>
       </c>
@@ -12173,7 +12262,7 @@
       </c>
       <c r="E178" s="2"/>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>11</v>
       </c>
@@ -12190,7 +12279,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>146</v>
       </c>
@@ -12199,7 +12288,7 @@
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>13</v>
       </c>
@@ -12214,7 +12303,7 @@
       </c>
       <c r="E181" s="2"/>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>14</v>
       </c>
@@ -12229,7 +12318,7 @@
       </c>
       <c r="E182" s="2"/>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>15</v>
       </c>
@@ -12246,7 +12335,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>16</v>
       </c>
@@ -12263,7 +12352,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>17</v>
       </c>
@@ -12280,7 +12369,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>18</v>
       </c>
@@ -12297,7 +12386,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>19</v>
       </c>
@@ -12314,7 +12403,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>20</v>
       </c>
@@ -12331,7 +12420,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>21</v>
       </c>
@@ -12348,7 +12437,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>22</v>
       </c>
@@ -12363,7 +12452,7 @@
       </c>
       <c r="E190" s="2"/>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>23</v>
       </c>
@@ -12378,7 +12467,7 @@
       </c>
       <c r="E191" s="2"/>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>24</v>
       </c>
@@ -12393,7 +12482,7 @@
       </c>
       <c r="E192" s="2"/>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>25</v>
       </c>
@@ -12410,7 +12499,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>26</v>
       </c>
@@ -12427,7 +12516,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>27</v>
       </c>
@@ -12444,7 +12533,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>28</v>
       </c>
@@ -12459,7 +12548,7 @@
       </c>
       <c r="E196" s="2"/>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>29</v>
       </c>
@@ -12474,7 +12563,7 @@
       </c>
       <c r="E197" s="2"/>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>164</v>
       </c>
@@ -12483,7 +12572,7 @@
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>31</v>
       </c>
@@ -12498,7 +12587,7 @@
       </c>
       <c r="E199" s="2"/>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>32</v>
       </c>
@@ -12513,7 +12602,7 @@
       </c>
       <c r="E200" s="2"/>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>33</v>
       </c>
@@ -12528,7 +12617,7 @@
       </c>
       <c r="E201" s="2"/>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>34</v>
       </c>
@@ -12545,7 +12634,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>35</v>
       </c>
@@ -12560,7 +12649,7 @@
       </c>
       <c r="E203" s="2"/>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>36</v>
       </c>
@@ -12575,7 +12664,7 @@
       </c>
       <c r="E204" s="2"/>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>37</v>
       </c>
@@ -12590,7 +12679,7 @@
       </c>
       <c r="E205" s="2"/>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>38</v>
       </c>
@@ -12605,7 +12694,7 @@
       </c>
       <c r="E206" s="2"/>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>39</v>
       </c>
@@ -12620,7 +12709,7 @@
       </c>
       <c r="E207" s="2"/>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>167</v>
       </c>
@@ -12629,7 +12718,7 @@
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>41</v>
       </c>
@@ -12646,7 +12735,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>42</v>
       </c>
@@ -12663,7 +12752,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>43</v>
       </c>
@@ -12680,7 +12769,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>44</v>
       </c>
@@ -12695,7 +12784,7 @@
       </c>
       <c r="E212" s="2"/>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>45</v>
       </c>
@@ -12712,7 +12801,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>46</v>
       </c>
@@ -12727,7 +12816,7 @@
       </c>
       <c r="E214" s="2"/>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>47</v>
       </c>
@@ -12744,7 +12833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>48</v>
       </c>
@@ -12759,7 +12848,7 @@
       </c>
       <c r="E216" s="2"/>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>49</v>
       </c>
@@ -12776,7 +12865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>50</v>
       </c>
@@ -12791,7 +12880,7 @@
       </c>
       <c r="E218" s="2"/>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>51</v>
       </c>
@@ -12808,7 +12897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>52</v>
       </c>
@@ -12823,7 +12912,7 @@
       </c>
       <c r="E220" s="2"/>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>53</v>
       </c>
@@ -12840,7 +12929,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>54</v>
       </c>
@@ -12855,7 +12944,7 @@
       </c>
       <c r="E222" s="2"/>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>55</v>
       </c>
@@ -12872,7 +12961,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>56</v>
       </c>
@@ -12887,7 +12976,7 @@
       </c>
       <c r="E224" s="2"/>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>57</v>
       </c>
@@ -12902,7 +12991,7 @@
       </c>
       <c r="E225" s="2"/>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>58</v>
       </c>
@@ -12917,7 +13006,7 @@
       </c>
       <c r="E226" s="2"/>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>181</v>
       </c>
@@ -12926,7 +13015,7 @@
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>60</v>
       </c>
@@ -12943,7 +13032,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>61</v>
       </c>
@@ -12958,7 +13047,7 @@
       </c>
       <c r="E229" s="2"/>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>62</v>
       </c>
@@ -12973,7 +13062,7 @@
       </c>
       <c r="E230" s="2"/>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>63</v>
       </c>
@@ -12990,7 +13079,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>64</v>
       </c>
@@ -13007,7 +13096,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>65</v>
       </c>
@@ -13022,7 +13111,7 @@
       </c>
       <c r="E233" s="2"/>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>66</v>
       </c>
@@ -13033,7 +13122,7 @@
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>67</v>
       </c>
@@ -13050,7 +13139,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>68</v>
       </c>
@@ -13067,7 +13156,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>69</v>
       </c>
@@ -13082,7 +13171,7 @@
       </c>
       <c r="E237" s="2"/>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>70</v>
       </c>
@@ -13097,7 +13186,7 @@
       </c>
       <c r="E238" s="5"/>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>71</v>
       </c>
@@ -13114,7 +13203,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>72</v>
       </c>
@@ -13129,7 +13218,7 @@
       </c>
       <c r="E240" s="2"/>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>73</v>
       </c>
@@ -13146,7 +13235,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>74</v>
       </c>
@@ -13161,7 +13250,7 @@
       </c>
       <c r="E242" s="2"/>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>75</v>
       </c>
@@ -13176,7 +13265,7 @@
       </c>
       <c r="E243" s="2"/>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>76</v>
       </c>
@@ -13191,7 +13280,7 @@
       </c>
       <c r="E244" s="2"/>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>77</v>
       </c>
@@ -13208,7 +13297,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>78</v>
       </c>
@@ -13223,7 +13312,7 @@
       </c>
       <c r="E246" s="2"/>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>79</v>
       </c>
@@ -13238,7 +13327,7 @@
       </c>
       <c r="E247" s="2"/>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>80</v>
       </c>
@@ -13253,7 +13342,7 @@
       </c>
       <c r="E248" s="2"/>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>81</v>
       </c>
@@ -13270,7 +13359,7 @@
         <v>3.4628376482734602E+18</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>82</v>
       </c>
@@ -13285,7 +13374,7 @@
       </c>
       <c r="E250" s="2"/>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>83</v>
       </c>
@@ -13300,7 +13389,7 @@
       </c>
       <c r="E251" s="2"/>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>84</v>
       </c>
@@ -13315,7 +13404,7 @@
       </c>
       <c r="E252" s="2"/>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>85</v>
       </c>
@@ -13332,7 +13421,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>86</v>
       </c>
@@ -13347,7 +13436,7 @@
       </c>
       <c r="E254" s="2"/>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>87</v>
       </c>
@@ -13362,7 +13451,7 @@
       </c>
       <c r="E255" s="2"/>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>88</v>
       </c>
@@ -13377,7 +13466,7 @@
       </c>
       <c r="E256" s="2"/>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>89</v>
       </c>
@@ -13394,7 +13483,7 @@
         <v>3.4628376482734602E+18</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>90</v>
       </c>
@@ -13409,7 +13498,7 @@
       </c>
       <c r="E258" s="2"/>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>91</v>
       </c>
@@ -13424,7 +13513,7 @@
       </c>
       <c r="E259" s="2"/>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>92</v>
       </c>
@@ -13441,7 +13530,7 @@
         <v>44854</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>93</v>
       </c>
@@ -13458,7 +13547,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>94</v>
       </c>
@@ -13473,7 +13562,7 @@
       </c>
       <c r="E262" s="2"/>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>95</v>
       </c>
@@ -13488,7 +13577,7 @@
       </c>
       <c r="E263" s="2"/>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>96</v>
       </c>
@@ -13503,7 +13592,7 @@
       </c>
       <c r="E264" s="2"/>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>97</v>
       </c>
@@ -13518,7 +13607,7 @@
       </c>
       <c r="E265" s="2"/>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>98</v>
       </c>
@@ -13533,7 +13622,7 @@
       </c>
       <c r="E266" s="2"/>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>118</v>
       </c>
@@ -13542,7 +13631,7 @@
       <c r="D267" s="2"/>
       <c r="E267" s="2"/>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>100</v>
       </c>
@@ -13557,7 +13646,7 @@
       </c>
       <c r="E268" s="2"/>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>101</v>
       </c>
@@ -13574,7 +13663,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>102</v>
       </c>
@@ -13589,7 +13678,7 @@
       </c>
       <c r="E270" s="2"/>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>103</v>
       </c>
@@ -13604,7 +13693,7 @@
       </c>
       <c r="E271" s="2"/>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>104</v>
       </c>
@@ -13621,7 +13710,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>105</v>
       </c>
@@ -13638,7 +13727,7 @@
         <v>7600</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>106</v>
       </c>
@@ -13655,7 +13744,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>107</v>
       </c>
@@ -13672,7 +13761,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>108</v>
       </c>
@@ -13687,7 +13776,7 @@
       </c>
       <c r="E276" s="2"/>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>109</v>
       </c>
@@ -13702,7 +13791,7 @@
       </c>
       <c r="E277" s="2"/>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>131</v>
       </c>
@@ -13711,7 +13800,7 @@
       <c r="D278" s="2"/>
       <c r="E278" s="2"/>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>111</v>
       </c>
@@ -13726,7 +13815,7 @@
       </c>
       <c r="E279" s="2"/>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>112</v>
       </c>
@@ -13741,7 +13830,7 @@
       </c>
       <c r="E280" s="2"/>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>113</v>
       </c>
@@ -13756,7 +13845,7 @@
       </c>
       <c r="E281" s="2"/>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>114</v>
       </c>
@@ -13771,7 +13860,7 @@
       </c>
       <c r="E282" s="2"/>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>115</v>
       </c>
@@ -13786,7 +13875,7 @@
       </c>
       <c r="E283" s="2"/>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>116</v>
       </c>
@@ -13801,7 +13890,7 @@
       </c>
       <c r="E284" s="2"/>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>117</v>
       </c>
@@ -13816,7 +13905,7 @@
       </c>
       <c r="E285" s="2"/>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>118</v>
       </c>
@@ -13831,7 +13920,7 @@
       </c>
       <c r="E286" s="2"/>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>119</v>
       </c>
@@ -13846,7 +13935,7 @@
       </c>
       <c r="E287" s="2"/>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>120</v>
       </c>
@@ -13863,7 +13952,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>121</v>
       </c>
@@ -13880,7 +13969,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>122</v>
       </c>
@@ -13897,7 +13986,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>123</v>
       </c>
@@ -13914,7 +14003,7 @@
         <v>12323</v>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>124</v>
       </c>
@@ -13929,7 +14018,7 @@
       </c>
       <c r="E292" s="2"/>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>125</v>
       </c>
@@ -13944,7 +14033,7 @@
       </c>
       <c r="E293" s="2"/>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>126</v>
       </c>
@@ -13959,7 +14048,7 @@
       </c>
       <c r="E294" s="2"/>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>253</v>
       </c>
@@ -13968,7 +14057,7 @@
       <c r="D295" s="2"/>
       <c r="E295" s="2"/>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>128</v>
       </c>
@@ -13983,7 +14072,7 @@
       </c>
       <c r="E296" s="2"/>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>129</v>
       </c>
@@ -13998,7 +14087,7 @@
       </c>
       <c r="E297" s="2"/>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>130</v>
       </c>
@@ -14013,7 +14102,7 @@
       </c>
       <c r="E298" s="2"/>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>131</v>
       </c>
@@ -14028,7 +14117,7 @@
       </c>
       <c r="E299" s="2"/>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <v>132</v>
       </c>
@@ -14045,7 +14134,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <v>133</v>
       </c>
@@ -14060,7 +14149,7 @@
       </c>
       <c r="E301" s="2"/>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>134</v>
       </c>
@@ -14075,7 +14164,7 @@
       </c>
       <c r="E302" s="2"/>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>129</v>
       </c>
@@ -14086,7 +14175,7 @@
       <c r="D303" s="2"/>
       <c r="E303" s="2"/>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <v>3</v>
       </c>
@@ -14103,7 +14192,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>4</v>
       </c>
@@ -14118,7 +14207,7 @@
       </c>
       <c r="E305" s="2"/>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>5</v>
       </c>
@@ -14133,7 +14222,7 @@
       </c>
       <c r="E306" s="2"/>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>6</v>
       </c>
@@ -14148,7 +14237,7 @@
       </c>
       <c r="E307" s="2"/>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>7</v>
       </c>
@@ -14163,7 +14252,7 @@
       </c>
       <c r="E308" s="2"/>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>8</v>
       </c>
@@ -14178,7 +14267,7 @@
       </c>
       <c r="E309" s="2"/>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>9</v>
       </c>
@@ -14193,7 +14282,7 @@
       </c>
       <c r="E310" s="2"/>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>204</v>
       </c>
@@ -14202,7 +14291,7 @@
       <c r="D311" s="2"/>
       <c r="E311" s="2"/>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>11</v>
       </c>
@@ -14219,7 +14308,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>12</v>
       </c>
@@ -14236,7 +14325,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <v>13</v>
       </c>
@@ -14253,7 +14342,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <v>14</v>
       </c>
@@ -14270,7 +14359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <v>15</v>
       </c>
@@ -14287,7 +14376,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <v>16</v>
       </c>
@@ -14304,7 +14393,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <v>17</v>
       </c>
@@ -14321,7 +14410,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <v>18</v>
       </c>
@@ -14338,7 +14427,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <v>19</v>
       </c>
@@ -14355,7 +14444,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <v>20</v>
       </c>
@@ -14372,7 +14461,7 @@
         <v>12122</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <v>21</v>
       </c>
@@ -14389,7 +14478,7 @@
         <v>2311323</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <v>22</v>
       </c>
@@ -14406,7 +14495,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <v>23</v>
       </c>
@@ -14421,7 +14510,7 @@
       </c>
       <c r="E324" s="5"/>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <v>24</v>
       </c>
@@ -14436,7 +14525,7 @@
       </c>
       <c r="E325" s="2"/>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <v>25</v>
       </c>
@@ -14451,7 +14540,7 @@
       </c>
       <c r="E326" s="2"/>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <v>26</v>
       </c>
@@ -14466,7 +14555,7 @@
       </c>
       <c r="E327" s="2"/>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <v>27</v>
       </c>
@@ -14481,7 +14570,7 @@
       </c>
       <c r="E328" s="2"/>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <v>28</v>
       </c>
@@ -14496,7 +14585,7 @@
       </c>
       <c r="E329" s="2"/>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <v>29</v>
       </c>
@@ -14513,7 +14602,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>146</v>
       </c>
@@ -14522,7 +14611,7 @@
       <c r="D331" s="2"/>
       <c r="E331" s="2"/>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <v>31</v>
       </c>
@@ -14537,7 +14626,7 @@
       </c>
       <c r="E332" s="2"/>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <v>32</v>
       </c>
@@ -14552,7 +14641,7 @@
       </c>
       <c r="E333" s="2"/>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <v>33</v>
       </c>
@@ -14569,7 +14658,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <v>34</v>
       </c>
@@ -14586,7 +14675,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <v>35</v>
       </c>
@@ -14603,7 +14692,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <v>36</v>
       </c>
@@ -14620,7 +14709,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <v>37</v>
       </c>
@@ -14637,7 +14726,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <v>38</v>
       </c>
@@ -14654,7 +14743,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="2">
         <v>39</v>
       </c>
@@ -14671,7 +14760,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
         <v>40</v>
       </c>
@@ -14686,7 +14775,7 @@
       </c>
       <c r="E341" s="2"/>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
         <v>41</v>
       </c>
@@ -14701,7 +14790,7 @@
       </c>
       <c r="E342" s="2"/>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="2">
         <v>42</v>
       </c>
@@ -14716,7 +14805,7 @@
       </c>
       <c r="E343" s="2"/>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="2">
         <v>43</v>
       </c>
@@ -14731,7 +14820,7 @@
       </c>
       <c r="E344" s="2"/>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="2">
         <v>44</v>
       </c>
@@ -14746,7 +14835,7 @@
       </c>
       <c r="E345" s="2"/>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="2">
         <v>45</v>
       </c>
@@ -14763,7 +14852,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="2">
         <v>46</v>
       </c>
@@ -14778,7 +14867,7 @@
       </c>
       <c r="E347" s="2"/>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="2">
         <v>47</v>
       </c>
@@ -14795,7 +14884,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="2">
         <v>48</v>
       </c>
@@ -14812,7 +14901,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="2">
         <v>49</v>
       </c>
@@ -14829,7 +14918,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="2">
         <v>50</v>
       </c>
@@ -14844,7 +14933,7 @@
       </c>
       <c r="E351" s="2"/>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="2">
         <v>51</v>
       </c>
@@ -14861,7 +14950,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="353" spans="1:5">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="2">
         <v>52</v>
       </c>
@@ -14876,7 +14965,7 @@
       </c>
       <c r="E353" s="2"/>
     </row>
-    <row r="354" spans="1:5">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="2">
         <v>53</v>
       </c>
@@ -14893,7 +14982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="1:5">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="2">
         <v>54</v>
       </c>
@@ -14908,7 +14997,7 @@
       </c>
       <c r="E355" s="2"/>
     </row>
-    <row r="356" spans="1:5">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="2">
         <v>55</v>
       </c>
@@ -14925,7 +15014,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="357" spans="1:5">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="2">
         <v>56</v>
       </c>
@@ -14940,7 +15029,7 @@
       </c>
       <c r="E357" s="2"/>
     </row>
-    <row r="358" spans="1:5">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="2">
         <v>57</v>
       </c>
@@ -14957,7 +15046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:5">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="2">
         <v>58</v>
       </c>
@@ -14972,7 +15061,7 @@
       </c>
       <c r="E359" s="2"/>
     </row>
-    <row r="360" spans="1:5">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="2">
         <v>59</v>
       </c>
@@ -14989,7 +15078,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="361" spans="1:5">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="2">
         <v>60</v>
       </c>
@@ -15006,7 +15095,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="362" spans="1:5">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="2">
         <v>61</v>
       </c>
@@ -15021,7 +15110,7 @@
       </c>
       <c r="E362" s="2"/>
     </row>
-    <row r="363" spans="1:5">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="2">
         <v>62</v>
       </c>
@@ -15036,7 +15125,7 @@
       </c>
       <c r="E363" s="2"/>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="2">
         <v>63</v>
       </c>
@@ -15051,7 +15140,7 @@
       </c>
       <c r="E364" s="2"/>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>205</v>
       </c>
@@ -15060,7 +15149,7 @@
       <c r="D365" s="2"/>
       <c r="E365" s="2"/>
     </row>
-    <row r="366" spans="1:5">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="2">
         <v>65</v>
       </c>
@@ -15075,7 +15164,7 @@
       </c>
       <c r="E366" s="2"/>
     </row>
-    <row r="367" spans="1:5">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="2">
         <v>66</v>
       </c>
@@ -15090,7 +15179,7 @@
       </c>
       <c r="E367" s="2"/>
     </row>
-    <row r="368" spans="1:5">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="2">
         <v>67</v>
       </c>
@@ -15105,7 +15194,7 @@
       </c>
       <c r="E368" s="5"/>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="2">
         <v>68</v>
       </c>
@@ -15120,7 +15209,7 @@
       </c>
       <c r="E369" s="2"/>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="2">
         <v>69</v>
       </c>
@@ -15135,7 +15224,7 @@
       </c>
       <c r="E370" s="2"/>
     </row>
-    <row r="371" spans="1:5">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="2">
         <v>70</v>
       </c>
@@ -15150,7 +15239,7 @@
       </c>
       <c r="E371" s="2"/>
     </row>
-    <row r="372" spans="1:5">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="2">
         <v>71</v>
       </c>
@@ -15165,7 +15254,7 @@
       </c>
       <c r="E372" s="2"/>
     </row>
-    <row r="373" spans="1:5">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="2">
         <v>72</v>
       </c>
@@ -15180,7 +15269,7 @@
       </c>
       <c r="E373" s="2"/>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="2">
         <v>73</v>
       </c>
@@ -15195,7 +15284,7 @@
       </c>
       <c r="E374" s="2"/>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>252</v>
       </c>
@@ -15206,7 +15295,7 @@
       <c r="D375" s="2"/>
       <c r="E375" s="2"/>
     </row>
-    <row r="376" spans="1:5">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="2">
         <v>3</v>
       </c>
@@ -15223,7 +15312,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="377" spans="1:5">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="2">
         <v>4</v>
       </c>
@@ -15238,7 +15327,7 @@
       </c>
       <c r="E377" s="2"/>
     </row>
-    <row r="378" spans="1:5">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="2">
         <v>5</v>
       </c>
@@ -15253,7 +15342,7 @@
       </c>
       <c r="E378" s="2"/>
     </row>
-    <row r="379" spans="1:5">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="2">
         <v>6</v>
       </c>
@@ -15268,7 +15357,7 @@
       </c>
       <c r="E379" s="2"/>
     </row>
-    <row r="380" spans="1:5">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="2">
         <v>7</v>
       </c>
@@ -15283,7 +15372,7 @@
       </c>
       <c r="E380" s="2"/>
     </row>
-    <row r="381" spans="1:5">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="2">
         <v>8</v>
       </c>
@@ -15298,7 +15387,7 @@
       </c>
       <c r="E381" s="2"/>
     </row>
-    <row r="382" spans="1:5">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="2">
         <v>9</v>
       </c>
@@ -15313,7 +15402,7 @@
       </c>
       <c r="E382" s="2"/>
     </row>
-    <row r="383" spans="1:5">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="2">
         <v>10</v>
       </c>
@@ -15328,7 +15417,7 @@
       </c>
       <c r="E383" s="2"/>
     </row>
-    <row r="384" spans="1:5">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="2">
         <v>11</v>
       </c>
@@ -15345,7 +15434,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="2">
         <v>12</v>
       </c>
@@ -15360,7 +15449,7 @@
       </c>
       <c r="E385" s="2"/>
     </row>
-    <row r="386" spans="1:5">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="2">
         <v>13</v>
       </c>
@@ -15375,7 +15464,7 @@
       </c>
       <c r="E386" s="2"/>
     </row>
-    <row r="387" spans="1:5">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="2">
         <v>14</v>
       </c>
@@ -15390,7 +15479,7 @@
       </c>
       <c r="E387" s="2"/>
     </row>
-    <row r="388" spans="1:5">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="2">
         <v>15</v>
       </c>
@@ -15405,7 +15494,7 @@
       </c>
       <c r="E388" s="2"/>
     </row>
-    <row r="389" spans="1:5">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="2">
         <v>16</v>
       </c>
@@ -15420,7 +15509,7 @@
       </c>
       <c r="E389" s="2"/>
     </row>
-    <row r="390" spans="1:5">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="2">
         <v>17</v>
       </c>
@@ -15435,7 +15524,7 @@
       </c>
       <c r="E390" s="2"/>
     </row>
-    <row r="391" spans="1:5">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="2">
         <v>18</v>
       </c>
@@ -15450,7 +15539,7 @@
       </c>
       <c r="E391" s="2"/>
     </row>
-    <row r="392" spans="1:5">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="2">
         <v>19</v>
       </c>
@@ -15465,7 +15554,7 @@
       </c>
       <c r="E392" s="2"/>
     </row>
-    <row r="393" spans="1:5">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="2">
         <v>20</v>
       </c>
@@ -15480,7 +15569,7 @@
       </c>
       <c r="E393" s="2"/>
     </row>
-    <row r="394" spans="1:5">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="2">
         <v>21</v>
       </c>
@@ -15495,7 +15584,7 @@
       </c>
       <c r="E394" s="2"/>
     </row>
-    <row r="395" spans="1:5">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="2">
         <v>22</v>
       </c>
@@ -15510,7 +15599,7 @@
       </c>
       <c r="E395" s="2"/>
     </row>
-    <row r="396" spans="1:5">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="2">
         <v>23</v>
       </c>
@@ -15525,7 +15614,7 @@
       </c>
       <c r="E396" s="2"/>
     </row>
-    <row r="397" spans="1:5">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="2">
         <v>24</v>
       </c>
@@ -15540,7 +15629,7 @@
       </c>
       <c r="E397" s="2"/>
     </row>
-    <row r="398" spans="1:5">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="2">
         <v>25</v>
       </c>
@@ -15555,7 +15644,7 @@
       </c>
       <c r="E398" s="2"/>
     </row>
-    <row r="399" spans="1:5">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="2">
         <v>26</v>
       </c>
@@ -15570,7 +15659,7 @@
       </c>
       <c r="E399" s="2"/>
     </row>
-    <row r="400" spans="1:5">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="2">
         <v>27</v>
       </c>
@@ -15585,7 +15674,7 @@
       </c>
       <c r="E400" s="2"/>
     </row>
-    <row r="401" spans="1:5">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="2">
         <v>28</v>
       </c>
@@ -15600,7 +15689,7 @@
       </c>
       <c r="E401" s="2"/>
     </row>
-    <row r="402" spans="1:5">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="2">
         <v>29</v>
       </c>
@@ -15615,7 +15704,7 @@
       </c>
       <c r="E402" s="2"/>
     </row>
-    <row r="403" spans="1:5">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="2">
         <v>30</v>
       </c>
@@ -15630,7 +15719,7 @@
       </c>
       <c r="E403" s="2"/>
     </row>
-    <row r="404" spans="1:5">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="2">
         <v>31</v>
       </c>
@@ -15645,7 +15734,7 @@
       </c>
       <c r="E404" s="2"/>
     </row>
-    <row r="405" spans="1:5">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="2">
         <v>32</v>
       </c>
@@ -15660,7 +15749,7 @@
       </c>
       <c r="E405" s="2"/>
     </row>
-    <row r="406" spans="1:5">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="2">
         <v>33</v>
       </c>
@@ -15675,7 +15764,7 @@
       </c>
       <c r="E406" s="2"/>
     </row>
-    <row r="407" spans="1:5">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="2">
         <v>34</v>
       </c>
@@ -15690,7 +15779,7 @@
       </c>
       <c r="E407" s="2"/>
     </row>
-    <row r="408" spans="1:5">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" s="2">
         <v>35</v>
       </c>
@@ -15705,7 +15794,7 @@
       </c>
       <c r="E408" s="2"/>
     </row>
-    <row r="409" spans="1:5">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" s="2">
         <v>36</v>
       </c>
@@ -15720,7 +15809,7 @@
       </c>
       <c r="E409" s="2"/>
     </row>
-    <row r="410" spans="1:5">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" s="2">
         <v>37</v>
       </c>
@@ -15735,7 +15824,7 @@
       </c>
       <c r="E410" s="2"/>
     </row>
-    <row r="411" spans="1:5">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="2">
         <v>38</v>
       </c>
@@ -15750,7 +15839,7 @@
       </c>
       <c r="E411" s="2"/>
     </row>
-    <row r="412" spans="1:5">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="2">
         <v>39</v>
       </c>
@@ -15765,14 +15854,14 @@
       </c>
       <c r="E412" s="2"/>
     </row>
-    <row r="413" spans="1:5">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="2"/>
       <c r="B413" s="3"/>
       <c r="C413" s="2"/>
       <c r="D413" s="2"/>
       <c r="E413" s="2"/>
     </row>
-    <row r="414" spans="1:5">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>243</v>
       </c>
@@ -15783,7 +15872,7 @@
       <c r="D414" s="2"/>
       <c r="E414" s="2"/>
     </row>
-    <row r="415" spans="1:5">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="2">
         <v>3</v>
       </c>
@@ -15800,7 +15889,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="416" spans="1:5">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="2">
         <v>4</v>
       </c>
@@ -15815,7 +15904,7 @@
       </c>
       <c r="E416" s="2"/>
     </row>
-    <row r="417" spans="1:5">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="2">
         <v>5</v>
       </c>
@@ -15830,7 +15919,7 @@
       </c>
       <c r="E417" s="2"/>
     </row>
-    <row r="418" spans="1:5">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="2">
         <v>6</v>
       </c>
@@ -15845,7 +15934,7 @@
       </c>
       <c r="E418" s="2"/>
     </row>
-    <row r="419" spans="1:5">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="2">
         <v>7</v>
       </c>
@@ -15860,7 +15949,7 @@
       </c>
       <c r="E419" s="2"/>
     </row>
-    <row r="420" spans="1:5">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="2">
         <v>8</v>
       </c>
@@ -15875,7 +15964,7 @@
       </c>
       <c r="E420" s="2"/>
     </row>
-    <row r="421" spans="1:5">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="2">
         <v>9</v>
       </c>
@@ -15890,7 +15979,7 @@
       </c>
       <c r="E421" s="2"/>
     </row>
-    <row r="422" spans="1:5">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="2">
         <v>10</v>
       </c>
@@ -15907,7 +15996,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="423" spans="1:5">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" s="2">
         <v>11</v>
       </c>
@@ -15924,7 +16013,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="424" spans="1:5">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="2">
         <v>12</v>
       </c>
@@ -15939,7 +16028,7 @@
       </c>
       <c r="E424" s="2"/>
     </row>
-    <row r="425" spans="1:5">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="2">
         <v>13</v>
       </c>
@@ -15956,7 +16045,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="426" spans="1:5">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="2">
         <v>14</v>
       </c>
@@ -15971,7 +16060,7 @@
       </c>
       <c r="E426" s="2"/>
     </row>
-    <row r="427" spans="1:5">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="2">
         <v>15</v>
       </c>
@@ -15986,7 +16075,7 @@
       </c>
       <c r="E427" s="2"/>
     </row>
-    <row r="428" spans="1:5">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="2">
         <v>16</v>
       </c>
@@ -16001,7 +16090,7 @@
       </c>
       <c r="E428" s="2"/>
     </row>
-    <row r="429" spans="1:5">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>141</v>
       </c>
@@ -16010,7 +16099,7 @@
       <c r="D429" s="2"/>
       <c r="E429" s="2"/>
     </row>
-    <row r="430" spans="1:5">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="2">
         <v>143</v>
       </c>
@@ -16025,7 +16114,7 @@
       </c>
       <c r="E430" s="2"/>
     </row>
-    <row r="431" spans="1:5">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" s="2">
         <v>144</v>
       </c>
@@ -16040,7 +16129,7 @@
       </c>
       <c r="E431" s="2"/>
     </row>
-    <row r="432" spans="1:5">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="2">
         <v>145</v>
       </c>
@@ -16055,7 +16144,7 @@
       </c>
       <c r="E432" s="2"/>
     </row>
-    <row r="433" spans="1:5">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="2">
         <v>146</v>
       </c>
@@ -16070,7 +16159,7 @@
       </c>
       <c r="E433" s="2"/>
     </row>
-    <row r="434" spans="1:5">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>128</v>
       </c>
@@ -16079,7 +16168,7 @@
       <c r="D434" s="2"/>
       <c r="E434" s="2"/>
     </row>
-    <row r="435" spans="1:5">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="2">
         <v>148</v>
       </c>
@@ -16094,7 +16183,7 @@
       </c>
       <c r="E435" s="2"/>
     </row>
-    <row r="436" spans="1:5">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="2">
         <v>149</v>
       </c>
@@ -16109,7 +16198,7 @@
       </c>
       <c r="E436" s="2"/>
     </row>
-    <row r="437" spans="1:5">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="2">
         <v>150</v>
       </c>
@@ -16124,7 +16213,7 @@
       </c>
       <c r="E437" s="2"/>
     </row>
-    <row r="438" spans="1:5">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="2">
         <v>151</v>
       </c>
@@ -16139,7 +16228,7 @@
       </c>
       <c r="E438" s="2"/>
     </row>
-    <row r="439" spans="1:5">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="2">
         <v>152</v>
       </c>
@@ -16154,7 +16243,7 @@
       </c>
       <c r="E439" s="2"/>
     </row>
-    <row r="440" spans="1:5">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>200</v>
       </c>
@@ -16163,7 +16252,7 @@
       <c r="D440" s="2"/>
       <c r="E440" s="2"/>
     </row>
-    <row r="441" spans="1:5">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" s="2">
         <v>154</v>
       </c>
@@ -16178,7 +16267,7 @@
       </c>
       <c r="E441" s="2"/>
     </row>
-    <row r="442" spans="1:5">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="2">
         <v>155</v>
       </c>
@@ -16193,7 +16282,7 @@
       </c>
       <c r="E442" s="2"/>
     </row>
-    <row r="443" spans="1:5">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="2">
         <v>156</v>
       </c>
@@ -16208,7 +16297,7 @@
       </c>
       <c r="E443" s="2"/>
     </row>
-    <row r="444" spans="1:5">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="2">
         <v>157</v>
       </c>
@@ -16223,7 +16312,7 @@
       </c>
       <c r="E444" s="2"/>
     </row>
-    <row r="445" spans="1:5">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="2">
         <v>158</v>
       </c>
@@ -16238,7 +16327,7 @@
       </c>
       <c r="E445" s="2"/>
     </row>
-    <row r="446" spans="1:5">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="2">
         <v>159</v>
       </c>
@@ -16253,7 +16342,7 @@
       </c>
       <c r="E446" s="2"/>
     </row>
-    <row r="447" spans="1:5">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="2">
         <v>160</v>
       </c>
@@ -16270,19 +16359,19 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E337" r:id="rId1"/>
-    <hyperlink ref="E186" r:id="rId2"/>
-    <hyperlink ref="E54" r:id="rId3"/>
-    <hyperlink ref="E33" r:id="rId4"/>
+    <hyperlink ref="E337" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="E186" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="E54" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="E33" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.140625" customWidth="1"/>
@@ -16291,7 +16380,7 @@
     <col min="5" max="5" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -16308,7 +16397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>243</v>
       </c>
@@ -16319,7 +16408,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -16336,7 +16425,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -16351,7 +16440,7 @@
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -16366,7 +16455,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -16381,7 +16470,7 @@
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -16396,7 +16485,7 @@
       </c>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -16411,7 +16500,7 @@
       </c>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>255</v>
@@ -16420,22 +16509,22 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -16445,14 +16534,14 @@
       <c r="C11" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -16462,65 +16551,65 @@
       <c r="C12" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>223</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -16531,11 +16620,11 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -16545,6 +16634,419 @@
         <v>11</v>
       </c>
       <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3904" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3907" uniqueCount="273">
   <si>
     <t>Keyword</t>
   </si>
@@ -848,6 +848,9 @@
   </si>
   <si>
     <t>EXITTOUR</t>
+  </si>
+  <si>
+    <t>UPLOADWARNING</t>
   </si>
 </sst>
 </file>
@@ -16341,7 +16344,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E143"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
@@ -18129,26 +18132,24 @@
       </c>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="2">
-        <v>14</v>
-      </c>
+      <c r="A120" s="2"/>
       <c r="B120" s="2" t="s">
-        <v>69</v>
+        <v>272</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D120" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E120" s="2"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>250</v>
@@ -18160,199 +18161,199 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
+        <v>15</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E122" s="2"/>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="2">
         <v>16</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C122" s="2" t="s">
+      <c r="B123" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D122" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" s="2"/>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="2" t="s">
+      <c r="D123" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" s="2"/>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124" s="2">
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="2">
         <v>99</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C124" s="2" t="s">
+      <c r="B125" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" s="2"/>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="2"/>
-      <c r="B125" s="2" t="s">
+      <c r="D125" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="2"/>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="2">
-        <v>100</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
       <c r="E126" s="2"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E127" s="2"/>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E128" s="2"/>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E129" s="2"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
+        <v>103</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" s="2"/>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="2">
         <v>104</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B131" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D130" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E130" s="2"/>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="A131" s="2" t="s">
+      <c r="D131" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" s="2"/>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
-    </row>
-    <row r="132" spans="1:5">
-      <c r="A132" s="2">
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="2">
         <v>106</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C132" s="2" t="s">
+      <c r="B133" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E132" s="2"/>
-    </row>
-    <row r="133" spans="1:5">
-      <c r="A133" s="2"/>
-      <c r="B133" s="2" t="s">
+      <c r="D133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="2"/>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="2"/>
+      <c r="B134" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
-    </row>
-    <row r="134" spans="1:5">
-      <c r="A134" s="2">
-        <v>107</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
       <c r="E134" s="2"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E135" s="2"/>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>11</v>
@@ -18361,13 +18362,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>11</v>
@@ -18376,13 +18377,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>11</v>
@@ -18391,78 +18392,93 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>112</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>5</v>
+        <v>111</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D139" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D139" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E139" s="2"/>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>8</v>
+        <v>197</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E140" s="2"/>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>114</v>
-      </c>
-      <c r="B141" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B141" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E141" s="2"/>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E142" s="2"/>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
+        <v>115</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="2"/>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="2">
         <v>116</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C143" s="2" t="s">
+      <c r="B144" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D143" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E143" s="2"/>
+      <c r="D144" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Challan Mapping" sheetId="4" r:id="rId4"/>
     <sheet name="Predict Default" sheetId="5" r:id="rId5"/>
     <sheet name="Regression Test" sheetId="8" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="9" r:id="rId7"/>
+    <sheet name="Demo" sheetId="9" r:id="rId7"/>
     <sheet name="Sheet2" sheetId="10" r:id="rId8"/>
     <sheet name="Ereturn" sheetId="6" r:id="rId9"/>
   </sheets>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3907" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3840" uniqueCount="273">
   <si>
     <t>Keyword</t>
   </si>
@@ -16344,7 +16344,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
@@ -16439,40 +16439,40 @@
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2">
-        <v>7</v>
+      <c r="A7" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2">
-        <v>7</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
@@ -16480,337 +16480,333 @@
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2">
-        <v>59</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="A10" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>52</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2">
-        <v>61</v>
-      </c>
+      <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>23</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="2">
+        <v>10000</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E14" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>20</v>
+      <c r="E16" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>59</v>
+        <v>8</v>
+      </c>
+      <c r="E17" s="2">
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>23</v>
+        <v>103</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>20</v>
+      <c r="E22" s="2">
+        <v>12122</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2311323</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>32</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="2">
+        <v>30</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="D27" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="2">
-        <v>5</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A28" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B30" s="2"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>8</v>
@@ -16818,12 +16814,14 @@
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="2"/>
+      <c r="A32" s="2">
+        <v>33</v>
+      </c>
       <c r="B32" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>8</v>
@@ -16832,232 +16830,224 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="2">
-        <v>10000</v>
+      <c r="E33" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="2">
-        <v>100</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E35" s="2">
-        <v>100</v>
+      <c r="E35" s="5" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="2">
-        <v>10</v>
+      <c r="E36" s="5" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="2">
-        <v>120</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>103</v>
+        <v>173</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="2">
-        <v>10</v>
-      </c>
+      <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>84</v>
+        <v>173</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="2">
-        <v>40</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>90</v>
-      </c>
+      <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>91</v>
+      <c r="E41" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="2">
-        <v>12122</v>
-      </c>
+      <c r="E42" s="2"/>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E43" s="2">
-        <v>2311323</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>219</v>
+        <v>176</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>92</v>
+      <c r="E45" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>8</v>
@@ -17066,61 +17056,77 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>30</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>17</v>
+        <v>53</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>34</v>
+        <v>177</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E47" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="A48" s="2">
+        <v>54</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="2"/>
+      <c r="A50" s="2">
+        <v>56</v>
+      </c>
       <c r="B50" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>8</v>
@@ -17129,111 +17135,85 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="2">
-        <v>34</v>
-      </c>
+      <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>269</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="2">
-        <v>35</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A54" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
       <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>168</v>
+        <v>64</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>169</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E55" s="2"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="2">
-        <v>42</v>
-      </c>
+      <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>171</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>172</v>
+        <v>65</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="2">
-        <v>10000</v>
-      </c>
+      <c r="E57" s="2"/>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>173</v>
+        <v>65</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>8</v>
@@ -17242,205 +17222,201 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="2">
-        <v>1000</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" s="2">
-        <v>2</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E61" s="2"/>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E63" s="2">
-        <v>20</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E65" s="2">
-        <v>2</v>
+        <v>117</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>177</v>
+        <v>86</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E66" s="2"/>
+      <c r="E66" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>177</v>
+        <v>258</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E67" s="2">
-        <v>20</v>
+        <v>2311323</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E68" s="2"/>
+      <c r="E68" s="2">
+        <v>12323</v>
+      </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>179</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E69" s="2"/>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E70" s="2"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>8</v>
@@ -17448,71 +17424,77 @@
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="2">
-        <v>58</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A72" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
       <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="2"/>
+      <c r="A73" s="2">
+        <v>128</v>
+      </c>
       <c r="B73" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="2"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="2"/>
+      <c r="A76" s="2">
+        <v>130</v>
+      </c>
       <c r="B76" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>65</v>
+        <v>202</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>8</v>
@@ -17521,43 +17503,45 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E78" s="2"/>
+      <c r="E78" s="5" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>11</v>
@@ -17565,29 +17549,23 @@
       <c r="E80" s="2"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="2">
-        <v>116</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A81" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
       <c r="E81" s="2"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>11</v>
@@ -17596,13 +17574,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>11</v>
@@ -17610,97 +17588,83 @@
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="2">
-        <v>119</v>
-      </c>
+      <c r="A84" s="2"/>
       <c r="B84" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
       <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>203</v>
+        <v>5</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>121</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E85" s="5"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>86</v>
+        <v>207</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>91</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E86" s="2"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>258</v>
+        <v>208</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E87" s="2">
-        <v>2311323</v>
-      </c>
+      <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>87</v>
+        <v>209</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E88" s="2">
-        <v>12323</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E88" s="2"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>11</v>
@@ -17709,46 +17673,48 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>137</v>
+        <v>210</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B92" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>128</v>
+        <v>8</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>5</v>
@@ -17772,13 +17738,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>8</v>
@@ -17787,114 +17753,122 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="2"/>
+      <c r="E96" s="5" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>202</v>
+        <v>247</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E97" s="2"/>
+      <c r="E97" s="5" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>184</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>5</v>
+        <v>223</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>166</v>
+        <v>224</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E99" s="2"/>
+      <c r="E99" s="2" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="2">
-        <v>134</v>
-      </c>
+      <c r="A100" s="2"/>
       <c r="B100" s="2" t="s">
-        <v>17</v>
+        <v>272</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>11</v>
+        <v>225</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E100" s="2"/>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
+      <c r="A101" s="2">
+        <v>14</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E101" s="2"/>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>64</v>
+        <v>250</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E102" s="2"/>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>64</v>
+        <v>251</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>11</v>
@@ -17902,53 +17876,47 @@
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2" t="s">
-        <v>255</v>
-      </c>
+      <c r="A104" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C105" s="12" t="s">
-        <v>206</v>
+      <c r="C105" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E105" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="E105" s="2"/>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="2">
-        <v>68</v>
-      </c>
+      <c r="A106" s="2"/>
       <c r="B106" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
       <c r="E106" s="2"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>208</v>
+        <v>138</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>8</v>
@@ -17957,13 +17925,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>209</v>
+        <v>56</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>11</v>
@@ -17972,28 +17940,28 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>211</v>
+        <v>140</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E109" s="2"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>210</v>
+        <v>142</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>11</v>
@@ -18002,13 +17970,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>212</v>
+        <v>57</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>11</v>
@@ -18017,18 +17985,16 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>255</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>5</v>
@@ -18052,13 +18018,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>221</v>
+        <v>65</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>8</v>
@@ -18067,47 +18033,43 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>246</v>
+        <v>127</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>248</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E116" s="2"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>247</v>
+        <v>126</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>249</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E117" s="2"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>222</v>
+        <v>55</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>11</v>
@@ -18116,43 +18078,43 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>223</v>
+        <v>17</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>224</v>
+        <v>57</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>245</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E119" s="2"/>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="2"/>
-      <c r="B120" s="2" t="s">
-        <v>272</v>
+      <c r="A120" s="2">
+        <v>112</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E120" s="2"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>14</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>69</v>
+        <v>113</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>250</v>
+        <v>199</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>8</v>
@@ -18161,324 +18123,48 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>250</v>
+        <v>211</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E122" s="2"/>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E123" s="2"/>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
+      <c r="A124" s="2">
+        <v>116</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E124" s="2"/>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="2">
-        <v>99</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E125" s="2"/>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="2"/>
-      <c r="B126" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="2">
-        <v>100</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E127" s="2"/>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="A128" s="2">
-        <v>101</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E128" s="2"/>
-    </row>
-    <row r="129" spans="1:5">
-      <c r="A129" s="2">
-        <v>102</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E129" s="2"/>
-    </row>
-    <row r="130" spans="1:5">
-      <c r="A130" s="2">
-        <v>103</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E130" s="2"/>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="A131" s="2">
-        <v>104</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E131" s="2"/>
-    </row>
-    <row r="132" spans="1:5">
-      <c r="A132" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
-    </row>
-    <row r="133" spans="1:5">
-      <c r="A133" s="2">
-        <v>106</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E133" s="2"/>
-    </row>
-    <row r="134" spans="1:5">
-      <c r="A134" s="2"/>
-      <c r="B134" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
-    </row>
-    <row r="135" spans="1:5">
-      <c r="A135" s="2">
-        <v>107</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E135" s="2"/>
-    </row>
-    <row r="136" spans="1:5">
-      <c r="A136" s="2">
-        <v>108</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E136" s="2"/>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" s="2">
-        <v>109</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E137" s="2"/>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" s="2">
-        <v>110</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E138" s="2"/>
-    </row>
-    <row r="139" spans="1:5">
-      <c r="A139" s="2">
-        <v>111</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E139" s="2"/>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="A140" s="2">
-        <v>112</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E140" s="2"/>
-    </row>
-    <row r="141" spans="1:5">
-      <c r="A141" s="2">
-        <v>113</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E141" s="2"/>
-    </row>
-    <row r="142" spans="1:5">
-      <c r="A142" s="2">
-        <v>114</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E142" s="2"/>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" s="2">
-        <v>115</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E143" s="2"/>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" s="2">
-        <v>116</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E144" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3840" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3942" uniqueCount="274">
   <si>
     <t>Keyword</t>
   </si>
@@ -851,6 +851,9 @@
   </si>
   <si>
     <t>UPLOADWARNING</t>
+  </si>
+  <si>
+    <t>ereturnvalidation</t>
   </si>
 </sst>
 </file>
@@ -16344,7 +16347,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
@@ -16517,11 +16520,9 @@
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="2">
-        <v>15</v>
-      </c>
+      <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>79</v>
@@ -16529,36 +16530,34 @@
       <c r="D13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="2">
-        <v>10000</v>
-      </c>
+      <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="2">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
@@ -16569,259 +16568,261 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="2">
-        <v>120</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="2">
-        <v>10</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="2">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>90</v>
+      <c r="E20" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="2">
-        <v>12122</v>
+      <c r="E22" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="2">
-        <v>2311323</v>
+        <v>12122</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>219</v>
+        <v>88</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2311323</v>
+      </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
+        <v>29</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="2">
         <v>30</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="2">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="2">
         <v>31</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="2">
-        <v>32</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>8</v>
@@ -16830,108 +16831,108 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>269</v>
-      </c>
+      <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>268</v>
+        <v>144</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>168</v>
+        <v>268</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>169</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="2">
-        <v>10000</v>
+      <c r="E37" s="5" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="2"/>
+      <c r="E38" s="2">
+        <v>10000</v>
+      </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>173</v>
@@ -16939,31 +16940,31 @@
       <c r="D39" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E39" s="2">
-        <v>1000</v>
-      </c>
+      <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E40" s="2"/>
+      <c r="E40" s="2">
+        <v>1000</v>
+      </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>174</v>
@@ -16971,31 +16972,31 @@
       <c r="D41" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E41" s="2">
-        <v>2</v>
-      </c>
+      <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>175</v>
@@ -17003,31 +17004,31 @@
       <c r="D43" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E43" s="2">
-        <v>20</v>
-      </c>
+      <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>176</v>
@@ -17035,31 +17036,31 @@
       <c r="D45" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="2">
-        <v>2</v>
-      </c>
+      <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E46" s="2"/>
+      <c r="E46" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>177</v>
@@ -17067,31 +17068,31 @@
       <c r="D47" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="2">
-        <v>20</v>
-      </c>
+      <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="2"/>
+      <c r="E48" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>178</v>
@@ -17099,118 +17100,118 @@
       <c r="D49" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="E49" s="2"/>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
+        <v>57</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="2">
         <v>58</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="2"/>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2" t="s">
+      <c r="D53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="2">
+      <c r="A55" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="2">
         <v>111</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C55" s="2" t="s">
+      <c r="B56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="2"/>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2" t="s">
+      <c r="D56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="2">
-        <v>112</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
       <c r="E57" s="2"/>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>65</v>
@@ -17222,28 +17223,28 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>11</v>
@@ -17252,13 +17253,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>11</v>
@@ -17267,13 +17268,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>11</v>
@@ -17282,13 +17283,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>11</v>
@@ -17297,13 +17298,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>11</v>
@@ -17312,174 +17313,174 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>203</v>
+        <v>136</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>121</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>86</v>
+        <v>203</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>258</v>
+        <v>86</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E67" s="2">
-        <v>2311323</v>
+      <c r="E67" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>87</v>
+        <v>258</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E68" s="2">
-        <v>12323</v>
+        <v>2311323</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>195</v>
+        <v>87</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E69" s="2">
+        <v>12323</v>
+      </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E70" s="2"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
+        <v>125</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="2">
         <v>126</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B72" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E71" s="2"/>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="2" t="s">
+      <c r="D72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="2"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="2">
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="2">
         <v>128</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="2" t="s">
+      <c r="B74" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="2"/>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2" t="s">
+      <c r="D74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="2"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="2">
-        <v>129</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>8</v>
@@ -17488,13 +17489,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>8</v>
@@ -17503,81 +17504,81 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E78" s="5" t="s">
-        <v>184</v>
-      </c>
+      <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E79" s="2"/>
+      <c r="E79" s="5" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
+        <v>133</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="2">
         <v>134</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B81" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C81" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D80" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="2"/>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="2" t="s">
+      <c r="D81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="2">
-        <v>65</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
       <c r="E82" s="2"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>64</v>
@@ -17588,83 +17589,83 @@
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="2"/>
+      <c r="A84" s="2">
+        <v>66</v>
+      </c>
       <c r="B84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="2">
-        <v>67</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" s="5"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>207</v>
+      <c r="C86" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E86" s="5"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E88" s="2"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>11</v>
@@ -17673,13 +17674,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>11</v>
@@ -17688,36 +17689,40 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
+        <v>72</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="2"/>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="2">
         <v>73</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C91" s="2" t="s">
+      <c r="B92" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E91" s="2"/>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
+      <c r="D92" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>64</v>
@@ -17728,105 +17733,103 @@
       <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="2"/>
+      <c r="A94" s="2">
+        <v>8</v>
+      </c>
       <c r="B94" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="2">
-        <v>9</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
       <c r="E95" s="2"/>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>10</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>248</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="2"/>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>11</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>249</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="2"/>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>12</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
+        <v>12</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="2">
         <v>13</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2" t="s">
-        <v>272</v>
+      <c r="B100" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+        <v>226</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="E100" s="2"/>
     </row>
@@ -17834,14 +17837,14 @@
       <c r="A101" s="2">
         <v>14</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>69</v>
+      <c r="B101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E101" s="2"/>
     </row>
@@ -17849,14 +17852,14 @@
       <c r="A102" s="2">
         <v>15</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>8</v>
+        <v>227</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E102" s="2"/>
     </row>
@@ -17865,226 +17868,250 @@
         <v>16</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D103" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
+      <c r="A104" s="2">
+        <v>17</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>99</v>
-      </c>
-      <c r="B105" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B105" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D105" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E105" s="2"/>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
+      <c r="A106" s="2">
+        <v>19</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="E106" s="2"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>100</v>
-      </c>
-      <c r="B107" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B107" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>8</v>
+        <v>229</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E107" s="2"/>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>101</v>
-      </c>
-      <c r="B108" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D108" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E108" s="2"/>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>102</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>8</v>
+        <v>232</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E109" s="2"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>103</v>
-      </c>
-      <c r="B110" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D110" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E110" s="2"/>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>104</v>
-      </c>
-      <c r="B111" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="2"/>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="2">
+        <v>25</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" s="2"/>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
+      <c r="C112" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="E112" s="2"/>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>106</v>
-      </c>
-      <c r="B113" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B113" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D113" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D113" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E113" s="2"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="2"/>
-      <c r="B114" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
+      <c r="A114" s="2">
+        <v>27</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="E114" s="2"/>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>107</v>
-      </c>
-      <c r="B115" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B115" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>8</v>
+        <v>235</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E115" s="2"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>108</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>5</v>
+        <v>29</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D116" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D116" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E116" s="2"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>109</v>
-      </c>
-      <c r="B117" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B117" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D117" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D117" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E117" s="2"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>110</v>
-      </c>
-      <c r="B118" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D118" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E118" s="2"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>111</v>
-      </c>
-      <c r="B119" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>57</v>
+        <v>242</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>11</v>
@@ -18093,13 +18120,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>11</v>
@@ -18108,63 +18135,524 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>8</v>
+        <v>240</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E121" s="2"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>114</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>5</v>
+        <v>35</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D122" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D122" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E122" s="2"/>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="2">
-        <v>115</v>
+      <c r="A123" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
       <c r="E123" s="2"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
+        <v>8</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="2"/>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="2"/>
+      <c r="B125" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="2">
+        <v>9</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="2"/>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="2">
+        <v>10</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="2">
+        <v>11</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="2">
+        <v>12</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="2"/>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="2">
+        <v>13</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="2"/>
+      <c r="B131" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" s="2"/>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="2">
+        <v>14</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="2"/>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="2">
+        <v>15</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="2"/>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="2">
+        <v>16</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="2"/>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="2"/>
+      <c r="B135" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" s="2"/>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="2"/>
+      <c r="B136" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" s="2"/>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="2">
+        <v>99</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="2"/>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="2"/>
+      <c r="B139" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="2">
+        <v>100</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="2"/>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="2">
+        <v>101</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" s="2"/>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="2">
+        <v>102</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="2"/>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="2">
+        <v>103</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" s="2"/>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="2">
+        <v>104</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" s="2"/>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="2">
+        <v>106</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="2"/>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="2"/>
+      <c r="B147" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="2">
+        <v>107</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="2"/>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="2">
+        <v>108</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="2"/>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="2">
+        <v>109</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" s="2"/>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="2">
+        <v>110</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" s="2"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="2">
+        <v>111</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="2"/>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="2">
+        <v>112</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="2"/>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="2">
+        <v>113</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E154" s="2"/>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="2">
+        <v>114</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" s="2"/>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="2">
+        <v>115</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" s="2"/>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="2">
         <v>116</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C124" s="2" t="s">
+      <c r="B157" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" s="2"/>
+      <c r="D157" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18174,7 +18662,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
@@ -18257,391 +18745,383 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2">
-        <v>7</v>
-      </c>
+      <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2">
-        <v>7</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2">
-        <v>60</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="A10" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>23</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2">
-        <v>62</v>
-      </c>
+      <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E13" s="2">
+        <v>10000</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>20</v>
+      <c r="E15" s="2">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>59</v>
+        <v>8</v>
+      </c>
+      <c r="E16" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>23</v>
+        <v>83</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2">
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E19" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E20" s="5" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>20</v>
+      <c r="E21" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
+      </c>
+      <c r="E22" s="2">
+        <v>12122</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>32</v>
+        <v>88</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2311323</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>15</v>
+        <v>219</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="2" t="s">
-        <v>129</v>
+      <c r="A26" s="2">
+        <v>29</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>5</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>5</v>
+        <v>30</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="2">
+        <v>31</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="2">
-        <v>6</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="D29" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="2">
-        <v>7</v>
-      </c>
+      <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="2"/>
+      <c r="A31" s="2">
+        <v>32</v>
+      </c>
       <c r="B31" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>8</v>
@@ -18650,310 +19130,318 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="2">
-        <v>10000</v>
-      </c>
+      <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="2">
-        <v>100</v>
+      <c r="E33" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="2">
-        <v>100</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E35" s="2">
-        <v>10</v>
+      <c r="E35" s="5" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="2">
-        <v>120</v>
+      <c r="E36" s="5" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="2">
-        <v>10</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>84</v>
+        <v>173</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="2">
-        <v>40</v>
-      </c>
+      <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>85</v>
+        <v>173</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>90</v>
+      <c r="E39" s="2">
+        <v>1000</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E41" s="2">
-        <v>12122</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="2">
-        <v>2311323</v>
-      </c>
+      <c r="E42" s="2"/>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E43" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>30</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>17</v>
+        <v>52</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>34</v>
+        <v>177</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
+      <c r="A47" s="2">
+        <v>53</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="2"/>
+      <c r="A49" s="2">
+        <v>55</v>
+      </c>
       <c r="B49" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>8</v>
@@ -18962,96 +19450,70 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
+        <v>58</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>269</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E52" s="2"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="2">
-        <v>35</v>
-      </c>
+      <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
       <c r="E53" s="2"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="2">
-        <v>41</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>169</v>
-      </c>
+      <c r="A54" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>171</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E55" s="2"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="2">
-        <v>43</v>
-      </c>
+      <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="2">
-        <v>10000</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>173</v>
+        <v>65</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>8</v>
@@ -19060,190 +19522,186 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>173</v>
+        <v>65</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="2">
-        <v>1000</v>
-      </c>
+      <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E60" s="2">
-        <v>2</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E61" s="2"/>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E62" s="2">
-        <v>20</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>176</v>
+        <v>135</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E64" s="2">
-        <v>2</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E64" s="2"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E65" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>177</v>
+        <v>86</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E66" s="2">
-        <v>20</v>
+      <c r="E66" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>178</v>
+        <v>258</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E67" s="2"/>
+      <c r="E67" s="2">
+        <v>2311323</v>
+      </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>179</v>
+      <c r="E68" s="2">
+        <v>12323</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>11</v>
@@ -19252,13 +19710,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>8</v>
@@ -19267,70 +19725,76 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>34</v>
+        <v>196</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2" t="s">
-        <v>255</v>
-      </c>
+      <c r="A72" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
+      <c r="A73" s="2">
+        <v>128</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="2">
-        <v>111</v>
-      </c>
+      <c r="A74" s="2"/>
       <c r="B74" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="2"/>
+      <c r="A75" s="2">
+        <v>129</v>
+      </c>
       <c r="B75" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>65</v>
+        <v>270</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>8</v>
@@ -19339,13 +19803,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>65</v>
+        <v>202</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>8</v>
@@ -19354,43 +19818,45 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>11</v>
@@ -19398,29 +19864,23 @@
       <c r="E80" s="2"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="2">
-        <v>117</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A81" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
       <c r="E81" s="2"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>11</v>
@@ -19429,13 +19889,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>11</v>
@@ -19443,82 +19903,68 @@
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="2">
-        <v>120</v>
-      </c>
+      <c r="A84" s="2"/>
       <c r="B84" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>121</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>86</v>
+        <v>5</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E85" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="E85" s="5"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" s="2">
-        <v>2311323</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E86" s="2"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>87</v>
+        <v>208</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E87" s="2">
-        <v>12323</v>
-      </c>
+      <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>11</v>
@@ -19527,91 +19973,93 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
+      <c r="A91" s="2">
+        <v>73</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="2">
-        <v>128</v>
+      <c r="A92" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C92" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="2">
+        <v>8</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="2"/>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2" t="s">
+      <c r="D93" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="2">
-        <v>129</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
       <c r="E94" s="2"/>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>270</v>
+        <v>221</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>8</v>
@@ -19620,138 +20068,148 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>202</v>
+        <v>246</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="2"/>
+      <c r="E96" s="5" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>132</v>
+        <v>11</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>170</v>
+        <v>247</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>184</v>
+        <v>249</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>17</v>
+        <v>223</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>34</v>
+        <v>224</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
+      <c r="A100" s="2"/>
+      <c r="B100" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="E100" s="2"/>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>64</v>
+        <v>250</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E101" s="2"/>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>64</v>
+        <v>250</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E102" s="2"/>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="2"/>
+      <c r="A103" s="2">
+        <v>16</v>
+      </c>
       <c r="B103" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="2">
-        <v>67</v>
-      </c>
+      <c r="A104" s="2"/>
       <c r="B104" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C104" s="12" t="s">
-        <v>206</v>
+        <v>69</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E104" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="2">
-        <v>68</v>
-      </c>
+      <c r="A105" s="2"/>
       <c r="B105" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>207</v>
+        <v>273</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>11</v>
@@ -19759,29 +20217,23 @@
       <c r="E105" s="2"/>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="2">
-        <v>69</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A106" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
       <c r="E106" s="2"/>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>209</v>
+        <v>64</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>11</v>
@@ -19789,44 +20241,38 @@
       <c r="E107" s="2"/>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="2">
-        <v>71</v>
-      </c>
+      <c r="A108" s="2"/>
       <c r="B108" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
       <c r="E108" s="2"/>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>210</v>
+        <v>138</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E109" s="2"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>11</v>
@@ -19834,25 +20280,29 @@
       <c r="E110" s="2"/>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="2" t="s">
-        <v>243</v>
+      <c r="A111" s="2">
+        <v>102</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E111" s="2"/>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>11</v>
@@ -19860,139 +20310,202 @@
       <c r="E112" s="2"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="2"/>
+      <c r="A113" s="2">
+        <v>104</v>
+      </c>
       <c r="B113" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E113" s="2"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="2">
-        <v>9</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A114" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
       <c r="E114" s="2"/>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>246</v>
+        <v>64</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>248</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E115" s="2"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="2">
-        <v>11</v>
-      </c>
+      <c r="A116" s="2"/>
       <c r="B116" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>249</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>222</v>
+        <v>65</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E117" s="2"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>223</v>
+        <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>224</v>
+        <v>127</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>245</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E118" s="2"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>250</v>
+        <v>126</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E119" s="2"/>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E120" s="2"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>251</v>
+        <v>57</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E121" s="2"/>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="2">
+        <v>112</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="2"/>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="2">
+        <v>113</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E123" s="2"/>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="2">
+        <v>114</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="2"/>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="2">
+        <v>115</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E125" s="2"/>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="2">
+        <v>116</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20001,7 +20514,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
@@ -20267,21 +20780,25 @@
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>64</v>
+        <v>273</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>11</v>
@@ -20289,63 +20806,59 @@
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
-        <v>255</v>
-      </c>
+      <c r="A20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="13" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="13" t="s">
+      <c r="D23" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>8</v>
+      <c r="D24" s="13" t="s">
+        <v>11</v>
       </c>
       <c r="E24" s="2"/>
     </row>
@@ -20355,42 +20868,46 @@
         <v>5</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="D27" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>11</v>
@@ -20398,10 +20915,10 @@
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2" t="s">
-        <v>255</v>
-      </c>
+      <c r="A29" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
@@ -20412,24 +20929,20 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5">
@@ -20438,10 +20951,10 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2"/>
     </row>
@@ -20451,7 +20964,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>11</v>
@@ -20461,10 +20974,10 @@
     <row r="34" spans="1:5">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>11</v>
@@ -20477,7 +20990,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>11</v>
@@ -20487,13 +21000,13 @@
     <row r="36" spans="1:5">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>199</v>
+        <v>57</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2"/>
     </row>
@@ -20503,7 +21016,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>11</v>
@@ -20516,7 +21029,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
@@ -20529,7 +21042,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>55</v>
+        <v>211</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>11</v>
@@ -20539,10 +21052,10 @@
     <row r="40" spans="1:5">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
@@ -20555,23 +21068,23 @@
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2"/>
     </row>
@@ -20581,10 +21094,10 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2"/>
     </row>
@@ -20594,7 +21107,7 @@
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>11</v>
@@ -20607,7 +21120,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>11</v>
@@ -20617,10 +21130,10 @@
     <row r="46" spans="1:5">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>11</v>
@@ -20630,10 +21143,10 @@
     <row r="47" spans="1:5">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>11</v>
@@ -20646,7 +21159,7 @@
         <v>17</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>11</v>
@@ -20659,7 +21172,7 @@
         <v>17</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>11</v>
@@ -20672,12 +21185,38 @@
         <v>17</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="2"/>
+      <c r="D52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -13,9 +13,8 @@
     <sheet name="Challan Mapping" sheetId="4" r:id="rId4"/>
     <sheet name="Predict Default" sheetId="5" r:id="rId5"/>
     <sheet name="Regression Test" sheetId="8" r:id="rId6"/>
-    <sheet name="Demo" sheetId="9" r:id="rId7"/>
-    <sheet name="Sheet2" sheetId="10" r:id="rId8"/>
-    <sheet name="Ereturn" sheetId="6" r:id="rId9"/>
+    <sheet name="Ereturn" sheetId="6" r:id="rId7"/>
+    <sheet name="Demo" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3942" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3583" uniqueCount="274">
   <si>
     <t>Keyword</t>
   </si>
@@ -16347,6 +16346,718 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E52"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="42.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="41.85546875" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -18658,2568 +19369,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E126"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="47.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="2">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="2">
-        <v>15</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="2">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="2">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="2">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="2">
-        <v>19</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="2">
-        <v>20</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="2">
-        <v>21</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="2">
-        <v>22</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="2">
-        <v>23</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="2">
-        <v>24</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2">
-        <v>12122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="2">
-        <v>25</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2">
-        <v>2311323</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="2">
-        <v>26</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="2">
-        <v>27</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="2">
-        <v>29</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="2">
-        <v>30</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="2">
-        <v>31</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="2">
-        <v>32</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="2">
-        <v>33</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="2">
-        <v>34</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="2">
-        <v>35</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="2">
-        <v>41</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="2">
-        <v>42</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="2">
-        <v>43</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="2">
-        <v>44</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="2">
-        <v>45</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2">
-        <v>46</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="2">
-        <v>47</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="2">
-        <v>48</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="2">
-        <v>49</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="2">
-        <v>50</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="2">
-        <v>51</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="2">
-        <v>52</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2"/>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="2">
-        <v>53</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="2">
-        <v>54</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="2"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="2">
-        <v>55</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="2">
-        <v>56</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="2"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="2">
-        <v>57</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="2"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="2">
-        <v>58</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="2"/>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="2">
-        <v>111</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="2"/>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="2">
-        <v>112</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="2"/>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="2">
-        <v>113</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="2"/>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="2">
-        <v>114</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="2"/>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="2">
-        <v>115</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="2"/>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="2">
-        <v>116</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" s="2"/>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="2">
-        <v>117</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="2"/>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="2">
-        <v>118</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="2"/>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="2">
-        <v>119</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="2"/>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="2">
-        <v>120</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="2">
-        <v>121</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="2">
-        <v>122</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E67" s="2">
-        <v>2311323</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="2">
-        <v>123</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E68" s="2">
-        <v>12323</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="2">
-        <v>124</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="2"/>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="2">
-        <v>125</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E70" s="2"/>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="2">
-        <v>126</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E71" s="2"/>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="2">
-        <v>128</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="2"/>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="2">
-        <v>129</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E75" s="2"/>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="2">
-        <v>130</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" s="2"/>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="2">
-        <v>131</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="2"/>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="2">
-        <v>132</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="2">
-        <v>133</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E79" s="2"/>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="2">
-        <v>134</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="2"/>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="2">
-        <v>65</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="2"/>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="2">
-        <v>66</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" s="2"/>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="2">
-        <v>67</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" s="5"/>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="2">
-        <v>68</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" s="2"/>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="2">
-        <v>69</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E87" s="2"/>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="2">
-        <v>70</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="2"/>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="2">
-        <v>71</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E89" s="2"/>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="2">
-        <v>72</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="2"/>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="2">
-        <v>73</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E91" s="2"/>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="2">
-        <v>8</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E93" s="2"/>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="2">
-        <v>9</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E95" s="2"/>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="2">
-        <v>10</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="2">
-        <v>11</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="2">
-        <v>12</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" s="2"/>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="2">
-        <v>13</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="2"/>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="2">
-        <v>14</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="2"/>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="2">
-        <v>15</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E102" s="2"/>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="2">
-        <v>16</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E103" s="2"/>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="2"/>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E105" s="2"/>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="2">
-        <v>99</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E107" s="2"/>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="2">
-        <v>100</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E109" s="2"/>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="2">
-        <v>101</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E110" s="2"/>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="2">
-        <v>102</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E111" s="2"/>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="2">
-        <v>103</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="2"/>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="2">
-        <v>104</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E113" s="2"/>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="2">
-        <v>106</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E115" s="2"/>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="2">
-        <v>107</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E117" s="2"/>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118" s="2">
-        <v>108</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E118" s="2"/>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="A119" s="2">
-        <v>109</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E119" s="2"/>
-    </row>
-    <row r="120" spans="1:5">
-      <c r="A120" s="2">
-        <v>110</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E120" s="2"/>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121" s="2">
-        <v>111</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E121" s="2"/>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122" s="2">
-        <v>112</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" s="2"/>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="2">
-        <v>113</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E123" s="2"/>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124" s="2">
-        <v>114</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" s="2"/>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="2">
-        <v>115</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E125" s="2"/>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="2">
-        <v>116</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E126" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E52"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="42.85546875" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" customWidth="1"/>
-    <col min="5" max="5" width="31" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="2"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="2"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="2"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="2"/>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="2"/>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="2"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="2"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="2"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="2"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="7"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3583" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3289" uniqueCount="273">
   <si>
     <t>Keyword</t>
   </si>
@@ -403,9 +403,6 @@
   </si>
   <si>
     <t>Edit And Update Challan</t>
-  </si>
-  <si>
-    <t>Delete Single Challan</t>
   </si>
   <si>
     <t>singlechallanselect</t>
@@ -1312,7 +1309,7 @@
         <v>71</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1370,7 +1367,7 @@
         <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -2587,7 +2584,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.5703125" customWidth="1"/>
@@ -2616,10 +2613,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2686,1545 +2683,6 @@
         <v>11</v>
       </c>
       <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2">
-        <v>12122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2">
-        <v>2311323</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="2">
-        <v>29</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="2">
-        <v>30</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="6">
-        <v>22343244410021</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="7"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="7"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="6">
-        <v>22343244410021</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="7"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="7"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="6">
-        <v>22343244410021</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="7"/>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2">
-        <v>39</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="7"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="2">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="6">
-        <v>22343244410021</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="2">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="2"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="2">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="7"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="2">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="6">
-        <v>22343244410021</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="2">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="7"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="2">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="7"/>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="2">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="6">
-        <v>22343244410021</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="2">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="7"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="2">
-        <v>48</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="2"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="2">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="6">
-        <v>22343244410021</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="2">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="2"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="2">
-        <v>51</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="2"/>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="2">
-        <v>52</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="2">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="2"/>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="2">
-        <v>54</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="2"/>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="2">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E56" s="8">
-        <v>44594</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="2">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="2">
-        <v>57</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="2"/>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="2">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="2"/>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="2">
-        <v>59</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="2"/>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="2">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" s="2"/>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="2">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="2"/>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="2">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E63" s="2"/>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="2">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E64" s="6">
-        <v>3234</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="2">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E65" s="9">
-        <v>13234</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="2">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" s="2"/>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="2">
-        <v>66</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="2"/>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="2">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E68" s="2"/>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="2">
-        <v>68</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="2"/>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="2">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E71" s="2"/>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="2">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E72" s="6">
-        <v>7826423</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="2">
-        <v>72</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="2">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="2">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E75" s="2">
-        <v>3478323</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="2">
-        <v>75</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" s="2"/>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="2">
-        <v>76</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E77" s="2"/>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="2">
-        <v>77</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="2"/>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="2">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E79" s="2"/>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B80" s="3"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="2">
-        <v>80</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="2">
-        <v>81</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E82" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="2">
-        <v>82</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="2">
-        <v>83</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E84" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="2">
-        <v>84</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="2">
-        <v>85</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" s="2"/>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="2">
-        <v>86</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E87" s="2"/>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="2">
-        <v>87</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E88" s="2"/>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="2">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="6">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="2">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="2">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="2">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E92" s="2">
-        <v>3478323</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="2">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E93" s="2"/>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="2">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E94" s="2"/>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="2">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" s="2"/>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="2">
-        <v>96</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E98" s="2"/>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="2">
-        <v>97</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="2"/>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="2">
-        <v>98</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="2"/>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="2">
-        <v>99</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E101" s="2"/>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="2">
-        <v>100</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="2"/>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="2">
-        <v>101</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="2"/>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="2">
-        <v>102</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E105" s="2"/>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="2">
-        <v>103</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="2"/>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="2">
-        <v>104</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E107" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4264,10 +2722,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4328,7 +2786,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -4368,7 +2826,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -4382,7 +2840,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -4397,7 +2855,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
@@ -4412,18 +2870,18 @@
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -4438,7 +2896,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
@@ -4448,7 +2906,7 @@
     <row r="15" spans="1:5">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -4462,7 +2920,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
@@ -4477,13 +2935,13 @@
         <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -4500,7 +2958,7 @@
         <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4511,13 +2969,13 @@
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4528,7 +2986,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -4545,13 +3003,13 @@
         <v>3</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4562,13 +3020,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -4579,13 +3037,13 @@
         <v>21</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -4596,7 +3054,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>8</v>
@@ -4626,7 +3084,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
@@ -4641,13 +3099,13 @@
         <v>3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -4675,13 +3133,13 @@
         <v>21</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -4692,7 +3150,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>8</v>
@@ -4716,7 +3174,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -4741,7 +3199,7 @@
     <row r="34" spans="1:5">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -4755,7 +3213,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>8</v>
@@ -4770,7 +3228,7 @@
         <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>8</v>
@@ -4785,13 +3243,13 @@
         <v>3</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -4802,7 +3260,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>11</v>
@@ -4817,7 +3275,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>8</v>
@@ -4871,7 +3329,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4886,13 +3344,13 @@
         <v>21</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -4903,13 +3361,13 @@
         <v>21</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -4920,7 +3378,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>8</v>
@@ -4937,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>8</v>
@@ -4952,7 +3410,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>8</v>
@@ -4969,7 +3427,7 @@
         <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>8</v>
@@ -4984,7 +3442,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>8</v>
@@ -5001,7 +3459,7 @@
         <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>8</v>
@@ -5016,7 +3474,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>8</v>
@@ -5033,7 +3491,7 @@
         <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>8</v>
@@ -5048,7 +3506,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>8</v>
@@ -5065,7 +3523,7 @@
         <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>8</v>
@@ -5080,7 +3538,7 @@
         <v>3</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>8</v>
@@ -5097,7 +3555,7 @@
         <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>8</v>
@@ -5112,13 +3570,13 @@
         <v>3</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -5129,7 +3587,7 @@
         <v>17</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>11</v>
@@ -5144,7 +3602,7 @@
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>8</v>
@@ -5168,7 +3626,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -5183,13 +3641,13 @@
         <v>3</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -5200,7 +3658,7 @@
         <v>69</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>11</v>
@@ -5215,7 +3673,7 @@
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>11</v>
@@ -5230,13 +3688,13 @@
         <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -5247,7 +3705,7 @@
         <v>3</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>8</v>
@@ -5264,7 +3722,7 @@
         <v>5</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>8</v>
@@ -5290,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -5307,7 +3765,7 @@
         <v>3</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>8</v>
@@ -5339,7 +3797,7 @@
         <v>17</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>11</v>
@@ -5354,13 +3812,13 @@
         <v>21</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -5371,7 +3829,7 @@
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>8</v>
@@ -5386,7 +3844,7 @@
         <v>3</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>8</v>
@@ -5418,7 +3876,7 @@
         <v>17</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>11</v>
@@ -5433,7 +3891,7 @@
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>8</v>
@@ -5448,7 +3906,7 @@
         <v>3</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>8</v>
@@ -5480,7 +3938,7 @@
         <v>17</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>11</v>
@@ -5495,7 +3953,7 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>8</v>
@@ -5510,7 +3968,7 @@
         <v>3</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>8</v>
@@ -5542,7 +4000,7 @@
         <v>17</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>11</v>
@@ -5557,7 +4015,7 @@
         <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>8</v>
@@ -5572,7 +4030,7 @@
         <v>3</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>8</v>
@@ -5604,7 +4062,7 @@
         <v>17</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>11</v>
@@ -5619,7 +4077,7 @@
         <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>8</v>
@@ -5634,7 +4092,7 @@
         <v>3</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>8</v>
@@ -5666,7 +4124,7 @@
         <v>17</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>11</v>
@@ -5681,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>8</v>
@@ -5698,7 +4156,7 @@
         <v>3</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>8</v>
@@ -5745,7 +4203,7 @@
         <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>8</v>
@@ -5760,7 +4218,7 @@
         <v>5</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>11</v>
@@ -5775,7 +4233,7 @@
         <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>8</v>
@@ -5799,7 +4257,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>8</v>
@@ -5814,13 +4272,13 @@
         <v>3</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5831,7 +4289,7 @@
         <v>69</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>11</v>
@@ -5846,7 +4304,7 @@
         <v>5</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>11</v>
@@ -5861,13 +4319,13 @@
         <v>21</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5878,7 +4336,7 @@
         <v>3</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>8</v>
@@ -5895,13 +4353,13 @@
         <v>21</v>
       </c>
       <c r="C109" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E109" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5912,13 +4370,13 @@
         <v>3</v>
       </c>
       <c r="C110" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5929,7 +4387,7 @@
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>8</v>
@@ -5953,7 +4411,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -5978,7 +4436,7 @@
     <row r="115" spans="1:5">
       <c r="A115" s="2"/>
       <c r="B115" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
@@ -6022,7 +4480,7 @@
         <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>11</v>
@@ -6037,7 +4495,7 @@
         <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>11</v>
@@ -6052,7 +4510,7 @@
         <v>17</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>11</v>
@@ -6067,7 +4525,7 @@
         <v>17</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>11</v>
@@ -6082,7 +4540,7 @@
         <v>17</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>11</v>
@@ -6097,7 +4555,7 @@
         <v>17</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>11</v>
@@ -6112,7 +4570,7 @@
         <v>21</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>117</v>
@@ -6146,7 +4604,7 @@
         <v>3</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>8</v>
@@ -6180,7 +4638,7 @@
         <v>5</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>11</v>
@@ -6195,7 +4653,7 @@
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>8</v>
@@ -6210,7 +4668,7 @@
         <v>17</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>8</v>
@@ -6219,7 +4677,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -6244,7 +4702,7 @@
     <row r="133" spans="1:5">
       <c r="A133" s="2"/>
       <c r="B133" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -6258,7 +4716,7 @@
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>8</v>
@@ -6273,7 +4731,7 @@
         <v>5</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>8</v>
@@ -6288,7 +4746,7 @@
         <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>8</v>
@@ -6303,13 +4761,13 @@
         <v>21</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -6320,7 +4778,7 @@
         <v>5</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>8</v>
@@ -6344,7 +4802,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -6369,7 +4827,7 @@
     <row r="142" spans="1:5">
       <c r="A142" s="2"/>
       <c r="B142" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
@@ -6383,7 +4841,7 @@
         <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>8</v>
@@ -6398,7 +4856,7 @@
         <v>5</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>11</v>
@@ -6413,7 +4871,7 @@
         <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>8</v>
@@ -6428,7 +4886,7 @@
         <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>11</v>
@@ -6452,7 +4910,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -6482,7 +4940,7 @@
         <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>8</v>
@@ -6497,7 +4955,7 @@
         <v>5</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>11</v>
@@ -6512,7 +4970,7 @@
         <v>17</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>11</v>
@@ -6521,7 +4979,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -6551,7 +5009,7 @@
         <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>11</v>
@@ -6566,7 +5024,7 @@
         <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>11</v>
@@ -6605,7 +5063,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -6620,7 +5078,7 @@
         <v>69</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>11</v>
@@ -6635,7 +5093,7 @@
         <v>5</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>11</v>
@@ -6650,7 +5108,7 @@
         <v>5</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>8</v>
@@ -6665,7 +5123,7 @@
         <v>5</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>11</v>
@@ -6680,7 +5138,7 @@
         <v>5</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>8</v>
@@ -6758,10 +5216,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -6847,7 +5305,7 @@
     <row r="8" spans="1:5">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -6885,7 +5343,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -7159,7 +5617,7 @@
     <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -7173,7 +5631,7 @@
         <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>8</v>
@@ -7188,7 +5646,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>8</v>
@@ -7203,18 +5661,18 @@
         <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -7229,7 +5687,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>8</v>
@@ -7244,7 +5702,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>8</v>
@@ -7259,13 +5717,13 @@
         <v>3</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -7282,7 +5740,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -7293,13 +5751,13 @@
         <v>3</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -7310,7 +5768,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
@@ -7327,13 +5785,13 @@
         <v>3</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -7344,13 +5802,13 @@
         <v>3</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -7361,13 +5819,13 @@
         <v>21</v>
       </c>
       <c r="C41" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -7378,7 +5836,7 @@
         <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
@@ -7418,7 +5876,7 @@
     <row r="45" spans="1:5">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -7432,7 +5890,7 @@
         <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>8</v>
@@ -7447,7 +5905,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>8</v>
@@ -7462,13 +5920,13 @@
         <v>3</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -7479,7 +5937,7 @@
         <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>11</v>
@@ -7494,13 +5952,13 @@
         <v>21</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -7511,13 +5969,13 @@
         <v>21</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -7528,7 +5986,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>8</v>
@@ -7545,7 +6003,7 @@
         <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>8</v>
@@ -7560,7 +6018,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>8</v>
@@ -7577,7 +6035,7 @@
         <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>8</v>
@@ -7592,7 +6050,7 @@
         <v>3</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>8</v>
@@ -7609,7 +6067,7 @@
         <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>8</v>
@@ -7624,7 +6082,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>8</v>
@@ -7641,7 +6099,7 @@
         <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>8</v>
@@ -7656,7 +6114,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>8</v>
@@ -7673,7 +6131,7 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>8</v>
@@ -7688,7 +6146,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>8</v>
@@ -7705,13 +6163,13 @@
         <v>3</v>
       </c>
       <c r="C63" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -7722,7 +6180,7 @@
         <v>17</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>11</v>
@@ -7737,7 +6195,7 @@
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>8</v>
@@ -7761,7 +6219,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -7801,7 +6259,7 @@
     <row r="70" spans="1:5">
       <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -7815,7 +6273,7 @@
         <v>5</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>8</v>
@@ -7830,7 +6288,7 @@
         <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>11</v>
@@ -7845,7 +6303,7 @@
         <v>5</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>8</v>
@@ -7860,7 +6318,7 @@
         <v>5</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>11</v>
@@ -7875,7 +6333,7 @@
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>11</v>
@@ -7890,7 +6348,7 @@
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>11</v>
@@ -7905,7 +6363,7 @@
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>11</v>
@@ -7914,7 +6372,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -7939,7 +6397,7 @@
     <row r="80" spans="1:5">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -7953,7 +6411,7 @@
         <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>8</v>
@@ -7983,7 +6441,7 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>8</v>
@@ -7998,7 +6456,7 @@
         <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>11</v>
@@ -8028,7 +6486,7 @@
         <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>8</v>
@@ -8043,13 +6501,13 @@
         <v>3</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -8060,7 +6518,7 @@
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>11</v>
@@ -8075,7 +6533,7 @@
         <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>8</v>
@@ -8090,7 +6548,7 @@
         <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>11</v>
@@ -8105,13 +6563,13 @@
         <v>21</v>
       </c>
       <c r="C91" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -8122,7 +6580,7 @@
         <v>21</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>8</v>
@@ -8137,7 +6595,7 @@
         <v>3</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>8</v>
@@ -8154,7 +6612,7 @@
         <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>8</v>
@@ -8169,7 +6627,7 @@
         <v>3</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>8</v>
@@ -8186,7 +6644,7 @@
         <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>8</v>
@@ -8226,7 +6684,7 @@
     <row r="99" spans="1:5">
       <c r="A99" s="2"/>
       <c r="B99" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -8240,7 +6698,7 @@
         <v>5</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>8</v>
@@ -8255,7 +6713,7 @@
         <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>11</v>
@@ -8270,7 +6728,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>11</v>
@@ -8285,7 +6743,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>11</v>
@@ -8294,7 +6752,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -8319,7 +6777,7 @@
     <row r="106" spans="1:5">
       <c r="A106" s="2"/>
       <c r="B106" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -8333,7 +6791,7 @@
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>8</v>
@@ -8363,7 +6821,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>8</v>
@@ -8378,7 +6836,7 @@
         <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>11</v>
@@ -8402,7 +6860,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -8427,7 +6885,7 @@
     <row r="114" spans="1:5">
       <c r="A114" s="2"/>
       <c r="B114" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
@@ -8456,7 +6914,7 @@
         <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>11</v>
@@ -8471,7 +6929,7 @@
         <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>11</v>
@@ -8516,7 +6974,7 @@
         <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>11</v>
@@ -8531,7 +6989,7 @@
         <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>8</v>
@@ -8546,7 +7004,7 @@
         <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>11</v>
@@ -8561,7 +7019,7 @@
         <v>5</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>8</v>
@@ -8623,10 +7081,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -8687,7 +7145,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -8727,7 +7185,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -8741,7 +7199,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>8</v>
@@ -8756,7 +7214,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>11</v>
@@ -8768,16 +7226,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8788,7 +7246,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>8</v>
@@ -8803,7 +7261,7 @@
         <v>69</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
@@ -8818,7 +7276,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>11</v>
@@ -8833,7 +7291,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>11</v>
@@ -8848,7 +7306,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>11</v>
@@ -8863,7 +7321,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>11</v>
@@ -8878,7 +7336,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>11</v>
@@ -8893,7 +7351,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>11</v>
@@ -8908,7 +7366,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>11</v>
@@ -8923,7 +7381,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>11</v>
@@ -8938,7 +7396,7 @@
         <v>17</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>11</v>
@@ -8953,7 +7411,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>11</v>
@@ -8968,7 +7426,7 @@
         <v>5</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>11</v>
@@ -8983,7 +7441,7 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>11</v>
@@ -8998,7 +7456,7 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>11</v>
@@ -9013,7 +7471,7 @@
         <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>11</v>
@@ -9028,7 +7486,7 @@
         <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>11</v>
@@ -9043,7 +7501,7 @@
         <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>11</v>
@@ -9058,7 +7516,7 @@
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>11</v>
@@ -9073,7 +7531,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>11</v>
@@ -9088,7 +7546,7 @@
         <v>17</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>11</v>
@@ -9103,7 +7561,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>11</v>
@@ -9118,7 +7576,7 @@
         <v>17</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>11</v>
@@ -9133,7 +7591,7 @@
         <v>17</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>11</v>
@@ -9173,7 +7631,7 @@
     <row r="39" spans="1:5">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -9187,7 +7645,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
@@ -9202,7 +7660,7 @@
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>11</v>
@@ -9211,7 +7669,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -9241,7 +7699,7 @@
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>8</v>
@@ -9256,7 +7714,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>11</v>
@@ -9280,7 +7738,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -9310,7 +7768,7 @@
         <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>11</v>
@@ -9325,7 +7783,7 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>11</v>
@@ -9364,7 +7822,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -9379,7 +7837,7 @@
         <v>69</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>11</v>
@@ -9394,7 +7852,7 @@
         <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>11</v>
@@ -9409,7 +7867,7 @@
         <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>8</v>
@@ -9424,7 +7882,7 @@
         <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>11</v>
@@ -9439,7 +7897,7 @@
         <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>8</v>
@@ -9515,7 +7973,7 @@
         <v>71</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -10657,10 +9115,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -10859,7 +9317,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -11061,7 +9519,7 @@
         <v>17</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>11</v>
@@ -11508,7 +9966,7 @@
         <v>3</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>117</v>
@@ -11833,7 +10291,7 @@
         <v>5</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>11</v>
@@ -12098,7 +10556,7 @@
         <v>5</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>11</v>
@@ -12107,10 +10565,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
@@ -12171,7 +10629,7 @@
         <v>5</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>11</v>
@@ -12216,7 +10674,7 @@
         <v>5</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>8</v>
@@ -12231,7 +10689,7 @@
         <v>5</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>8</v>
@@ -12246,18 +10704,18 @@
         <v>3</v>
       </c>
       <c r="C180" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E180" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E180" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -12272,7 +10730,7 @@
         <v>5</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>8</v>
@@ -12287,7 +10745,7 @@
         <v>5</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>8</v>
@@ -12302,13 +10760,13 @@
         <v>3</v>
       </c>
       <c r="C184" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E184" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E184" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -12325,7 +10783,7 @@
         <v>11</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -12336,13 +10794,13 @@
         <v>3</v>
       </c>
       <c r="C186" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E186" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D186" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -12353,7 +10811,7 @@
         <v>3</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>8</v>
@@ -12370,13 +10828,13 @@
         <v>3</v>
       </c>
       <c r="C188" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E188" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -12387,13 +10845,13 @@
         <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E189" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -12404,13 +10862,13 @@
         <v>21</v>
       </c>
       <c r="C190" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="D190" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -12421,7 +10879,7 @@
         <v>5</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>8</v>
@@ -12451,7 +10909,7 @@
         <v>5</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>8</v>
@@ -12466,13 +10924,13 @@
         <v>3</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -12500,13 +10958,13 @@
         <v>21</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -12517,7 +10975,7 @@
         <v>5</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>8</v>
@@ -12541,7 +10999,7 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -12571,7 +11029,7 @@
         <v>5</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>8</v>
@@ -12586,7 +11044,7 @@
         <v>5</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>8</v>
@@ -12601,13 +11059,13 @@
         <v>3</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -12618,7 +11076,7 @@
         <v>5</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>11</v>
@@ -12633,7 +11091,7 @@
         <v>5</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>8</v>
@@ -12687,7 +11145,7 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -12702,13 +11160,13 @@
         <v>21</v>
       </c>
       <c r="C210" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E210" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E210" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -12719,13 +11177,13 @@
         <v>21</v>
       </c>
       <c r="C211" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E211" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E211" s="5" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -12736,7 +11194,7 @@
         <v>3</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>8</v>
@@ -12753,7 +11211,7 @@
         <v>5</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>8</v>
@@ -12768,7 +11226,7 @@
         <v>3</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>8</v>
@@ -12785,7 +11243,7 @@
         <v>5</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>8</v>
@@ -12800,7 +11258,7 @@
         <v>3</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>8</v>
@@ -12817,7 +11275,7 @@
         <v>5</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>8</v>
@@ -12832,7 +11290,7 @@
         <v>3</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>8</v>
@@ -12849,7 +11307,7 @@
         <v>5</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>8</v>
@@ -12864,7 +11322,7 @@
         <v>3</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>8</v>
@@ -12881,7 +11339,7 @@
         <v>5</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>8</v>
@@ -12896,7 +11354,7 @@
         <v>3</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>8</v>
@@ -12913,7 +11371,7 @@
         <v>5</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>8</v>
@@ -12928,13 +11386,13 @@
         <v>3</v>
       </c>
       <c r="C224" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E224" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -12945,7 +11403,7 @@
         <v>17</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>11</v>
@@ -12960,7 +11418,7 @@
         <v>5</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>8</v>
@@ -12984,7 +11442,7 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -12999,13 +11457,13 @@
         <v>3</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -13016,7 +11474,7 @@
         <v>69</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>11</v>
@@ -13031,7 +11489,7 @@
         <v>5</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>11</v>
@@ -13046,13 +11504,13 @@
         <v>21</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E232" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -13063,7 +11521,7 @@
         <v>3</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>8</v>
@@ -13080,7 +11538,7 @@
         <v>5</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>8</v>
@@ -13106,13 +11564,13 @@
         <v>21</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -13123,7 +11581,7 @@
         <v>3</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>8</v>
@@ -13155,7 +11613,7 @@
         <v>17</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>11</v>
@@ -13170,13 +11628,13 @@
         <v>21</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -13187,7 +11645,7 @@
         <v>5</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>8</v>
@@ -13202,7 +11660,7 @@
         <v>3</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>8</v>
@@ -13234,7 +11692,7 @@
         <v>17</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>11</v>
@@ -13249,7 +11707,7 @@
         <v>5</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>8</v>
@@ -13264,7 +11722,7 @@
         <v>3</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>8</v>
@@ -13296,7 +11754,7 @@
         <v>17</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>11</v>
@@ -13311,7 +11769,7 @@
         <v>5</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>8</v>
@@ -13326,7 +11784,7 @@
         <v>3</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>8</v>
@@ -13358,7 +11816,7 @@
         <v>17</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>11</v>
@@ -13373,7 +11831,7 @@
         <v>5</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>8</v>
@@ -13388,7 +11846,7 @@
         <v>3</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>8</v>
@@ -13420,7 +11878,7 @@
         <v>17</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>11</v>
@@ -13435,7 +11893,7 @@
         <v>5</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>8</v>
@@ -13450,7 +11908,7 @@
         <v>3</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>8</v>
@@ -13482,7 +11940,7 @@
         <v>17</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>11</v>
@@ -13497,7 +11955,7 @@
         <v>3</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>8</v>
@@ -13514,7 +11972,7 @@
         <v>3</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>8</v>
@@ -13561,7 +12019,7 @@
         <v>5</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>8</v>
@@ -13576,7 +12034,7 @@
         <v>5</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>11</v>
@@ -13591,7 +12049,7 @@
         <v>5</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>8</v>
@@ -13615,7 +12073,7 @@
         <v>5</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>8</v>
@@ -13630,13 +12088,13 @@
         <v>3</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -13647,7 +12105,7 @@
         <v>69</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>11</v>
@@ -13662,7 +12120,7 @@
         <v>5</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>11</v>
@@ -13677,13 +12135,13 @@
         <v>21</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -13694,7 +12152,7 @@
         <v>3</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>8</v>
@@ -13711,13 +12169,13 @@
         <v>21</v>
       </c>
       <c r="C275" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E275" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="D275" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E275" s="5" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -13728,13 +12186,13 @@
         <v>3</v>
       </c>
       <c r="C276" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E276" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E276" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -13745,7 +12203,7 @@
         <v>5</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>8</v>
@@ -13769,7 +12227,7 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -13829,7 +12287,7 @@
         <v>5</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>11</v>
@@ -13844,7 +12302,7 @@
         <v>5</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>11</v>
@@ -13859,7 +12317,7 @@
         <v>17</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>11</v>
@@ -13874,7 +12332,7 @@
         <v>17</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>11</v>
@@ -13889,7 +12347,7 @@
         <v>17</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>11</v>
@@ -13904,7 +12362,7 @@
         <v>17</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>11</v>
@@ -13919,7 +12377,7 @@
         <v>21</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>117</v>
@@ -13987,7 +12445,7 @@
         <v>5</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>11</v>
@@ -14002,7 +12460,7 @@
         <v>5</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>8</v>
@@ -14017,7 +12475,7 @@
         <v>17</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>8</v>
@@ -14026,7 +12484,7 @@
     </row>
     <row r="296" spans="1:5">
       <c r="A296" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -14056,7 +12514,7 @@
         <v>5</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>8</v>
@@ -14071,7 +12529,7 @@
         <v>5</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>8</v>
@@ -14086,7 +12544,7 @@
         <v>5</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>8</v>
@@ -14101,13 +12559,13 @@
         <v>21</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E301" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -14118,7 +12576,7 @@
         <v>5</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>8</v>
@@ -14142,10 +12600,10 @@
     </row>
     <row r="304" spans="1:5">
       <c r="A304" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" s="2"/>
@@ -14260,7 +12718,7 @@
     </row>
     <row r="312" spans="1:5">
       <c r="A312" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -14539,7 +12997,7 @@
         <v>5</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>8</v>
@@ -14554,7 +13012,7 @@
         <v>5</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>8</v>
@@ -14569,18 +13027,18 @@
         <v>3</v>
       </c>
       <c r="C331" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E331" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="D331" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E331" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="332" spans="1:5">
       <c r="A332" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B332" s="2"/>
       <c r="C332" s="2"/>
@@ -14595,7 +13053,7 @@
         <v>5</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>8</v>
@@ -14610,7 +13068,7 @@
         <v>5</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>8</v>
@@ -14625,13 +13083,13 @@
         <v>3</v>
       </c>
       <c r="C335" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E335" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D335" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E335" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -14648,7 +13106,7 @@
         <v>11</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -14659,13 +13117,13 @@
         <v>3</v>
       </c>
       <c r="C337" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E337" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D337" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E337" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -14676,7 +13134,7 @@
         <v>3</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>8</v>
@@ -14693,13 +13151,13 @@
         <v>3</v>
       </c>
       <c r="C339" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E339" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D339" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E339" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -14710,13 +13168,13 @@
         <v>3</v>
       </c>
       <c r="C340" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E340" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D340" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E340" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -14727,13 +13185,13 @@
         <v>21</v>
       </c>
       <c r="C341" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E341" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="D341" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E341" s="5" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -14744,7 +13202,7 @@
         <v>5</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>8</v>
@@ -14789,7 +13247,7 @@
         <v>5</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>8</v>
@@ -14804,7 +13262,7 @@
         <v>5</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>8</v>
@@ -14819,13 +13277,13 @@
         <v>3</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -14836,7 +13294,7 @@
         <v>5</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>11</v>
@@ -14851,13 +13309,13 @@
         <v>21</v>
       </c>
       <c r="C349" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E349" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="D349" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E349" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -14868,13 +13326,13 @@
         <v>21</v>
       </c>
       <c r="C350" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E350" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="D350" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E350" s="5" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -14885,7 +13343,7 @@
         <v>3</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D351" s="2" t="s">
         <v>8</v>
@@ -14902,7 +13360,7 @@
         <v>5</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D352" s="2" t="s">
         <v>8</v>
@@ -14917,7 +13375,7 @@
         <v>3</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D353" s="2" t="s">
         <v>8</v>
@@ -14934,7 +13392,7 @@
         <v>5</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D354" s="2" t="s">
         <v>8</v>
@@ -14949,7 +13407,7 @@
         <v>3</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D355" s="2" t="s">
         <v>8</v>
@@ -14966,7 +13424,7 @@
         <v>5</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>8</v>
@@ -14981,7 +13439,7 @@
         <v>3</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>8</v>
@@ -14998,7 +13456,7 @@
         <v>5</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>8</v>
@@ -15013,7 +13471,7 @@
         <v>3</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D359" s="2" t="s">
         <v>8</v>
@@ -15030,7 +13488,7 @@
         <v>5</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>8</v>
@@ -15045,7 +13503,7 @@
         <v>3</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>8</v>
@@ -15062,13 +13520,13 @@
         <v>3</v>
       </c>
       <c r="C362" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E362" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D362" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E362" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -15079,7 +13537,7 @@
         <v>17</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>11</v>
@@ -15094,7 +13552,7 @@
         <v>5</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>8</v>
@@ -15118,7 +13576,7 @@
     </row>
     <row r="366" spans="1:5">
       <c r="A366" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
@@ -15163,7 +13621,7 @@
         <v>5</v>
       </c>
       <c r="C369" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D369" s="2" t="s">
         <v>8</v>
@@ -15178,7 +13636,7 @@
         <v>5</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D370" s="2" t="s">
         <v>11</v>
@@ -15193,7 +13651,7 @@
         <v>5</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D371" s="2" t="s">
         <v>8</v>
@@ -15208,7 +13666,7 @@
         <v>5</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D372" s="2" t="s">
         <v>11</v>
@@ -15223,7 +13681,7 @@
         <v>5</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>11</v>
@@ -15238,7 +13696,7 @@
         <v>5</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>11</v>
@@ -15253,7 +13711,7 @@
         <v>5</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D375" s="2" t="s">
         <v>11</v>
@@ -15262,10 +13720,10 @@
     </row>
     <row r="376" spans="1:5">
       <c r="A376" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C376" s="2"/>
       <c r="D376" s="2"/>
@@ -15326,7 +13784,7 @@
         <v>5</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D380" s="2" t="s">
         <v>11</v>
@@ -15371,7 +13829,7 @@
         <v>5</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D383" s="3" t="s">
         <v>8</v>
@@ -15386,7 +13844,7 @@
         <v>5</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D384" s="3" t="s">
         <v>11</v>
@@ -15398,16 +13856,16 @@
         <v>11</v>
       </c>
       <c r="B385" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C385" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C385" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D385" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -15418,7 +13876,7 @@
         <v>5</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D386" s="3" t="s">
         <v>8</v>
@@ -15433,7 +13891,7 @@
         <v>69</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D387" s="2" t="s">
         <v>11</v>
@@ -15448,7 +13906,7 @@
         <v>5</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D388" s="2" t="s">
         <v>11</v>
@@ -15463,7 +13921,7 @@
         <v>5</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D389" s="3" t="s">
         <v>11</v>
@@ -15478,7 +13936,7 @@
         <v>17</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D390" s="3" t="s">
         <v>11</v>
@@ -15493,7 +13951,7 @@
         <v>5</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D391" s="3" t="s">
         <v>11</v>
@@ -15508,7 +13966,7 @@
         <v>5</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D392" s="3" t="s">
         <v>11</v>
@@ -15523,7 +13981,7 @@
         <v>17</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D393" s="3" t="s">
         <v>11</v>
@@ -15538,7 +13996,7 @@
         <v>5</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D394" s="3" t="s">
         <v>11</v>
@@ -15553,7 +14011,7 @@
         <v>5</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D395" s="3" t="s">
         <v>11</v>
@@ -15568,7 +14026,7 @@
         <v>17</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D396" s="3" t="s">
         <v>11</v>
@@ -15583,7 +14041,7 @@
         <v>5</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D397" s="3" t="s">
         <v>11</v>
@@ -15598,7 +14056,7 @@
         <v>5</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D398" s="3" t="s">
         <v>11</v>
@@ -15613,7 +14071,7 @@
         <v>17</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>11</v>
@@ -15628,7 +14086,7 @@
         <v>5</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D400" s="3" t="s">
         <v>11</v>
@@ -15643,7 +14101,7 @@
         <v>17</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D401" s="3" t="s">
         <v>11</v>
@@ -15658,7 +14116,7 @@
         <v>5</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D402" s="3" t="s">
         <v>11</v>
@@ -15673,7 +14131,7 @@
         <v>17</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D403" s="3" t="s">
         <v>11</v>
@@ -15688,7 +14146,7 @@
         <v>5</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D404" s="3" t="s">
         <v>11</v>
@@ -15703,7 +14161,7 @@
         <v>5</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D405" s="3" t="s">
         <v>11</v>
@@ -15718,7 +14176,7 @@
         <v>17</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D406" s="2" t="s">
         <v>11</v>
@@ -15733,7 +14191,7 @@
         <v>5</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D407" s="3" t="s">
         <v>11</v>
@@ -15748,7 +14206,7 @@
         <v>17</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D408" s="3" t="s">
         <v>11</v>
@@ -15763,7 +14221,7 @@
         <v>17</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D409" s="3" t="s">
         <v>11</v>
@@ -15808,7 +14266,7 @@
         <v>5</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D412" s="2" t="s">
         <v>8</v>
@@ -15823,7 +14281,7 @@
         <v>5</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D413" s="2" t="s">
         <v>11</v>
@@ -15839,10 +14297,10 @@
     </row>
     <row r="415" spans="1:5">
       <c r="A415" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C415" s="2"/>
       <c r="D415" s="2"/>
@@ -15903,7 +14361,7 @@
         <v>5</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D419" s="2" t="s">
         <v>11</v>
@@ -15948,7 +14406,7 @@
         <v>5</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D422" s="3" t="s">
         <v>8</v>
@@ -15963,13 +14421,13 @@
         <v>21</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D423" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E423" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -15980,13 +14438,13 @@
         <v>21</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D424" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E424" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -15997,7 +14455,7 @@
         <v>5</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D425" s="3" t="s">
         <v>11</v>
@@ -16009,16 +14467,16 @@
         <v>13</v>
       </c>
       <c r="B426" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C426" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C426" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D426" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -16029,7 +14487,7 @@
         <v>69</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D427" s="3" t="s">
         <v>8</v>
@@ -16044,7 +14502,7 @@
         <v>5</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D428" s="2" t="s">
         <v>8</v>
@@ -16059,7 +14517,7 @@
         <v>5</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D429" s="2" t="s">
         <v>11</v>
@@ -16068,7 +14526,7 @@
     </row>
     <row r="430" spans="1:5">
       <c r="A430" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
@@ -16098,7 +14556,7 @@
         <v>5</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D432" s="2" t="s">
         <v>8</v>
@@ -16113,7 +14571,7 @@
         <v>5</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D433" s="2" t="s">
         <v>11</v>
@@ -16128,7 +14586,7 @@
         <v>17</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D434" s="2" t="s">
         <v>11</v>
@@ -16137,7 +14595,7 @@
     </row>
     <row r="435" spans="1:5">
       <c r="A435" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
@@ -16167,7 +14625,7 @@
         <v>5</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D437" s="2" t="s">
         <v>11</v>
@@ -16182,7 +14640,7 @@
         <v>5</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D438" s="2" t="s">
         <v>11</v>
@@ -16221,7 +14679,7 @@
     </row>
     <row r="441" spans="1:5">
       <c r="A441" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
@@ -16236,7 +14694,7 @@
         <v>69</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D442" s="2" t="s">
         <v>11</v>
@@ -16251,7 +14709,7 @@
         <v>5</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D443" s="2" t="s">
         <v>11</v>
@@ -16266,7 +14724,7 @@
         <v>5</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D444" s="2" t="s">
         <v>8</v>
@@ -16281,7 +14739,7 @@
         <v>5</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>11</v>
@@ -16296,7 +14754,7 @@
         <v>5</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D446" s="2" t="s">
         <v>8</v>
@@ -16375,10 +14833,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -16439,7 +14897,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -16479,7 +14937,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -16493,7 +14951,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -16508,13 +14966,13 @@
         <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -16525,13 +14983,13 @@
         <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -16542,7 +15000,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>11</v>
@@ -16554,16 +15012,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -16574,7 +15032,7 @@
         <v>69</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
@@ -16589,7 +15047,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
@@ -16604,7 +15062,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>11</v>
@@ -16617,7 +15075,7 @@
         <v>69</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>11</v>
@@ -16630,7 +15088,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>11</v>
@@ -16639,7 +15097,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -16662,7 +15120,7 @@
     <row r="22" spans="1:5">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -16674,7 +15132,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>8</v>
@@ -16687,7 +15145,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>11</v>
@@ -16713,7 +15171,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>8</v>
@@ -16726,7 +15184,7 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>11</v>
@@ -16748,7 +15206,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -16771,7 +15229,7 @@
     <row r="31" spans="1:5">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -16796,7 +15254,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>11</v>
@@ -16809,7 +15267,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>11</v>
@@ -16848,7 +15306,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>11</v>
@@ -16861,7 +15319,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
@@ -16874,7 +15332,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>11</v>
@@ -16887,7 +15345,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
@@ -16913,7 +15371,7 @@
         <v>69</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
@@ -16926,7 +15384,7 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>8</v>
@@ -16939,7 +15397,7 @@
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>11</v>
@@ -16952,7 +15410,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>11</v>
@@ -16965,7 +15423,7 @@
         <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>11</v>
@@ -16978,7 +15436,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>11</v>
@@ -16991,7 +15449,7 @@
         <v>17</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>11</v>
@@ -17004,7 +15462,7 @@
         <v>17</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>11</v>
@@ -17017,7 +15475,7 @@
         <v>17</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>11</v>
@@ -17030,7 +15488,7 @@
         <v>17</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>11</v>
@@ -17043,7 +15501,7 @@
         <v>17</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>11</v>
@@ -17090,7 +15548,7 @@
         <v>71</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -17146,7 +15604,7 @@
     <row r="6" spans="1:5">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -17154,10 +15612,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -17195,7 +15653,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -17438,7 +15896,7 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>11</v>
@@ -17494,7 +15952,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -17519,7 +15977,7 @@
     <row r="31" spans="1:5">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -17533,7 +15991,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>8</v>
@@ -17548,7 +16006,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>8</v>
@@ -17563,13 +16021,13 @@
         <v>3</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -17580,7 +16038,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>11</v>
@@ -17595,13 +16053,13 @@
         <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -17612,13 +16070,13 @@
         <v>21</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -17629,7 +16087,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
@@ -17646,7 +16104,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>8</v>
@@ -17661,7 +16119,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
@@ -17678,7 +16136,7 @@
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>8</v>
@@ -17693,7 +16151,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
@@ -17710,7 +16168,7 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>8</v>
@@ -17725,7 +16183,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>8</v>
@@ -17742,7 +16200,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>8</v>
@@ -17757,7 +16215,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>8</v>
@@ -17774,7 +16232,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>8</v>
@@ -17789,7 +16247,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>8</v>
@@ -17806,7 +16264,7 @@
         <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>8</v>
@@ -17821,13 +16279,13 @@
         <v>3</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -17838,7 +16296,7 @@
         <v>17</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>11</v>
@@ -17853,7 +16311,7 @@
         <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>8</v>
@@ -17878,7 +16336,7 @@
     <row r="54" spans="1:5">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -17886,7 +16344,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -17911,7 +16369,7 @@
     <row r="57" spans="1:5">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -17955,7 +16413,7 @@
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>11</v>
@@ -17970,7 +16428,7 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>11</v>
@@ -17985,7 +16443,7 @@
         <v>17</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>11</v>
@@ -18000,7 +16458,7 @@
         <v>17</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>11</v>
@@ -18015,7 +16473,7 @@
         <v>17</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>11</v>
@@ -18030,7 +16488,7 @@
         <v>17</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>11</v>
@@ -18045,7 +16503,7 @@
         <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>117</v>
@@ -18079,7 +16537,7 @@
         <v>3</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>8</v>
@@ -18113,7 +16571,7 @@
         <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>11</v>
@@ -18128,7 +16586,7 @@
         <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>8</v>
@@ -18143,7 +16601,7 @@
         <v>17</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>8</v>
@@ -18152,7 +16610,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -18177,7 +16635,7 @@
     <row r="75" spans="1:5">
       <c r="A75" s="2"/>
       <c r="B75" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -18191,7 +16649,7 @@
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>8</v>
@@ -18206,7 +16664,7 @@
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>8</v>
@@ -18221,7 +16679,7 @@
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>8</v>
@@ -18236,13 +16694,13 @@
         <v>21</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -18253,7 +16711,7 @@
         <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>8</v>
@@ -18277,7 +16735,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -18317,7 +16775,7 @@
     <row r="85" spans="1:5">
       <c r="A85" s="2"/>
       <c r="B85" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -18331,7 +16789,7 @@
         <v>5</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>8</v>
@@ -18346,7 +16804,7 @@
         <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>11</v>
@@ -18361,7 +16819,7 @@
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>8</v>
@@ -18376,7 +16834,7 @@
         <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>11</v>
@@ -18391,7 +16849,7 @@
         <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>11</v>
@@ -18406,7 +16864,7 @@
         <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>11</v>
@@ -18421,7 +16879,7 @@
         <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>11</v>
@@ -18461,7 +16919,7 @@
     <row r="95" spans="1:5">
       <c r="A95" s="2"/>
       <c r="B95" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
@@ -18475,7 +16933,7 @@
         <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
@@ -18490,7 +16948,7 @@
         <v>5</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>11</v>
@@ -18502,16 +16960,16 @@
         <v>11</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D98" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -18519,10 +16977,10 @@
         <v>12</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>11</v>
@@ -18537,7 +16995,7 @@
         <v>69</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>11</v>
@@ -18552,7 +17010,7 @@
         <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>11</v>
@@ -18567,7 +17025,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>11</v>
@@ -18582,7 +17040,7 @@
         <v>17</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>11</v>
@@ -18597,7 +17055,7 @@
         <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>11</v>
@@ -18612,7 +17070,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>11</v>
@@ -18627,7 +17085,7 @@
         <v>17</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>11</v>
@@ -18642,7 +17100,7 @@
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>11</v>
@@ -18657,7 +17115,7 @@
         <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>11</v>
@@ -18672,7 +17130,7 @@
         <v>17</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>11</v>
@@ -18687,7 +17145,7 @@
         <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>11</v>
@@ -18702,7 +17160,7 @@
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>11</v>
@@ -18717,7 +17175,7 @@
         <v>17</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>11</v>
@@ -18732,7 +17190,7 @@
         <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>11</v>
@@ -18747,7 +17205,7 @@
         <v>17</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>11</v>
@@ -18762,7 +17220,7 @@
         <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>11</v>
@@ -18777,7 +17235,7 @@
         <v>17</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>11</v>
@@ -18792,7 +17250,7 @@
         <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>11</v>
@@ -18807,7 +17265,7 @@
         <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>11</v>
@@ -18822,7 +17280,7 @@
         <v>17</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>11</v>
@@ -18837,7 +17295,7 @@
         <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>11</v>
@@ -18852,7 +17310,7 @@
         <v>17</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>11</v>
@@ -18867,7 +17325,7 @@
         <v>17</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>11</v>
@@ -18876,10 +17334,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
@@ -18903,7 +17361,7 @@
     <row r="125" spans="1:5">
       <c r="A125" s="2"/>
       <c r="B125" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
@@ -18917,7 +17375,7 @@
         <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>8</v>
@@ -18932,13 +17390,13 @@
         <v>21</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -18949,13 +17407,13 @@
         <v>21</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -18966,7 +17424,7 @@
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>11</v>
@@ -18978,25 +17436,25 @@
         <v>13</v>
       </c>
       <c r="B130" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D130" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2"/>
       <c r="B131" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>11</v>
@@ -19011,7 +17469,7 @@
         <v>69</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>8</v>
@@ -19026,7 +17484,7 @@
         <v>5</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>8</v>
@@ -19041,7 +17499,7 @@
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>11</v>
@@ -19054,7 +17512,7 @@
         <v>69</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>11</v>
@@ -19067,7 +17525,7 @@
         <v>17</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>11</v>
@@ -19076,7 +17534,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -19101,7 +17559,7 @@
     <row r="139" spans="1:5">
       <c r="A139" s="2"/>
       <c r="B139" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -19115,7 +17573,7 @@
         <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>8</v>
@@ -19145,7 +17603,7 @@
         <v>5</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>8</v>
@@ -19160,7 +17618,7 @@
         <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>11</v>
@@ -19184,7 +17642,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -19209,7 +17667,7 @@
     <row r="147" spans="1:5">
       <c r="A147" s="2"/>
       <c r="B147" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
@@ -19238,7 +17696,7 @@
         <v>5</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>11</v>
@@ -19253,7 +17711,7 @@
         <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>11</v>
@@ -19298,7 +17756,7 @@
         <v>5</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>11</v>
@@ -19313,7 +17771,7 @@
         <v>5</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>8</v>
@@ -19328,7 +17786,7 @@
         <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>11</v>
@@ -19343,7 +17801,7 @@
         <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>8</v>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3289" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3583" uniqueCount="274">
   <si>
     <t>Keyword</t>
   </si>
@@ -403,6 +403,9 @@
   </si>
   <si>
     <t>Edit And Update Challan</t>
+  </si>
+  <si>
+    <t>Delete Single Challan</t>
   </si>
   <si>
     <t>singlechallanselect</t>
@@ -1309,7 +1312,7 @@
         <v>71</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1367,7 +1370,7 @@
         <v>70</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -2584,7 +2587,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.5703125" customWidth="1"/>
@@ -2613,10 +2616,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2683,6 +2686,1545 @@
         <v>11</v>
       </c>
       <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2">
+        <v>12122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2311323</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="2">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="2">
+        <v>30</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="6">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="6">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="6">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="7"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="7"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="6">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="6">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="7"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="6">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="7"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="6">
+        <v>22343244410021</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E56" s="8">
+        <v>44594</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="6">
+        <v>3234</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="9">
+        <v>13234</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="2"/>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="2">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="6">
+        <v>7826423</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="2">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="2">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" s="2">
+        <v>3478323</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="2"/>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="2">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="2">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B80" s="3"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="2">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="2">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="2">
+        <v>84</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="2">
+        <v>86</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="2">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="6">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="2">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" s="2">
+        <v>3478323</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="2">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="2"/>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="2">
+        <v>96</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="2"/>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="2">
+        <v>97</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="2">
+        <v>98</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="2"/>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="2">
+        <v>99</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="2"/>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="2">
+        <v>100</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="2"/>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="2">
+        <v>101</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="2"/>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="2">
+        <v>102</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="2"/>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="2">
+        <v>103</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="2"/>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="2">
+        <v>104</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2722,10 +4264,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2786,7 +4328,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -2826,7 +4368,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -2840,7 +4382,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -2855,7 +4397,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
@@ -2870,18 +4412,18 @@
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2896,7 +4438,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
@@ -2906,7 +4448,7 @@
     <row r="15" spans="1:5">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -2920,7 +4462,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
@@ -2935,13 +4477,13 @@
         <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2958,7 +4500,7 @@
         <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2969,13 +4511,13 @@
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2986,7 +4528,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -3003,13 +4545,13 @@
         <v>3</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3020,13 +4562,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3037,13 +4579,13 @@
         <v>21</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3054,7 +4596,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>8</v>
@@ -3084,7 +4626,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
@@ -3099,13 +4641,13 @@
         <v>3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3133,13 +4675,13 @@
         <v>21</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3150,7 +4692,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>8</v>
@@ -3174,7 +4716,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3199,7 +4741,7 @@
     <row r="34" spans="1:5">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -3213,7 +4755,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>8</v>
@@ -3228,7 +4770,7 @@
         <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>8</v>
@@ -3243,13 +4785,13 @@
         <v>3</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3260,7 +4802,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>11</v>
@@ -3275,7 +4817,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>8</v>
@@ -3329,7 +4871,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -3344,13 +4886,13 @@
         <v>21</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -3361,13 +4903,13 @@
         <v>21</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -3378,7 +4920,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>8</v>
@@ -3395,7 +4937,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>8</v>
@@ -3410,7 +4952,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>8</v>
@@ -3427,7 +4969,7 @@
         <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>8</v>
@@ -3442,7 +4984,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>8</v>
@@ -3459,7 +5001,7 @@
         <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>8</v>
@@ -3474,7 +5016,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>8</v>
@@ -3491,7 +5033,7 @@
         <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>8</v>
@@ -3506,7 +5048,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>8</v>
@@ -3523,7 +5065,7 @@
         <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>8</v>
@@ -3538,7 +5080,7 @@
         <v>3</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>8</v>
@@ -3555,7 +5097,7 @@
         <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>8</v>
@@ -3570,13 +5112,13 @@
         <v>3</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3587,7 +5129,7 @@
         <v>17</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>11</v>
@@ -3602,7 +5144,7 @@
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>8</v>
@@ -3626,7 +5168,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3641,13 +5183,13 @@
         <v>3</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3658,7 +5200,7 @@
         <v>69</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>11</v>
@@ -3673,7 +5215,7 @@
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>11</v>
@@ -3688,13 +5230,13 @@
         <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3705,7 +5247,7 @@
         <v>3</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>8</v>
@@ -3722,7 +5264,7 @@
         <v>5</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>8</v>
@@ -3748,13 +5290,13 @@
         <v>21</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3765,7 +5307,7 @@
         <v>3</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>8</v>
@@ -3797,7 +5339,7 @@
         <v>17</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>11</v>
@@ -3812,13 +5354,13 @@
         <v>21</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3829,7 +5371,7 @@
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>8</v>
@@ -3844,7 +5386,7 @@
         <v>3</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>8</v>
@@ -3876,7 +5418,7 @@
         <v>17</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>11</v>
@@ -3891,7 +5433,7 @@
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>8</v>
@@ -3906,7 +5448,7 @@
         <v>3</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>8</v>
@@ -3938,7 +5480,7 @@
         <v>17</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>11</v>
@@ -3953,7 +5495,7 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>8</v>
@@ -3968,7 +5510,7 @@
         <v>3</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>8</v>
@@ -4000,7 +5542,7 @@
         <v>17</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>11</v>
@@ -4015,7 +5557,7 @@
         <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>8</v>
@@ -4030,7 +5572,7 @@
         <v>3</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>8</v>
@@ -4062,7 +5604,7 @@
         <v>17</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>11</v>
@@ -4077,7 +5619,7 @@
         <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>8</v>
@@ -4092,7 +5634,7 @@
         <v>3</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>8</v>
@@ -4124,7 +5666,7 @@
         <v>17</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>11</v>
@@ -4139,7 +5681,7 @@
         <v>3</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>8</v>
@@ -4156,7 +5698,7 @@
         <v>3</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>8</v>
@@ -4203,7 +5745,7 @@
         <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>8</v>
@@ -4218,7 +5760,7 @@
         <v>5</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>11</v>
@@ -4233,7 +5775,7 @@
         <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>8</v>
@@ -4257,7 +5799,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>8</v>
@@ -4272,13 +5814,13 @@
         <v>3</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -4289,7 +5831,7 @@
         <v>69</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>11</v>
@@ -4304,7 +5846,7 @@
         <v>5</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>11</v>
@@ -4319,13 +5861,13 @@
         <v>21</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -4336,7 +5878,7 @@
         <v>3</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>8</v>
@@ -4353,13 +5895,13 @@
         <v>21</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -4370,13 +5912,13 @@
         <v>3</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -4387,7 +5929,7 @@
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>8</v>
@@ -4411,7 +5953,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -4436,7 +5978,7 @@
     <row r="115" spans="1:5">
       <c r="A115" s="2"/>
       <c r="B115" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
@@ -4480,7 +6022,7 @@
         <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>11</v>
@@ -4495,7 +6037,7 @@
         <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>11</v>
@@ -4510,7 +6052,7 @@
         <v>17</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>11</v>
@@ -4525,7 +6067,7 @@
         <v>17</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>11</v>
@@ -4540,7 +6082,7 @@
         <v>17</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>11</v>
@@ -4555,7 +6097,7 @@
         <v>17</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>11</v>
@@ -4570,7 +6112,7 @@
         <v>21</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>117</v>
@@ -4604,7 +6146,7 @@
         <v>3</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>8</v>
@@ -4638,7 +6180,7 @@
         <v>5</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>11</v>
@@ -4653,7 +6195,7 @@
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>8</v>
@@ -4668,7 +6210,7 @@
         <v>17</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>8</v>
@@ -4677,7 +6219,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -4702,7 +6244,7 @@
     <row r="133" spans="1:5">
       <c r="A133" s="2"/>
       <c r="B133" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -4716,7 +6258,7 @@
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>8</v>
@@ -4731,7 +6273,7 @@
         <v>5</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>8</v>
@@ -4746,7 +6288,7 @@
         <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>8</v>
@@ -4761,13 +6303,13 @@
         <v>21</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -4778,7 +6320,7 @@
         <v>5</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>8</v>
@@ -4802,7 +6344,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -4827,7 +6369,7 @@
     <row r="142" spans="1:5">
       <c r="A142" s="2"/>
       <c r="B142" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
@@ -4841,7 +6383,7 @@
         <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>8</v>
@@ -4856,7 +6398,7 @@
         <v>5</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>11</v>
@@ -4871,7 +6413,7 @@
         <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>8</v>
@@ -4886,7 +6428,7 @@
         <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>11</v>
@@ -4910,7 +6452,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -4940,7 +6482,7 @@
         <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>8</v>
@@ -4955,7 +6497,7 @@
         <v>5</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>11</v>
@@ -4970,7 +6512,7 @@
         <v>17</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>11</v>
@@ -4979,7 +6521,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -5009,7 +6551,7 @@
         <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>11</v>
@@ -5024,7 +6566,7 @@
         <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>11</v>
@@ -5063,7 +6605,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -5078,7 +6620,7 @@
         <v>69</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>11</v>
@@ -5093,7 +6635,7 @@
         <v>5</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>11</v>
@@ -5108,7 +6650,7 @@
         <v>5</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>8</v>
@@ -5123,7 +6665,7 @@
         <v>5</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>11</v>
@@ -5138,7 +6680,7 @@
         <v>5</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>8</v>
@@ -5216,10 +6758,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -5305,7 +6847,7 @@
     <row r="8" spans="1:5">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -5343,7 +6885,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -5617,7 +7159,7 @@
     <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -5631,7 +7173,7 @@
         <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>8</v>
@@ -5646,7 +7188,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>8</v>
@@ -5661,18 +7203,18 @@
         <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -5687,7 +7229,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>8</v>
@@ -5702,7 +7244,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>8</v>
@@ -5717,13 +7259,13 @@
         <v>3</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -5740,7 +7282,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -5751,13 +7293,13 @@
         <v>3</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -5768,7 +7310,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
@@ -5785,13 +7327,13 @@
         <v>3</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -5802,13 +7344,13 @@
         <v>3</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -5819,13 +7361,13 @@
         <v>21</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -5836,7 +7378,7 @@
         <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
@@ -5876,7 +7418,7 @@
     <row r="45" spans="1:5">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -5890,7 +7432,7 @@
         <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>8</v>
@@ -5905,7 +7447,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>8</v>
@@ -5920,13 +7462,13 @@
         <v>3</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -5937,7 +7479,7 @@
         <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>11</v>
@@ -5952,13 +7494,13 @@
         <v>21</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -5969,13 +7511,13 @@
         <v>21</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -5986,7 +7528,7 @@
         <v>3</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>8</v>
@@ -6003,7 +7545,7 @@
         <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>8</v>
@@ -6018,7 +7560,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>8</v>
@@ -6035,7 +7577,7 @@
         <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>8</v>
@@ -6050,7 +7592,7 @@
         <v>3</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>8</v>
@@ -6067,7 +7609,7 @@
         <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>8</v>
@@ -6082,7 +7624,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>8</v>
@@ -6099,7 +7641,7 @@
         <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>8</v>
@@ -6114,7 +7656,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>8</v>
@@ -6131,7 +7673,7 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>8</v>
@@ -6146,7 +7688,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>8</v>
@@ -6163,13 +7705,13 @@
         <v>3</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -6180,7 +7722,7 @@
         <v>17</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>11</v>
@@ -6195,7 +7737,7 @@
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>8</v>
@@ -6219,7 +7761,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -6259,7 +7801,7 @@
     <row r="70" spans="1:5">
       <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -6273,7 +7815,7 @@
         <v>5</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>8</v>
@@ -6288,7 +7830,7 @@
         <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>11</v>
@@ -6303,7 +7845,7 @@
         <v>5</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>8</v>
@@ -6318,7 +7860,7 @@
         <v>5</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>11</v>
@@ -6333,7 +7875,7 @@
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>11</v>
@@ -6348,7 +7890,7 @@
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>11</v>
@@ -6363,7 +7905,7 @@
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>11</v>
@@ -6372,7 +7914,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -6397,7 +7939,7 @@
     <row r="80" spans="1:5">
       <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -6411,7 +7953,7 @@
         <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>8</v>
@@ -6441,7 +7983,7 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>8</v>
@@ -6456,7 +7998,7 @@
         <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>11</v>
@@ -6486,7 +8028,7 @@
         <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>8</v>
@@ -6501,13 +8043,13 @@
         <v>3</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -6518,7 +8060,7 @@
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>11</v>
@@ -6533,7 +8075,7 @@
         <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>8</v>
@@ -6548,7 +8090,7 @@
         <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>11</v>
@@ -6563,13 +8105,13 @@
         <v>21</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -6580,7 +8122,7 @@
         <v>21</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>8</v>
@@ -6595,7 +8137,7 @@
         <v>3</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>8</v>
@@ -6612,7 +8154,7 @@
         <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>8</v>
@@ -6627,7 +8169,7 @@
         <v>3</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>8</v>
@@ -6644,7 +8186,7 @@
         <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>8</v>
@@ -6684,7 +8226,7 @@
     <row r="99" spans="1:5">
       <c r="A99" s="2"/>
       <c r="B99" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -6698,7 +8240,7 @@
         <v>5</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>8</v>
@@ -6713,7 +8255,7 @@
         <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>11</v>
@@ -6728,7 +8270,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>11</v>
@@ -6743,7 +8285,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>11</v>
@@ -6752,7 +8294,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -6777,7 +8319,7 @@
     <row r="106" spans="1:5">
       <c r="A106" s="2"/>
       <c r="B106" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -6791,7 +8333,7 @@
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>8</v>
@@ -6821,7 +8363,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>8</v>
@@ -6836,7 +8378,7 @@
         <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>11</v>
@@ -6860,7 +8402,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -6885,7 +8427,7 @@
     <row r="114" spans="1:5">
       <c r="A114" s="2"/>
       <c r="B114" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
@@ -6914,7 +8456,7 @@
         <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>11</v>
@@ -6929,7 +8471,7 @@
         <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>11</v>
@@ -6974,7 +8516,7 @@
         <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>11</v>
@@ -6989,7 +8531,7 @@
         <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>8</v>
@@ -7004,7 +8546,7 @@
         <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>11</v>
@@ -7019,7 +8561,7 @@
         <v>5</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>8</v>
@@ -7081,10 +8623,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -7145,7 +8687,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -7185,7 +8727,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -7199,7 +8741,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>8</v>
@@ -7214,7 +8756,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>11</v>
@@ -7226,16 +8768,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7246,7 +8788,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>8</v>
@@ -7261,7 +8803,7 @@
         <v>69</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
@@ -7276,7 +8818,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>11</v>
@@ -7291,7 +8833,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>11</v>
@@ -7306,7 +8848,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>11</v>
@@ -7321,7 +8863,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>11</v>
@@ -7336,7 +8878,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>11</v>
@@ -7351,7 +8893,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>11</v>
@@ -7366,7 +8908,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>11</v>
@@ -7381,7 +8923,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>11</v>
@@ -7396,7 +8938,7 @@
         <v>17</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>11</v>
@@ -7411,7 +8953,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>11</v>
@@ -7426,7 +8968,7 @@
         <v>5</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>11</v>
@@ -7441,7 +8983,7 @@
         <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>11</v>
@@ -7456,7 +8998,7 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>11</v>
@@ -7471,7 +9013,7 @@
         <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>11</v>
@@ -7486,7 +9028,7 @@
         <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>11</v>
@@ -7501,7 +9043,7 @@
         <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>11</v>
@@ -7516,7 +9058,7 @@
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>11</v>
@@ -7531,7 +9073,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>11</v>
@@ -7546,7 +9088,7 @@
         <v>17</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>11</v>
@@ -7561,7 +9103,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>11</v>
@@ -7576,7 +9118,7 @@
         <v>17</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>11</v>
@@ -7591,7 +9133,7 @@
         <v>17</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>11</v>
@@ -7631,7 +9173,7 @@
     <row r="39" spans="1:5">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -7645,7 +9187,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
@@ -7660,7 +9202,7 @@
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>11</v>
@@ -7669,7 +9211,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -7699,7 +9241,7 @@
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>8</v>
@@ -7714,7 +9256,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>11</v>
@@ -7738,7 +9280,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -7768,7 +9310,7 @@
         <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>11</v>
@@ -7783,7 +9325,7 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>11</v>
@@ -7822,7 +9364,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -7837,7 +9379,7 @@
         <v>69</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>11</v>
@@ -7852,7 +9394,7 @@
         <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>11</v>
@@ -7867,7 +9409,7 @@
         <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>8</v>
@@ -7882,7 +9424,7 @@
         <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>11</v>
@@ -7897,7 +9439,7 @@
         <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>8</v>
@@ -7973,7 +9515,7 @@
         <v>71</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -9115,10 +10657,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -9317,7 +10859,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -9519,7 +11061,7 @@
         <v>17</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>11</v>
@@ -9966,7 +11508,7 @@
         <v>3</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>117</v>
@@ -10291,7 +11833,7 @@
         <v>5</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>11</v>
@@ -10556,7 +12098,7 @@
         <v>5</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>11</v>
@@ -10565,10 +12107,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
@@ -10629,7 +12171,7 @@
         <v>5</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>11</v>
@@ -10674,7 +12216,7 @@
         <v>5</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>8</v>
@@ -10689,7 +12231,7 @@
         <v>5</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>8</v>
@@ -10704,18 +12246,18 @@
         <v>3</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -10730,7 +12272,7 @@
         <v>5</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>8</v>
@@ -10745,7 +12287,7 @@
         <v>5</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>8</v>
@@ -10760,13 +12302,13 @@
         <v>3</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -10783,7 +12325,7 @@
         <v>11</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -10794,13 +12336,13 @@
         <v>3</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -10811,7 +12353,7 @@
         <v>3</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>8</v>
@@ -10828,13 +12370,13 @@
         <v>3</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -10845,13 +12387,13 @@
         <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -10862,13 +12404,13 @@
         <v>21</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -10879,7 +12421,7 @@
         <v>5</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>8</v>
@@ -10909,7 +12451,7 @@
         <v>5</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>8</v>
@@ -10924,13 +12466,13 @@
         <v>3</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -10958,13 +12500,13 @@
         <v>21</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -10975,7 +12517,7 @@
         <v>5</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>8</v>
@@ -10999,7 +12541,7 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -11029,7 +12571,7 @@
         <v>5</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>8</v>
@@ -11044,7 +12586,7 @@
         <v>5</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>8</v>
@@ -11059,13 +12601,13 @@
         <v>3</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -11076,7 +12618,7 @@
         <v>5</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>11</v>
@@ -11091,7 +12633,7 @@
         <v>5</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>8</v>
@@ -11145,7 +12687,7 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -11160,13 +12702,13 @@
         <v>21</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -11177,13 +12719,13 @@
         <v>21</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -11194,7 +12736,7 @@
         <v>3</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>8</v>
@@ -11211,7 +12753,7 @@
         <v>5</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>8</v>
@@ -11226,7 +12768,7 @@
         <v>3</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>8</v>
@@ -11243,7 +12785,7 @@
         <v>5</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>8</v>
@@ -11258,7 +12800,7 @@
         <v>3</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>8</v>
@@ -11275,7 +12817,7 @@
         <v>5</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>8</v>
@@ -11290,7 +12832,7 @@
         <v>3</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>8</v>
@@ -11307,7 +12849,7 @@
         <v>5</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>8</v>
@@ -11322,7 +12864,7 @@
         <v>3</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>8</v>
@@ -11339,7 +12881,7 @@
         <v>5</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>8</v>
@@ -11354,7 +12896,7 @@
         <v>3</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>8</v>
@@ -11371,7 +12913,7 @@
         <v>5</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>8</v>
@@ -11386,13 +12928,13 @@
         <v>3</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -11403,7 +12945,7 @@
         <v>17</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>11</v>
@@ -11418,7 +12960,7 @@
         <v>5</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>8</v>
@@ -11442,7 +12984,7 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -11457,13 +12999,13 @@
         <v>3</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -11474,7 +13016,7 @@
         <v>69</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>11</v>
@@ -11489,7 +13031,7 @@
         <v>5</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>11</v>
@@ -11504,13 +13046,13 @@
         <v>21</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E232" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -11521,7 +13063,7 @@
         <v>3</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>8</v>
@@ -11538,7 +13080,7 @@
         <v>5</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>8</v>
@@ -11564,13 +13106,13 @@
         <v>21</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -11581,7 +13123,7 @@
         <v>3</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>8</v>
@@ -11613,7 +13155,7 @@
         <v>17</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>11</v>
@@ -11628,13 +13170,13 @@
         <v>21</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -11645,7 +13187,7 @@
         <v>5</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>8</v>
@@ -11660,7 +13202,7 @@
         <v>3</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>8</v>
@@ -11692,7 +13234,7 @@
         <v>17</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>11</v>
@@ -11707,7 +13249,7 @@
         <v>5</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>8</v>
@@ -11722,7 +13264,7 @@
         <v>3</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>8</v>
@@ -11754,7 +13296,7 @@
         <v>17</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>11</v>
@@ -11769,7 +13311,7 @@
         <v>5</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>8</v>
@@ -11784,7 +13326,7 @@
         <v>3</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>8</v>
@@ -11816,7 +13358,7 @@
         <v>17</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>11</v>
@@ -11831,7 +13373,7 @@
         <v>5</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>8</v>
@@ -11846,7 +13388,7 @@
         <v>3</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>8</v>
@@ -11878,7 +13420,7 @@
         <v>17</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>11</v>
@@ -11893,7 +13435,7 @@
         <v>5</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>8</v>
@@ -11908,7 +13450,7 @@
         <v>3</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>8</v>
@@ -11940,7 +13482,7 @@
         <v>17</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>11</v>
@@ -11955,7 +13497,7 @@
         <v>3</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>8</v>
@@ -11972,7 +13514,7 @@
         <v>3</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>8</v>
@@ -12019,7 +13561,7 @@
         <v>5</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>8</v>
@@ -12034,7 +13576,7 @@
         <v>5</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>11</v>
@@ -12049,7 +13591,7 @@
         <v>5</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>8</v>
@@ -12073,7 +13615,7 @@
         <v>5</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>8</v>
@@ -12088,13 +13630,13 @@
         <v>3</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -12105,7 +13647,7 @@
         <v>69</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>11</v>
@@ -12120,7 +13662,7 @@
         <v>5</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>11</v>
@@ -12135,13 +13677,13 @@
         <v>21</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -12152,7 +13694,7 @@
         <v>3</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>8</v>
@@ -12169,13 +13711,13 @@
         <v>21</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -12186,13 +13728,13 @@
         <v>3</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -12203,7 +13745,7 @@
         <v>5</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>8</v>
@@ -12227,7 +13769,7 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -12287,7 +13829,7 @@
         <v>5</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>11</v>
@@ -12302,7 +13844,7 @@
         <v>5</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>11</v>
@@ -12317,7 +13859,7 @@
         <v>17</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>11</v>
@@ -12332,7 +13874,7 @@
         <v>17</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>11</v>
@@ -12347,7 +13889,7 @@
         <v>17</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>11</v>
@@ -12362,7 +13904,7 @@
         <v>17</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>11</v>
@@ -12377,7 +13919,7 @@
         <v>21</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>117</v>
@@ -12445,7 +13987,7 @@
         <v>5</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>11</v>
@@ -12460,7 +14002,7 @@
         <v>5</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>8</v>
@@ -12475,7 +14017,7 @@
         <v>17</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>8</v>
@@ -12484,7 +14026,7 @@
     </row>
     <row r="296" spans="1:5">
       <c r="A296" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -12514,7 +14056,7 @@
         <v>5</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>8</v>
@@ -12529,7 +14071,7 @@
         <v>5</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>8</v>
@@ -12544,7 +14086,7 @@
         <v>5</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>8</v>
@@ -12559,13 +14101,13 @@
         <v>21</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E301" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -12576,7 +14118,7 @@
         <v>5</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>8</v>
@@ -12600,10 +14142,10 @@
     </row>
     <row r="304" spans="1:5">
       <c r="A304" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" s="2"/>
@@ -12718,7 +14260,7 @@
     </row>
     <row r="312" spans="1:5">
       <c r="A312" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -12997,7 +14539,7 @@
         <v>5</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>8</v>
@@ -13012,7 +14554,7 @@
         <v>5</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>8</v>
@@ -13027,18 +14569,18 @@
         <v>3</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="332" spans="1:5">
       <c r="A332" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B332" s="2"/>
       <c r="C332" s="2"/>
@@ -13053,7 +14595,7 @@
         <v>5</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>8</v>
@@ -13068,7 +14610,7 @@
         <v>5</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>8</v>
@@ -13083,13 +14625,13 @@
         <v>3</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -13106,7 +14648,7 @@
         <v>11</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -13117,13 +14659,13 @@
         <v>3</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -13134,7 +14676,7 @@
         <v>3</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>8</v>
@@ -13151,13 +14693,13 @@
         <v>3</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -13168,13 +14710,13 @@
         <v>3</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -13185,13 +14727,13 @@
         <v>21</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E341" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -13202,7 +14744,7 @@
         <v>5</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>8</v>
@@ -13247,7 +14789,7 @@
         <v>5</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>8</v>
@@ -13262,7 +14804,7 @@
         <v>5</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>8</v>
@@ -13277,13 +14819,13 @@
         <v>3</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -13294,7 +14836,7 @@
         <v>5</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>11</v>
@@ -13309,13 +14851,13 @@
         <v>21</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E349" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -13326,13 +14868,13 @@
         <v>21</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D350" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E350" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -13343,7 +14885,7 @@
         <v>3</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D351" s="2" t="s">
         <v>8</v>
@@ -13360,7 +14902,7 @@
         <v>5</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D352" s="2" t="s">
         <v>8</v>
@@ -13375,7 +14917,7 @@
         <v>3</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D353" s="2" t="s">
         <v>8</v>
@@ -13392,7 +14934,7 @@
         <v>5</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D354" s="2" t="s">
         <v>8</v>
@@ -13407,7 +14949,7 @@
         <v>3</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D355" s="2" t="s">
         <v>8</v>
@@ -13424,7 +14966,7 @@
         <v>5</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>8</v>
@@ -13439,7 +14981,7 @@
         <v>3</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>8</v>
@@ -13456,7 +14998,7 @@
         <v>5</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>8</v>
@@ -13471,7 +15013,7 @@
         <v>3</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D359" s="2" t="s">
         <v>8</v>
@@ -13488,7 +15030,7 @@
         <v>5</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>8</v>
@@ -13503,7 +15045,7 @@
         <v>3</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>8</v>
@@ -13520,13 +15062,13 @@
         <v>3</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -13537,7 +15079,7 @@
         <v>17</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>11</v>
@@ -13552,7 +15094,7 @@
         <v>5</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>8</v>
@@ -13576,7 +15118,7 @@
     </row>
     <row r="366" spans="1:5">
       <c r="A366" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
@@ -13621,7 +15163,7 @@
         <v>5</v>
       </c>
       <c r="C369" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D369" s="2" t="s">
         <v>8</v>
@@ -13636,7 +15178,7 @@
         <v>5</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D370" s="2" t="s">
         <v>11</v>
@@ -13651,7 +15193,7 @@
         <v>5</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D371" s="2" t="s">
         <v>8</v>
@@ -13666,7 +15208,7 @@
         <v>5</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D372" s="2" t="s">
         <v>11</v>
@@ -13681,7 +15223,7 @@
         <v>5</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>11</v>
@@ -13696,7 +15238,7 @@
         <v>5</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>11</v>
@@ -13711,7 +15253,7 @@
         <v>5</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D375" s="2" t="s">
         <v>11</v>
@@ -13720,10 +15262,10 @@
     </row>
     <row r="376" spans="1:5">
       <c r="A376" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C376" s="2"/>
       <c r="D376" s="2"/>
@@ -13784,7 +15326,7 @@
         <v>5</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D380" s="2" t="s">
         <v>11</v>
@@ -13829,7 +15371,7 @@
         <v>5</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D383" s="3" t="s">
         <v>8</v>
@@ -13844,7 +15386,7 @@
         <v>5</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D384" s="3" t="s">
         <v>11</v>
@@ -13856,16 +15398,16 @@
         <v>11</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D385" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -13876,7 +15418,7 @@
         <v>5</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D386" s="3" t="s">
         <v>8</v>
@@ -13891,7 +15433,7 @@
         <v>69</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D387" s="2" t="s">
         <v>11</v>
@@ -13906,7 +15448,7 @@
         <v>5</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D388" s="2" t="s">
         <v>11</v>
@@ -13921,7 +15463,7 @@
         <v>5</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D389" s="3" t="s">
         <v>11</v>
@@ -13936,7 +15478,7 @@
         <v>17</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D390" s="3" t="s">
         <v>11</v>
@@ -13951,7 +15493,7 @@
         <v>5</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D391" s="3" t="s">
         <v>11</v>
@@ -13966,7 +15508,7 @@
         <v>5</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D392" s="3" t="s">
         <v>11</v>
@@ -13981,7 +15523,7 @@
         <v>17</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D393" s="3" t="s">
         <v>11</v>
@@ -13996,7 +15538,7 @@
         <v>5</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D394" s="3" t="s">
         <v>11</v>
@@ -14011,7 +15553,7 @@
         <v>5</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D395" s="3" t="s">
         <v>11</v>
@@ -14026,7 +15568,7 @@
         <v>17</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D396" s="3" t="s">
         <v>11</v>
@@ -14041,7 +15583,7 @@
         <v>5</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D397" s="3" t="s">
         <v>11</v>
@@ -14056,7 +15598,7 @@
         <v>5</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D398" s="3" t="s">
         <v>11</v>
@@ -14071,7 +15613,7 @@
         <v>17</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>11</v>
@@ -14086,7 +15628,7 @@
         <v>5</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D400" s="3" t="s">
         <v>11</v>
@@ -14101,7 +15643,7 @@
         <v>17</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D401" s="3" t="s">
         <v>11</v>
@@ -14116,7 +15658,7 @@
         <v>5</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D402" s="3" t="s">
         <v>11</v>
@@ -14131,7 +15673,7 @@
         <v>17</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D403" s="3" t="s">
         <v>11</v>
@@ -14146,7 +15688,7 @@
         <v>5</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D404" s="3" t="s">
         <v>11</v>
@@ -14161,7 +15703,7 @@
         <v>5</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D405" s="3" t="s">
         <v>11</v>
@@ -14176,7 +15718,7 @@
         <v>17</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D406" s="2" t="s">
         <v>11</v>
@@ -14191,7 +15733,7 @@
         <v>5</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D407" s="3" t="s">
         <v>11</v>
@@ -14206,7 +15748,7 @@
         <v>17</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D408" s="3" t="s">
         <v>11</v>
@@ -14221,7 +15763,7 @@
         <v>17</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D409" s="3" t="s">
         <v>11</v>
@@ -14266,7 +15808,7 @@
         <v>5</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D412" s="2" t="s">
         <v>8</v>
@@ -14281,7 +15823,7 @@
         <v>5</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D413" s="2" t="s">
         <v>11</v>
@@ -14297,10 +15839,10 @@
     </row>
     <row r="415" spans="1:5">
       <c r="A415" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C415" s="2"/>
       <c r="D415" s="2"/>
@@ -14361,7 +15903,7 @@
         <v>5</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D419" s="2" t="s">
         <v>11</v>
@@ -14406,7 +15948,7 @@
         <v>5</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D422" s="3" t="s">
         <v>8</v>
@@ -14421,13 +15963,13 @@
         <v>21</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D423" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E423" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -14438,13 +15980,13 @@
         <v>21</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D424" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E424" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -14455,7 +15997,7 @@
         <v>5</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D425" s="3" t="s">
         <v>11</v>
@@ -14467,16 +16009,16 @@
         <v>13</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D426" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -14487,7 +16029,7 @@
         <v>69</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D427" s="3" t="s">
         <v>8</v>
@@ -14502,7 +16044,7 @@
         <v>5</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D428" s="2" t="s">
         <v>8</v>
@@ -14517,7 +16059,7 @@
         <v>5</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D429" s="2" t="s">
         <v>11</v>
@@ -14526,7 +16068,7 @@
     </row>
     <row r="430" spans="1:5">
       <c r="A430" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
@@ -14556,7 +16098,7 @@
         <v>5</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D432" s="2" t="s">
         <v>8</v>
@@ -14571,7 +16113,7 @@
         <v>5</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D433" s="2" t="s">
         <v>11</v>
@@ -14586,7 +16128,7 @@
         <v>17</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D434" s="2" t="s">
         <v>11</v>
@@ -14595,7 +16137,7 @@
     </row>
     <row r="435" spans="1:5">
       <c r="A435" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
@@ -14625,7 +16167,7 @@
         <v>5</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D437" s="2" t="s">
         <v>11</v>
@@ -14640,7 +16182,7 @@
         <v>5</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D438" s="2" t="s">
         <v>11</v>
@@ -14679,7 +16221,7 @@
     </row>
     <row r="441" spans="1:5">
       <c r="A441" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
@@ -14694,7 +16236,7 @@
         <v>69</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D442" s="2" t="s">
         <v>11</v>
@@ -14709,7 +16251,7 @@
         <v>5</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D443" s="2" t="s">
         <v>11</v>
@@ -14724,7 +16266,7 @@
         <v>5</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D444" s="2" t="s">
         <v>8</v>
@@ -14739,7 +16281,7 @@
         <v>5</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>11</v>
@@ -14754,7 +16296,7 @@
         <v>5</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D446" s="2" t="s">
         <v>8</v>
@@ -14833,10 +16375,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -14897,7 +16439,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -14937,7 +16479,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -14951,7 +16493,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -14966,13 +16508,13 @@
         <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -14983,13 +16525,13 @@
         <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -15000,7 +16542,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>11</v>
@@ -15012,16 +16554,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -15032,7 +16574,7 @@
         <v>69</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
@@ -15047,7 +16589,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
@@ -15062,7 +16604,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>11</v>
@@ -15075,7 +16617,7 @@
         <v>69</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>11</v>
@@ -15088,7 +16630,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>11</v>
@@ -15097,7 +16639,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -15120,7 +16662,7 @@
     <row r="22" spans="1:5">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -15132,7 +16674,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>8</v>
@@ -15145,7 +16687,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>11</v>
@@ -15171,7 +16713,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>8</v>
@@ -15184,7 +16726,7 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>11</v>
@@ -15206,7 +16748,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -15229,7 +16771,7 @@
     <row r="31" spans="1:5">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -15254,7 +16796,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>11</v>
@@ -15267,7 +16809,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>11</v>
@@ -15306,7 +16848,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>11</v>
@@ -15319,7 +16861,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
@@ -15332,7 +16874,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>11</v>
@@ -15345,7 +16887,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
@@ -15371,7 +16913,7 @@
         <v>69</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
@@ -15384,7 +16926,7 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>8</v>
@@ -15397,7 +16939,7 @@
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>11</v>
@@ -15410,7 +16952,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>11</v>
@@ -15423,7 +16965,7 @@
         <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>11</v>
@@ -15436,7 +16978,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>11</v>
@@ -15449,7 +16991,7 @@
         <v>17</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>11</v>
@@ -15462,7 +17004,7 @@
         <v>17</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>11</v>
@@ -15475,7 +17017,7 @@
         <v>17</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>11</v>
@@ -15488,7 +17030,7 @@
         <v>17</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>11</v>
@@ -15501,7 +17043,7 @@
         <v>17</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>11</v>
@@ -15548,7 +17090,7 @@
         <v>71</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -15604,7 +17146,7 @@
     <row r="6" spans="1:5">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -15612,10 +17154,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -15653,7 +17195,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -15896,7 +17438,7 @@
         <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>11</v>
@@ -15952,7 +17494,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -15977,7 +17519,7 @@
     <row r="31" spans="1:5">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -15991,7 +17533,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>8</v>
@@ -16006,7 +17548,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>8</v>
@@ -16021,13 +17563,13 @@
         <v>3</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -16038,7 +17580,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>11</v>
@@ -16053,13 +17595,13 @@
         <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -16070,13 +17612,13 @@
         <v>21</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -16087,7 +17629,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
@@ -16104,7 +17646,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>8</v>
@@ -16119,7 +17661,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
@@ -16136,7 +17678,7 @@
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>8</v>
@@ -16151,7 +17693,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
@@ -16168,7 +17710,7 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>8</v>
@@ -16183,7 +17725,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>8</v>
@@ -16200,7 +17742,7 @@
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>8</v>
@@ -16215,7 +17757,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>8</v>
@@ -16232,7 +17774,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>8</v>
@@ -16247,7 +17789,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>8</v>
@@ -16264,7 +17806,7 @@
         <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>8</v>
@@ -16279,13 +17821,13 @@
         <v>3</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -16296,7 +17838,7 @@
         <v>17</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>11</v>
@@ -16311,7 +17853,7 @@
         <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>8</v>
@@ -16336,7 +17878,7 @@
     <row r="54" spans="1:5">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -16344,7 +17886,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -16369,7 +17911,7 @@
     <row r="57" spans="1:5">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -16413,7 +17955,7 @@
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>11</v>
@@ -16428,7 +17970,7 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>11</v>
@@ -16443,7 +17985,7 @@
         <v>17</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>11</v>
@@ -16458,7 +18000,7 @@
         <v>17</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>11</v>
@@ -16473,7 +18015,7 @@
         <v>17</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>11</v>
@@ -16488,7 +18030,7 @@
         <v>17</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>11</v>
@@ -16503,7 +18045,7 @@
         <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>117</v>
@@ -16537,7 +18079,7 @@
         <v>3</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>8</v>
@@ -16571,7 +18113,7 @@
         <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>11</v>
@@ -16586,7 +18128,7 @@
         <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>8</v>
@@ -16601,7 +18143,7 @@
         <v>17</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>8</v>
@@ -16610,7 +18152,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -16635,7 +18177,7 @@
     <row r="75" spans="1:5">
       <c r="A75" s="2"/>
       <c r="B75" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -16649,7 +18191,7 @@
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>8</v>
@@ -16664,7 +18206,7 @@
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>8</v>
@@ -16679,7 +18221,7 @@
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>8</v>
@@ -16694,13 +18236,13 @@
         <v>21</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -16711,7 +18253,7 @@
         <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>8</v>
@@ -16735,7 +18277,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -16775,7 +18317,7 @@
     <row r="85" spans="1:5">
       <c r="A85" s="2"/>
       <c r="B85" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -16789,7 +18331,7 @@
         <v>5</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>8</v>
@@ -16804,7 +18346,7 @@
         <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>11</v>
@@ -16819,7 +18361,7 @@
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>8</v>
@@ -16834,7 +18376,7 @@
         <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>11</v>
@@ -16849,7 +18391,7 @@
         <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>11</v>
@@ -16864,7 +18406,7 @@
         <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>11</v>
@@ -16879,7 +18421,7 @@
         <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>11</v>
@@ -16919,7 +18461,7 @@
     <row r="95" spans="1:5">
       <c r="A95" s="2"/>
       <c r="B95" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
@@ -16933,7 +18475,7 @@
         <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
@@ -16948,7 +18490,7 @@
         <v>5</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>11</v>
@@ -16960,16 +18502,16 @@
         <v>11</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -16977,10 +18519,10 @@
         <v>12</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>11</v>
@@ -16995,7 +18537,7 @@
         <v>69</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>11</v>
@@ -17010,7 +18552,7 @@
         <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>11</v>
@@ -17025,7 +18567,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>11</v>
@@ -17040,7 +18582,7 @@
         <v>17</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>11</v>
@@ -17055,7 +18597,7 @@
         <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>11</v>
@@ -17070,7 +18612,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>11</v>
@@ -17085,7 +18627,7 @@
         <v>17</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>11</v>
@@ -17100,7 +18642,7 @@
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>11</v>
@@ -17115,7 +18657,7 @@
         <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>11</v>
@@ -17130,7 +18672,7 @@
         <v>17</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>11</v>
@@ -17145,7 +18687,7 @@
         <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>11</v>
@@ -17160,7 +18702,7 @@
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>11</v>
@@ -17175,7 +18717,7 @@
         <v>17</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>11</v>
@@ -17190,7 +18732,7 @@
         <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>11</v>
@@ -17205,7 +18747,7 @@
         <v>17</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>11</v>
@@ -17220,7 +18762,7 @@
         <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>11</v>
@@ -17235,7 +18777,7 @@
         <v>17</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>11</v>
@@ -17250,7 +18792,7 @@
         <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>11</v>
@@ -17265,7 +18807,7 @@
         <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>11</v>
@@ -17280,7 +18822,7 @@
         <v>17</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>11</v>
@@ -17295,7 +18837,7 @@
         <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>11</v>
@@ -17310,7 +18852,7 @@
         <v>17</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>11</v>
@@ -17325,7 +18867,7 @@
         <v>17</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>11</v>
@@ -17334,10 +18876,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
@@ -17361,7 +18903,7 @@
     <row r="125" spans="1:5">
       <c r="A125" s="2"/>
       <c r="B125" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
@@ -17375,7 +18917,7 @@
         <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>8</v>
@@ -17390,13 +18932,13 @@
         <v>21</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -17407,13 +18949,13 @@
         <v>21</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -17424,7 +18966,7 @@
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>11</v>
@@ -17436,25 +18978,25 @@
         <v>13</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2"/>
       <c r="B131" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>11</v>
@@ -17469,7 +19011,7 @@
         <v>69</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>8</v>
@@ -17484,7 +19026,7 @@
         <v>5</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>8</v>
@@ -17499,7 +19041,7 @@
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>11</v>
@@ -17512,7 +19054,7 @@
         <v>69</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>11</v>
@@ -17525,7 +19067,7 @@
         <v>17</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>11</v>
@@ -17534,7 +19076,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -17559,7 +19101,7 @@
     <row r="139" spans="1:5">
       <c r="A139" s="2"/>
       <c r="B139" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -17573,7 +19115,7 @@
         <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>8</v>
@@ -17603,7 +19145,7 @@
         <v>5</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>8</v>
@@ -17618,7 +19160,7 @@
         <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>11</v>
@@ -17642,7 +19184,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -17667,7 +19209,7 @@
     <row r="147" spans="1:5">
       <c r="A147" s="2"/>
       <c r="B147" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
@@ -17696,7 +19238,7 @@
         <v>5</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>11</v>
@@ -17711,7 +19253,7 @@
         <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>11</v>
@@ -17756,7 +19298,7 @@
         <v>5</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>11</v>
@@ -17771,7 +19313,7 @@
         <v>5</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>8</v>
@@ -17786,7 +19328,7 @@
         <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>11</v>
@@ -17801,7 +19343,7 @@
         <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>8</v>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0423AB8D-48B9-424B-95D4-B1CCA3BF3A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF10AC4E-9A3E-46CE-8C8C-54AD24735D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3634" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3670" uniqueCount="281">
   <si>
     <t>Keyword</t>
   </si>
@@ -816,9 +816,6 @@
     <t>verifyerrorone</t>
   </si>
   <si>
-    <t>verifyerrortwo</t>
-  </si>
-  <si>
     <t>veifyerrorthree</t>
   </si>
   <si>
@@ -862,6 +859,12 @@
   </si>
   <si>
     <t>savesettings</t>
+  </si>
+  <si>
+    <t>LINK MONEY CHANGERS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>IMPLICTWAIT</t>
   </si>
 </sst>
 </file>
@@ -1349,7 +1352,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1385,7 +1388,7 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -2665,7 +2668,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2701,7 +2704,7 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -4350,7 +4353,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -4388,7 +4391,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -6840,7 +6843,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -6876,7 +6879,7 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -8714,7 +8717,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8752,7 +8755,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -9599,7 +9602,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -16410,14 +16413,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.85546875" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" customWidth="1"/>
-    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="1" max="1" width="42.85546875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="41.85546875" style="11" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="31" style="11" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -16462,7 +16466,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -16500,7 +16504,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -16620,7 +16624,7 @@
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>225</v>
@@ -16676,12 +16680,14 @@
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
       <c r="B18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>11</v>
@@ -16689,12 +16695,14 @@
       <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
       <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>11</v>
@@ -16702,7 +16710,9 @@
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
       <c r="B20" s="2" t="s">
         <v>255</v>
       </c>
@@ -16711,7 +16721,9 @@
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>5</v>
       </c>
@@ -16724,87 +16736,101 @@
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
       <c r="B22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>276</v>
-      </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
       <c r="B24" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="D27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
       <c r="B28" s="2" t="s">
         <v>255</v>
       </c>
@@ -16813,7 +16839,9 @@
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
       <c r="B29" s="2" t="s">
         <v>5</v>
       </c>
@@ -16826,7 +16854,9 @@
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
       <c r="B30" s="2" t="s">
         <v>69</v>
       </c>
@@ -16839,7 +16869,9 @@
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
       <c r="B31" s="2" t="s">
         <v>5</v>
       </c>
@@ -16852,7 +16884,9 @@
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
       <c r="B32" s="2" t="s">
         <v>5</v>
       </c>
@@ -16865,7 +16899,9 @@
       <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
       <c r="B33" s="2" t="s">
         <v>69</v>
       </c>
@@ -16878,7 +16914,9 @@
       <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
       <c r="B34" s="2" t="s">
         <v>5</v>
       </c>
@@ -16891,446 +16929,694 @@
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2" t="s">
+      <c r="D49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="D51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="2"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="D52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="2"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="D53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="D54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="2"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2" t="s">
+      <c r="D55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="2"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="D56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="2"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2" t="s">
+      <c r="D58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="2"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="D60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="2"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C50" s="2" t="s">
+      <c r="D61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="2"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="D62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="2"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2" t="s">
+      <c r="D63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="2"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="D64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="2"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="D65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="2"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C55" s="2" t="s">
+      <c r="D66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="2"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="D67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="2"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" s="2" t="s">
+      <c r="D68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="2"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" s="2"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2" t="s">
+      <c r="D69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C59" s="2" t="s">
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="2"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2" t="s">
+      <c r="D71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E60" s="2"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="D72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="2"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" s="2"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="2" t="s">
+      <c r="D73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" s="2"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="2"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C63" s="2" t="s">
+      <c r="D74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="2"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="2"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C64" s="2" t="s">
+      <c r="D76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="2"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="2"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C65" s="2" t="s">
+      <c r="D77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="2"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2" t="s">
+      <c r="D78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" s="2"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2" t="s">
+      <c r="D79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="2"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2" t="s">
+      <c r="D80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C81" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="2"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2" t="s">
+      <c r="D81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C82" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="2"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" s="2"/>
+      <c r="D82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17392,7 +17678,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -17428,7 +17714,7 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -17851,7 +18137,7 @@
         <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -17862,7 +18148,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>11</v>
@@ -18488,7 +18774,7 @@
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>8</v>
@@ -18801,7 +19087,7 @@
         <v>12</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>225</v>
@@ -19275,7 +19561,7 @@
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>225</v>
@@ -19336,7 +19622,7 @@
         <v>69</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>11</v>
@@ -19349,7 +19635,7 @@
         <v>17</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>11</v>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF10AC4E-9A3E-46CE-8C8C-54AD24735D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5D73AB-221F-4EB6-974E-EEE09C343D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3670" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3724" uniqueCount="287">
   <si>
     <t>Keyword</t>
   </si>
@@ -865,6 +865,24 @@
   </si>
   <si>
     <t>IMPLICTWAIT</t>
+  </si>
+  <si>
+    <t>challancompanies</t>
+  </si>
+  <si>
+    <t>challanprint</t>
+  </si>
+  <si>
+    <t>downloadchallan</t>
+  </si>
+  <si>
+    <t>allchallans</t>
+  </si>
+  <si>
+    <t>firstdeductionedit</t>
+  </si>
+  <si>
+    <t>deletechallanindeduction</t>
   </si>
 </sst>
 </file>
@@ -2616,7 +2634,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.5703125" customWidth="1"/>
@@ -3083,85 +3101,83 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>29</v>
-      </c>
+      <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>67</v>
+        <v>281</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
+        <v>29</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>30</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="D33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>31</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="6">
-        <v>22343244410021</v>
-      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="E35" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>33</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>11</v>
@@ -3170,45 +3186,45 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>34</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>3</v>
+        <v>33</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="6">
-        <v>22343244410021</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E37" s="7"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="E38" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>36</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>17</v>
+        <v>35</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>11</v>
@@ -3217,45 +3233,45 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>37</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>3</v>
+        <v>36</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="6">
-        <v>22343244410021</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E40" s="7"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="E41" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>39</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>11</v>
@@ -3264,92 +3280,92 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>40</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>3</v>
+        <v>39</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="6">
-        <v>22343244410021</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E44" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>42</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="7"/>
+      <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>43</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>3</v>
+        <v>42</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="6">
-        <v>22343244410021</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E46" s="7"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="E47" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>45</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>17</v>
+        <v>44</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>11</v>
@@ -3358,92 +3374,92 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>46</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>3</v>
+        <v>45</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="6">
-        <v>22343244410021</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E49" s="7"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="E50" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>48</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>17</v>
+        <v>47</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" s="7"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>49</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>3</v>
+        <v>48</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="6">
-        <v>22343244410021</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E52" s="2"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E53" s="6">
+        <v>22343244410021</v>
+      </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>51</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>17</v>
+        <v>50</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>11</v>
@@ -3452,45 +3468,45 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>52</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>3</v>
+        <v>51</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="2">
-        <v>12</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E55" s="2"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E56" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>54</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>17</v>
+        <v>53</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>11</v>
@@ -3499,62 +3515,62 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>55</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>3</v>
+        <v>54</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>218</v>
+        <v>110</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E58" s="8">
-        <v>44594</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>88</v>
+        <v>218</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="2">
-        <v>12</v>
+        <v>117</v>
+      </c>
+      <c r="E59" s="8">
+        <v>44594</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>57</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>17</v>
+        <v>56</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E60" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>58</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>5</v>
+        <v>57</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>11</v>
@@ -3563,13 +3579,13 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>59</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>11</v>
@@ -3578,107 +3594,107 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>60</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>5</v>
+        <v>59</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E66" s="6">
-        <v>3234</v>
-      </c>
+      <c r="E66" s="2"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E67" s="9">
-        <v>13234</v>
+      <c r="E67" s="6">
+        <v>3234</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E68" s="9">
+        <v>13234</v>
+      </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>66</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>17</v>
+        <v>65</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>11</v>
@@ -3687,165 +3703,165 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>67</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>5</v>
+        <v>66</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E70" s="2"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
+        <v>67</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
         <v>68</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C71" s="2" t="s">
+      <c r="B72" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" s="2"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
+      <c r="D72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="2"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>70</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E74" s="6">
-        <v>7826423</v>
-      </c>
+      <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>121</v>
+      <c r="E75" s="6">
+        <v>7826423</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E77" s="2">
-        <v>3478323</v>
+      <c r="E77" s="5" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E78" s="2"/>
+      <c r="E78" s="2">
+        <v>3478323</v>
+      </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>220</v>
+        <v>67</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>77</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>17</v>
+        <v>76</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>11</v>
@@ -3854,246 +3870,224 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
+        <v>77</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
         <v>78</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C81" s="2" t="s">
+      <c r="B82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
+      <c r="D82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B82" s="3"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
-        <v>80</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" s="2"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
-        <v>81</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E84" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
-        <v>82</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
-        <v>83</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
-        <v>84</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E87" s="2">
-        <v>10</v>
-      </c>
+      <c r="B87" s="3"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E88" s="2"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2" t="s">
-        <v>5</v>
+      <c r="A89" s="2">
+        <v>81</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E89" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E89" s="2">
+        <v>1000</v>
+      </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E90" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="2"/>
+      <c r="E91" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>88</v>
-      </c>
-      <c r="B92" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E92" s="6">
-        <v>200</v>
+      <c r="E92" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>89</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>21</v>
+        <v>85</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E93" s="5" t="s">
-        <v>121</v>
-      </c>
+      <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
-        <v>90</v>
-      </c>
+      <c r="A94" s="2"/>
       <c r="B94" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>86</v>
+        <v>220</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>119</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E94" s="2"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>91</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>3</v>
+        <v>86</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E95" s="2">
-        <v>3478323</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E95" s="2"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <v>92</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>5</v>
+        <v>87</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>8</v>
@@ -4102,61 +4096,81 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E97" s="6">
+        <v>200</v>
+      </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
+      <c r="A98" s="2">
+        <v>89</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="2"/>
+      <c r="A100" s="2">
+        <v>91</v>
+      </c>
       <c r="B100" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="2">
+        <v>3478323</v>
+      </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>8</v>
@@ -4165,13 +4179,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>11</v>
@@ -4179,29 +4193,23 @@
       <c r="E102" s="2"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
-        <v>98</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A103" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>11</v>
@@ -4209,38 +4217,38 @@
       <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
-        <v>100</v>
-      </c>
+      <c r="A105" s="2"/>
       <c r="B105" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
       <c r="E105" s="2"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
+      <c r="A106" s="2">
+        <v>96</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E106" s="2"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>11</v>
@@ -4249,7 +4257,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>5</v>
@@ -4264,7 +4272,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>5</v>
@@ -4279,7 +4287,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>17</v>
@@ -4291,6 +4299,75 @@
         <v>11</v>
       </c>
       <c r="E110" s="2"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>101</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="2"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>102</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="2"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>103</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="2"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>104</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6791,7 +6868,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -7894,59 +7971,55 @@
       <c r="E72" s="5"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>68</v>
-      </c>
+      <c r="A73" s="2"/>
       <c r="B73" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>207</v>
+      <c r="C73" s="12" t="s">
+        <v>284</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E73" s="2"/>
+      <c r="E73" s="5"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
-        <v>71</v>
-      </c>
+      <c r="A76" s="2"/>
       <c r="B76" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>211</v>
+        <v>64</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>11</v>
@@ -7954,107 +8027,97 @@
       <c r="E76" s="2"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
-        <v>72</v>
-      </c>
+      <c r="A77" s="2"/>
       <c r="B77" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>210</v>
+        <v>138</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
-        <v>73</v>
-      </c>
+      <c r="A78" s="2"/>
       <c r="B78" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>212</v>
+        <v>285</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="D79" s="2"/>
-      <c r="E79" s="5"/>
+      <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
-        <v>75</v>
-      </c>
+      <c r="A80" s="2"/>
       <c r="B80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="5"/>
+        <v>120</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="2"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
-        <v>76</v>
-      </c>
+      <c r="A82" s="2"/>
       <c r="B82" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E82" s="2"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
-        <v>77</v>
-      </c>
+      <c r="A83" s="2"/>
       <c r="B83" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>56</v>
+        <v>193</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
-        <v>78</v>
-      </c>
+      <c r="A84" s="2"/>
       <c r="B84" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>140</v>
+        <v>285</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>8</v>
@@ -8062,106 +8125,94 @@
       <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
-        <v>79</v>
-      </c>
+      <c r="A85" s="2"/>
       <c r="B85" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E85" s="2"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
-        <v>80</v>
-      </c>
+      <c r="A86" s="2"/>
       <c r="B86" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" s="2"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
-        <v>81</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E87" s="2"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
-        <v>82</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="C88" s="2" t="s">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>150</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E88" s="2"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
-        <v>83</v>
-      </c>
+      <c r="A89" s="2"/>
       <c r="B89" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>165</v>
+      <c r="C89" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E90" s="7"/>
+        <v>11</v>
+      </c>
+      <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>11</v>
@@ -8170,94 +8221,76 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>169</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E93" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
-        <v>88</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="2">
-        <v>1000000</v>
-      </c>
+      <c r="A94" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="5"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>173</v>
+        <v>64</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E95" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="E95" s="5"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>90</v>
-      </c>
+      <c r="A96" s="2"/>
       <c r="B96" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="2">
-        <v>10340</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="5"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>8</v>
@@ -8266,13 +8299,13 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>11</v>
@@ -8281,106 +8314,120 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E99" s="2"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="2"/>
+      <c r="A100" s="2">
+        <v>79</v>
+      </c>
       <c r="B100" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E100" s="2"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C101" s="12" t="s">
-        <v>206</v>
+        <v>17</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E101" s="2"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>215</v>
+        <v>143</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E102" s="2"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>211</v>
+        <v>144</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E103" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>97</v>
-      </c>
-      <c r="B104" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D104" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
+      <c r="A105" s="2">
+        <v>84</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E105" s="7"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>64</v>
+        <v>213</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>11</v>
@@ -8388,53 +8435,63 @@
       <c r="E106" s="2"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="2"/>
+      <c r="A107" s="2">
+        <v>86</v>
+      </c>
       <c r="B107" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E108" s="2"/>
+      <c r="E108" s="5"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E109" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E109" s="2">
+        <v>1000000</v>
+      </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>8</v>
@@ -8443,46 +8500,54 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E111" s="2">
+        <v>10340</v>
+      </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" s="2"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>92</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="2"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
+      <c r="C113" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E113" s="2"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>5</v>
@@ -8506,13 +8571,13 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>65</v>
+      <c r="C116" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>8</v>
@@ -8521,13 +8586,13 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>127</v>
+        <v>215</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>11</v>
@@ -8536,13 +8601,13 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>126</v>
+        <v>211</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>11</v>
@@ -8551,108 +8616,309 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <v>110</v>
-      </c>
-      <c r="B119" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D119" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D119" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E119" s="2"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
-        <v>111</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A120" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
       <c r="E120" s="2"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
-        <v>112</v>
-      </c>
-      <c r="B121" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D121" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E121" s="2"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
-        <v>113</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A122" s="2"/>
+      <c r="B122" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
       <c r="E122" s="2"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>211</v>
+        <v>138</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E123" s="2"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>198</v>
+        <v>56</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E124" s="2"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
+        <v>102</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E125" s="2"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>103</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" s="2"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="2">
+        <v>104</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="2"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="2">
+        <v>106</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="2"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="2"/>
+      <c r="B130" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="2">
+        <v>107</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="2"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>108</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E132" s="2"/>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="2">
+        <v>109</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="2"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>110</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="2"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="2">
+        <v>111</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" s="2"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
+        <v>112</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" s="2"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>113</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="2"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
+        <v>114</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="2"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="2">
+        <v>115</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="2"/>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
         <v>116</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C125" s="2" t="s">
+      <c r="B140" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E125" s="2"/>
+      <c r="D140" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3731" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3740" uniqueCount="289">
   <si>
     <t>Keyword</t>
   </si>
@@ -16669,7 +16669,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.85546875" style="11" customWidth="1"/>
@@ -16891,100 +16891,90 @@
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
+      <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>250</v>
+        <v>64</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
+      <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>250</v>
+        <v>64</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
+      <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3"/>
       <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>64</v>
+        <v>251</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>11</v>
@@ -16993,75 +16983,69 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>275</v>
+        <v>64</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>276</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
@@ -17070,54 +17054,60 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>64</v>
+        <v>275</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>8</v>
@@ -17126,43 +17116,39 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>262</v>
+        <v>64</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>11</v>
@@ -17171,146 +17157,150 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>279</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>64</v>
+        <v>275</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>8</v>
@@ -17319,43 +17309,39 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
       <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>272</v>
+        <v>64</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>11</v>
@@ -17364,37 +17350,43 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="A48" s="2">
+        <v>43</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>64</v>
+        <v>251</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>11</v>
@@ -17403,54 +17395,52 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>138</v>
+        <v>272</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="2">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A52" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
       <c r="E52" s="2"/>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>11</v>
@@ -17459,43 +17449,39 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
       <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E55" s="2"/>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>57</v>
+        <v>238</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>11</v>
@@ -17503,79 +17489,83 @@
       <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
+      <c r="A57" s="2">
+        <v>52</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E57" s="2"/>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="2">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A61" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
       <c r="E61" s="2"/>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>11</v>
@@ -17584,43 +17574,39 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
       <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>11</v>
@@ -17629,28 +17615,28 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E66" s="2"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>211</v>
+        <v>55</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>11</v>
@@ -17659,28 +17645,28 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>198</v>
+        <v>57</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E68" s="2"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>55</v>
+        <v>197</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>11</v>
@@ -17689,24 +17675,28 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E70" s="2"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>64</v>
+        <v>211</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>11</v>
@@ -17715,13 +17705,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>8</v>
@@ -17730,84 +17720,84 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>11</v>
@@ -17816,28 +17806,24 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
       <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>11</v>
@@ -17846,13 +17832,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>11</v>
@@ -17861,18 +17847,78 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
+        <v>77</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="2">
+        <v>78</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="2">
+        <v>79</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="2">
+        <v>80</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="2">
         <v>81</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B86" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C86" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D82" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="2"/>
+      <c r="D86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -9122,14 +9122,14 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>5</v>
+      <c r="B13" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>225</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2"/>
     </row>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E5F1A7-A5B4-4B56-952F-BD1B9EC6184B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74744A2-22E9-45E0-BE6C-02B647DD0CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4265" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4268" uniqueCount="295">
   <si>
     <t>Keyword</t>
   </si>
@@ -2659,7 +2659,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE905EB-A419-4DDF-9097-B54DF6A0C605}">
-  <dimension ref="A1:E166"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2882,7 +2882,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
@@ -2897,7 +2897,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>149</v>
+        <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
@@ -2914,13 +2914,13 @@
         <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>151</v>
+        <v>8</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2931,13 +2931,13 @@
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>152</v>
+        <v>31</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2945,237 +2945,211 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>155</v>
+        <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>156</v>
+      <c r="E21" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>157</v>
+        <v>27</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>158</v>
+      <c r="E22" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>21</v>
-      </c>
+      <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>159</v>
+        <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>160</v>
+      <c r="E23" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>22</v>
-      </c>
+      <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="E24" s="4"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>23</v>
-      </c>
+      <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>24</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>162</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>26</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>59</v>
-      </c>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>27</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>163</v>
-      </c>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>28</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="A32" s="2">
+        <v>25</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
+        <v>26</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="D33" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="2"/>
+      <c r="E33" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
+      <c r="A34" s="2">
+        <v>27</v>
+      </c>
       <c r="B34" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>138</v>
+        <v>15</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>8</v>
@@ -3184,45 +3158,37 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>34</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>150</v>
-      </c>
+      <c r="A37" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>165</v>
+        <v>294</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>11</v>
@@ -3230,341 +3196,333 @@
       <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>36</v>
-      </c>
+      <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
       <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
+      <c r="A43" s="2">
+        <v>35</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>169</v>
-      </c>
+      <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>171</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2">
-        <v>10000</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>45</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="2">
-        <v>1000</v>
-      </c>
+      <c r="A48" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E49" s="2"/>
+      <c r="E49" s="5" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E50" s="2">
-        <v>2</v>
+      <c r="E50" s="5" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" s="2">
+        <v>10000</v>
+      </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="2">
-        <v>20</v>
-      </c>
+      <c r="E52" s="2"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E53" s="2"/>
+      <c r="E53" s="2">
+        <v>1000</v>
+      </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E54" s="2">
-        <v>2</v>
-      </c>
+      <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E55" s="2"/>
+      <c r="E55" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E56" s="2">
-        <v>20</v>
-      </c>
+      <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E59" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>8</v>
@@ -3573,54 +3531,62 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>34</v>
+        <v>177</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E61" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+      <c r="A62" s="2">
+        <v>54</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>11</v>
@@ -3629,195 +3595,187 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>183</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E66" s="2"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>64</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E67" s="2">
-        <v>100</v>
-      </c>
+      <c r="A67" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E68" s="2"/>
+      <c r="E68" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E69" s="2"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>184</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E70" s="2"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E71" s="2">
-        <v>100</v>
+      <c r="E71" s="10" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>93</v>
+        <v>172</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E72" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>186</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" s="5" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E76" s="2">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>5</v>
@@ -3832,75 +3790,77 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E78" s="2"/>
+      <c r="E78" s="5"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E79" s="2"/>
+      <c r="E79" s="5" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E80" s="2">
-        <v>262</v>
-      </c>
+      <c r="E80" s="2"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>93</v>
+        <v>173</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E81" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E81" s="2">
+        <v>1000</v>
+      </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>188</v>
+        <v>93</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>11</v>
@@ -3909,60 +3869,60 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E84" s="6">
-        <v>3.4628376482734602E+18</v>
-      </c>
+      <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E85" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E85" s="2">
+        <v>262</v>
+      </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>11</v>
@@ -3971,60 +3931,60 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E88" s="2">
-        <v>262</v>
-      </c>
+      <c r="E88" s="2"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E89" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E89" s="6">
+        <v>3.4628376482734602E+18</v>
+      </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>11</v>
@@ -4033,60 +3993,60 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E92" s="6">
-        <v>3.4628376482734602E+18</v>
-      </c>
+      <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>99</v>
+        <v>176</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E93" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E93" s="2">
+        <v>262</v>
+      </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>11</v>
@@ -4095,27 +4055,25 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E95" s="8">
-        <v>44854</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E95" s="2"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>177</v>
@@ -4123,34 +4081,34 @@
       <c r="D96" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="2">
-        <v>21</v>
-      </c>
+      <c r="E96" s="2"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E97" s="6">
+        <v>3.4628376482734602E+18</v>
+      </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>11</v>
@@ -4159,99 +4117,107 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E99" s="2"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E100" s="8">
+        <v>44854</v>
+      </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="2"/>
+      <c r="E101" s="2">
+        <v>21</v>
+      </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
+      <c r="A102" s="2">
+        <v>94</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E102" s="2"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>162</v>
-      </c>
+      <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>11</v>
@@ -4260,159 +4226,167 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E106" s="2"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
-        <v>104</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>194</v>
-      </c>
+      <c r="A107" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E108" s="2">
-        <v>7600</v>
-      </c>
+      <c r="E108" s="2"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E109" s="5" t="s">
-        <v>171</v>
+      <c r="E109" s="2" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>179</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E110" s="2"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E111" s="2"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>34</v>
+        <v>168</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
+      <c r="A113" s="2">
+        <v>105</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E113" s="2">
+        <v>7600</v>
+      </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>294</v>
+        <v>170</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="2"/>
+      <c r="A115" s="2">
+        <v>107</v>
+      </c>
       <c r="B115" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>8</v>
@@ -4421,43 +4395,37 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E117" s="2"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
-        <v>114</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A118" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
       <c r="E118" s="2"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>11</v>
@@ -4465,59 +4433,53 @@
       <c r="E119" s="2"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
-        <v>116</v>
-      </c>
+      <c r="A120" s="2"/>
       <c r="B120" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
       <c r="E120" s="2"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E121" s="2"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E122" s="2"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>11</v>
@@ -4526,81 +4488,73 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>203</v>
+        <v>127</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>121</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E124" s="2"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E125" s="5" t="s">
-        <v>91</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E125" s="2"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>258</v>
+        <v>134</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E126" s="2">
-        <v>2311323</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E126" s="2"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E127" s="2">
-        <v>12323</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E127" s="2"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>195</v>
+        <v>136</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>11</v>
@@ -4609,76 +4563,96 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E129" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>196</v>
+        <v>86</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E130" s="2"/>
+      <c r="E130" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
+      <c r="A131" s="2">
+        <v>122</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="2">
+        <v>2311323</v>
+      </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>294</v>
+        <v>87</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E132" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E132" s="2">
+        <v>12323</v>
+      </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="2"/>
+      <c r="A133" s="2">
+        <v>124</v>
+      </c>
       <c r="B133" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E133" s="2"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>8</v>
@@ -4687,13 +4661,13 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>254</v>
+        <v>196</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>8</v>
@@ -4701,109 +4675,109 @@
       <c r="E135" s="2"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
-        <v>131</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A136" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
       <c r="E136" s="2"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>170</v>
+        <v>294</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>184</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E137" s="2"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
-        <v>133</v>
-      </c>
+      <c r="A138" s="2"/>
       <c r="B138" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
       <c r="E138" s="2"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>34</v>
+        <v>138</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E139" s="2"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B140" s="2"/>
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
+      <c r="A140" s="2">
+        <v>130</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E140" s="2"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>294</v>
+        <v>202</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E141" s="2"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="2"/>
+      <c r="A142" s="2">
+        <v>132</v>
+      </c>
       <c r="B142" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>8</v>
@@ -4812,13 +4786,13 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>125</v>
+        <v>34</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>11</v>
@@ -4826,29 +4800,23 @@
       <c r="E144" s="2"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
+      <c r="A145" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
       <c r="E145" s="2"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>142</v>
+        <v>294</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>11</v>
@@ -4856,38 +4824,38 @@
       <c r="E146" s="2"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
-        <v>141</v>
-      </c>
+      <c r="A147" s="2"/>
       <c r="B147" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
       <c r="E147" s="2"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
+      <c r="A148" s="2">
+        <v>137</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E148" s="2"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>11</v>
@@ -4896,7 +4864,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>5</v>
@@ -4911,7 +4879,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>5</v>
@@ -4926,13 +4894,13 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>257</v>
+        <v>57</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>11</v>
@@ -4941,7 +4909,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -4950,43 +4918,43 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E154" s="2"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E155" s="2"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>11</v>
@@ -4995,13 +4963,13 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>55</v>
+        <v>257</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>11</v>
@@ -5009,38 +4977,38 @@
       <c r="E157" s="2"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
-        <v>152</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A158" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
       <c r="E158" s="2"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B159" s="2"/>
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
+      <c r="A159" s="2">
+        <v>148</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E159" s="2"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>11</v>
@@ -5049,13 +5017,13 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>11</v>
@@ -5064,28 +5032,28 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>199</v>
+        <v>55</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E162" s="2"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>11</v>
@@ -5093,29 +5061,23 @@
       <c r="E163" s="2"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
-        <v>158</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A164" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
       <c r="E164" s="2"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>55</v>
+        <v>197</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>11</v>
@@ -5124,22 +5086,97 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
+        <v>155</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" s="2"/>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="2">
+        <v>156</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E167" s="2"/>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="2">
+        <v>157</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" s="2"/>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="2">
+        <v>158</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E169" s="2"/>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="2">
+        <v>159</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" s="2"/>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="2">
         <v>160</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="B171" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="C171" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D166" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E166" s="2"/>
+      <c r="D171" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E171" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E20" r:id="rId1" xr:uid="{6C66B0C2-355F-4F66-BB69-B640411EA7F6}"/>
+    <hyperlink ref="E23" r:id="rId1" xr:uid="{C3B37C7D-5C2A-43D1-B74A-4D26BA51457C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74744A2-22E9-45E0-BE6C-02B647DD0CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCCE117-A159-4C80-98DC-818A1989FDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4268" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4257" uniqueCount="303">
   <si>
     <t>Keyword</t>
   </si>
@@ -908,6 +908,30 @@
   </si>
   <si>
     <t>26Qtab</t>
+  </si>
+  <si>
+    <t>GETATTRIBUTE</t>
+  </si>
+  <si>
+    <t>deductionincometaxrate</t>
+  </si>
+  <si>
+    <t>192A</t>
+  </si>
+  <si>
+    <t>194C</t>
+  </si>
+  <si>
+    <t>U-Section 206AB applicable - Higher rate</t>
+  </si>
+  <si>
+    <t>deducteeclick</t>
+  </si>
+  <si>
+    <t>deducteeclick2</t>
+  </si>
+  <si>
+    <t>E-No deduction due to Board Circular 3 of 2002 / 11 of 2002 / 18 of 2017</t>
   </si>
 </sst>
 </file>
@@ -988,7 +1012,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1004,6 +1028,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2659,7 +2684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE905EB-A419-4DDF-9097-B54DF6A0C605}">
-  <dimension ref="A1:E171"/>
+  <dimension ref="A1:E163"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3047,43 +3072,79 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
+        <v>24</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>26</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>27</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>8</v>
@@ -3092,127 +3153,123 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>162</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>26</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>59</v>
-      </c>
+      <c r="A33" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>22</v>
+        <v>294</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>23</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>28</v>
-      </c>
+      <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>34</v>
+        <v>138</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
+      <c r="A37" s="2">
+        <v>33</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>294</v>
+        <v>144</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
+      <c r="A39" s="2">
+        <v>35</v>
+      </c>
       <c r="B39" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
@@ -3221,45 +3278,43 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>143</v>
+        <v>16</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>150</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E42" s="2"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>11</v>
@@ -3267,262 +3322,266 @@
       <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>36</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A44" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
       <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>93</v>
+        <v>170</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E47" s="2">
+        <v>10000</v>
+      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
+      <c r="A48" s="2">
+        <v>44</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>169</v>
-      </c>
+      <c r="E49" s="2"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>171</v>
+      <c r="E50" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E51" s="2">
-        <v>10000</v>
-      </c>
+      <c r="E51" s="2"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="2"/>
+      <c r="E52" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E53" s="2">
-        <v>1000</v>
-      </c>
+      <c r="E53" s="2"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E54" s="2"/>
+      <c r="E54" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E55" s="2">
-        <v>2</v>
-      </c>
+      <c r="E55" s="2"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E56" s="2"/>
+      <c r="E56" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="2">
-        <v>20</v>
-      </c>
+      <c r="E57" s="2"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="E58" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="2">
-        <v>2</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>8</v>
@@ -3531,62 +3590,54 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>177</v>
+        <v>34</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" s="2">
-        <v>20</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E61" s="2"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
-        <v>54</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A62" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>11</v>
@@ -3595,187 +3646,195 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>34</v>
+        <v>168</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
+      <c r="A67" s="2">
+        <v>64</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>162</v>
-      </c>
+      <c r="E68" s="2"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
       <c r="E69" s="2"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E71" s="10" t="s">
-        <v>183</v>
+      <c r="E71" s="2">
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E72" s="2">
-        <v>100</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E73" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="E73" s="5"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>184</v>
-      </c>
+      <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E76" s="2">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>5</v>
@@ -3790,77 +3849,75 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E78" s="5"/>
+      <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E79" s="5" t="s">
-        <v>186</v>
-      </c>
+      <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E80" s="2"/>
+      <c r="E80" s="2">
+        <v>262</v>
+      </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>173</v>
+        <v>93</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E81" s="2">
-        <v>1000</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E81" s="2"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>93</v>
+        <v>188</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>11</v>
@@ -3869,60 +3926,60 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E84" s="2"/>
+      <c r="E84" s="6">
+        <v>3.4628376482734602E+18</v>
+      </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>174</v>
+        <v>95</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" s="2">
-        <v>262</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E85" s="2"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>93</v>
+        <v>189</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>11</v>
@@ -3931,60 +3988,60 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E88" s="2"/>
+      <c r="E88" s="2">
+        <v>262</v>
+      </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="6">
-        <v>3.4628376482734602E+18</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>95</v>
+        <v>188</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>11</v>
@@ -3993,60 +4050,60 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E92" s="2"/>
+      <c r="E92" s="6">
+        <v>3.4628376482734602E+18</v>
+      </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>176</v>
+        <v>99</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E93" s="2">
-        <v>262</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>11</v>
@@ -4055,25 +4112,27 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E95" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E95" s="8">
+        <v>44854</v>
+      </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>177</v>
@@ -4081,34 +4140,34 @@
       <c r="D96" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="2"/>
+      <c r="E96" s="2">
+        <v>21</v>
+      </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E97" s="6">
-        <v>3.4628376482734602E+18</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E97" s="2"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>11</v>
@@ -4117,107 +4176,99 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E99" s="2"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="8">
-        <v>44854</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E100" s="2"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="2">
-        <v>21</v>
-      </c>
+      <c r="E101" s="2"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
-        <v>94</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A102" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
       <c r="E102" s="2"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>191</v>
+        <v>144</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E104" s="2"/>
+      <c r="E104" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>192</v>
+        <v>301</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>11</v>
@@ -4226,167 +4277,159 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>193</v>
+        <v>301</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E106" s="2"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
+      <c r="A107" s="2">
+        <v>104</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E108" s="2"/>
+      <c r="E108" s="2">
+        <v>7600</v>
+      </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E109" s="2" t="s">
-        <v>162</v>
+      <c r="E109" s="13" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E110" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E111" s="2"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>194</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E112" s="2"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
-        <v>105</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E113" s="2">
-        <v>7600</v>
-      </c>
+      <c r="A113" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>170</v>
+        <v>294</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>171</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E114" s="2"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
-        <v>107</v>
-      </c>
+      <c r="A115" s="2"/>
       <c r="B115" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>179</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>8</v>
@@ -4395,37 +4438,43 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E117" s="2"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
+      <c r="A118" s="2">
+        <v>114</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E118" s="2"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>294</v>
+        <v>127</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>11</v>
@@ -4433,53 +4482,59 @@
       <c r="E119" s="2"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="2"/>
+      <c r="A120" s="2">
+        <v>116</v>
+      </c>
       <c r="B120" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E120" s="2"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E121" s="2"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>65</v>
+        <v>135</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E122" s="2"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>11</v>
@@ -4488,73 +4543,81 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E125" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E126" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E126" s="2">
+        <v>2311323</v>
+      </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E127" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E127" s="2">
+        <v>12323</v>
+      </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>11</v>
@@ -4563,96 +4626,76 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>203</v>
+        <v>137</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>121</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E129" s="2"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>86</v>
+        <v>196</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E130" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="E130" s="2"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
-        <v>122</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E131" s="2">
-        <v>2311323</v>
-      </c>
+      <c r="A131" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>87</v>
+        <v>294</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E132" s="2">
-        <v>12323</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E132" s="2"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
-        <v>124</v>
-      </c>
+      <c r="A133" s="2"/>
       <c r="B133" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
       <c r="E133" s="2"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>8</v>
@@ -4661,13 +4704,13 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>8</v>
@@ -4675,109 +4718,109 @@
       <c r="E135" s="2"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B136" s="2"/>
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
+      <c r="A136" s="2">
+        <v>131</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E136" s="2"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>294</v>
+        <v>170</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E137" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E137" s="13" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="2"/>
+      <c r="A138" s="2">
+        <v>133</v>
+      </c>
       <c r="B138" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E138" s="2"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E139" s="2"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
-        <v>130</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A140" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
       <c r="E140" s="2"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>202</v>
+        <v>294</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E141" s="2"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
-        <v>132</v>
-      </c>
+      <c r="A142" s="2"/>
       <c r="B142" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>184</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>8</v>
@@ -4786,13 +4829,13 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>11</v>
@@ -4800,23 +4843,29 @@
       <c r="E144" s="2"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="2" t="s">
+      <c r="A145" s="2">
         <v>139</v>
       </c>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
+      <c r="B145" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E145" s="2"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>294</v>
+        <v>142</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>11</v>
@@ -4824,38 +4873,38 @@
       <c r="E146" s="2"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="2"/>
+      <c r="A147" s="2">
+        <v>141</v>
+      </c>
       <c r="B147" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E147" s="2"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
-        <v>137</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A148" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
       <c r="E148" s="2"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>11</v>
@@ -4864,7 +4913,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>5</v>
@@ -4879,7 +4928,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>5</v>
@@ -4894,13 +4943,13 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>57</v>
+        <v>257</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>11</v>
@@ -4909,7 +4958,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -4918,43 +4967,43 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E154" s="2"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E155" s="2"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>11</v>
@@ -4963,52 +5012,52 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="2"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>152</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E157" s="2"/>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B158" s="2"/>
-      <c r="C158" s="2"/>
-      <c r="D158" s="2"/>
+      <c r="C158" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E158" s="2"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
-        <v>148</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A159" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B159" s="3"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
       <c r="E159" s="2"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
-        <v>149</v>
-      </c>
-      <c r="B160" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B160" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>11</v>
@@ -5017,24 +5066,24 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
-        <v>150</v>
-      </c>
-      <c r="B161" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B161" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E161" s="2"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
-        <v>151</v>
-      </c>
-      <c r="B162" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B162" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C162" s="2" t="s">
@@ -5047,9 +5096,9 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
-        <v>152</v>
-      </c>
-      <c r="B163" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B163" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C163" s="2" t="s">
@@ -5059,126 +5108,13 @@
         <v>11</v>
       </c>
       <c r="E163" s="2"/>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B164" s="2"/>
-      <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
-      <c r="E164" s="2"/>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
-        <v>154</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E165" s="2"/>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
-        <v>155</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E166" s="2"/>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
-        <v>156</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E167" s="2"/>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
-        <v>157</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E168" s="2"/>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="2">
-        <v>158</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E169" s="2"/>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="2">
-        <v>159</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E170" s="2"/>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="2">
-        <v>160</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E171" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E23" r:id="rId1" xr:uid="{C3B37C7D-5C2A-43D1-B74A-4D26BA51457C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25225"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCCE117-A159-4C80-98DC-818A1989FDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DBE73A-315B-4170-BF53-495B52EE8DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4257" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4252" uniqueCount="311">
   <si>
     <t>Keyword</t>
   </si>
@@ -928,10 +928,34 @@
     <t>deducteeclick</t>
   </si>
   <si>
-    <t>deducteeclick2</t>
-  </si>
-  <si>
-    <t>E-No deduction due to Board Circular 3 of 2002 / 11 of 2002 / 18 of 2017</t>
+    <t>anotheremployee</t>
+  </si>
+  <si>
+    <t>26qdeduction</t>
+  </si>
+  <si>
+    <t>invalidamount</t>
+  </si>
+  <si>
+    <t>totalamounterror</t>
+  </si>
+  <si>
+    <t>confirmclear</t>
+  </si>
+  <si>
+    <t>verify26qincometax</t>
+  </si>
+  <si>
+    <t>verify26qsurge</t>
+  </si>
+  <si>
+    <t>verify26qcess</t>
+  </si>
+  <si>
+    <t>verify26qtdstotal</t>
+  </si>
+  <si>
+    <t>A-LOWER DEDUCTION/NO DEDUCTION U/S 197</t>
   </si>
 </sst>
 </file>
@@ -1012,7 +1036,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1029,6 +1053,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2684,7 +2709,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE905EB-A419-4DDF-9097-B54DF6A0C605}">
-  <dimension ref="A1:E163"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2827,10 +2852,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>138</v>
+        <v>302</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -3207,10 +3232,10 @@
         <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>138</v>
+        <v>302</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2"/>
     </row>
@@ -3344,7 +3369,7 @@
         <v>8</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -3361,7 +3386,7 @@
         <v>8</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3459,7 +3484,7 @@
         <v>8</v>
       </c>
       <c r="E52" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3523,15 +3548,13 @@
         <v>8</v>
       </c>
       <c r="E56" s="2">
-        <v>20</v>
+        <v>40.799999999999997</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>54</v>
-      </c>
+      <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>178</v>
@@ -3539,34 +3562,34 @@
       <c r="D57" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>180</v>
+        <v>34</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>11</v>
@@ -3574,521 +3597,505 @@
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>57</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A60" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>144</v>
+        <v>301</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>162</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
-        <v>63</v>
-      </c>
+      <c r="A66" s="2"/>
       <c r="B66" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E66" s="10" t="s">
-        <v>298</v>
+      <c r="E66" s="14">
+        <v>23123121223123</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>64</v>
-      </c>
+      <c r="A67" s="2"/>
       <c r="B67" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E67" s="2">
-        <v>100</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E67" s="5"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>65</v>
-      </c>
+      <c r="A68" s="2"/>
       <c r="B68" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>166</v>
+        <v>303</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E68" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="E68" s="5"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>66</v>
-      </c>
+      <c r="A69" s="2"/>
       <c r="B69" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="5"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
-        <v>67</v>
-      </c>
+      <c r="A70" s="2"/>
       <c r="B70" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>170</v>
+        <v>296</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>299</v>
+      <c r="E70" s="5">
+        <v>128</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>68</v>
-      </c>
+      <c r="A71" s="2"/>
       <c r="B71" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E71" s="2">
-        <v>100</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E71" s="5"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>69</v>
-      </c>
+      <c r="A72" s="2"/>
       <c r="B72" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>93</v>
+        <v>188</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E72" s="2"/>
+      <c r="E72" s="5"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E74" s="13" t="s">
-        <v>186</v>
+      <c r="E74" s="6">
+        <v>3.4628376482734602E+18</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>173</v>
+        <v>97</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
-        <v>73</v>
-      </c>
+      <c r="A76" s="2"/>
       <c r="B76" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" s="2">
-        <v>1000</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E76" s="2"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>93</v>
+        <v>174</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E78" s="2">
+        <v>262</v>
+      </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>174</v>
+        <v>99</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E80" s="2">
-        <v>262</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E80" s="2"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E81" s="2"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E82" s="6">
+        <v>3.4628376482734602E+18</v>
+      </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E84" s="6">
-        <v>3.4628376482734602E+18</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E85" s="2"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E86" s="2">
+        <v>262</v>
+      </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>176</v>
+        <v>104</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E88" s="2">
-        <v>262</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E88" s="2"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E90" s="6">
+        <v>3.4628376482734602E+18</v>
+      </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E92" s="6">
-        <v>3.4628376482734602E+18</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
-        <v>90</v>
-      </c>
+      <c r="A93" s="2"/>
       <c r="B93" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>11</v>
@@ -4096,14 +4103,12 @@
       <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
-        <v>91</v>
-      </c>
+      <c r="A94" s="2"/>
       <c r="B94" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>189</v>
+        <v>304</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>11</v>
@@ -4128,31 +4133,27 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>93</v>
-      </c>
+      <c r="A96" s="2"/>
       <c r="B96" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="2">
-        <v>21</v>
-      </c>
+      <c r="E96" s="8"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>11</v>
@@ -4161,111 +4162,111 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>191</v>
+        <v>305</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E99" s="2"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E100" s="2"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
-        <v>98</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A101" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
       <c r="E101" s="2"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
+      <c r="A102" s="2">
+        <v>100</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E102" s="2"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E103" s="2"/>
+      <c r="E103" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>144</v>
+        <v>301</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>162</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>301</v>
@@ -4277,96 +4278,84 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>301</v>
+        <v>168</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E107" s="5" t="s">
-        <v>298</v>
+      <c r="E107" s="2">
+        <v>7600</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E108" s="2">
-        <v>7600</v>
-      </c>
+      <c r="E108" s="2"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
-        <v>106</v>
-      </c>
+      <c r="A109" s="2"/>
       <c r="B109" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E109" s="13" t="s">
-        <v>186</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E109" s="2"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
-        <v>107</v>
-      </c>
+      <c r="A110" s="2"/>
       <c r="B110" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>179</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>8</v>
@@ -4375,37 +4364,43 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E112" s="2"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
+      <c r="A113" s="2">
+        <v>114</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E113" s="2"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>294</v>
+        <v>127</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>11</v>
@@ -4413,53 +4408,59 @@
       <c r="E114" s="2"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="2"/>
+      <c r="A115" s="2">
+        <v>116</v>
+      </c>
       <c r="B115" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E115" s="2"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>65</v>
+        <v>307</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E116" s="2"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>65</v>
+        <v>308</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E117" s="2"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>132</v>
+        <v>309</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>11</v>
@@ -4468,73 +4469,81 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E119" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E120" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E121" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E121" s="2">
+        <v>2311323</v>
+      </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E122" s="2">
+        <v>12323</v>
+      </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>11</v>
@@ -4543,111 +4552,91 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>203</v>
+        <v>137</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>297</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E124" s="2"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>86</v>
+        <v>196</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E125" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="E125" s="2"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
-        <v>122</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E126" s="2">
-        <v>2311323</v>
-      </c>
+      <c r="A126" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>87</v>
+        <v>294</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E127" s="2">
-        <v>12323</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E127" s="2"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
-        <v>124</v>
-      </c>
+      <c r="A128" s="2"/>
       <c r="B128" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
       <c r="E128" s="2"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>137</v>
+        <v>302</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E129" s="2"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>8</v>
@@ -4655,124 +4644,124 @@
       <c r="E130" s="2"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
+      <c r="A131" s="2">
+        <v>131</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E131" s="2"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>294</v>
+        <v>170</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E132" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="2"/>
+      <c r="A133" s="2">
+        <v>133</v>
+      </c>
       <c r="B133" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E133" s="2"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E134" s="2"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
-        <v>130</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A135" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
       <c r="E135" s="2"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>202</v>
+        <v>294</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E136" s="2"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
-        <v>132</v>
-      </c>
+      <c r="A137" s="2"/>
       <c r="B137" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E137" s="13" t="s">
-        <v>186</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>166</v>
+        <v>302</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E138" s="2"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>11</v>
@@ -4780,23 +4769,29 @@
       <c r="E139" s="2"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
+      <c r="A140" s="2">
         <v>139</v>
       </c>
-      <c r="B140" s="2"/>
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
+      <c r="B140" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E140" s="2"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>294</v>
+        <v>142</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>11</v>
@@ -4804,38 +4799,38 @@
       <c r="E141" s="2"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="2"/>
+      <c r="A142" s="2">
+        <v>141</v>
+      </c>
       <c r="B142" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E142" s="2"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="2">
-        <v>137</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A143" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
       <c r="E143" s="2"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>11</v>
@@ -4844,7 +4839,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>5</v>
@@ -4859,7 +4854,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>5</v>
@@ -4874,13 +4869,13 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>57</v>
+        <v>257</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>11</v>
@@ -4889,7 +4884,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -4898,43 +4893,43 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E149" s="2"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E150" s="2"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>11</v>
@@ -4943,52 +4938,50 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="2"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="2">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E152" s="2"/>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B153" s="2"/>
-      <c r="C153" s="2"/>
-      <c r="D153" s="2"/>
+      <c r="C153" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E153" s="2"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
-        <v>148</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A154" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
       <c r="E154" s="2"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
-        <v>149</v>
-      </c>
+      <c r="A155" s="2"/>
       <c r="B155" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>11</v>
@@ -4996,14 +4989,12 @@
       <c r="E155" s="2"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
-        <v>150</v>
-      </c>
+      <c r="A156" s="2"/>
       <c r="B156" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>11</v>
@@ -5011,29 +5002,27 @@
       <c r="E156" s="2"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
-        <v>151</v>
-      </c>
+      <c r="A157" s="2"/>
       <c r="B157" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E157" s="2"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
-        <v>152</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>17</v>
+        <v>82</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>11</v>
@@ -5041,23 +5030,29 @@
       <c r="E158" s="2"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B159" s="3"/>
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
+      <c r="A159" s="2">
+        <v>83</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E159" s="2"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>11</v>
@@ -5066,48 +5061,18 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E161" s="2"/>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
-        <v>84</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E162" s="2"/>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="2">
-        <v>85</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E163" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5479" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5602" uniqueCount="321">
   <si>
     <t>Keyword</t>
   </si>
@@ -959,19 +959,7 @@
     <t>utilizeamount</t>
   </si>
   <si>
-    <t>unutilizeamountverify</t>
-  </si>
-  <si>
     <t>switchchallan</t>
-  </si>
-  <si>
-    <t>CLICk</t>
-  </si>
-  <si>
-    <t>challanmappinganothercheckbox</t>
-  </si>
-  <si>
-    <t>challanmappingthirdcheckbox</t>
   </si>
   <si>
     <t>autoadjust</t>
@@ -1051,7 +1039,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1074,23 +1062,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1109,7 +1086,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -4793,14 +4769,14 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" customWidth="1"/>
-    <col min="3" max="3" width="33.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="37.5703125" customWidth="1"/>
+    <col min="1" max="1" width="50.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="52.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4879,9 +4855,7 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2">
-        <v>6</v>
-      </c>
+      <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>267</v>
       </c>
@@ -4891,13 +4865,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>291</v>
+        <v>64</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -4906,13 +4880,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>291</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -4920,9 +4894,7 @@
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2">
-        <v>9</v>
-      </c>
+      <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>259</v>
       </c>
@@ -4932,7 +4904,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -4947,7 +4919,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -4971,7 +4943,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>3</v>
@@ -4988,7 +4960,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>3</v>
@@ -5000,12 +4972,12 @@
         <v>8</v>
       </c>
       <c r="E14" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>3</v>
@@ -5017,12 +4989,12 @@
         <v>8</v>
       </c>
       <c r="E15" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>3</v>
@@ -5039,7 +5011,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>3</v>
@@ -5056,7 +5028,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>3</v>
@@ -5073,7 +5045,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>3</v>
@@ -5090,7 +5062,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>21</v>
@@ -5107,7 +5079,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>21</v>
@@ -5124,7 +5096,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>3</v>
@@ -5141,7 +5113,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>3</v>
@@ -5158,7 +5130,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>3</v>
@@ -5175,7 +5147,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>5</v>
@@ -5190,7 +5162,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>17</v>
@@ -5205,13 +5177,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>291</v>
+        <v>64</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>11</v>
@@ -5220,13 +5192,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>291</v>
+        <v>64</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>11</v>
@@ -5234,9 +5206,7 @@
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="2">
-        <v>29</v>
-      </c>
+      <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
         <v>255</v>
       </c>
@@ -5246,22 +5216,22 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>5</v>
@@ -5276,7 +5246,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>3</v>
@@ -5302,7 +5272,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>5</v>
@@ -5317,348 +5287,358 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>63</v>
+        <v>149</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="2"/>
+      <c r="E36" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>37</v>
+        <v>152</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>44</v>
+      <c r="E38" s="2" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>32</v>
+        <v>155</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>26</v>
+      <c r="E41" s="2" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>27</v>
+        <v>159</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>28</v>
+        <v>161</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="4"/>
+      <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="2">
-        <v>46</v>
-      </c>
+      <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>291</v>
+        <v>138</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>299</v>
+        <v>144</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>150</v>
+      <c r="E51" s="5" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>297</v>
+        <v>170</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
+      <c r="A53" s="2">
+        <v>49</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2">
+        <v>1000000</v>
+      </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>295</v>
-      </c>
+      <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>307</v>
+      <c r="E55" s="2">
+        <v>100000</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E56" s="2">
-        <v>1000000</v>
-      </c>
+      <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>174</v>
@@ -5666,31 +5646,31 @@
       <c r="D57" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="2">
-        <v>2</v>
-      </c>
+      <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>175</v>
@@ -5698,31 +5678,31 @@
       <c r="D59" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="2"/>
+      <c r="E59" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E60" s="2">
-        <v>40</v>
-      </c>
+      <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>176</v>
@@ -5730,31 +5710,31 @@
       <c r="D61" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E61" s="2"/>
+      <c r="E61" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E62" s="2">
-        <v>2</v>
-      </c>
+      <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>177</v>
@@ -5762,45 +5742,45 @@
       <c r="D63" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E63" s="2"/>
+      <c r="E63" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E64" s="2">
-        <v>40.799999999999997</v>
+      <c r="E64" s="2" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>179</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>5</v>
@@ -5815,7 +5795,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>17</v>
@@ -5839,13 +5819,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>291</v>
+        <v>64</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>11</v>
@@ -5854,13 +5834,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>291</v>
+        <v>64</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>11</v>
@@ -5868,9 +5848,7 @@
       <c r="E70" s="2"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="2">
-        <v>71</v>
-      </c>
+      <c r="A71" s="2"/>
       <c r="B71" s="2" t="s">
         <v>255</v>
       </c>
@@ -5880,7 +5858,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>5</v>
@@ -5891,12 +5869,10 @@
       <c r="D72" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="2"/>
+      <c r="E72" s="5"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="2">
-        <v>73</v>
-      </c>
+      <c r="A73" s="2"/>
       <c r="B73" s="2" t="s">
         <v>5</v>
       </c>
@@ -5906,11 +5882,11 @@
       <c r="D73" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E73" s="2"/>
+      <c r="E73" s="5"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>5</v>
@@ -5924,9 +5900,7 @@
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="2">
-        <v>76</v>
-      </c>
+      <c r="A75" s="2"/>
       <c r="B75" s="2" t="s">
         <v>120</v>
       </c>
@@ -5936,639 +5910,545 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>291</v>
+        <v>208</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="2">
-        <v>78</v>
-      </c>
+      <c r="A77" s="2"/>
       <c r="B77" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="2"/>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="2">
+      <c r="D79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" s="2">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="2">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="2"/>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="2"/>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="2"/>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="2" t="s">
+      <c r="D96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E105" s="2">
+        <v>12122</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E106" s="2">
+        <v>2311323</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E108" s="5"/>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="2"/>
+      <c r="B109" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="2"/>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="2"/>
+      <c r="B111" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="2"/>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" s="2"/>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E78" s="2"/>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="2">
-        <v>80</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E79" s="2"/>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="2">
-        <v>81</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E80" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="2">
-        <v>82</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="2">
-        <v>83</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="2"/>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="2">
-        <v>84</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" s="2"/>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="2">
-        <v>85</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E84" s="2"/>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="2">
-        <v>86</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" s="2"/>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="2">
-        <v>87</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" s="2"/>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="2">
-        <v>88</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="2">
-        <v>89</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="2">
-        <v>90</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="2"/>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="2">
-        <v>91</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E90" s="2">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="2">
-        <v>92</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="2"/>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="2">
-        <v>93</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E92" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="2">
-        <v>94</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E93" s="2"/>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="2">
-        <v>95</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E94" s="2"/>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="2">
-        <v>96</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E95" s="2"/>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="2">
-        <v>97</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" s="2"/>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="2">
-        <v>98</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="2">
-        <v>99</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E98" s="2"/>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="2">
-        <v>100</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E99" s="2"/>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="2">
-        <v>101</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="2">
-        <v>102</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="2">
-        <v>103</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E102" s="2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="2">
-        <v>104</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E103" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="2">
-        <v>105</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E104" s="2">
+      <c r="D113" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E113" s="2"/>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E114" s="2"/>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="2">
-        <v>106</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E105" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="2">
-        <v>107</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E106" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="2">
-        <v>108</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="2">
-        <v>109</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="2">
-        <v>110</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E109" s="2">
-        <v>12121</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="2">
-        <v>111</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E110" s="2">
-        <v>2311323</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="2">
-        <v>112</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="2">
-        <v>113</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E112" s="5"/>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="2">
-        <v>114</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E113" s="2"/>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="2">
-        <v>115</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" s="2"/>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="2">
-        <v>116</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="2">
-        <v>117</v>
-      </c>
+      <c r="A116" s="2"/>
       <c r="B116" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C116" s="12" t="s">
-        <v>206</v>
+      <c r="C116" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>8</v>
@@ -6576,14 +6456,12 @@
       <c r="E116" s="2"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="2">
-        <v>118</v>
-      </c>
+      <c r="A117" s="2"/>
       <c r="B117" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>207</v>
+        <v>47</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>11</v>
@@ -6591,14 +6469,12 @@
       <c r="E117" s="2"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="2">
-        <v>119</v>
-      </c>
+      <c r="A118" s="2"/>
       <c r="B118" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>8</v>
@@ -6606,149 +6482,133 @@
       <c r="E118" s="2"/>
     </row>
     <row r="119" spans="1:5">
-      <c r="A119" s="2">
-        <v>120</v>
-      </c>
+      <c r="A119" s="2"/>
       <c r="B119" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E119" s="2"/>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="2">
-        <v>121</v>
-      </c>
+      <c r="A120" s="2"/>
       <c r="B120" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>310</v>
+        <v>214</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E120" s="6">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E120" s="2"/>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2"/>
       <c r="B121" s="2" t="s">
-        <v>318</v>
+        <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E121" s="7" t="s">
-        <v>317</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E121" s="2"/>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2"/>
       <c r="B122" s="2" t="s">
-        <v>318</v>
+        <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>310</v>
+        <v>166</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>317</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E122" s="2"/>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2"/>
       <c r="B123" s="2" t="s">
-        <v>318</v>
+        <v>17</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>310</v>
+        <v>47</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E123" s="7" t="s">
-        <v>317</v>
-      </c>
+      <c r="E123" s="2"/>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2"/>
       <c r="B124" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>310</v>
+        <v>193</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" s="17">
-        <v>36</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E124" s="2"/>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2"/>
       <c r="B125" s="2" t="s">
-        <v>319</v>
+        <v>5</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>310</v>
+        <v>64</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E125" s="17"/>
+      <c r="E125" s="2"/>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="2">
-        <v>122</v>
-      </c>
+      <c r="A126" s="2"/>
       <c r="B126" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>207</v>
+      <c r="C126" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E126" s="2"/>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E127" s="2"/>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>11</v>
@@ -6757,28 +6617,28 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E129" s="2"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>311</v>
+        <v>212</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>11</v>
@@ -6786,59 +6646,47 @@
       <c r="E130" s="2"/>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="2">
-        <v>127</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E131" s="2"/>
+      <c r="A131" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="5"/>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>138</v>
+        <v>64</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E132" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="E132" s="5"/>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="2">
-        <v>129</v>
-      </c>
+      <c r="A133" s="2"/>
       <c r="B133" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E133" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="5"/>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>283</v>
+        <v>138</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>8</v>
@@ -6847,65 +6695,73 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E135" s="2"/>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>313</v>
+        <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>312</v>
+        <v>140</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E136" s="2"/>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>283</v>
+        <v>142</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E137" s="2"/>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E138" s="2"/>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>8</v>
@@ -6914,118 +6770,124 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E140" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E141" s="2"/>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>282</v>
+        <v>214</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E142" s="2"/>
+      <c r="E142" s="7"/>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E143" s="2"/>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E144" s="2"/>
+      <c r="E144" s="5" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E145" s="2"/>
+      <c r="E145" s="5"/>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>47</v>
+        <v>172</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E146" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E146" s="2">
+        <v>1000000</v>
+      </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>8</v>
@@ -7034,28 +6896,30 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>291</v>
+        <v>173</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E148" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E148" s="2">
+        <v>10340</v>
+      </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C149" s="12" t="s">
-        <v>206</v>
+      <c r="C149" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>8</v>
@@ -7064,13 +6928,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>11</v>
@@ -7079,13 +6943,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>210</v>
+        <v>64</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>11</v>
@@ -7093,44 +6957,38 @@
       <c r="E151" s="2"/>
     </row>
     <row r="152" spans="1:5">
-      <c r="A152" s="2">
-        <v>148</v>
-      </c>
+      <c r="A152" s="2"/>
       <c r="B152" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
       <c r="E152" s="2"/>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>209</v>
+      <c r="C153" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E153" s="2"/>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>310</v>
+        <v>215</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>11</v>
@@ -7139,90 +6997,76 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>151</v>
-      </c>
-      <c r="B155" s="16" t="s">
-        <v>309</v>
+        <v>96</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>310</v>
+        <v>211</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E155" s="2">
-        <v>1000</v>
-      </c>
+      <c r="E155" s="2"/>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>152</v>
-      </c>
-      <c r="B156" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C156" t="s">
-        <v>314</v>
-      </c>
-      <c r="D156" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D156" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E156" s="2"/>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="2">
-        <v>153</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A157" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
       <c r="E157" s="2"/>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>154</v>
-      </c>
-      <c r="B158" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C158" t="s">
-        <v>315</v>
-      </c>
-      <c r="D158" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D158" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E158" s="2"/>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="2">
-        <v>155</v>
-      </c>
+      <c r="A159" s="2"/>
       <c r="B159" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
       <c r="E159" s="2"/>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>316</v>
+        <v>138</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>8</v>
@@ -7230,156 +7074,152 @@
       <c r="E160" s="2"/>
     </row>
     <row r="161" spans="1:5">
-      <c r="A161" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B161" s="2"/>
-      <c r="C161" s="2"/>
-      <c r="D161" s="2"/>
-      <c r="E161" s="5"/>
+      <c r="A161" s="2">
+        <v>101</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" s="2"/>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>308</v>
+        <v>140</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E162" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="E162" s="2"/>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>159</v>
+        <v>103</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C163" s="2"/>
-      <c r="D163" s="2"/>
-      <c r="E163" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" s="2"/>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E164" s="2"/>
     </row>
     <row r="165" spans="1:5">
-      <c r="A165" s="2">
-        <v>161</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A165" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
       <c r="E165" s="2"/>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E166" s="2"/>
     </row>
     <row r="167" spans="1:5">
-      <c r="A167" s="2">
-        <v>163</v>
-      </c>
+      <c r="A167" s="2"/>
       <c r="B167" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
       <c r="E167" s="2"/>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E168" s="2"/>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E169" s="2"/>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>150</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E170" s="2"/>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>297</v>
+        <v>55</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>11</v>
@@ -7388,77 +7228,73 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>214</v>
+        <v>57</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E172" s="7"/>
+        <v>11</v>
+      </c>
+      <c r="E172" s="2"/>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>169</v>
-      </c>
-      <c r="B173" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B173" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>8</v>
+        <v>197</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E173" s="2"/>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>170</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>3</v>
+        <v>113</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E174" s="2">
-        <v>1000000</v>
-      </c>
+      <c r="E174" s="2"/>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>295</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E175" s="2"/>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>293</v>
+        <v>198</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>8</v>
@@ -7467,486 +7303,22 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>293</v>
+        <v>55</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E177" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" s="2">
-        <v>174</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E178" s="2"/>
-    </row>
-    <row r="179" spans="1:5">
-      <c r="A179" s="2">
-        <v>175</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E179" s="6">
-        <v>10340</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
-      <c r="A180" s="2">
-        <v>176</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E180" s="2"/>
-    </row>
-    <row r="181" spans="1:5">
-      <c r="A181" s="2">
-        <v>177</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E181" s="2"/>
-    </row>
-    <row r="182" spans="1:5">
-      <c r="A182" s="2">
-        <v>178</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E182" s="2"/>
-    </row>
-    <row r="183" spans="1:5">
-      <c r="A183" s="2">
-        <v>179</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C183" s="2"/>
-      <c r="D183" s="2"/>
-      <c r="E183" s="2"/>
-    </row>
-    <row r="184" spans="1:5">
-      <c r="A184" s="2">
-        <v>180</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C184" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E184" s="2"/>
-    </row>
-    <row r="185" spans="1:5">
-      <c r="A185" s="2">
-        <v>181</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E185" s="2"/>
-    </row>
-    <row r="186" spans="1:5">
-      <c r="A186" s="2">
-        <v>182</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D186" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E186" s="2"/>
-    </row>
-    <row r="187" spans="1:5">
-      <c r="A187" s="2">
-        <v>183</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E187" s="2"/>
-    </row>
-    <row r="188" spans="1:5">
-      <c r="A188" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C188" s="2"/>
-      <c r="D188" s="2"/>
-      <c r="E188" s="2"/>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189" s="2">
-        <v>185</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E189" s="2"/>
-    </row>
-    <row r="190" spans="1:5">
-      <c r="A190" s="2">
-        <v>186</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D190" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E190" s="2"/>
-    </row>
-    <row r="191" spans="1:5">
-      <c r="A191" s="2">
-        <v>187</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E191" s="2"/>
-    </row>
-    <row r="192" spans="1:5">
-      <c r="A192" s="2">
-        <v>188</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E192" s="2"/>
-    </row>
-    <row r="193" spans="1:5">
-      <c r="A193" s="2">
-        <v>189</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E193" s="2"/>
-    </row>
-    <row r="194" spans="1:5">
-      <c r="A194" s="2">
-        <v>190</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E194" s="2"/>
-    </row>
-    <row r="195" spans="1:5">
-      <c r="A195" s="2">
-        <v>191</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E195" s="2"/>
-    </row>
-    <row r="196" spans="1:5">
-      <c r="A196" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B196" s="2"/>
-      <c r="C196" s="2"/>
-      <c r="D196" s="2"/>
-      <c r="E196" s="2"/>
-    </row>
-    <row r="197" spans="1:5">
-      <c r="A197" s="2">
-        <v>193</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E197" s="2"/>
-    </row>
-    <row r="198" spans="1:5">
-      <c r="A198" s="2">
-        <v>194</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E198" s="2"/>
-    </row>
-    <row r="199" spans="1:5">
-      <c r="A199" s="2">
-        <v>195</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E199" s="2"/>
-    </row>
-    <row r="200" spans="1:5">
-      <c r="A200" s="2">
-        <v>196</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E200" s="2"/>
-    </row>
-    <row r="201" spans="1:5">
-      <c r="A201" s="2">
-        <v>197</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E201" s="2"/>
-    </row>
-    <row r="202" spans="1:5">
-      <c r="A202" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B202" s="2"/>
-      <c r="C202" s="2"/>
-      <c r="D202" s="2"/>
-      <c r="E202" s="2"/>
-    </row>
-    <row r="203" spans="1:5">
-      <c r="A203" s="2">
-        <v>198</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E203" s="2"/>
-    </row>
-    <row r="204" spans="1:5">
-      <c r="A204" s="2">
-        <v>199</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E204" s="2"/>
-    </row>
-    <row r="205" spans="1:5">
-      <c r="A205" s="2">
-        <v>200</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E205" s="2"/>
-    </row>
-    <row r="206" spans="1:5">
-      <c r="A206" s="2">
-        <v>201</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E206" s="2"/>
-    </row>
-    <row r="207" spans="1:5">
-      <c r="A207" s="2">
-        <v>202</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E207" s="2"/>
-    </row>
-    <row r="208" spans="1:5">
-      <c r="A208" s="2">
-        <v>203</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E208" s="2"/>
-    </row>
-    <row r="209" spans="1:5">
-      <c r="A209" s="2">
-        <v>204</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E209" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="E177" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E43" r:id="rId1"/>
+    <hyperlink ref="E39" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14557,7 +13929,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -14585,8 +13957,8 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>129</v>
+      <c r="A2" s="2">
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>255</v>
@@ -14643,7 +14015,9 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
       <c r="B6" s="2" t="s">
         <v>267</v>
       </c>
@@ -14653,7 +14027,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>69</v>
@@ -14668,7 +14042,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -14682,7 +14056,9 @@
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>259</v>
       </c>
@@ -14692,7 +14068,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -14707,7 +14083,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -14721,8 +14097,8 @@
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2" t="s">
-        <v>204</v>
+      <c r="A12" s="2">
+        <v>12</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -14731,7 +14107,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>3</v>
@@ -14748,7 +14124,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>3</v>
@@ -14760,12 +14136,12 @@
         <v>8</v>
       </c>
       <c r="E14" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>3</v>
@@ -14777,12 +14153,12 @@
         <v>8</v>
       </c>
       <c r="E15" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>3</v>
@@ -14799,7 +14175,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>3</v>
@@ -14816,7 +14192,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>3</v>
@@ -14833,7 +14209,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>3</v>
@@ -14850,7 +14226,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>21</v>
@@ -14867,7 +14243,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>21</v>
@@ -14884,7 +14260,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>3</v>
@@ -14896,12 +14272,12 @@
         <v>8</v>
       </c>
       <c r="E22" s="2">
-        <v>12122</v>
+        <v>12124</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>3</v>
@@ -14918,7 +14294,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>3</v>
@@ -14935,7 +14311,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>5</v>
@@ -14950,7 +14326,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>17</v>
@@ -14965,7 +14341,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>69</v>
@@ -14980,7 +14356,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>5</v>
@@ -14994,7 +14370,9 @@
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="2"/>
+      <c r="A29" s="2">
+        <v>29</v>
+      </c>
       <c r="B29" s="2" t="s">
         <v>255</v>
       </c>
@@ -15004,7 +14382,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>5</v>
@@ -15019,7 +14397,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>5</v>
@@ -15034,7 +14412,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>3</v>
@@ -15050,8 +14428,8 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="2" t="s">
-        <v>146</v>
+      <c r="A33" s="2">
+        <v>33</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -15060,7 +14438,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>5</v>
@@ -15075,7 +14453,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>5</v>
@@ -15090,7 +14468,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>3</v>
@@ -15107,7 +14485,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>3</v>
@@ -15124,7 +14502,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>3</v>
@@ -15141,7 +14519,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>3</v>
@@ -15158,7 +14536,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>3</v>
@@ -15175,7 +14553,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>3</v>
@@ -15192,7 +14570,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>21</v>
@@ -15209,7 +14587,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>5</v>
@@ -15224,7 +14602,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>17</v>
@@ -15239,7 +14617,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>5</v>
@@ -15253,7 +14631,9 @@
       <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="2"/>
+      <c r="A46" s="2">
+        <v>46</v>
+      </c>
       <c r="B46" s="2" t="s">
         <v>255</v>
       </c>
@@ -15263,7 +14643,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>5</v>
@@ -15278,7 +14658,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>5</v>
@@ -15293,7 +14673,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>3</v>
@@ -15310,7 +14690,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>5</v>
@@ -15325,7 +14705,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>21</v>
@@ -15342,7 +14722,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>21</v>
@@ -15359,7 +14739,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>3</v>
@@ -15371,12 +14751,12 @@
         <v>8</v>
       </c>
       <c r="E53" s="2">
-        <v>10000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
@@ -15391,7 +14771,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>3</v>
@@ -15403,12 +14783,12 @@
         <v>8</v>
       </c>
       <c r="E55" s="2">
-        <v>1000</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>5</v>
@@ -15423,7 +14803,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>3</v>
@@ -15440,7 +14820,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>5</v>
@@ -15455,7 +14835,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>3</v>
@@ -15472,7 +14852,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>5</v>
@@ -15487,7 +14867,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>3</v>
@@ -15504,7 +14884,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>5</v>
@@ -15519,7 +14899,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>3</v>
@@ -15536,7 +14916,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>3</v>
@@ -15553,7 +14933,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>17</v>
@@ -15568,7 +14948,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>5</v>
@@ -15583,7 +14963,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>17</v>
@@ -15597,8 +14977,8 @@
       <c r="E67" s="2"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="2" t="s">
-        <v>205</v>
+      <c r="A68" s="2">
+        <v>68</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -15607,7 +14987,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>69</v>
@@ -15622,7 +15002,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>5</v>
@@ -15636,7 +15016,9 @@
       <c r="E70" s="2"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="2"/>
+      <c r="A71" s="2">
+        <v>71</v>
+      </c>
       <c r="B71" s="2" t="s">
         <v>255</v>
       </c>
@@ -15646,7 +15028,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>5</v>
@@ -15660,7 +15042,9 @@
       <c r="E72" s="5"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="2"/>
+      <c r="A73" s="2">
+        <v>73</v>
+      </c>
       <c r="B73" s="2" t="s">
         <v>5</v>
       </c>
@@ -15674,7 +15058,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>5</v>
@@ -15689,217 +15073,253 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
+        <v>75</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="2">
+        <v>76</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="2"/>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="2">
+        <v>77</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E75" s="2"/>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C76" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="2"/>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C77" s="2" t="s">
+      <c r="D77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="2">
+        <v>78</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="2">
+        <v>79</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="2"/>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="2" t="s">
+      <c r="D79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="2">
+        <v>80</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E78" s="2"/>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E79" s="2"/>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
+      <c r="D80" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E80" s="2"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="2"/>
+      <c r="A81" s="2">
+        <v>81</v>
+      </c>
       <c r="B81" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="2">
+        <v>82</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="2">
+        <v>83</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2" t="s">
+      <c r="D83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="2">
+        <v>84</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C84" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D82" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="2"/>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="2"/>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C84" s="2" t="s">
+      <c r="D84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="2">
+        <v>85</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="2">
+        <v>86</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="2">
+        <v>87</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E84" s="2"/>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" s="2"/>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" s="2"/>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C87" s="2" t="s">
+      <c r="D87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="2">
+        <v>88</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="2">
+        <v>89</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="2"/>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="2">
+        <v>90</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="2">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="2">
+        <v>91</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E87" s="2"/>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="2"/>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="2"/>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="2"/>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C91" s="12" t="s">
-        <v>206</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>8</v>
@@ -15908,13 +15328,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>11</v>
@@ -15923,13 +15343,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>211</v>
+        <v>64</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>11</v>
@@ -15938,277 +15358,307 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E94" s="2"/>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>212</v>
+        <v>66</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E95" s="2"/>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="5"/>
+      <c r="A96" s="2">
+        <v>96</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="2">
+        <v>10000</v>
+      </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="E97" s="2">
+        <v>200</v>
+      </c>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="2"/>
+      <c r="A98" s="2">
+        <v>98</v>
+      </c>
       <c r="B98" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="5"/>
+        <v>3</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="2">
+        <v>200</v>
+      </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E99" s="2"/>
+      <c r="E99" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E100" s="2">
+        <v>120</v>
+      </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="2"/>
+      <c r="E101" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E102" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E103" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E104" s="2"/>
+      <c r="E104" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>144</v>
+        <v>87</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>150</v>
+      <c r="E105" s="2">
+        <v>12122</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E106" s="2">
+        <v>2311323</v>
+      </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E107" s="7"/>
+      <c r="E107" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>213</v>
+        <v>67</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E108" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="E108" s="5"/>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>86</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>21</v>
+        <v>109</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>169</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E109" s="2"/>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>170</v>
+        <v>64</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E110" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="E110" s="2"/>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>172</v>
+        <v>64</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E111" s="2">
-        <v>1000000</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E111" s="2"/>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>173</v>
+      <c r="C112" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>8</v>
@@ -16217,60 +15667,60 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>173</v>
+        <v>5</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>316</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E113" s="2">
-        <v>10340</v>
-      </c>
+      <c r="E113" s="2"/>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>166</v>
+        <v>3</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>317</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E114" s="2"/>
+      <c r="E114" s="2">
+        <v>10404</v>
+      </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>34</v>
+        <v>5</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>318</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E115" s="2"/>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>64</v>
+        <v>207</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>11</v>
@@ -16278,38 +15728,44 @@
       <c r="E116" s="2"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="2"/>
+      <c r="A117" s="2">
+        <v>117</v>
+      </c>
       <c r="B117" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E117" s="2"/>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C118" s="12" t="s">
-        <v>206</v>
+      <c r="C118" s="2" t="s">
+        <v>319</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E118" s="2"/>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>215</v>
+        <v>310</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>11</v>
@@ -16318,91 +15774,113 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>211</v>
+        <v>310</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E120" s="2"/>
+      <c r="E120" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>97</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>5</v>
+        <v>121</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>314</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E121" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
+      <c r="A122" s="2">
+        <v>122</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>5</v>
+        <v>314</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>64</v>
+        <v>310</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E123" s="2"/>
+      <c r="E123" s="7" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="2"/>
+      <c r="A124" s="2">
+        <v>124</v>
+      </c>
       <c r="B124" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="16">
+        <v>36</v>
+      </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>5</v>
+        <v>315</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>138</v>
+        <v>310</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E125" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="E125" s="16"/>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>56</v>
+        <v>207</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>11</v>
@@ -16411,13 +15889,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>8</v>
@@ -16426,13 +15904,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>142</v>
+        <v>207</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>11</v>
@@ -16441,106 +15919,114 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>57</v>
+        <v>208</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E129" s="2"/>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
+      <c r="A130" s="2">
+        <v>130</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E130" s="2"/>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E131" s="2"/>
     </row>
     <row r="132" spans="1:5">
-      <c r="A132" s="2"/>
+      <c r="A132" s="2">
+        <v>132</v>
+      </c>
       <c r="B132" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E132" s="2"/>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E133" s="2"/>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>127</v>
+        <v>283</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E134" s="2"/>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
       <c r="E135" s="2"/>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>55</v>
+        <v>311</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>11</v>
@@ -16549,43 +16035,39 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>57</v>
+        <v>283</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E137" s="2"/>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>112</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
       <c r="E138" s="2"/>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>113</v>
-      </c>
-      <c r="B139" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>8</v>
@@ -16594,13 +16076,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>211</v>
+        <v>47</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>11</v>
@@ -16609,13 +16091,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>8</v>
@@ -16624,18 +16106,1125 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C142" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="2"/>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="2">
+        <v>143</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="2"/>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="2">
+        <v>144</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="2"/>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="2">
+        <v>145</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="2"/>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="2">
+        <v>146</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="2"/>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="2">
+        <v>147</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="2"/>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="2">
+        <v>148</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" s="2"/>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="2">
+        <v>149</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="2"/>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="2">
+        <v>150</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" s="2"/>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="2">
+        <v>151</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" s="2"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="2">
+        <v>152</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="2"/>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="2">
+        <v>153</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="2"/>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="2">
+        <v>154</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" s="2"/>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="2">
+        <v>155</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" s="2"/>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="2">
+        <v>156</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" s="2"/>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="2">
+        <v>157</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="2"/>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="2">
+        <v>158</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" s="2"/>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="2">
+        <v>159</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159" s="2"/>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="2">
+        <v>160</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" s="2"/>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="2">
+        <v>161</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" s="2"/>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="2">
+        <v>162</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" s="2"/>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="2">
+        <v>163</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="2">
+        <v>164</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E164" s="2"/>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="2">
+        <v>165</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" s="2"/>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="2">
+        <v>166</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E166" s="2"/>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="2">
+        <v>167</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" s="2"/>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="2">
+        <v>168</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" s="2"/>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="2">
+        <v>169</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" s="2"/>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="2">
+        <v>170</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" s="2"/>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="2">
+        <v>171</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E171" s="2"/>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="2">
+        <v>172</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E172" s="5"/>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="2">
+        <v>173</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="5"/>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="2">
+        <v>174</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" s="2"/>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="2">
+        <v>175</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="2"/>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="2">
+        <v>176</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E176" s="2"/>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="2">
+        <v>177</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" s="2"/>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="2">
+        <v>178</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" s="2"/>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="2">
+        <v>179</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E179" s="2"/>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="2">
+        <v>180</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="2">
+        <v>181</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" s="2"/>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="2">
+        <v>182</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E182" s="7"/>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="2">
+        <v>183</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E183" s="2"/>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="2">
+        <v>184</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E184" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="2">
+        <v>185</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E185" s="5"/>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="2">
+        <v>186</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E186" s="2">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="2">
+        <v>187</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" s="2"/>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="2">
+        <v>188</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E188" s="2">
+        <v>10540</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="2">
+        <v>189</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E189" s="2"/>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="2">
+        <v>190</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E190" s="2"/>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="2">
+        <v>191</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E191" s="2"/>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="2">
+        <v>192</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+      <c r="E192" s="2"/>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="2">
+        <v>193</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C193" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E193" s="2"/>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>194</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" s="2"/>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>195</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E195" s="2"/>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>196</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" s="2"/>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>197</v>
+      </c>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
+      <c r="E197" s="2"/>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>198</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" s="2"/>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>199</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+      <c r="E199" s="2"/>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>200</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E200" s="2"/>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>201</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E201" s="2"/>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>202</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E202" s="2"/>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>203</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E203" s="2"/>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>204</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E204" s="2"/>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>205</v>
+      </c>
+      <c r="B205" s="2"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
+      <c r="E205" s="2"/>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>206</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" s="2"/>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>207</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
+      <c r="E207" s="2"/>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>208</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E208" s="2"/>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>209</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E209" s="2"/>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>210</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E210" s="2"/>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>211</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D142" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E142" s="2"/>
+      <c r="D211" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E211" s="2"/>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>212</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" s="2"/>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>213</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" s="2"/>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>214</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E214" s="2"/>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>215</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" s="2"/>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>216</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E216" s="2"/>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>217</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E217" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -18436,7 +19025,7 @@
         <v>5</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>8</v>
@@ -18449,7 +19038,7 @@
         <v>3</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>8</v>
@@ -18464,7 +19053,7 @@
         <v>5</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>8</v>
@@ -18507,7 +19096,7 @@
         <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>11</v>
@@ -18549,7 +19138,7 @@
     <row r="125" spans="1:5">
       <c r="A125" s="2"/>
       <c r="B125" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>310</v>
@@ -18558,13 +19147,13 @@
         <v>11</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2"/>
       <c r="B126" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>310</v>
@@ -18573,13 +19162,13 @@
         <v>11</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2"/>
       <c r="B127" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>310</v>
@@ -18588,7 +19177,7 @@
         <v>11</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -18602,14 +19191,14 @@
       <c r="D128" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E128" s="17">
+      <c r="E128" s="16">
         <v>36</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2"/>
       <c r="B129" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>310</v>
@@ -18617,7 +19206,7 @@
       <c r="D129" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E129" s="17"/>
+      <c r="E129" s="16"/>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
@@ -18730,7 +19319,7 @@
         <v>5</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>11</v>
@@ -18771,7 +19360,7 @@
         <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>11</v>
@@ -19266,7 +19855,7 @@
         <v>5</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>8</v>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -17,14 +17,15 @@
     <sheet name="Regression Test" sheetId="8" r:id="rId8"/>
     <sheet name="Ereturn" sheetId="6" r:id="rId9"/>
     <sheet name="Demo" sheetId="9" r:id="rId10"/>
-    <sheet name="Sheet1" sheetId="12" r:id="rId11"/>
+    <sheet name="26QPredictDefault" sheetId="13" r:id="rId11"/>
+    <sheet name="Sheet1" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5602" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5516" uniqueCount="337">
   <si>
     <t>Keyword</t>
   </si>
@@ -987,6 +988,54 @@
   </si>
   <si>
     <t>switchtochallan</t>
+  </si>
+  <si>
+    <t>./src/test/java/pro/saral/testData/BLRL03775C-TDSForm26Q1 -predict-default.xlsx</t>
+  </si>
+  <si>
+    <t>shortdeductionverify</t>
+  </si>
+  <si>
+    <t>shortdeductionview</t>
+  </si>
+  <si>
+    <t>latepaymentinterestview</t>
+  </si>
+  <si>
+    <t>26qlatepaymentinterestpanverify</t>
+  </si>
+  <si>
+    <t>latedeductioninterestview</t>
+  </si>
+  <si>
+    <t>latepaymentinterestslnoverify</t>
+  </si>
+  <si>
+    <t>26qchallanstatusverify</t>
+  </si>
+  <si>
+    <t>26qhigherrateverify</t>
+  </si>
+  <si>
+    <t>challadeductionmappingstatusverify</t>
+  </si>
+  <si>
+    <t>26qpanverify</t>
+  </si>
+  <si>
+    <t>lowerdeductionverifyclick</t>
+  </si>
+  <si>
+    <t>26lowerdeductionverify</t>
+  </si>
+  <si>
+    <t>26qshortpaymentverify</t>
+  </si>
+  <si>
+    <t>26qmappedprice</t>
+  </si>
+  <si>
+    <t>26qunmappedprice</t>
   </si>
 </sst>
 </file>
@@ -4769,6 +4818,993 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E68"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="40.5703125" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="79.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="2">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="2">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="2">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="2">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="2">
+        <v>23</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="2">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="2">
+        <v>25</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="2">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="2">
+        <v>27</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="2">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2">
+        <v>29</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="2">
+        <v>30</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2">
+        <v>31</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2">
+        <v>32</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2">
+        <v>33</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2"/>
+      <c r="B39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2"/>
+      <c r="B41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="2"/>
+      <c r="B42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2"/>
+      <c r="B43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2">
+        <v>34</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="2">
+        <v>35</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="2">
+        <v>36</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2">
+        <v>37</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="2">
+        <v>38</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="2">
+        <v>41</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="2">
+        <v>42</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="2">
+        <v>43</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="2">
+        <v>44</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="2">
+        <v>45</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="2">
+        <v>46</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="2">
+        <v>47</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="2">
+        <v>48</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="2">
+        <v>49</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="2">
+        <v>52</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="2">
+        <v>53</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="2">
+        <v>54</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="2">
+        <v>55</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="2">
+        <v>56</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="2">
+        <v>57</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="2">
+        <v>58</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4780,1385 +5816,661 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>255</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>270</v>
-      </c>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
-        <v>267</v>
-      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
-        <v>259</v>
-      </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="2">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2" t="s">
-        <v>204</v>
-      </c>
+      <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="2">
-        <v>10000</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="2">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="2">
-        <v>100</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="2">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="2">
-        <v>100</v>
-      </c>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="2">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2">
-        <v>10</v>
-      </c>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="2">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="2">
-        <v>120</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="2">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2">
-        <v>10</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="2">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2">
-        <v>40</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="2">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>90</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="5"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="2">
-        <v>19</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="2">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2">
-        <v>12122</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="2">
-        <v>21</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2">
-        <v>2311323</v>
-      </c>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="2">
-        <v>22</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="2">
-        <v>23</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="2">
-        <v>24</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A26" s="2"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="2"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="2">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="2">
-        <v>26</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2"/>
-      <c r="B29" s="2" t="s">
-        <v>255</v>
-      </c>
+      <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="2">
-        <v>27</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="2">
-        <v>28</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="2">
-        <v>29</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>145</v>
-      </c>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="2" t="s">
-        <v>146</v>
-      </c>
+      <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="2">
-        <v>31</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="2">
-        <v>32</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="2">
-        <v>33</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>150</v>
-      </c>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="2">
-        <v>34</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="2">
-        <v>35</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>153</v>
-      </c>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="2">
-        <v>36</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="4"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="2">
-        <v>37</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>156</v>
-      </c>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="2">
-        <v>38</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>158</v>
-      </c>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="2">
-        <v>39</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>160</v>
-      </c>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="2">
-        <v>40</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
       <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="2">
-        <v>41</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
       <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="2">
-        <v>42</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
       <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2"/>
-      <c r="B46" s="2" t="s">
-        <v>255</v>
-      </c>
+      <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="2">
-        <v>43</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
       <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="2">
-        <v>44</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
       <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="2">
-        <v>45</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>150</v>
-      </c>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="2">
-        <v>46</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
       <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="2">
-        <v>47</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>169</v>
-      </c>
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="2">
-        <v>48</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>171</v>
-      </c>
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="2">
-        <v>49</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="2">
-        <v>1000000</v>
-      </c>
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="2">
-        <v>50</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
       <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="2">
-        <v>51</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="2">
-        <v>100000</v>
-      </c>
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="2">
-        <v>52</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
       <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="2">
-        <v>53</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="2">
-        <v>2</v>
-      </c>
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="2">
-        <v>54</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
       <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="2">
-        <v>55</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="2">
-        <v>20</v>
-      </c>
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="2">
-        <v>56</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="2">
-        <v>57</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" s="2">
-        <v>2</v>
-      </c>
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="2">
-        <v>58</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="2">
-        <v>59</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E63" s="2">
-        <v>20</v>
-      </c>
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="2">
-        <v>60</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="2">
-        <v>61</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
       <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="2">
-        <v>62</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
       <c r="E66" s="2"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="2">
-        <v>63</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
       <c r="E67" s="2"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="2" t="s">
-        <v>205</v>
-      </c>
+      <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="2">
-        <v>65</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
       <c r="E69" s="2"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="2">
-        <v>66</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
       <c r="E70" s="2"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2"/>
-      <c r="B71" s="2" t="s">
-        <v>255</v>
-      </c>
+      <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="2">
-        <v>67</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="2"/>
       <c r="E72" s="5"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2"/>
-      <c r="B73" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="2"/>
       <c r="E73" s="5"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="2">
-        <v>68</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2"/>
-      <c r="B75" s="2" t="s">
-        <v>120</v>
-      </c>
+      <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="2">
-        <v>69</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
       <c r="E76" s="2"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2"/>
-      <c r="B77" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2"/>
-      <c r="B78" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
       <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2"/>
-      <c r="B79" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
       <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2"/>
-      <c r="B80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
       <c r="E80" s="2"/>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2"/>
-      <c r="B81" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
       <c r="E81" s="2"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2"/>
-      <c r="B82" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E82" s="2">
-        <v>100000</v>
-      </c>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2"/>
-      <c r="B83" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2"/>
-      <c r="B84" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
       <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2"/>
-      <c r="B85" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
       <c r="E85" s="2"/>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2"/>
-      <c r="B86" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
       <c r="E86" s="2"/>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2"/>
-      <c r="B87" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
       <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2"/>
-      <c r="B88" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
       <c r="E88" s="2"/>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2"/>
-      <c r="B89" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="2">
-        <v>8000</v>
-      </c>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2"/>
-      <c r="B90" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
       <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2"/>
-      <c r="B91" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2"/>
-      <c r="B92" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
       <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2"/>
-      <c r="B93" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
       <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2"/>
-      <c r="B94" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
       <c r="E94" s="2"/>
     </row>
     <row r="95" spans="1:5">
@@ -7317,9 +7629,6 @@
       <c r="E177" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E39" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="10"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5516" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5534" uniqueCount="339">
   <si>
     <t>Keyword</t>
   </si>
@@ -1036,6 +1036,12 @@
   </si>
   <si>
     <t>26qunmappedprice</t>
+  </si>
+  <si>
+    <t>24latepaymentinterestverify</t>
+  </si>
+  <si>
+    <t>24latedeductioninterest</t>
   </si>
 </sst>
 </file>
@@ -20897,7 +20903,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
@@ -21410,14 +21416,12 @@
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
+      <c r="A35" s="2"/>
       <c r="B35" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>11</v>
@@ -21425,14 +21429,12 @@
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
+      <c r="A36" s="2"/>
       <c r="B36" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>241</v>
+        <v>337</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>11</v>
@@ -21440,92 +21442,96 @@
       <c r="E36" s="2"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>69</v>
+      <c r="A37" s="2"/>
+      <c r="B37" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D37" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="s">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D38" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2"/>
-      <c r="B39" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
+      <c r="B39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="2">
-        <v>38</v>
-      </c>
-      <c r="B40" s="2" t="s">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>229</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D41" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
+      <c r="A42" s="2">
+        <v>35</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>11</v>
@@ -21534,82 +21540,76 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="2">
-        <v>43</v>
-      </c>
+      <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
       <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
+      <c r="A47" s="2">
+        <v>39</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="2">
-        <v>45</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A48" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
       <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>11</v>
@@ -21618,28 +21618,28 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>11</v>
@@ -21648,7 +21648,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>17</v>
@@ -21663,7 +21663,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2" t="s">
-        <v>200</v>
+        <v>128</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -21672,28 +21672,28 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>197</v>
+        <v>65</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>11</v>
@@ -21702,28 +21702,28 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
+        <v>48</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>11</v>
@@ -21732,48 +21732,132 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>198</v>
+        <v>57</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="2">
-        <v>57</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A59" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
+        <v>52</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="2">
+        <v>53</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="2">
+        <v>54</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="2">
+        <v>55</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="2">
+        <v>56</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="2">
+        <v>57</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="2">
         <v>58</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B66" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="2"/>
+      <c r="D66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,15 @@
     <sheet name="Demo" sheetId="9" r:id="rId10"/>
     <sheet name="26QPredictDefault" sheetId="13" r:id="rId11"/>
     <sheet name="Sheet1" sheetId="12" r:id="rId12"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId13"/>
+    <sheet name="26QEreturn" sheetId="15" r:id="rId14"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5534" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5810" uniqueCount="342">
   <si>
     <t>Keyword</t>
   </si>
@@ -1042,6 +1044,15 @@
   </si>
   <si>
     <t>24latedeductioninterest</t>
+  </si>
+  <si>
+    <t>./src/test/java/pro/saral/testData/BLRL03775C-TDSForm26Q1.xlsx</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>26qereturnvalidation</t>
   </si>
 </sst>
 </file>
@@ -7639,6 +7650,1415 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E97"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="41" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" customWidth="1"/>
+    <col min="5" max="5" width="61.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="2">
+        <v>14</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="2">
+        <v>15</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2">
+        <v>16</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="2">
+        <v>17</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2">
+        <v>18</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2">
+        <v>19</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2">
+        <v>20</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2">
+        <v>21</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2">
+        <v>22</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2">
+        <v>23</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2">
+        <v>24</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="2">
+        <v>25</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2">
+        <v>26</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2">
+        <v>27</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="2">
+        <v>28</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="2">
+        <v>29</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2">
+        <v>30</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2">
+        <v>31</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="2">
+        <v>32</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="2">
+        <v>33</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="2">
+        <v>34</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="2">
+        <v>35</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="2">
+        <v>36</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="2">
+        <v>37</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="2">
+        <v>38</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="2">
+        <v>39</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="2">
+        <v>40</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="2">
+        <v>41</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="2">
+        <v>42</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="2">
+        <v>43</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="2">
+        <v>44</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="2">
+        <v>45</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="2">
+        <v>46</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="2">
+        <v>48</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="2">
+        <v>49</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="2">
+        <v>50</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="2">
+        <v>52</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="2"/>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="2">
+        <v>53</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="2">
+        <v>54</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="2"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="2">
+        <v>55</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="2">
+        <v>57</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="2"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="2">
+        <v>58</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="2">
+        <v>59</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="2">
+        <v>60</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="2"/>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="2">
+        <v>61</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="2">
+        <v>62</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="2">
+        <v>63</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="2">
+        <v>64</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="2">
+        <v>65</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="2">
+        <v>66</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="2">
+        <v>67</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="2">
+        <v>68</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="2">
+        <v>69</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="2">
+        <v>70</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="2">
+        <v>71</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="2">
+        <v>72</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="2">
+        <v>73</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="2"/>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="2">
+        <v>74</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="2">
+        <v>75</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="2"/>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="2">
+        <v>76</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="2"/>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="2">
+        <v>77</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="2">
+        <v>78</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="2">
+        <v>79</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" s="2"/>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="2">
+        <v>80</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="2"/>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="2">
+        <v>81</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E161"/>

--- a/Gstsaralprotesting/TestCase.xlsx
+++ b/Gstsaralprotesting/TestCase.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="13"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="KeywordFramework" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Demo" sheetId="9" r:id="rId10"/>
     <sheet name="26QPredictDefault" sheetId="13" r:id="rId11"/>
     <sheet name="Sheet1" sheetId="12" r:id="rId12"/>
-    <sheet name="Sheet2" sheetId="14" r:id="rId13"/>
+    <sheet name="27QDeduction" sheetId="14" r:id="rId13"/>
     <sheet name="26QEreturn" sheetId="15" r:id="rId14"/>
   </sheets>
   <calcPr calcId="124519"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5810" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" co